--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closing Prices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Closing Prices" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,92 +437,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2026-04-29 Close</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2026-04-29 Change</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2026-04-29 Change %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2026-04-30 Close</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2026-04-30 Change</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2026-04-30 Change %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2026-05-04 Close</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2026-05-04 Change</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2026-05-04 Change %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2026-05-05 Close</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2026-05-05 Change</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2026-05-05 Change %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2026-05-06 Close</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2026-05-06 Change</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>2026-05-06 Change %</t>
         </is>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Closing Prices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closing Prices" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,92 +449,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2026-04-29 Close</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2026-04-29 Change</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026-04-29 Change %</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2026-04-30 Close</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2026-04-30 Change</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2026-04-30 Change %</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-05-04 Close</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2026-05-04 Change</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2026-05-04 Change %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>2026-05-05 Close</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>2026-05-05 Change</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>2026-05-05 Change %</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>2026-05-06 Close</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>2026-05-06 Change</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>2026-05-06 Change %</t>
         </is>
@@ -2567,7 +2579,7 @@
         <v>0.08</v>
       </c>
       <c r="F35" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="G35" t="n">
         <v>4.78</v>
@@ -2576,34 +2588,34 @@
         <v>-0.03</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.71</v>
+        <v>-0.62</v>
       </c>
       <c r="J35" t="n">
         <v>4.87</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="M35" t="n">
         <v>4.82</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.15</v>
+        <v>-1.03</v>
       </c>
       <c r="P35" t="n">
         <v>4.82</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.15</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="36">
@@ -3367,7 +3379,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -3376,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="H48" t="n">
         <v>-0.01</v>
@@ -3385,7 +3397,7 @@
         <v>-2.82</v>
       </c>
       <c r="J48" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="K48" t="n">
         <v>0.01</v>
@@ -3394,7 +3406,7 @@
         <v>2.9</v>
       </c>
       <c r="M48" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
       <c r="N48" t="n">
         <v>0.02</v>
@@ -3406,7 +3418,7 @@
         <v>0.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R48" t="n">
         <v>1.33</v>
@@ -3766,16 +3778,16 @@
         <v>2.38</v>
       </c>
       <c r="M54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="N54" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="O54" t="n">
         <v>-1.16</v>
       </c>
       <c r="P54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -3801,10 +3813,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.7</v>
+        <v>0.705</v>
       </c>
       <c r="E55" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
         <v>-0.7</v>
@@ -3813,7 +3825,7 @@
         <v>0.68</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.02</v>
+        <v>-0.025</v>
       </c>
       <c r="I55" t="n">
         <v>-3.55</v>
@@ -3828,16 +3840,16 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="N55" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="O55" t="n">
         <v>-0.74</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="Q55" t="n">
         <v>0.01</v>
@@ -3863,16 +3875,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.49</v>
+        <v>0.485</v>
       </c>
       <c r="E56" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
         <v>-1.02</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5</v>
+        <v>0.495</v>
       </c>
       <c r="H56" t="n">
         <v>0.01</v>
@@ -3881,7 +3893,7 @@
         <v>2.06</v>
       </c>
       <c r="J56" t="n">
-        <v>0.49</v>
+        <v>0.485</v>
       </c>
       <c r="K56" t="n">
         <v>-0.01</v>
@@ -3890,7 +3902,7 @@
         <v>-2.02</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5</v>
+        <v>0.495</v>
       </c>
       <c r="N56" t="n">
         <v>0.01</v>
@@ -3902,7 +3914,7 @@
         <v>0.49</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="R56" t="n">
         <v>-1.01</v>
@@ -3987,16 +3999,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="E58" t="n">
-        <v>-0</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
         <v>-1.25</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -4005,19 +4017,19 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L58" t="n">
         <v>2.53</v>
       </c>
       <c r="M58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="N58" t="n">
-        <v>-0</v>
+        <v>-0.002</v>
       </c>
       <c r="O58" t="n">
         <v>-2.47</v>
@@ -4026,7 +4038,7 @@
         <v>0.08</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="R58" t="n">
         <v>1.27</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-04-29 Close</t>
+          <t>2026-04-30 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-04-29 Change</t>
+          <t>2026-04-30 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-04-29 Change %</t>
+          <t>2026-04-30 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-04-30 Close</t>
+          <t>2026-05-04 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-04-30 Change</t>
+          <t>2026-05-04 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-04-30 Change %</t>
+          <t>2026-05-04 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-04 Close</t>
+          <t>2026-05-05 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-04 Change</t>
+          <t>2026-05-05 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-04 Change %</t>
+          <t>2026-05-05 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-05 Close</t>
+          <t>2026-05-06 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change</t>
+          <t>2026-05-06 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change %</t>
+          <t>2026-05-06 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-06 Close</t>
+          <t>2026-05-07 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change</t>
+          <t>2026-05-07 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change %</t>
+          <t>2026-05-07 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141</v>
+        <v>140.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.28</v>
+        <v>-0.57</v>
       </c>
       <c r="G3" t="n">
-        <v>140.2</v>
+        <v>143.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.57</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
-        <v>143.4</v>
+        <v>136</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>-7.4</v>
       </c>
       <c r="L3" t="n">
-        <v>2.28</v>
+        <v>-5.16</v>
       </c>
       <c r="M3" t="n">
-        <v>136</v>
+        <v>140.5</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.16</v>
+        <v>3.31</v>
       </c>
       <c r="P3" t="n">
-        <v>140.5</v>
+        <v>143.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>187.2</v>
+        <v>190.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>1.92</v>
       </c>
       <c r="G4" t="n">
-        <v>190.8</v>
+        <v>197</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>197</v>
+        <v>192.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>-4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>-2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>192.2</v>
+        <v>201.6</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.8</v>
+        <v>9.4</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.44</v>
+        <v>4.89</v>
       </c>
       <c r="P4" t="n">
-        <v>201.6</v>
+        <v>203.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>4.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.17</v>
+        <v>6.08</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="G5" t="n">
-        <v>6.08</v>
+        <v>5.94</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.46</v>
+        <v>-2.3</v>
       </c>
       <c r="J5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="M5" t="n">
         <v>5.94</v>
       </c>
-      <c r="K5" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.87</v>
-      </c>
       <c r="N5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.22</v>
+        <v>7.03</v>
       </c>
       <c r="E6" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.04</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.05</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.18</v>
+        <v>5.06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>-2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>5.06</v>
+        <v>5.09</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.32</v>
+        <v>0.59</v>
       </c>
       <c r="J7" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L7" t="n">
-        <v>0.59</v>
+        <v>-0.79</v>
       </c>
       <c r="M7" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04</v>
+        <v>0.1</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.79</v>
+        <v>1.98</v>
       </c>
       <c r="P7" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.98</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.99</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="F8" t="n">
-        <v>1.12</v>
+        <v>-2.34</v>
       </c>
       <c r="G8" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J8" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="H8" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8.84</v>
-      </c>
       <c r="K8" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.68</v>
+        <v>-0.68</v>
       </c>
       <c r="M8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06</v>
+        <v>0.15</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.68</v>
+        <v>1.71</v>
       </c>
       <c r="P8" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -949,34 +949,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.35</v>
+        <v>7.15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03</v>
+        <v>-0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.41</v>
+        <v>-2.72</v>
       </c>
       <c r="G9" t="n">
-        <v>7.15</v>
+        <v>7.12</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.72</v>
+        <v>-0.42</v>
       </c>
       <c r="J9" t="n">
-        <v>7.12</v>
+        <v>7.18</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.42</v>
+        <v>0.84</v>
       </c>
       <c r="M9" t="n">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="N9" t="n">
         <v>0.06</v>
@@ -985,13 +985,13 @@
         <v>0.84</v>
       </c>
       <c r="P9" t="n">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="R9" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.98</v>
+        <v>47.1</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.12</v>
+        <v>-0.88</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.23</v>
+        <v>-1.83</v>
       </c>
       <c r="G10" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J10" t="n">
         <v>47.1</v>
       </c>
-      <c r="H10" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="J10" t="n">
-        <v>47.08</v>
-      </c>
       <c r="K10" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="M10" t="n">
-        <v>47.1</v>
+        <v>47.04</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="P10" t="n">
-        <v>47.04</v>
+        <v>47.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.06</v>
+        <v>0.78</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.13</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="E11" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="N11" t="n">
         <v>0.11</v>
       </c>
-      <c r="F11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="O11" t="n">
-        <v>-0.43</v>
+        <v>2.39</v>
       </c>
       <c r="P11" t="n">
-        <v>4.71</v>
+        <v>4.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="R11" t="n">
-        <v>2.39</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.98</v>
+        <v>12.03</v>
       </c>
       <c r="E12" t="n">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>0.42</v>
       </c>
       <c r="G12" t="n">
-        <v>12.03</v>
+        <v>11.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>-0.33</v>
       </c>
       <c r="I12" t="n">
-        <v>0.42</v>
+        <v>-2.74</v>
       </c>
       <c r="J12" t="n">
-        <v>11.7</v>
+        <v>11.68</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.74</v>
+        <v>-0.17</v>
       </c>
       <c r="M12" t="n">
         <v>11.68</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>11.68</v>
+        <v>10.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-8.48</v>
       </c>
     </row>
     <row r="13">
@@ -1200,46 +1200,46 @@
         <v>29.38</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>29.38</v>
+        <v>28.62</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-2.59</v>
       </c>
       <c r="J13" t="n">
-        <v>28.62</v>
+        <v>28.56</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.76</v>
+        <v>-0.06</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.59</v>
+        <v>-0.21</v>
       </c>
       <c r="M13" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.06</v>
+        <v>-0.52</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.21</v>
+        <v>-1.82</v>
       </c>
       <c r="P13" t="n">
-        <v>28.04</v>
+        <v>26.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.52</v>
+        <v>-1.62</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.82</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="F14" t="n">
-        <v>4.51</v>
+        <v>-3.24</v>
       </c>
       <c r="G14" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.09</v>
+        <v>0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.24</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>2.83</v>
       </c>
       <c r="K14" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-3.89</v>
       </c>
       <c r="P14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>-3.89</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>0.78</v>
+        <v>1.17</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="I15" t="n">
-        <v>1.17</v>
+        <v>-2.12</v>
       </c>
       <c r="J15" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.12</v>
+        <v>-0.39</v>
       </c>
       <c r="M15" t="n">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.39</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.35</v>
+        <v>5.26</v>
       </c>
       <c r="E16" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.01</v>
       </c>
-      <c r="F16" t="n">
+      <c r="L16" t="n">
         <v>0.19</v>
       </c>
-      <c r="G16" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.19</v>
-      </c>
       <c r="M16" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0.19</v>
+        <v>-0.38</v>
       </c>
       <c r="P16" t="n">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.38</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06</v>
+        <v>-0.22</v>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>-5.49</v>
       </c>
       <c r="G17" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.22</v>
+        <v>0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.49</v>
+        <v>1.06</v>
       </c>
       <c r="J17" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="L17" t="n">
-        <v>1.06</v>
+        <v>-1.31</v>
       </c>
       <c r="M17" t="n">
         <v>3.78</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>2.49</v>
+        <v>-2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>3.62</v>
+        <v>3.51</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.16</v>
+        <v>-3.04</v>
       </c>
       <c r="J18" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.04</v>
+        <v>-0.28</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.28</v>
+        <v>1.14</v>
       </c>
       <c r="P18" t="n">
         <v>3.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1569,25 +1569,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="E19" t="n">
-        <v>3.65</v>
+        <v>-0.7</v>
       </c>
       <c r="F19" t="n">
-        <v>6.08</v>
+        <v>-1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>63</v>
+        <v>63.25</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7</v>
+        <v>0.25</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
-        <v>63.25</v>
+        <v>63.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.25</v>
@@ -1596,22 +1596,22 @@
         <v>0.4</v>
       </c>
       <c r="M19" t="n">
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="P19" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.4</v>
+        <v>28.62</v>
       </c>
       <c r="E20" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="F20" t="n">
-        <v>5.14</v>
+        <v>4.45</v>
       </c>
       <c r="G20" t="n">
-        <v>28.62</v>
+        <v>28.78</v>
       </c>
       <c r="H20" t="n">
-        <v>1.22</v>
+        <v>0.16</v>
       </c>
       <c r="I20" t="n">
-        <v>4.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>28.78</v>
+        <v>29.12</v>
       </c>
       <c r="K20" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="M20" t="n">
-        <v>29.12</v>
+        <v>29.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.34</v>
+        <v>0.78</v>
       </c>
       <c r="O20" t="n">
-        <v>1.18</v>
+        <v>2.68</v>
       </c>
       <c r="P20" t="n">
-        <v>29.9</v>
+        <v>31.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.78</v>
+        <v>1.28</v>
       </c>
       <c r="R20" t="n">
-        <v>2.68</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.27</v>
+        <v>5.21</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>1.93</v>
+        <v>-1.14</v>
       </c>
       <c r="G21" t="n">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.14</v>
+        <v>-1.34</v>
       </c>
       <c r="J21" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.34</v>
+        <v>-0.19</v>
       </c>
       <c r="M21" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.19</v>
+        <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>5.19</v>
+        <v>5.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.45</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8</v>
+        <v>-0.85</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="G22" t="n">
-        <v>84.59999999999999</v>
+        <v>83.95</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.85</v>
+        <v>-0.65</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.99</v>
+        <v>-0.77</v>
       </c>
       <c r="J22" t="n">
-        <v>83.95</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.65</v>
+        <v>-0.1</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.77</v>
+        <v>-0.12</v>
       </c>
       <c r="M22" t="n">
-        <v>83.84999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1</v>
+        <v>0.85</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.12</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>84.7</v>
+        <v>85.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.74</v>
+        <v>24.94</v>
       </c>
       <c r="E23" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="F23" t="n">
-        <v>1.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>24.94</v>
+        <v>26.14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.81</v>
       </c>
       <c r="J23" t="n">
-        <v>26.14</v>
+        <v>26.08</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2</v>
+        <v>-0.06</v>
       </c>
       <c r="L23" t="n">
-        <v>4.81</v>
+        <v>-0.23</v>
       </c>
       <c r="M23" t="n">
-        <v>26.08</v>
+        <v>27.4</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.06</v>
+        <v>1.32</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.23</v>
+        <v>5.06</v>
       </c>
       <c r="P23" t="n">
-        <v>27.4</v>
+        <v>27.52</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.32</v>
+        <v>0.12</v>
       </c>
       <c r="R23" t="n">
-        <v>5.06</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25.4</v>
+        <v>25.02</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04</v>
+        <v>-0.38</v>
       </c>
       <c r="F24" t="n">
-        <v>0.16</v>
+        <v>-1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>25.02</v>
+        <v>24.12</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.38</v>
+        <v>-0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5</v>
+        <v>-3.6</v>
       </c>
       <c r="J24" t="n">
-        <v>24.12</v>
+        <v>24.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9</v>
+        <v>0.18</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.6</v>
+        <v>0.75</v>
       </c>
       <c r="M24" t="n">
-        <v>24.3</v>
+        <v>24.68</v>
       </c>
       <c r="N24" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="O24" t="n">
-        <v>0.75</v>
+        <v>1.56</v>
       </c>
       <c r="P24" t="n">
-        <v>24.68</v>
+        <v>26.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.14</v>
+        <v>29.02</v>
       </c>
       <c r="E25" t="n">
-        <v>0.22</v>
+        <v>-1.12</v>
       </c>
       <c r="F25" t="n">
-        <v>0.74</v>
+        <v>-3.72</v>
       </c>
       <c r="G25" t="n">
-        <v>29.02</v>
+        <v>30.98</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.12</v>
+        <v>1.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.72</v>
+        <v>6.75</v>
       </c>
       <c r="J25" t="n">
-        <v>30.98</v>
+        <v>30.46</v>
       </c>
       <c r="K25" t="n">
-        <v>1.96</v>
+        <v>-0.52</v>
       </c>
       <c r="L25" t="n">
-        <v>6.75</v>
+        <v>-1.68</v>
       </c>
       <c r="M25" t="n">
-        <v>30.46</v>
+        <v>30.82</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.52</v>
+        <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.68</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>30.82</v>
+        <v>31.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>43.06</v>
+        <v>46.6</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.48</v>
+        <v>3.54</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.45</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>46.6</v>
+        <v>48.7</v>
       </c>
       <c r="H26" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="I26" t="n">
-        <v>8.220000000000001</v>
+        <v>4.51</v>
       </c>
       <c r="J26" t="n">
-        <v>48.7</v>
+        <v>47</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="L26" t="n">
-        <v>4.51</v>
+        <v>-3.49</v>
       </c>
       <c r="M26" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.7</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.49</v>
+        <v>8.51</v>
       </c>
       <c r="P26" t="n">
-        <v>51</v>
+        <v>58.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>7.55</v>
       </c>
       <c r="R26" t="n">
-        <v>8.51</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>479.2</v>
+        <v>467.8</v>
       </c>
       <c r="E27" t="n">
-        <v>5.4</v>
+        <v>-11.4</v>
       </c>
       <c r="F27" t="n">
-        <v>1.14</v>
+        <v>-2.38</v>
       </c>
       <c r="G27" t="n">
-        <v>467.8</v>
+        <v>473</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.4</v>
+        <v>5.2</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.38</v>
+        <v>1.11</v>
       </c>
       <c r="J27" t="n">
-        <v>473</v>
+        <v>472.2</v>
       </c>
       <c r="K27" t="n">
-        <v>5.2</v>
+        <v>-0.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.11</v>
+        <v>-0.17</v>
       </c>
       <c r="M27" t="n">
-        <v>472.2</v>
+        <v>463</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.17</v>
+        <v>-1.95</v>
       </c>
       <c r="P27" t="n">
-        <v>463</v>
+        <v>477.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.95</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>130.6</v>
+        <v>126</v>
       </c>
       <c r="E28" t="n">
-        <v>4.1</v>
+        <v>-4.6</v>
       </c>
       <c r="F28" t="n">
-        <v>3.24</v>
+        <v>-3.52</v>
       </c>
       <c r="G28" t="n">
-        <v>126</v>
+        <v>131.7</v>
       </c>
       <c r="H28" t="n">
-        <v>-4.6</v>
+        <v>5.7</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.52</v>
+        <v>4.52</v>
       </c>
       <c r="J28" t="n">
-        <v>131.7</v>
+        <v>131.2</v>
       </c>
       <c r="K28" t="n">
-        <v>5.7</v>
+        <v>-0.5</v>
       </c>
       <c r="L28" t="n">
-        <v>4.52</v>
+        <v>-0.38</v>
       </c>
       <c r="M28" t="n">
-        <v>131.2</v>
+        <v>134.2</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.5</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.38</v>
+        <v>2.29</v>
       </c>
       <c r="P28" t="n">
-        <v>134.2</v>
+        <v>140.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="R28" t="n">
-        <v>2.29</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>117.5</v>
+        <v>116.3</v>
       </c>
       <c r="E29" t="n">
-        <v>2.2</v>
+        <v>-1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.91</v>
+        <v>-1.02</v>
       </c>
       <c r="G29" t="n">
-        <v>116.3</v>
+        <v>116.8</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.2</v>
+        <v>0.5</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.02</v>
+        <v>0.43</v>
       </c>
       <c r="J29" t="n">
-        <v>116.8</v>
+        <v>116.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.43</v>
+        <v>-0.51</v>
       </c>
       <c r="M29" t="n">
-        <v>116.2</v>
+        <v>116.4</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.51</v>
+        <v>0.17</v>
       </c>
       <c r="P29" t="n">
-        <v>116.4</v>
+        <v>119</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0.17</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>83.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="E30" t="n">
-        <v>2.85</v>
+        <v>0.1</v>
       </c>
       <c r="F30" t="n">
-        <v>3.55</v>
+        <v>0.12</v>
       </c>
       <c r="G30" t="n">
-        <v>83.25</v>
+        <v>84.45</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.12</v>
+        <v>1.44</v>
       </c>
       <c r="J30" t="n">
-        <v>84.45</v>
+        <v>83.55</v>
       </c>
       <c r="K30" t="n">
-        <v>1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>-1.07</v>
       </c>
       <c r="M30" t="n">
-        <v>83.55</v>
+        <v>82.5</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.9</v>
+        <v>-1.05</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.07</v>
+        <v>-1.26</v>
       </c>
       <c r="P30" t="n">
-        <v>82.5</v>
+        <v>84.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.05</v>
+        <v>1.75</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.26</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>119.9</v>
+        <v>118.7</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.4</v>
+        <v>-1.2</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.76</v>
+        <v>-1</v>
       </c>
       <c r="G31" t="n">
-        <v>118.7</v>
+        <v>122.8</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.2</v>
+        <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>-1</v>
+        <v>3.45</v>
       </c>
       <c r="J31" t="n">
-        <v>122.8</v>
+        <v>125.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="L31" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="M31" t="n">
-        <v>125.4</v>
+        <v>131.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.12</v>
+        <v>4.94</v>
       </c>
       <c r="P31" t="n">
-        <v>131.6</v>
+        <v>137.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="R31" t="n">
-        <v>4.94</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>65.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.25</v>
+        <v>5.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.38</v>
+        <v>7.75</v>
       </c>
       <c r="G32" t="n">
-        <v>70.90000000000001</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>5.1</v>
+        <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>7.75</v>
+        <v>1.76</v>
       </c>
       <c r="J32" t="n">
-        <v>72.15000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K32" t="n">
-        <v>1.25</v>
+        <v>-1.35</v>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>-1.87</v>
       </c>
       <c r="M32" t="n">
-        <v>70.8</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.35</v>
+        <v>4.05</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.87</v>
+        <v>5.72</v>
       </c>
       <c r="P32" t="n">
-        <v>74.84999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="R32" t="n">
-        <v>5.72</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>108.3</v>
+        <v>102.5</v>
       </c>
       <c r="E33" t="n">
-        <v>4.6</v>
+        <v>-5.8</v>
       </c>
       <c r="F33" t="n">
-        <v>4.44</v>
+        <v>-5.36</v>
       </c>
       <c r="G33" t="n">
-        <v>102.5</v>
+        <v>103</v>
       </c>
       <c r="H33" t="n">
-        <v>-5.8</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="n">
-        <v>-5.36</v>
+        <v>0.49</v>
       </c>
       <c r="J33" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
       <c r="L33" t="n">
-        <v>0.49</v>
+        <v>-1.94</v>
       </c>
       <c r="M33" t="n">
-        <v>101</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.94</v>
+        <v>-2.08</v>
       </c>
       <c r="P33" t="n">
-        <v>98.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2.1</v>
+        <v>1.8</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.08</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>43.52</v>
+        <v>42.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1.24</v>
+        <v>-0.62</v>
       </c>
       <c r="F34" t="n">
-        <v>2.93</v>
+        <v>-1.42</v>
       </c>
       <c r="G34" t="n">
-        <v>42.9</v>
+        <v>44.46</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.62</v>
+        <v>1.56</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.42</v>
+        <v>3.64</v>
       </c>
       <c r="J34" t="n">
-        <v>44.46</v>
+        <v>44.18</v>
       </c>
       <c r="K34" t="n">
-        <v>1.56</v>
+        <v>-0.28</v>
       </c>
       <c r="L34" t="n">
-        <v>3.64</v>
+        <v>-0.63</v>
       </c>
       <c r="M34" t="n">
-        <v>44.18</v>
+        <v>45</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.28</v>
+        <v>0.82</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.63</v>
+        <v>1.86</v>
       </c>
       <c r="P34" t="n">
-        <v>45</v>
+        <v>48.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.82</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.86</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="F35" t="n">
-        <v>1.69</v>
+        <v>-0.62</v>
       </c>
       <c r="G35" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.62</v>
+        <v>1.88</v>
       </c>
       <c r="J35" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="M35" t="n">
         <v>4.87</v>
       </c>
-      <c r="K35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.82</v>
-      </c>
       <c r="N35" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P35" t="n">
-        <v>4.82</v>
+        <v>5.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.03</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.31</v>
+        <v>10.26</v>
       </c>
       <c r="E36" t="n">
-        <v>0.16</v>
+        <v>-0.05</v>
       </c>
       <c r="F36" t="n">
-        <v>1.58</v>
+        <v>-0.48</v>
       </c>
       <c r="G36" t="n">
-        <v>10.26</v>
+        <v>10.46</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.48</v>
+        <v>1.95</v>
       </c>
       <c r="J36" t="n">
-        <v>10.46</v>
+        <v>10.33</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="L36" t="n">
-        <v>1.95</v>
+        <v>-1.24</v>
       </c>
       <c r="M36" t="n">
-        <v>10.33</v>
+        <v>10.42</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="O36" t="n">
-        <v>-1.24</v>
+        <v>0.87</v>
       </c>
       <c r="P36" t="n">
-        <v>10.33</v>
+        <v>10.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.13</v>
+        <v>0.34</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.24</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>419.8</v>
+        <v>412.4</v>
       </c>
       <c r="E37" t="n">
-        <v>12.2</v>
+        <v>-7.4</v>
       </c>
       <c r="F37" t="n">
-        <v>2.99</v>
+        <v>-1.76</v>
       </c>
       <c r="G37" t="n">
-        <v>412.4</v>
+        <v>415</v>
       </c>
       <c r="H37" t="n">
-        <v>-7.4</v>
+        <v>2.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.76</v>
+        <v>0.63</v>
       </c>
       <c r="J37" t="n">
-        <v>415</v>
+        <v>418.2</v>
       </c>
       <c r="K37" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="M37" t="n">
-        <v>418.2</v>
+        <v>421.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="P37" t="n">
-        <v>421.2</v>
+        <v>427</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.34</v>
+        <v>16.32</v>
       </c>
       <c r="E38" t="n">
-        <v>0.39</v>
+        <v>-0.02</v>
       </c>
       <c r="F38" t="n">
-        <v>2.45</v>
+        <v>-0.12</v>
       </c>
       <c r="G38" t="n">
-        <v>16.32</v>
+        <v>15.95</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.02</v>
+        <v>-0.37</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.12</v>
+        <v>-2.27</v>
       </c>
       <c r="J38" t="n">
-        <v>15.95</v>
+        <v>15.92</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.37</v>
+        <v>-0.03</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.27</v>
+        <v>-0.19</v>
       </c>
       <c r="M38" t="n">
-        <v>15.92</v>
+        <v>16.24</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.03</v>
+        <v>0.32</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.19</v>
+        <v>2.01</v>
       </c>
       <c r="P38" t="n">
-        <v>16.24</v>
+        <v>16.39</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="R38" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>627.5</v>
+        <v>608</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5</v>
+        <v>-19.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.24</v>
+        <v>-3.11</v>
       </c>
       <c r="G39" t="n">
-        <v>608</v>
+        <v>631.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-19.5</v>
+        <v>23.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.11</v>
+        <v>3.87</v>
       </c>
       <c r="J39" t="n">
-        <v>631.5</v>
+        <v>655</v>
       </c>
       <c r="K39" t="n">
         <v>23.5</v>
       </c>
       <c r="L39" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="M39" t="n">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="N39" t="n">
-        <v>23.5</v>
+        <v>14</v>
       </c>
       <c r="O39" t="n">
-        <v>3.72</v>
+        <v>2.14</v>
       </c>
       <c r="P39" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.14</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.5</v>
+        <v>61</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9</v>
+        <v>-1.5</v>
       </c>
       <c r="F40" t="n">
-        <v>1.46</v>
+        <v>-2.4</v>
       </c>
       <c r="G40" t="n">
-        <v>61</v>
+        <v>62.55</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5</v>
+        <v>1.55</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.4</v>
+        <v>2.54</v>
       </c>
       <c r="J40" t="n">
-        <v>62.55</v>
+        <v>62.75</v>
       </c>
       <c r="K40" t="n">
-        <v>1.55</v>
+        <v>0.2</v>
       </c>
       <c r="L40" t="n">
-        <v>2.54</v>
+        <v>0.32</v>
       </c>
       <c r="M40" t="n">
-        <v>62.75</v>
+        <v>60.25</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2</v>
+        <v>-2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>0.32</v>
+        <v>-3.98</v>
       </c>
       <c r="P40" t="n">
-        <v>60.25</v>
+        <v>62.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>-2.5</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.98</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.66</v>
+        <v>21.9</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.02</v>
+        <v>0.24</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.09</v>
+        <v>1.11</v>
       </c>
       <c r="G41" t="n">
-        <v>21.9</v>
+        <v>21.87</v>
       </c>
       <c r="H41" t="n">
-        <v>0.24</v>
+        <v>-0.03</v>
       </c>
       <c r="I41" t="n">
-        <v>1.11</v>
+        <v>-0.14</v>
       </c>
       <c r="J41" t="n">
-        <v>21.87</v>
+        <v>21.83</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="M41" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.18</v>
+        <v>0.78</v>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="R41" t="n">
-        <v>0.78</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>56.56</v>
+        <v>58.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.19</v>
+        <v>1.94</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.33</v>
+        <v>3.43</v>
       </c>
       <c r="G42" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="H42" t="n">
-        <v>1.94</v>
+        <v>0.1</v>
       </c>
       <c r="I42" t="n">
-        <v>3.43</v>
+        <v>0.17</v>
       </c>
       <c r="J42" t="n">
-        <v>58.6</v>
+        <v>58.55</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="L42" t="n">
-        <v>0.17</v>
+        <v>-0.09</v>
       </c>
       <c r="M42" t="n">
-        <v>58.55</v>
+        <v>58.85</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.09</v>
+        <v>0.51</v>
       </c>
       <c r="P42" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="R42" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>35.78</v>
+        <v>36.15</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.18</v>
+        <v>0.37</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.5</v>
+        <v>1.03</v>
       </c>
       <c r="G43" t="n">
-        <v>36.15</v>
+        <v>36.17</v>
       </c>
       <c r="H43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J43" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="N43" t="n">
         <v>0.37</v>
       </c>
-      <c r="I43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J43" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M43" t="n">
-        <v>36.28</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.11</v>
-      </c>
       <c r="O43" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="P43" t="n">
-        <v>36.65</v>
+        <v>36.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="R43" t="n">
-        <v>1.02</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F44" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="P44" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="Q44" t="n">
         <v>-0.15</v>
       </c>
-      <c r="G44" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P44" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="R44" t="n">
-        <v>-1.94</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.42</v>
+        <v>-1.67</v>
       </c>
       <c r="G45" t="n">
         <v>2.35</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="P45" t="n">
         <v>2.35</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.37</v>
-      </c>
       <c r="Q45" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="E46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="K46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F46" t="n">
+      <c r="L46" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="M46" t="n">
         <v>3.32</v>
       </c>
-      <c r="K46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.29</v>
-      </c>
       <c r="N46" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.9</v>
+        <v>0.91</v>
       </c>
       <c r="P46" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>0.91</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.65</v>
+        <v>10.72</v>
       </c>
       <c r="E47" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>0.19</v>
+        <v>0.66</v>
       </c>
       <c r="G47" t="n">
-        <v>10.72</v>
+        <v>10.73</v>
       </c>
       <c r="H47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I47" t="n">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
       <c r="J47" t="n">
-        <v>10.73</v>
+        <v>10.79</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L47" t="n">
-        <v>0.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>10.79</v>
+        <v>10.92</v>
       </c>
       <c r="N47" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="P47" t="n">
-        <v>10.92</v>
+        <v>10.74</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="R47" t="n">
-        <v>1.2</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.355</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.345</v>
-      </c>
       <c r="H48" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I48" t="n">
-        <v>-2.82</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
-        <v>0.355</v>
+        <v>0.375</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L48" t="n">
-        <v>2.9</v>
+        <v>5.63</v>
       </c>
       <c r="M48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P48" t="n">
         <v>0.375</v>
       </c>
-      <c r="N48" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O48" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.38</v>
-      </c>
       <c r="Q48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>1.33</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.52</v>
+        <v>1.32</v>
       </c>
       <c r="G49" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.59</v>
       </c>
-      <c r="H49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.68</v>
-      </c>
       <c r="N49" t="n">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="O49" t="n">
-        <v>0.21</v>
+        <v>-1.92</v>
       </c>
       <c r="P49" t="n">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="R49" t="n">
-        <v>-1.92</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.05</v>
       </c>
-      <c r="E50" t="n">
+      <c r="H50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F50" t="n">
+      <c r="I50" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="G50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.95</v>
-      </c>
       <c r="J50" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="K50" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L50" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="O50" t="n">
-        <v>-2.86</v>
+        <v>-0.98</v>
       </c>
       <c r="P50" t="n">
         <v>1.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F51" t="n">
-        <v>0.46</v>
+        <v>-0.46</v>
       </c>
       <c r="G51" t="n">
-        <v>4.31</v>
+        <v>4.39</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.46</v>
+        <v>1.86</v>
       </c>
       <c r="J51" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="K51" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>1.86</v>
+        <v>-1.59</v>
       </c>
       <c r="M51" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.59</v>
+        <v>-4.17</v>
       </c>
       <c r="P51" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="R51" t="n">
-        <v>-4.17</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.8</v>
+        <v>10.87</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.83</v>
+        <v>0.65</v>
       </c>
       <c r="G52" t="n">
         <v>10.87</v>
       </c>
       <c r="H52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>10.87</v>
+        <v>10.97</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="M52" t="n">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="O52" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="P52" t="n">
-        <v>10.96</v>
+        <v>11.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.09</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.49</v>
+        <v>8.16</v>
       </c>
       <c r="E53" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J53" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="M53" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P53" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="Q53" t="n">
         <v>0.08</v>
       </c>
-      <c r="F53" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G53" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-3.89</v>
-      </c>
-      <c r="J53" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="M53" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="P53" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="R53" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="54">
@@ -3742,46 +3742,46 @@
         <v>0.42</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.33</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="J54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>2.38</v>
+        <v>-1.16</v>
       </c>
       <c r="M54" t="n">
         <v>0.425</v>
       </c>
       <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="O54" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.705</v>
+        <v>0.68</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.7</v>
+        <v>-3.55</v>
       </c>
       <c r="G55" t="n">
         <v>0.68</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>-3.55</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="M55" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.74</v>
+        <v>1.48</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>1.48</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.485</v>
       </c>
-      <c r="E56" t="n">
+      <c r="H56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F56" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="K56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.01</v>
-      </c>
       <c r="O56" t="n">
-        <v>2.06</v>
+        <v>-1.01</v>
       </c>
       <c r="P56" t="n">
-        <v>0.49</v>
+        <v>0.505</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.01</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.83</v>
+        <v>3.61</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.05</v>
+        <v>-0.22</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.29</v>
+        <v>-5.74</v>
       </c>
       <c r="G57" t="n">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.22</v>
+        <v>0.11</v>
       </c>
       <c r="I57" t="n">
-        <v>-5.74</v>
+        <v>3.05</v>
       </c>
       <c r="J57" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="P57" t="n">
         <v>3.72</v>
       </c>
-      <c r="K57" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3.75</v>
-      </c>
       <c r="Q57" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.53</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="58">
@@ -3990,46 +3990,46 @@
         <v>0.079</v>
       </c>
       <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="Q58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="F58" t="n">
+      <c r="R58" t="n">
         <v>-1.25</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="O58" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.27</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.29</v>
+        <v>21.7</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.26</v>
+        <v>0.41</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.21</v>
+        <v>1.93</v>
       </c>
       <c r="G59" t="n">
-        <v>21.7</v>
+        <v>21.36</v>
       </c>
       <c r="H59" t="n">
-        <v>0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="I59" t="n">
-        <v>1.93</v>
+        <v>-1.57</v>
       </c>
       <c r="J59" t="n">
-        <v>21.36</v>
+        <v>21.17</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.57</v>
+        <v>-0.89</v>
       </c>
       <c r="M59" t="n">
-        <v>21.17</v>
+        <v>21.39</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.19</v>
+        <v>0.22</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.89</v>
+        <v>1.04</v>
       </c>
       <c r="P59" t="n">
-        <v>21.39</v>
+        <v>20.95</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.22</v>
+        <v>-0.44</v>
       </c>
       <c r="R59" t="n">
-        <v>1.04</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.64</v>
+        <v>0.96</v>
       </c>
       <c r="G60" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="H60" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="I60" t="n">
-        <v>0.96</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="K60" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="L60" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="M60" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N60" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="O60" t="n">
-        <v>0.3</v>
+        <v>-2.42</v>
       </c>
       <c r="P60" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="R60" t="n">
-        <v>-2.42</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="E61" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="F61" t="n">
-        <v>6.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H61" t="n">
         <v>0.01</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J61" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="K61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N61" t="n">
         <v>0.01</v>
       </c>
-      <c r="L61" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q61" t="n">
         <v>0.04</v>
       </c>
-      <c r="O61" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R61" t="n">
-        <v>0.66</v>
+        <v>2.63</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-04-30 Close</t>
+          <t>2026-05-04 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-04-30 Change</t>
+          <t>2026-05-04 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-04-30 Change %</t>
+          <t>2026-05-04 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-04 Close</t>
+          <t>2026-05-05 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-04 Change</t>
+          <t>2026-05-05 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-04 Change %</t>
+          <t>2026-05-05 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-05 Close</t>
+          <t>2026-05-06 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change</t>
+          <t>2026-05-06 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change %</t>
+          <t>2026-05-06 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-06 Close</t>
+          <t>2026-05-07 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change</t>
+          <t>2026-05-07 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change %</t>
+          <t>2026-05-07 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-07 Close</t>
+          <t>2026-05-08 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change</t>
+          <t>2026-05-08 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change %</t>
+          <t>2026-05-08 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>140.2</v>
+        <v>143.4</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.57</v>
+        <v>2.28</v>
       </c>
       <c r="G3" t="n">
-        <v>143.4</v>
+        <v>136</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>-7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.28</v>
+        <v>-5.16</v>
       </c>
       <c r="J3" t="n">
-        <v>136</v>
+        <v>140.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.4</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.16</v>
+        <v>3.31</v>
       </c>
       <c r="M3" t="n">
-        <v>140.5</v>
+        <v>143.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
-        <v>143.1</v>
+        <v>138.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>-4.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.85</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>190.8</v>
+        <v>197</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="F4" t="n">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>197</v>
+        <v>192.2</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>-4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>-2.44</v>
       </c>
       <c r="J4" t="n">
-        <v>192.2</v>
+        <v>201.6</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.8</v>
+        <v>9.4</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.44</v>
+        <v>4.89</v>
       </c>
       <c r="M4" t="n">
-        <v>201.6</v>
+        <v>203.6</v>
       </c>
       <c r="N4" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>4.89</v>
+        <v>0.99</v>
       </c>
       <c r="P4" t="n">
-        <v>203.6</v>
+        <v>199</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>-4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0.99</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.08</v>
+        <v>5.94</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.46</v>
+        <v>-2.3</v>
       </c>
       <c r="G5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="J5" t="n">
         <v>5.94</v>
       </c>
-      <c r="H5" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.87</v>
-      </c>
       <c r="K5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P5" t="n">
         <v>5.94</v>
       </c>
-      <c r="N5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5.96</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.03</v>
+        <v>6.92</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.63</v>
+        <v>-1.56</v>
       </c>
       <c r="G6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P6" t="n">
         <v>6.92</v>
       </c>
-      <c r="H6" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6.99</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.58</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.06</v>
+        <v>5.09</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.32</v>
+        <v>0.59</v>
       </c>
       <c r="G7" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0.59</v>
+        <v>-0.79</v>
       </c>
       <c r="J7" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.04</v>
+        <v>0.1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.79</v>
+        <v>1.98</v>
       </c>
       <c r="M7" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.98</v>
+        <v>-0.19</v>
       </c>
       <c r="P7" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.19</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G8" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="E8" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8.84</v>
-      </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.68</v>
+        <v>-0.68</v>
       </c>
       <c r="J8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.06</v>
+        <v>0.15</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.68</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="9">
@@ -949,25 +949,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.15</v>
+        <v>7.12</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.72</v>
+        <v>-0.42</v>
       </c>
       <c r="G9" t="n">
-        <v>7.12</v>
+        <v>7.18</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.42</v>
+        <v>0.84</v>
       </c>
       <c r="J9" t="n">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="K9" t="n">
         <v>0.06</v>
@@ -976,22 +976,22 @@
         <v>0.84</v>
       </c>
       <c r="M9" t="n">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="O9" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="P9" t="n">
-        <v>7.27</v>
+        <v>7.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R9" t="n">
-        <v>0.41</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G10" t="n">
         <v>47.1</v>
       </c>
-      <c r="E10" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="G10" t="n">
-        <v>47.08</v>
-      </c>
       <c r="H10" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="J10" t="n">
-        <v>47.1</v>
+        <v>47.04</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="M10" t="n">
-        <v>47.04</v>
+        <v>47.82</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06</v>
+        <v>0.78</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.13</v>
+        <v>1.66</v>
       </c>
       <c r="P10" t="n">
-        <v>47.82</v>
+        <v>47.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.78</v>
+        <v>-0.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="P11" t="n">
         <v>4.61</v>
       </c>
-      <c r="E11" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.65</v>
-      </c>
       <c r="Q11" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.27</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.03</v>
+        <v>11.7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05</v>
+        <v>-0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>0.42</v>
+        <v>-2.74</v>
       </c>
       <c r="G12" t="n">
-        <v>11.7</v>
+        <v>11.68</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.74</v>
+        <v>-0.17</v>
       </c>
       <c r="J12" t="n">
         <v>11.68</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>11.68</v>
+        <v>10.69</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-8.48</v>
       </c>
       <c r="P12" t="n">
-        <v>10.69</v>
+        <v>10.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.99</v>
+        <v>-0.1</v>
       </c>
       <c r="R12" t="n">
-        <v>-8.48</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.38</v>
+        <v>28.62</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-2.59</v>
       </c>
       <c r="G13" t="n">
-        <v>28.62</v>
+        <v>28.56</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.76</v>
+        <v>-0.06</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.59</v>
+        <v>-0.21</v>
       </c>
       <c r="J13" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.06</v>
+        <v>-0.52</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.21</v>
+        <v>-1.82</v>
       </c>
       <c r="M13" t="n">
-        <v>28.04</v>
+        <v>26.42</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.52</v>
+        <v>-1.62</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.82</v>
+        <v>-5.78</v>
       </c>
       <c r="P13" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.62</v>
+        <v>0.02</v>
       </c>
       <c r="R13" t="n">
-        <v>-5.78</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.09</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.24</v>
+        <v>5.2</v>
       </c>
       <c r="G14" t="n">
         <v>2.83</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-3.89</v>
       </c>
       <c r="M14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.89</v>
+        <v>-0.37</v>
       </c>
       <c r="P14" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.37</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1.17</v>
+        <v>-2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.12</v>
+        <v>-0.39</v>
       </c>
       <c r="J15" t="n">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.39</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="O15" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G16" t="n">
         <v>5.26</v>
       </c>
-      <c r="E16" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.25</v>
-      </c>
       <c r="H16" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="J16" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="L16" t="n">
-        <v>0.19</v>
+        <v>-0.38</v>
       </c>
       <c r="M16" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P16" t="n">
         <v>5.24</v>
       </c>
-      <c r="N16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5.27</v>
-      </c>
       <c r="Q16" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="R16" t="n">
-        <v>0.57</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.22</v>
+        <v>0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.49</v>
+        <v>1.06</v>
       </c>
       <c r="G17" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>1.06</v>
+        <v>-1.31</v>
       </c>
       <c r="J17" t="n">
         <v>3.78</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P17" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.62</v>
+        <v>3.51</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.16</v>
+        <v>-3.04</v>
       </c>
       <c r="G18" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.04</v>
+        <v>-0.28</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.28</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
         <v>3.54</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0.04</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>63.25</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="G19" t="n">
-        <v>63.25</v>
+        <v>63.5</v>
       </c>
       <c r="H19" t="n">
         <v>0.25</v>
@@ -1587,31 +1587,31 @@
         <v>0.4</v>
       </c>
       <c r="J19" t="n">
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>66</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>-0.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.62</v>
+        <v>28.78</v>
       </c>
       <c r="E20" t="n">
-        <v>1.22</v>
+        <v>0.16</v>
       </c>
       <c r="F20" t="n">
-        <v>4.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>28.78</v>
+        <v>29.12</v>
       </c>
       <c r="H20" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="J20" t="n">
-        <v>29.12</v>
+        <v>29.9</v>
       </c>
       <c r="K20" t="n">
-        <v>0.34</v>
+        <v>0.78</v>
       </c>
       <c r="L20" t="n">
-        <v>1.18</v>
+        <v>2.68</v>
       </c>
       <c r="M20" t="n">
-        <v>29.9</v>
+        <v>31.18</v>
       </c>
       <c r="N20" t="n">
-        <v>0.78</v>
+        <v>1.28</v>
       </c>
       <c r="O20" t="n">
-        <v>2.68</v>
+        <v>4.28</v>
       </c>
       <c r="P20" t="n">
-        <v>31.18</v>
+        <v>31.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.28</v>
+        <v>0.08</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.14</v>
+        <v>-1.34</v>
       </c>
       <c r="G21" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.34</v>
+        <v>-0.19</v>
       </c>
       <c r="J21" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.19</v>
+        <v>1.17</v>
       </c>
       <c r="M21" t="n">
-        <v>5.19</v>
+        <v>5.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="O21" t="n">
-        <v>1.17</v>
+        <v>3.08</v>
       </c>
       <c r="P21" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>3.08</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>84.59999999999999</v>
+        <v>83.95</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.85</v>
+        <v>-0.65</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.99</v>
+        <v>-0.77</v>
       </c>
       <c r="G22" t="n">
-        <v>83.95</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.65</v>
+        <v>-0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.77</v>
+        <v>-0.12</v>
       </c>
       <c r="J22" t="n">
-        <v>83.84999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1</v>
+        <v>0.85</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.12</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>84.7</v>
+        <v>85.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="P22" t="n">
-        <v>85.3</v>
+        <v>85.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="R22" t="n">
-        <v>0.71</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.94</v>
+        <v>26.14</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.81</v>
       </c>
       <c r="G23" t="n">
-        <v>26.14</v>
+        <v>26.08</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2</v>
+        <v>-0.06</v>
       </c>
       <c r="I23" t="n">
-        <v>4.81</v>
+        <v>-0.23</v>
       </c>
       <c r="J23" t="n">
-        <v>26.08</v>
+        <v>27.4</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.06</v>
+        <v>1.32</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.23</v>
+        <v>5.06</v>
       </c>
       <c r="M23" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P23" t="n">
         <v>27.4</v>
       </c>
-      <c r="N23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O23" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="P23" t="n">
-        <v>27.52</v>
-      </c>
       <c r="Q23" t="n">
-        <v>0.12</v>
+        <v>-0.12</v>
       </c>
       <c r="R23" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25.02</v>
+        <v>24.12</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.38</v>
+        <v>-0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5</v>
+        <v>-3.6</v>
       </c>
       <c r="G24" t="n">
-        <v>24.12</v>
+        <v>24.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9</v>
+        <v>0.18</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.6</v>
+        <v>0.75</v>
       </c>
       <c r="J24" t="n">
-        <v>24.3</v>
+        <v>24.68</v>
       </c>
       <c r="K24" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="L24" t="n">
-        <v>0.75</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>24.68</v>
+        <v>26.46</v>
       </c>
       <c r="N24" t="n">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="O24" t="n">
-        <v>1.56</v>
+        <v>7.21</v>
       </c>
       <c r="P24" t="n">
-        <v>26.46</v>
+        <v>28.24</v>
       </c>
       <c r="Q24" t="n">
         <v>1.78</v>
       </c>
       <c r="R24" t="n">
-        <v>7.21</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29.02</v>
+        <v>30.98</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.12</v>
+        <v>1.96</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.72</v>
+        <v>6.75</v>
       </c>
       <c r="G25" t="n">
-        <v>30.98</v>
+        <v>30.46</v>
       </c>
       <c r="H25" t="n">
-        <v>1.96</v>
+        <v>-0.52</v>
       </c>
       <c r="I25" t="n">
-        <v>6.75</v>
+        <v>-1.68</v>
       </c>
       <c r="J25" t="n">
-        <v>30.46</v>
+        <v>30.82</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.52</v>
+        <v>0.36</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.68</v>
+        <v>1.18</v>
       </c>
       <c r="M25" t="n">
-        <v>30.82</v>
+        <v>31.12</v>
       </c>
       <c r="N25" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="P25" t="n">
-        <v>31.12</v>
+        <v>31.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>0.97</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46.6</v>
+        <v>48.7</v>
       </c>
       <c r="E26" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="F26" t="n">
-        <v>8.220000000000001</v>
+        <v>4.51</v>
       </c>
       <c r="G26" t="n">
-        <v>48.7</v>
+        <v>47</v>
       </c>
       <c r="H26" t="n">
-        <v>2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="I26" t="n">
-        <v>4.51</v>
+        <v>-3.49</v>
       </c>
       <c r="J26" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.7</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.49</v>
+        <v>8.51</v>
       </c>
       <c r="M26" t="n">
-        <v>51</v>
+        <v>58.55</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>7.55</v>
       </c>
       <c r="O26" t="n">
-        <v>8.51</v>
+        <v>14.8</v>
       </c>
       <c r="P26" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.55</v>
+        <v>-1.9</v>
       </c>
       <c r="R26" t="n">
-        <v>14.8</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>467.8</v>
+        <v>473</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.4</v>
+        <v>5.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.38</v>
+        <v>1.11</v>
       </c>
       <c r="G27" t="n">
-        <v>473</v>
+        <v>472.2</v>
       </c>
       <c r="H27" t="n">
-        <v>5.2</v>
+        <v>-0.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.11</v>
+        <v>-0.17</v>
       </c>
       <c r="J27" t="n">
-        <v>472.2</v>
+        <v>463</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.17</v>
+        <v>-1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>463</v>
+        <v>477.4</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.95</v>
+        <v>3.11</v>
       </c>
       <c r="P27" t="n">
-        <v>477.4</v>
+        <v>471.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>14.4</v>
+        <v>-6</v>
       </c>
       <c r="R27" t="n">
-        <v>3.11</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>126</v>
+        <v>131.7</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.6</v>
+        <v>5.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.52</v>
+        <v>4.52</v>
       </c>
       <c r="G28" t="n">
-        <v>131.7</v>
+        <v>131.2</v>
       </c>
       <c r="H28" t="n">
-        <v>5.7</v>
+        <v>-0.5</v>
       </c>
       <c r="I28" t="n">
-        <v>4.52</v>
+        <v>-0.38</v>
       </c>
       <c r="J28" t="n">
-        <v>131.2</v>
+        <v>134.2</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.5</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.38</v>
+        <v>2.29</v>
       </c>
       <c r="M28" t="n">
-        <v>134.2</v>
+        <v>140.9</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.29</v>
+        <v>4.99</v>
       </c>
       <c r="P28" t="n">
-        <v>140.9</v>
+        <v>139</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.7</v>
+        <v>-1.9</v>
       </c>
       <c r="R28" t="n">
-        <v>4.99</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>116.3</v>
+        <v>116.8</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.2</v>
+        <v>0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.02</v>
+        <v>0.43</v>
       </c>
       <c r="G29" t="n">
-        <v>116.8</v>
+        <v>116.2</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I29" t="n">
-        <v>0.43</v>
+        <v>-0.51</v>
       </c>
       <c r="J29" t="n">
-        <v>116.2</v>
+        <v>116.4</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.51</v>
+        <v>0.17</v>
       </c>
       <c r="M29" t="n">
-        <v>116.4</v>
+        <v>119</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0.17</v>
+        <v>2.23</v>
       </c>
       <c r="P29" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.6</v>
+        <v>-0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.23</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>83.25</v>
+        <v>84.45</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="F30" t="n">
-        <v>0.12</v>
+        <v>1.44</v>
       </c>
       <c r="G30" t="n">
-        <v>84.45</v>
+        <v>83.55</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>1.44</v>
+        <v>-1.07</v>
       </c>
       <c r="J30" t="n">
-        <v>83.55</v>
+        <v>82.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.9</v>
+        <v>-1.05</v>
       </c>
       <c r="L30" t="n">
-        <v>-1.07</v>
+        <v>-1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>82.5</v>
+        <v>84.25</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.05</v>
+        <v>1.75</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.26</v>
+        <v>2.12</v>
       </c>
       <c r="P30" t="n">
-        <v>84.25</v>
+        <v>84.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.75</v>
+        <v>-0.2</v>
       </c>
       <c r="R30" t="n">
-        <v>2.12</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>118.7</v>
+        <v>122.8</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.2</v>
+        <v>4.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-1</v>
+        <v>3.45</v>
       </c>
       <c r="G31" t="n">
-        <v>122.8</v>
+        <v>125.4</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="I31" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="J31" t="n">
-        <v>125.4</v>
+        <v>131.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="L31" t="n">
-        <v>2.12</v>
+        <v>4.94</v>
       </c>
       <c r="M31" t="n">
-        <v>131.6</v>
+        <v>137.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="O31" t="n">
-        <v>4.94</v>
+        <v>4.33</v>
       </c>
       <c r="P31" t="n">
-        <v>137.3</v>
+        <v>145.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="R31" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>70.90000000000001</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>5.1</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>7.75</v>
+        <v>1.76</v>
       </c>
       <c r="G32" t="n">
-        <v>72.15000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.25</v>
+        <v>-1.35</v>
       </c>
       <c r="I32" t="n">
-        <v>1.76</v>
+        <v>-1.87</v>
       </c>
       <c r="J32" t="n">
-        <v>70.8</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.35</v>
+        <v>4.05</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.87</v>
+        <v>5.72</v>
       </c>
       <c r="M32" t="n">
-        <v>74.84999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="N32" t="n">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>5.72</v>
+        <v>2.54</v>
       </c>
       <c r="P32" t="n">
-        <v>76.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.54</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>102.5</v>
+        <v>103</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.8</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.36</v>
+        <v>0.49</v>
       </c>
       <c r="G33" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
       <c r="I33" t="n">
-        <v>0.49</v>
+        <v>-1.94</v>
       </c>
       <c r="J33" t="n">
-        <v>101</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.94</v>
+        <v>-2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>98.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O33" t="n">
-        <v>-2.08</v>
+        <v>1.82</v>
       </c>
       <c r="P33" t="n">
-        <v>100.7</v>
+        <v>99.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>-0.95</v>
       </c>
       <c r="R33" t="n">
-        <v>1.82</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>42.9</v>
+        <v>44.46</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.62</v>
+        <v>1.56</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.42</v>
+        <v>3.64</v>
       </c>
       <c r="G34" t="n">
-        <v>44.46</v>
+        <v>44.18</v>
       </c>
       <c r="H34" t="n">
-        <v>1.56</v>
+        <v>-0.28</v>
       </c>
       <c r="I34" t="n">
-        <v>3.64</v>
+        <v>-0.63</v>
       </c>
       <c r="J34" t="n">
-        <v>44.18</v>
+        <v>45</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.28</v>
+        <v>0.82</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.63</v>
+        <v>1.86</v>
       </c>
       <c r="M34" t="n">
-        <v>45</v>
+        <v>48.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0.82</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.86</v>
+        <v>7.56</v>
       </c>
       <c r="P34" t="n">
-        <v>48.4</v>
+        <v>52.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="R34" t="n">
-        <v>7.56</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.62</v>
+        <v>1.88</v>
       </c>
       <c r="G35" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="J35" t="n">
         <v>4.87</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.82</v>
-      </c>
       <c r="K35" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.03</v>
+        <v>1.04</v>
       </c>
       <c r="M35" t="n">
-        <v>4.87</v>
+        <v>5.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="O35" t="n">
-        <v>1.04</v>
+        <v>2.87</v>
       </c>
       <c r="P35" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="R35" t="n">
-        <v>2.87</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.26</v>
+        <v>10.46</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.48</v>
+        <v>1.95</v>
       </c>
       <c r="G36" t="n">
-        <v>10.46</v>
+        <v>10.33</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="I36" t="n">
-        <v>1.95</v>
+        <v>-1.24</v>
       </c>
       <c r="J36" t="n">
-        <v>10.33</v>
+        <v>10.42</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.24</v>
+        <v>0.87</v>
       </c>
       <c r="M36" t="n">
-        <v>10.42</v>
+        <v>10.76</v>
       </c>
       <c r="N36" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="O36" t="n">
-        <v>0.87</v>
+        <v>3.26</v>
       </c>
       <c r="P36" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.34</v>
+        <v>-0.03</v>
       </c>
       <c r="R36" t="n">
-        <v>3.26</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>412.4</v>
+        <v>415</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.4</v>
+        <v>2.6</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.76</v>
+        <v>0.63</v>
       </c>
       <c r="G37" t="n">
-        <v>415</v>
+        <v>418.2</v>
       </c>
       <c r="H37" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="J37" t="n">
-        <v>418.2</v>
+        <v>421.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="M37" t="n">
-        <v>421.2</v>
+        <v>427</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
       <c r="P37" t="n">
-        <v>427</v>
+        <v>424.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.8</v>
+        <v>-2.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.32</v>
+        <v>15.95</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.02</v>
+        <v>-0.37</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.12</v>
+        <v>-2.27</v>
       </c>
       <c r="G38" t="n">
-        <v>15.95</v>
+        <v>15.92</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.37</v>
+        <v>-0.03</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.27</v>
+        <v>-0.19</v>
       </c>
       <c r="J38" t="n">
-        <v>15.92</v>
+        <v>16.24</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.03</v>
+        <v>0.32</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.19</v>
+        <v>2.01</v>
       </c>
       <c r="M38" t="n">
-        <v>16.24</v>
+        <v>16.39</v>
       </c>
       <c r="N38" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="O38" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
       <c r="P38" t="n">
-        <v>16.39</v>
+        <v>16.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="R38" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>608</v>
+        <v>631.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-19.5</v>
+        <v>23.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.11</v>
+        <v>3.87</v>
       </c>
       <c r="G39" t="n">
-        <v>631.5</v>
+        <v>655</v>
       </c>
       <c r="H39" t="n">
         <v>23.5</v>
       </c>
       <c r="I39" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="J39" t="n">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="K39" t="n">
-        <v>23.5</v>
+        <v>14</v>
       </c>
       <c r="L39" t="n">
-        <v>3.72</v>
+        <v>2.14</v>
       </c>
       <c r="M39" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="N39" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="O39" t="n">
-        <v>2.14</v>
+        <v>-0.6</v>
       </c>
       <c r="P39" t="n">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="Q39" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.6</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>61</v>
+        <v>62.55</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5</v>
+        <v>1.55</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.4</v>
+        <v>2.54</v>
       </c>
       <c r="G40" t="n">
-        <v>62.55</v>
+        <v>62.75</v>
       </c>
       <c r="H40" t="n">
-        <v>1.55</v>
+        <v>0.2</v>
       </c>
       <c r="I40" t="n">
-        <v>2.54</v>
+        <v>0.32</v>
       </c>
       <c r="J40" t="n">
-        <v>62.75</v>
+        <v>60.25</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2</v>
+        <v>-2.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.32</v>
+        <v>-3.98</v>
       </c>
       <c r="M40" t="n">
-        <v>60.25</v>
+        <v>62.25</v>
       </c>
       <c r="N40" t="n">
-        <v>-2.5</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.98</v>
+        <v>3.32</v>
       </c>
       <c r="P40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>-0.95</v>
       </c>
       <c r="R40" t="n">
-        <v>3.32</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.9</v>
+        <v>21.87</v>
       </c>
       <c r="E41" t="n">
-        <v>0.24</v>
+        <v>-0.03</v>
       </c>
       <c r="F41" t="n">
-        <v>1.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G41" t="n">
-        <v>21.87</v>
+        <v>21.83</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="J41" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.18</v>
+        <v>0.78</v>
       </c>
       <c r="M41" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="N41" t="n">
-        <v>0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="O41" t="n">
-        <v>0.78</v>
+        <v>-0.55</v>
       </c>
       <c r="P41" t="n">
-        <v>21.88</v>
+        <v>21.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.55</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="E42" t="n">
-        <v>1.94</v>
+        <v>0.1</v>
       </c>
       <c r="F42" t="n">
-        <v>3.43</v>
+        <v>0.17</v>
       </c>
       <c r="G42" t="n">
-        <v>58.6</v>
+        <v>58.55</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="I42" t="n">
-        <v>0.17</v>
+        <v>-0.09</v>
       </c>
       <c r="J42" t="n">
-        <v>58.55</v>
+        <v>58.85</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.09</v>
+        <v>0.51</v>
       </c>
       <c r="M42" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="N42" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="O42" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="P42" t="n">
-        <v>58.86</v>
+        <v>58.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="R42" t="n">
-        <v>0.02</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36.15</v>
+        <v>36.17</v>
       </c>
       <c r="E43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G43" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="K43" t="n">
         <v>0.37</v>
       </c>
-      <c r="F43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G43" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J43" t="n">
-        <v>36.28</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.11</v>
-      </c>
       <c r="L43" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="M43" t="n">
-        <v>36.65</v>
+        <v>36.7</v>
       </c>
       <c r="N43" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="O43" t="n">
-        <v>1.02</v>
+        <v>0.14</v>
       </c>
       <c r="P43" t="n">
-        <v>36.7</v>
+        <v>36.56</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="R43" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.65</v>
+        <v>6.68</v>
       </c>
       <c r="E44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="H44" t="n">
         <v>0.01</v>
       </c>
-      <c r="F44" t="n">
+      <c r="I44" t="n">
         <v>0.15</v>
       </c>
-      <c r="G44" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.45</v>
-      </c>
       <c r="J44" t="n">
-        <v>6.69</v>
+        <v>6.56</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01</v>
+        <v>-0.13</v>
       </c>
       <c r="L44" t="n">
-        <v>0.15</v>
+        <v>-1.94</v>
       </c>
       <c r="M44" t="n">
-        <v>6.56</v>
+        <v>6.41</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="O44" t="n">
-        <v>-1.94</v>
+        <v>-2.29</v>
       </c>
       <c r="P44" t="n">
-        <v>6.41</v>
+        <v>6.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.29</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3184,46 +3184,46 @@
         <v>2.35</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M45" t="n">
         <v>2.35</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.37</v>
-      </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.84</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3</v>
+        <v>0.61</v>
       </c>
       <c r="G46" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="J46" t="n">
         <v>3.32</v>
       </c>
-      <c r="H46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.29</v>
-      </c>
       <c r="K46" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.9</v>
+        <v>0.91</v>
       </c>
       <c r="M46" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="N46" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O46" t="n">
-        <v>0.91</v>
+        <v>1.2</v>
       </c>
       <c r="P46" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R46" t="n">
-        <v>1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.72</v>
+        <v>10.73</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F47" t="n">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
       <c r="G47" t="n">
-        <v>10.73</v>
+        <v>10.79</v>
       </c>
       <c r="H47" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>10.79</v>
+        <v>10.92</v>
       </c>
       <c r="K47" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="M47" t="n">
-        <v>10.92</v>
+        <v>10.74</v>
       </c>
       <c r="N47" t="n">
-        <v>0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="O47" t="n">
-        <v>1.2</v>
+        <v>-1.65</v>
       </c>
       <c r="P47" t="n">
-        <v>10.74</v>
+        <v>10.66</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.65</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.345</v>
+        <v>0.355</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.82</v>
+        <v>2.9</v>
       </c>
       <c r="G48" t="n">
-        <v>0.355</v>
+        <v>0.375</v>
       </c>
       <c r="H48" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>5.63</v>
       </c>
       <c r="J48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M48" t="n">
         <v>0.375</v>
       </c>
-      <c r="K48" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L48" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="P48" t="n">
         <v>0.38</v>
       </c>
-      <c r="N48" t="n">
+      <c r="Q48" t="n">
         <v>0.005</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>1.33</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="R48" t="n">
-        <v>-1.32</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J49" t="n">
         <v>4.59</v>
       </c>
-      <c r="E49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.68</v>
-      </c>
       <c r="K49" t="n">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="L49" t="n">
-        <v>0.21</v>
+        <v>-1.92</v>
       </c>
       <c r="M49" t="n">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.92</v>
+        <v>1.09</v>
       </c>
       <c r="P49" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="Q49" t="n">
         <v>0.05</v>
       </c>
       <c r="R49" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="50">
@@ -3491,40 +3491,40 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0.95</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H50" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I50" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="L50" t="n">
-        <v>-2.86</v>
+        <v>-0.98</v>
       </c>
       <c r="M50" t="n">
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.01</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.31</v>
+        <v>4.39</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.46</v>
+        <v>1.86</v>
       </c>
       <c r="G51" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="H51" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>1.86</v>
+        <v>-1.59</v>
       </c>
       <c r="J51" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.59</v>
+        <v>-4.17</v>
       </c>
       <c r="M51" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="O51" t="n">
-        <v>-4.17</v>
+        <v>-0.97</v>
       </c>
       <c r="P51" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.97</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="52">
@@ -3618,46 +3618,46 @@
         <v>10.87</v>
       </c>
       <c r="E52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>10.87</v>
+        <v>10.97</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="J52" t="n">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="L52" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="M52" t="n">
-        <v>10.96</v>
+        <v>11.14</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.09</v>
+        <v>1.64</v>
       </c>
       <c r="P52" t="n">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="R52" t="n">
-        <v>1.64</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.16</v>
+        <v>8.23</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.89</v>
+        <v>0.86</v>
       </c>
       <c r="G53" t="n">
-        <v>8.23</v>
+        <v>8.18</v>
       </c>
       <c r="H53" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="J53" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K53" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I53" t="n">
+      <c r="L53" t="n">
         <v>0.86</v>
       </c>
-      <c r="J53" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="K53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-0.61</v>
-      </c>
       <c r="M53" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="N53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="O53" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="P53" t="n">
-        <v>8.33</v>
+        <v>8.26</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R53" t="n">
-        <v>0.97</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="G54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="H54" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>2.38</v>
+        <v>-1.16</v>
       </c>
       <c r="J54" t="n">
         <v>0.425</v>
       </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L54" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="P54" t="n">
         <v>0.425</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.42</v>
-      </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="55">
@@ -3804,46 +3804,46 @@
         <v>0.68</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.55</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="J55" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="Q55" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L55" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.005</v>
-      </c>
       <c r="R55" t="n">
-        <v>0.73</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.495</v>
       </c>
-      <c r="E56" t="n">
+      <c r="H56" t="n">
         <v>0.01</v>
       </c>
-      <c r="F56" t="n">
+      <c r="I56" t="n">
         <v>2.06</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-2.02</v>
-      </c>
       <c r="J56" t="n">
-        <v>0.495</v>
+        <v>0.49</v>
       </c>
       <c r="K56" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>2.06</v>
+        <v>-1.01</v>
       </c>
       <c r="M56" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P56" t="n">
         <v>0.49</v>
       </c>
-      <c r="N56" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="O56" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.505</v>
-      </c>
       <c r="Q56" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="R56" t="n">
-        <v>3.06</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.22</v>
+        <v>0.11</v>
       </c>
       <c r="F57" t="n">
-        <v>-5.74</v>
+        <v>3.05</v>
       </c>
       <c r="G57" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="M57" t="n">
         <v>3.72</v>
       </c>
-      <c r="H57" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.75</v>
-      </c>
       <c r="N57" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.53</v>
+        <v>-0.8</v>
       </c>
       <c r="P57" t="n">
         <v>3.72</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.079</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.081</v>
-      </c>
       <c r="H58" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="I58" t="n">
-        <v>2.53</v>
+        <v>-2.47</v>
       </c>
       <c r="J58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.079</v>
       </c>
-      <c r="K58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="P58" t="n">
         <v>0.08</v>
       </c>
-      <c r="N58" t="n">
+      <c r="Q58" t="n">
         <v>0.001</v>
       </c>
-      <c r="O58" t="n">
+      <c r="R58" t="n">
         <v>1.27</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="R58" t="n">
-        <v>-1.25</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.7</v>
+        <v>21.36</v>
       </c>
       <c r="E59" t="n">
-        <v>0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="F59" t="n">
-        <v>1.93</v>
+        <v>-1.57</v>
       </c>
       <c r="G59" t="n">
-        <v>21.36</v>
+        <v>21.17</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.57</v>
+        <v>-0.89</v>
       </c>
       <c r="J59" t="n">
-        <v>21.17</v>
+        <v>21.39</v>
       </c>
       <c r="K59" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="P59" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="R59" t="n">
         <v>-0.19</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="M59" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P59" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="R59" t="n">
-        <v>-2.06</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="F60" t="n">
-        <v>0.96</v>
+        <v>5.1</v>
       </c>
       <c r="G60" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="H60" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3</v>
+        <v>-2.42</v>
       </c>
       <c r="M60" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="O60" t="n">
-        <v>-2.42</v>
+        <v>1.24</v>
       </c>
       <c r="P60" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>1.24</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="E61" t="n">
         <v>0.01</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G61" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="H61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K61" t="n">
         <v>0.01</v>
       </c>
-      <c r="I61" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P61" t="n">
         <v>1.51</v>
       </c>
-      <c r="K61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L61" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Q61" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R61" t="n">
-        <v>2.63</v>
+        <v>-3.21</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-04 Close</t>
+          <t>2026-05-05 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-04 Change</t>
+          <t>2026-05-05 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-04 Change %</t>
+          <t>2026-05-05 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-05 Close</t>
+          <t>2026-05-06 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change</t>
+          <t>2026-05-06 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change %</t>
+          <t>2026-05-06 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-06 Close</t>
+          <t>2026-05-07 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change</t>
+          <t>2026-05-07 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change %</t>
+          <t>2026-05-07 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-07 Close</t>
+          <t>2026-05-08 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change</t>
+          <t>2026-05-08 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change %</t>
+          <t>2026-05-08 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-08 Close</t>
+          <t>2026-05-11 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change</t>
+          <t>2026-05-11 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change %</t>
+          <t>2026-05-11 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>143.4</v>
+        <v>136</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2</v>
+        <v>-7.4</v>
       </c>
       <c r="F3" t="n">
-        <v>2.28</v>
+        <v>-5.16</v>
       </c>
       <c r="G3" t="n">
-        <v>136</v>
+        <v>140.5</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.4</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.16</v>
+        <v>3.31</v>
       </c>
       <c r="J3" t="n">
-        <v>140.5</v>
+        <v>143.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>143.1</v>
+        <v>138.7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>-4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>-3.07</v>
       </c>
       <c r="P3" t="n">
-        <v>138.7</v>
+        <v>141.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.4</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.07</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>197</v>
+        <v>192.2</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2</v>
+        <v>-4.8</v>
       </c>
       <c r="F4" t="n">
-        <v>3.25</v>
+        <v>-2.44</v>
       </c>
       <c r="G4" t="n">
-        <v>192.2</v>
+        <v>201.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.8</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.44</v>
+        <v>4.89</v>
       </c>
       <c r="J4" t="n">
-        <v>201.6</v>
+        <v>203.6</v>
       </c>
       <c r="K4" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>4.89</v>
+        <v>0.99</v>
       </c>
       <c r="M4" t="n">
-        <v>203.6</v>
+        <v>199</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>-4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0.99</v>
+        <v>-2.26</v>
       </c>
       <c r="P4" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.6</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.26</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="G5" t="n">
         <v>5.94</v>
       </c>
-      <c r="E5" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.87</v>
-      </c>
       <c r="H5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="J5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M5" t="n">
         <v>5.94</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.96</v>
-      </c>
       <c r="N5" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="P5" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.34</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M6" t="n">
         <v>6.92</v>
       </c>
-      <c r="E6" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.99</v>
-      </c>
       <c r="N6" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.58</v>
+        <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>6.92</v>
+        <v>6.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="R6" t="n">
-        <v>-1</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>0.59</v>
+        <v>-0.79</v>
       </c>
       <c r="G7" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.04</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.79</v>
+        <v>1.98</v>
       </c>
       <c r="J7" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>1.98</v>
+        <v>-0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.19</v>
+        <v>-0.58</v>
       </c>
       <c r="P7" t="n">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="P8" t="n">
         <v>8.84</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8.76</v>
-      </c>
       <c r="Q8" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.35</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="9">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.12</v>
+        <v>7.18</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.42</v>
+        <v>0.84</v>
       </c>
       <c r="G9" t="n">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="H9" t="n">
         <v>0.06</v>
@@ -967,31 +967,31 @@
         <v>0.84</v>
       </c>
       <c r="J9" t="n">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="L9" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="M9" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="P9" t="n">
         <v>7.27</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7.23</v>
-      </c>
       <c r="Q9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.55</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.08</v>
+        <v>47.1</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="G10" t="n">
-        <v>47.1</v>
+        <v>47.04</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="J10" t="n">
-        <v>47.04</v>
+        <v>47.82</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.06</v>
+        <v>0.78</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.13</v>
+        <v>1.66</v>
       </c>
       <c r="M10" t="n">
-        <v>47.82</v>
+        <v>47.24</v>
       </c>
       <c r="N10" t="n">
-        <v>0.78</v>
+        <v>-0.58</v>
       </c>
       <c r="O10" t="n">
-        <v>1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>47.24</v>
+        <v>47.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.21</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>0.22</v>
+        <v>-0.43</v>
       </c>
       <c r="G11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="P11" t="n">
         <v>4.6</v>
       </c>
-      <c r="H11" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.61</v>
-      </c>
       <c r="Q11" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.86</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.7</v>
+        <v>11.68</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.74</v>
+        <v>-0.17</v>
       </c>
       <c r="G12" t="n">
         <v>11.68</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11.68</v>
+        <v>10.69</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-8.48</v>
       </c>
       <c r="M12" t="n">
-        <v>10.69</v>
+        <v>10.59</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.99</v>
+        <v>-0.1</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>10.59</v>
+        <v>10.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.62</v>
+        <v>28.56</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.76</v>
+        <v>-0.06</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.59</v>
+        <v>-0.21</v>
       </c>
       <c r="G13" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.06</v>
+        <v>-0.52</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.21</v>
+        <v>-1.82</v>
       </c>
       <c r="J13" t="n">
-        <v>28.04</v>
+        <v>26.42</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.52</v>
+        <v>-1.62</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.82</v>
+        <v>-5.78</v>
       </c>
       <c r="M13" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.62</v>
+        <v>0.02</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.78</v>
+        <v>0.08</v>
       </c>
       <c r="P13" t="n">
-        <v>26.44</v>
+        <v>26.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="14">
@@ -1262,46 +1262,46 @@
         <v>2.83</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-3.89</v>
       </c>
       <c r="J14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.89</v>
+        <v>-0.37</v>
       </c>
       <c r="M14" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.37</v>
+        <v>-1.11</v>
       </c>
       <c r="P14" t="n">
         <v>2.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.12</v>
+        <v>-0.39</v>
       </c>
       <c r="G15" t="n">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.39</v>
+        <v>1.58</v>
       </c>
       <c r="J15" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="O15" t="n">
-        <v>1.75</v>
+        <v>-1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.15</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="G16" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>0.19</v>
+        <v>-0.38</v>
       </c>
       <c r="J16" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M16" t="n">
         <v>5.24</v>
       </c>
-      <c r="K16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5.27</v>
-      </c>
       <c r="N16" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="O16" t="n">
-        <v>0.57</v>
+        <v>-0.57</v>
       </c>
       <c r="P16" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.57</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.06</v>
+        <v>-1.31</v>
       </c>
       <c r="G17" t="n">
         <v>3.78</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M17" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>0.26</v>
       </c>
       <c r="P17" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0.26</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.28</v>
+        <v>1.14</v>
       </c>
       <c r="J18" t="n">
         <v>3.54</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N18" t="n">
         <v>0.04</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P18" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63.25</v>
+        <v>63.5</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -1578,40 +1578,40 @@
         <v>0.4</v>
       </c>
       <c r="G19" t="n">
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="H19" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="M19" t="n">
-        <v>66</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>-0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>-0.61</v>
       </c>
       <c r="P19" t="n">
-        <v>65.59999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.61</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.78</v>
+        <v>29.12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="G20" t="n">
-        <v>29.12</v>
+        <v>29.9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.34</v>
+        <v>0.78</v>
       </c>
       <c r="I20" t="n">
-        <v>1.18</v>
+        <v>2.68</v>
       </c>
       <c r="J20" t="n">
-        <v>29.9</v>
+        <v>31.18</v>
       </c>
       <c r="K20" t="n">
-        <v>0.78</v>
+        <v>1.28</v>
       </c>
       <c r="L20" t="n">
-        <v>2.68</v>
+        <v>4.28</v>
       </c>
       <c r="M20" t="n">
-        <v>31.18</v>
+        <v>31.26</v>
       </c>
       <c r="N20" t="n">
-        <v>1.28</v>
+        <v>0.08</v>
       </c>
       <c r="O20" t="n">
-        <v>4.28</v>
+        <v>0.26</v>
       </c>
       <c r="P20" t="n">
-        <v>31.26</v>
+        <v>31.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="R20" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.34</v>
+        <v>-0.19</v>
       </c>
       <c r="G21" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.19</v>
+        <v>1.17</v>
       </c>
       <c r="J21" t="n">
-        <v>5.19</v>
+        <v>5.35</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="L21" t="n">
-        <v>1.17</v>
+        <v>3.08</v>
       </c>
       <c r="M21" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="N21" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>3.08</v>
+        <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>5.42</v>
+        <v>5.49</v>
       </c>
       <c r="Q21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.95</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.65</v>
+        <v>-0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.77</v>
+        <v>-0.12</v>
       </c>
       <c r="G22" t="n">
-        <v>83.84999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1</v>
+        <v>0.85</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.12</v>
+        <v>1.01</v>
       </c>
       <c r="J22" t="n">
-        <v>84.7</v>
+        <v>85.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="M22" t="n">
-        <v>85.3</v>
+        <v>85.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0.71</v>
+        <v>0.18</v>
       </c>
       <c r="P22" t="n">
-        <v>85.45</v>
+        <v>86.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.14</v>
+        <v>26.08</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2</v>
+        <v>-0.06</v>
       </c>
       <c r="F23" t="n">
-        <v>4.81</v>
+        <v>-0.23</v>
       </c>
       <c r="G23" t="n">
-        <v>26.08</v>
+        <v>27.4</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.06</v>
+        <v>1.32</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.23</v>
+        <v>5.06</v>
       </c>
       <c r="J23" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M23" t="n">
         <v>27.4</v>
       </c>
-      <c r="K23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="M23" t="n">
-        <v>27.52</v>
-      </c>
       <c r="N23" t="n">
-        <v>0.12</v>
+        <v>-0.12</v>
       </c>
       <c r="O23" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="P23" t="n">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.44</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.12</v>
+        <v>24.3</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9</v>
+        <v>0.18</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6</v>
+        <v>0.75</v>
       </c>
       <c r="G24" t="n">
-        <v>24.3</v>
+        <v>24.68</v>
       </c>
       <c r="H24" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="I24" t="n">
-        <v>0.75</v>
+        <v>1.56</v>
       </c>
       <c r="J24" t="n">
-        <v>24.68</v>
+        <v>26.46</v>
       </c>
       <c r="K24" t="n">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>7.21</v>
       </c>
       <c r="M24" t="n">
-        <v>26.46</v>
+        <v>28.24</v>
       </c>
       <c r="N24" t="n">
         <v>1.78</v>
       </c>
       <c r="O24" t="n">
-        <v>7.21</v>
+        <v>6.73</v>
       </c>
       <c r="P24" t="n">
-        <v>28.24</v>
+        <v>28.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.78</v>
+        <v>0.62</v>
       </c>
       <c r="R24" t="n">
-        <v>6.73</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.98</v>
+        <v>30.46</v>
       </c>
       <c r="E25" t="n">
-        <v>1.96</v>
+        <v>-0.52</v>
       </c>
       <c r="F25" t="n">
-        <v>6.75</v>
+        <v>-1.68</v>
       </c>
       <c r="G25" t="n">
-        <v>30.46</v>
+        <v>30.82</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.52</v>
+        <v>0.36</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.68</v>
+        <v>1.18</v>
       </c>
       <c r="J25" t="n">
-        <v>30.82</v>
+        <v>31.12</v>
       </c>
       <c r="K25" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="M25" t="n">
-        <v>31.12</v>
+        <v>31.68</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>0.97</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>48.7</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="F26" t="n">
-        <v>4.51</v>
+        <v>-3.49</v>
       </c>
       <c r="G26" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.7</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.49</v>
+        <v>8.51</v>
       </c>
       <c r="J26" t="n">
-        <v>51</v>
+        <v>58.55</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>7.55</v>
       </c>
       <c r="L26" t="n">
-        <v>8.51</v>
+        <v>14.8</v>
       </c>
       <c r="M26" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="N26" t="n">
-        <v>7.55</v>
+        <v>-1.9</v>
       </c>
       <c r="O26" t="n">
-        <v>14.8</v>
+        <v>-3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>56.65</v>
+        <v>56.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.9</v>
+        <v>-0.05</v>
       </c>
       <c r="R26" t="n">
-        <v>-3.25</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>473</v>
+        <v>472.2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F27" t="n">
-        <v>1.11</v>
+        <v>-0.17</v>
       </c>
       <c r="G27" t="n">
-        <v>472.2</v>
+        <v>463</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.17</v>
+        <v>-1.95</v>
       </c>
       <c r="J27" t="n">
-        <v>463</v>
+        <v>477.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.95</v>
+        <v>3.11</v>
       </c>
       <c r="M27" t="n">
-        <v>477.4</v>
+        <v>471.4</v>
       </c>
       <c r="N27" t="n">
-        <v>14.4</v>
+        <v>-6</v>
       </c>
       <c r="O27" t="n">
-        <v>3.11</v>
+        <v>-1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>471.4</v>
+        <v>464.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.26</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>131.7</v>
+        <v>131.2</v>
       </c>
       <c r="E28" t="n">
-        <v>5.7</v>
+        <v>-0.5</v>
       </c>
       <c r="F28" t="n">
-        <v>4.52</v>
+        <v>-0.38</v>
       </c>
       <c r="G28" t="n">
-        <v>131.2</v>
+        <v>134.2</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.38</v>
+        <v>2.29</v>
       </c>
       <c r="J28" t="n">
-        <v>134.2</v>
+        <v>140.9</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="L28" t="n">
-        <v>2.29</v>
+        <v>4.99</v>
       </c>
       <c r="M28" t="n">
-        <v>140.9</v>
+        <v>139</v>
       </c>
       <c r="N28" t="n">
-        <v>6.7</v>
+        <v>-1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>4.99</v>
+        <v>-1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>139</v>
+        <v>133.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.9</v>
+        <v>-5.1</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.35</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>116.8</v>
+        <v>116.2</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="F29" t="n">
-        <v>0.43</v>
+        <v>-0.51</v>
       </c>
       <c r="G29" t="n">
-        <v>116.2</v>
+        <v>116.4</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.51</v>
+        <v>0.17</v>
       </c>
       <c r="J29" t="n">
-        <v>116.4</v>
+        <v>119</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.17</v>
+        <v>2.23</v>
       </c>
       <c r="M29" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>-0.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.23</v>
+        <v>-0.42</v>
       </c>
       <c r="P29" t="n">
         <v>118.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>84.45</v>
+        <v>83.55</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>1.44</v>
+        <v>-1.07</v>
       </c>
       <c r="G30" t="n">
-        <v>83.55</v>
+        <v>82.5</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.9</v>
+        <v>-1.05</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.07</v>
+        <v>-1.26</v>
       </c>
       <c r="J30" t="n">
-        <v>82.5</v>
+        <v>84.25</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.05</v>
+        <v>1.75</v>
       </c>
       <c r="L30" t="n">
-        <v>-1.26</v>
+        <v>2.12</v>
       </c>
       <c r="M30" t="n">
-        <v>84.25</v>
+        <v>84.05</v>
       </c>
       <c r="N30" t="n">
-        <v>1.75</v>
+        <v>-0.2</v>
       </c>
       <c r="O30" t="n">
-        <v>2.12</v>
+        <v>-0.24</v>
       </c>
       <c r="P30" t="n">
-        <v>84.05</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.24</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>122.8</v>
+        <v>125.4</v>
       </c>
       <c r="E31" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="F31" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="G31" t="n">
-        <v>125.4</v>
+        <v>131.6</v>
       </c>
       <c r="H31" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
-        <v>2.12</v>
+        <v>4.94</v>
       </c>
       <c r="J31" t="n">
-        <v>131.6</v>
+        <v>137.3</v>
       </c>
       <c r="K31" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L31" t="n">
-        <v>4.94</v>
+        <v>4.33</v>
       </c>
       <c r="M31" t="n">
-        <v>137.3</v>
+        <v>145.2</v>
       </c>
       <c r="N31" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="O31" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="P31" t="n">
-        <v>145.2</v>
+        <v>140.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.9</v>
+        <v>-4.3</v>
       </c>
       <c r="R31" t="n">
-        <v>5.75</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>72.15000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="E32" t="n">
-        <v>1.25</v>
+        <v>-1.35</v>
       </c>
       <c r="F32" t="n">
-        <v>1.76</v>
+        <v>-1.87</v>
       </c>
       <c r="G32" t="n">
-        <v>70.8</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.35</v>
+        <v>4.05</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.87</v>
+        <v>5.72</v>
       </c>
       <c r="J32" t="n">
-        <v>74.84999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="K32" t="n">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="L32" t="n">
-        <v>5.72</v>
+        <v>2.54</v>
       </c>
       <c r="M32" t="n">
-        <v>76.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>2.54</v>
+        <v>-4.43</v>
       </c>
       <c r="P32" t="n">
-        <v>73.34999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>-3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>-4.43</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
       <c r="F33" t="n">
-        <v>0.49</v>
+        <v>-1.94</v>
       </c>
       <c r="G33" t="n">
-        <v>101</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.94</v>
+        <v>-2.08</v>
       </c>
       <c r="J33" t="n">
-        <v>98.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.1</v>
+        <v>1.8</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.08</v>
+        <v>1.82</v>
       </c>
       <c r="M33" t="n">
-        <v>100.7</v>
+        <v>99.75</v>
       </c>
       <c r="N33" t="n">
-        <v>1.8</v>
+        <v>-0.95</v>
       </c>
       <c r="O33" t="n">
-        <v>1.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P33" t="n">
-        <v>99.75</v>
+        <v>101.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.95</v>
+        <v>1.95</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>44.46</v>
+        <v>44.18</v>
       </c>
       <c r="E34" t="n">
-        <v>1.56</v>
+        <v>-0.28</v>
       </c>
       <c r="F34" t="n">
-        <v>3.64</v>
+        <v>-0.63</v>
       </c>
       <c r="G34" t="n">
-        <v>44.18</v>
+        <v>45</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.28</v>
+        <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.63</v>
+        <v>1.86</v>
       </c>
       <c r="J34" t="n">
-        <v>45</v>
+        <v>48.4</v>
       </c>
       <c r="K34" t="n">
-        <v>0.82</v>
+        <v>3.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.86</v>
+        <v>7.56</v>
       </c>
       <c r="M34" t="n">
-        <v>48.4</v>
+        <v>52.95</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="O34" t="n">
-        <v>7.56</v>
+        <v>9.4</v>
       </c>
       <c r="P34" t="n">
-        <v>52.95</v>
+        <v>51.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.55</v>
+        <v>-1.35</v>
       </c>
       <c r="R34" t="n">
-        <v>9.4</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G35" t="n">
         <v>4.87</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4.82</v>
-      </c>
       <c r="H35" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.03</v>
+        <v>1.04</v>
       </c>
       <c r="J35" t="n">
-        <v>4.87</v>
+        <v>5.01</v>
       </c>
       <c r="K35" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="L35" t="n">
-        <v>1.04</v>
+        <v>2.87</v>
       </c>
       <c r="M35" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="O35" t="n">
-        <v>2.87</v>
+        <v>-0.2</v>
       </c>
       <c r="P35" t="n">
         <v>5</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.46</v>
+        <v>10.33</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="F36" t="n">
-        <v>1.95</v>
+        <v>-1.24</v>
       </c>
       <c r="G36" t="n">
-        <v>10.33</v>
+        <v>10.42</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.24</v>
+        <v>0.87</v>
       </c>
       <c r="J36" t="n">
-        <v>10.42</v>
+        <v>10.76</v>
       </c>
       <c r="K36" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="L36" t="n">
-        <v>0.87</v>
+        <v>3.26</v>
       </c>
       <c r="M36" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="N36" t="n">
-        <v>0.34</v>
+        <v>-0.03</v>
       </c>
       <c r="O36" t="n">
-        <v>3.26</v>
+        <v>-0.28</v>
       </c>
       <c r="P36" t="n">
         <v>10.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>415</v>
+        <v>418.2</v>
       </c>
       <c r="E37" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="F37" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="G37" t="n">
-        <v>418.2</v>
+        <v>421.2</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="J37" t="n">
-        <v>421.2</v>
+        <v>427</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="L37" t="n">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
       <c r="M37" t="n">
-        <v>427</v>
+        <v>424.2</v>
       </c>
       <c r="N37" t="n">
-        <v>5.8</v>
+        <v>-2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="P37" t="n">
-        <v>424.2</v>
+        <v>425.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.66</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.95</v>
+        <v>15.92</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.37</v>
+        <v>-0.03</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.27</v>
+        <v>-0.19</v>
       </c>
       <c r="G38" t="n">
-        <v>15.92</v>
+        <v>16.24</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.03</v>
+        <v>0.32</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.19</v>
+        <v>2.01</v>
       </c>
       <c r="J38" t="n">
-        <v>16.24</v>
+        <v>16.39</v>
       </c>
       <c r="K38" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="L38" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
       <c r="M38" t="n">
-        <v>16.39</v>
+        <v>16.42</v>
       </c>
       <c r="N38" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="O38" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
       <c r="P38" t="n">
-        <v>16.42</v>
+        <v>16.08</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.03</v>
+        <v>-0.34</v>
       </c>
       <c r="R38" t="n">
-        <v>0.18</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>631.5</v>
+        <v>655</v>
       </c>
       <c r="E39" t="n">
         <v>23.5</v>
       </c>
       <c r="F39" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="G39" t="n">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="H39" t="n">
-        <v>23.5</v>
+        <v>14</v>
       </c>
       <c r="I39" t="n">
-        <v>3.72</v>
+        <v>2.14</v>
       </c>
       <c r="J39" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="K39" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="L39" t="n">
-        <v>2.14</v>
+        <v>-0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="N39" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.6</v>
+        <v>-2.11</v>
       </c>
       <c r="P39" t="n">
-        <v>651</v>
+        <v>657.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>-14</v>
+        <v>6.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-2.11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.55</v>
+        <v>62.75</v>
       </c>
       <c r="E40" t="n">
-        <v>1.55</v>
+        <v>0.2</v>
       </c>
       <c r="F40" t="n">
-        <v>2.54</v>
+        <v>0.32</v>
       </c>
       <c r="G40" t="n">
-        <v>62.75</v>
+        <v>60.25</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2</v>
+        <v>-2.5</v>
       </c>
       <c r="I40" t="n">
-        <v>0.32</v>
+        <v>-3.98</v>
       </c>
       <c r="J40" t="n">
-        <v>60.25</v>
+        <v>62.25</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.5</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.98</v>
+        <v>3.32</v>
       </c>
       <c r="M40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>-0.95</v>
       </c>
       <c r="O40" t="n">
-        <v>3.32</v>
+        <v>-1.53</v>
       </c>
       <c r="P40" t="n">
-        <v>61.3</v>
+        <v>62.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.95</v>
+        <v>1.2</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.53</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.87</v>
+        <v>21.83</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="G41" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.18</v>
+        <v>0.78</v>
       </c>
       <c r="J41" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="K41" t="n">
-        <v>0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="L41" t="n">
-        <v>0.78</v>
+        <v>-0.55</v>
       </c>
       <c r="M41" t="n">
-        <v>21.88</v>
+        <v>21.92</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.55</v>
+        <v>0.18</v>
       </c>
       <c r="P41" t="n">
-        <v>21.92</v>
+        <v>22.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="R41" t="n">
-        <v>0.18</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.6</v>
+        <v>58.55</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.17</v>
+        <v>-0.09</v>
       </c>
       <c r="G42" t="n">
-        <v>58.55</v>
+        <v>58.85</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.09</v>
+        <v>0.51</v>
       </c>
       <c r="J42" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="L42" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="M42" t="n">
-        <v>58.86</v>
+        <v>58.68</v>
       </c>
       <c r="N42" t="n">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="O42" t="n">
-        <v>0.02</v>
+        <v>-0.31</v>
       </c>
       <c r="P42" t="n">
-        <v>58.68</v>
+        <v>58.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.18</v>
+        <v>0.09</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.31</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36.17</v>
+        <v>36.28</v>
       </c>
       <c r="E43" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="G43" t="n">
-        <v>36.28</v>
+        <v>36.65</v>
       </c>
       <c r="H43" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="J43" t="n">
-        <v>36.65</v>
+        <v>36.7</v>
       </c>
       <c r="K43" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="L43" t="n">
-        <v>1.02</v>
+        <v>0.14</v>
       </c>
       <c r="M43" t="n">
-        <v>36.7</v>
+        <v>36.56</v>
       </c>
       <c r="N43" t="n">
-        <v>0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="O43" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="P43" t="n">
-        <v>36.56</v>
+        <v>36.99</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.38</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.68</v>
+        <v>6.69</v>
       </c>
       <c r="E44" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F44" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="G44" t="n">
-        <v>6.69</v>
+        <v>6.56</v>
       </c>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>-0.13</v>
       </c>
       <c r="I44" t="n">
-        <v>0.15</v>
+        <v>-1.94</v>
       </c>
       <c r="J44" t="n">
-        <v>6.56</v>
+        <v>6.41</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.94</v>
+        <v>-2.29</v>
       </c>
       <c r="M44" t="n">
-        <v>6.41</v>
+        <v>6.35</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="O44" t="n">
-        <v>-2.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P44" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.06</v>
+        <v>-0.17</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J45" t="n">
         <v>2.35</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.37</v>
-      </c>
       <c r="K45" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="M45" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.84</v>
+        <v>-2.13</v>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.13</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="G46" t="n">
         <v>3.32</v>
       </c>
-      <c r="E46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.29</v>
-      </c>
       <c r="H46" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J46" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L46" t="n">
-        <v>0.91</v>
+        <v>1.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O46" t="n">
-        <v>1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="P46" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.6</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.73</v>
+        <v>10.79</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>10.79</v>
+        <v>10.92</v>
       </c>
       <c r="H47" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
-        <v>10.92</v>
+        <v>10.74</v>
       </c>
       <c r="K47" t="n">
-        <v>0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="L47" t="n">
-        <v>1.2</v>
+        <v>-1.65</v>
       </c>
       <c r="M47" t="n">
-        <v>10.74</v>
+        <v>10.66</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="O47" t="n">
-        <v>-1.65</v>
+        <v>-0.74</v>
       </c>
       <c r="P47" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.74</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.355</v>
+        <v>0.375</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F48" t="n">
-        <v>2.9</v>
+        <v>5.63</v>
       </c>
       <c r="G48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.375</v>
       </c>
-      <c r="H48" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="M48" t="n">
         <v>0.38</v>
       </c>
-      <c r="K48" t="n">
+      <c r="N48" t="n">
         <v>0.005</v>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>1.33</v>
       </c>
-      <c r="M48" t="n">
+      <c r="P48" t="n">
         <v>0.375</v>
       </c>
-      <c r="N48" t="n">
+      <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>-1.32</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.33</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="F49" t="n">
-        <v>1.74</v>
+        <v>0.21</v>
       </c>
       <c r="G49" t="n">
-        <v>4.68</v>
+        <v>4.59</v>
       </c>
       <c r="H49" t="n">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.21</v>
+        <v>-1.92</v>
       </c>
       <c r="J49" t="n">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.92</v>
+        <v>1.09</v>
       </c>
       <c r="M49" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="N49" t="n">
         <v>0.05</v>
       </c>
       <c r="O49" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P49" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="R49" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="50">
@@ -3491,31 +3491,31 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="E50" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F50" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="I50" t="n">
-        <v>-2.86</v>
+        <v>-0.98</v>
       </c>
       <c r="J50" t="n">
         <v>1.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>1.01</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="E51" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>1.86</v>
+        <v>-1.59</v>
       </c>
       <c r="G51" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.59</v>
+        <v>-4.17</v>
       </c>
       <c r="J51" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="L51" t="n">
-        <v>-4.17</v>
+        <v>-0.97</v>
       </c>
       <c r="M51" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.97</v>
+        <v>-2.44</v>
       </c>
       <c r="P51" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.44</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.87</v>
+        <v>10.97</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="G52" t="n">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="I52" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="J52" t="n">
-        <v>10.96</v>
+        <v>11.14</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.09</v>
+        <v>1.64</v>
       </c>
       <c r="M52" t="n">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
       <c r="N52" t="n">
-        <v>0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1.64</v>
+        <v>-1.8</v>
       </c>
       <c r="P52" t="n">
-        <v>10.94</v>
+        <v>10.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.8</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.23</v>
+        <v>8.18</v>
       </c>
       <c r="E53" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H53" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F53" t="n">
+      <c r="I53" t="n">
         <v>0.86</v>
       </c>
-      <c r="G53" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-0.61</v>
-      </c>
       <c r="J53" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="K53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L53" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="M53" t="n">
-        <v>8.33</v>
+        <v>8.26</v>
       </c>
       <c r="N53" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>0.97</v>
+        <v>-0.84</v>
       </c>
       <c r="P53" t="n">
-        <v>8.26</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.84</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>2.38</v>
+        <v>-1.16</v>
       </c>
       <c r="G54" t="n">
         <v>0.425</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I54" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="M54" t="n">
         <v>0.425</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.42</v>
-      </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P54" t="n">
         <v>0.425</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="P55" t="n">
         <v>0.68</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0.6850000000000001</v>
       </c>
       <c r="Q55" t="n">
         <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.485</v>
+        <v>0.495</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G56" t="n">
-        <v>0.495</v>
+        <v>0.49</v>
       </c>
       <c r="H56" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>2.06</v>
+        <v>-1.01</v>
       </c>
       <c r="J56" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M56" t="n">
         <v>0.49</v>
       </c>
-      <c r="K56" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.505</v>
-      </c>
       <c r="N56" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="O56" t="n">
-        <v>3.06</v>
+        <v>-2.97</v>
       </c>
       <c r="P56" t="n">
         <v>0.49</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="J57" t="n">
         <v>3.72</v>
       </c>
-      <c r="E57" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K57" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.53</v>
+        <v>-0.8</v>
       </c>
       <c r="M57" t="n">
         <v>3.72</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P58" t="n">
         <v>0.081</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="O58" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.08</v>
       </c>
       <c r="Q58" t="n">
         <v>0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.36</v>
+        <v>21.17</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.57</v>
+        <v>-0.89</v>
       </c>
       <c r="G59" t="n">
-        <v>21.17</v>
+        <v>21.39</v>
       </c>
       <c r="H59" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J59" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O59" t="n">
         <v>-0.19</v>
       </c>
-      <c r="I59" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="J59" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="M59" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="O59" t="n">
-        <v>-2.06</v>
-      </c>
       <c r="P59" t="n">
-        <v>20.91</v>
+        <v>20.96</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="E60" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="G60" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="H60" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>-2.42</v>
       </c>
       <c r="J60" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="K60" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q60" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L60" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="R60" t="n">
-        <v>-0.31</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="E61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H61" t="n">
         <v>0.01</v>
       </c>
-      <c r="F61" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G61" t="n">
+      <c r="I61" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M61" t="n">
         <v>1.51</v>
       </c>
-      <c r="H61" t="n">
+      <c r="N61" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q61" t="n">
         <v>0.04</v>
       </c>
-      <c r="I61" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O61" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="R61" t="n">
-        <v>-3.21</v>
+        <v>2.65</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-05 Close</t>
+          <t>2026-05-06 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change</t>
+          <t>2026-05-06 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-05 Change %</t>
+          <t>2026-05-06 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-06 Close</t>
+          <t>2026-05-07 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change</t>
+          <t>2026-05-07 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change %</t>
+          <t>2026-05-07 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-07 Close</t>
+          <t>2026-05-08 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change</t>
+          <t>2026-05-08 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change %</t>
+          <t>2026-05-08 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-08 Close</t>
+          <t>2026-05-11 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change</t>
+          <t>2026-05-11 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change %</t>
+          <t>2026-05-11 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-11 Close</t>
+          <t>2026-05-12 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change</t>
+          <t>2026-05-12 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change %</t>
+          <t>2026-05-12 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>136</v>
+        <v>140.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.4</v>
+        <v>4.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.16</v>
+        <v>3.31</v>
       </c>
       <c r="G3" t="n">
-        <v>140.5</v>
+        <v>143.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>143.1</v>
+        <v>138.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>-4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>-3.07</v>
       </c>
       <c r="M3" t="n">
-        <v>138.7</v>
+        <v>141.2</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P3" t="n">
-        <v>141.2</v>
+        <v>138.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>192.2</v>
+        <v>201.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.8</v>
+        <v>9.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.44</v>
+        <v>4.89</v>
       </c>
       <c r="G4" t="n">
-        <v>201.6</v>
+        <v>203.6</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.89</v>
+        <v>0.99</v>
       </c>
       <c r="J4" t="n">
-        <v>203.6</v>
+        <v>199</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>-4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.99</v>
+        <v>-2.26</v>
       </c>
       <c r="M4" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.6</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.26</v>
+        <v>2.01</v>
       </c>
       <c r="P4" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="R4" t="n">
-        <v>2.01</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.87</v>
+        <v>5.94</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J5" t="n">
         <v>5.94</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.96</v>
-      </c>
       <c r="K5" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="L5" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.34</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="R5" t="n">
-        <v>1.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.29</v>
+        <v>0.72</v>
       </c>
       <c r="G6" t="n">
-        <v>6.95</v>
+        <v>6.99</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="J6" t="n">
-        <v>6.99</v>
+        <v>6.92</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.58</v>
+        <v>-1</v>
       </c>
       <c r="M6" t="n">
-        <v>6.92</v>
+        <v>6.98</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="O6" t="n">
-        <v>-1</v>
+        <v>0.87</v>
       </c>
       <c r="P6" t="n">
-        <v>6.98</v>
+        <v>7.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.79</v>
+        <v>1.98</v>
       </c>
       <c r="G7" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1.98</v>
+        <v>-0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.19</v>
+        <v>-0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06</v>
+        <v>0.15</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.68</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>8.76</v>
+        <v>8.84</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.35</v>
+        <v>0.91</v>
       </c>
       <c r="P8" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="9">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="E9" t="n">
         <v>0.06</v>
@@ -958,34 +958,34 @@
         <v>0.84</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I9" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="J9" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="M9" t="n">
         <v>7.27</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="M9" t="n">
-        <v>7.23</v>
-      </c>
       <c r="N9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.55</v>
+        <v>0.55</v>
       </c>
       <c r="P9" t="n">
-        <v>7.27</v>
+        <v>7.31</v>
       </c>
       <c r="Q9" t="n">
         <v>0.04</v>
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.1</v>
+        <v>47.04</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="G10" t="n">
-        <v>47.04</v>
+        <v>47.82</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.06</v>
+        <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.13</v>
+        <v>1.66</v>
       </c>
       <c r="J10" t="n">
-        <v>47.82</v>
+        <v>47.24</v>
       </c>
       <c r="K10" t="n">
-        <v>0.78</v>
+        <v>-0.58</v>
       </c>
       <c r="L10" t="n">
-        <v>1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>47.24</v>
+        <v>47.46</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.21</v>
+        <v>0.47</v>
       </c>
       <c r="P10" t="n">
-        <v>47.46</v>
+        <v>47.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="R10" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="M11" t="n">
         <v>4.6</v>
       </c>
-      <c r="E11" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.61</v>
-      </c>
       <c r="N11" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.86</v>
+        <v>-0.22</v>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.22</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="12">
@@ -1138,46 +1138,46 @@
         <v>11.68</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>11.68</v>
+        <v>10.69</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-8.48</v>
       </c>
       <c r="J12" t="n">
-        <v>10.69</v>
+        <v>10.59</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.99</v>
+        <v>-0.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>10.59</v>
+        <v>10.64</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="P12" t="n">
-        <v>10.64</v>
+        <v>11.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="R12" t="n">
-        <v>0.47</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06</v>
+        <v>-0.52</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.21</v>
+        <v>-1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>28.04</v>
+        <v>26.42</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.52</v>
+        <v>-1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.82</v>
+        <v>-5.78</v>
       </c>
       <c r="J13" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.62</v>
+        <v>0.02</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.78</v>
+        <v>0.08</v>
       </c>
       <c r="M13" t="n">
-        <v>26.44</v>
+        <v>26.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
       <c r="P13" t="n">
-        <v>26.6</v>
+        <v>26.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-3.89</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.89</v>
+        <v>-0.37</v>
       </c>
       <c r="J14" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.37</v>
+        <v>-1.11</v>
       </c>
       <c r="M14" t="n">
         <v>2.68</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.11</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.39</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I15" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="J15" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>-1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.15</v>
+        <v>0.58</v>
       </c>
       <c r="P15" t="n">
-        <v>5.21</v>
+        <v>5.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="R15" t="n">
-        <v>0.58</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>0.19</v>
+        <v>-0.38</v>
       </c>
       <c r="G16" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J16" t="n">
         <v>5.24</v>
       </c>
-      <c r="H16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5.27</v>
-      </c>
       <c r="K16" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="L16" t="n">
-        <v>0.57</v>
+        <v>-0.57</v>
       </c>
       <c r="M16" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.57</v>
+        <v>-0.76</v>
       </c>
       <c r="P16" t="n">
         <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1448,46 +1448,46 @@
         <v>3.78</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="J17" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="K17" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>2.38</v>
+        <v>0.26</v>
       </c>
       <c r="M17" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="N17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0.01</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>0.26</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-1.03</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.28</v>
+        <v>1.14</v>
       </c>
       <c r="G18" t="n">
         <v>3.54</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.04</v>
       </c>
-      <c r="I18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M18" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O18" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
-        <v>66</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8</v>
+        <v>-0.4</v>
       </c>
       <c r="L19" t="n">
-        <v>2.8</v>
+        <v>-0.61</v>
       </c>
       <c r="M19" t="n">
-        <v>65.59999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.61</v>
+        <v>-0.84</v>
       </c>
       <c r="P19" t="n">
-        <v>65.05</v>
+        <v>65</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.84</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.12</v>
+        <v>29.9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.34</v>
+        <v>0.78</v>
       </c>
       <c r="F20" t="n">
-        <v>1.18</v>
+        <v>2.68</v>
       </c>
       <c r="G20" t="n">
-        <v>29.9</v>
+        <v>31.18</v>
       </c>
       <c r="H20" t="n">
-        <v>0.78</v>
+        <v>1.28</v>
       </c>
       <c r="I20" t="n">
-        <v>2.68</v>
+        <v>4.28</v>
       </c>
       <c r="J20" t="n">
-        <v>31.18</v>
+        <v>31.26</v>
       </c>
       <c r="K20" t="n">
-        <v>1.28</v>
+        <v>0.08</v>
       </c>
       <c r="L20" t="n">
-        <v>4.28</v>
+        <v>0.26</v>
       </c>
       <c r="M20" t="n">
-        <v>31.26</v>
+        <v>31.38</v>
       </c>
       <c r="N20" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="O20" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="P20" t="n">
-        <v>31.38</v>
+        <v>30.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.12</v>
+        <v>-0.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0.38</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.19</v>
+        <v>1.17</v>
       </c>
       <c r="G21" t="n">
-        <v>5.19</v>
+        <v>5.35</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="I21" t="n">
-        <v>1.17</v>
+        <v>3.08</v>
       </c>
       <c r="J21" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="K21" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>3.08</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>5.42</v>
+        <v>5.49</v>
       </c>
       <c r="N21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P21" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83.84999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1</v>
+        <v>0.85</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.12</v>
+        <v>1.01</v>
       </c>
       <c r="G22" t="n">
-        <v>84.7</v>
+        <v>85.3</v>
       </c>
       <c r="H22" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="J22" t="n">
-        <v>85.3</v>
+        <v>85.45</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="L22" t="n">
-        <v>0.71</v>
+        <v>0.18</v>
       </c>
       <c r="M22" t="n">
-        <v>85.45</v>
+        <v>86.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
       <c r="P22" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.08</v>
+        <v>27.4</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.06</v>
+        <v>1.32</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.23</v>
+        <v>5.06</v>
       </c>
       <c r="G23" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J23" t="n">
         <v>27.4</v>
       </c>
-      <c r="H23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="J23" t="n">
-        <v>27.52</v>
-      </c>
       <c r="K23" t="n">
-        <v>0.12</v>
+        <v>-0.12</v>
       </c>
       <c r="L23" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="M23" t="n">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>27.38</v>
+        <v>26.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.02</v>
+        <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.3</v>
+        <v>24.68</v>
       </c>
       <c r="E24" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="F24" t="n">
-        <v>0.75</v>
+        <v>1.56</v>
       </c>
       <c r="G24" t="n">
-        <v>24.68</v>
+        <v>26.46</v>
       </c>
       <c r="H24" t="n">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="I24" t="n">
-        <v>1.56</v>
+        <v>7.21</v>
       </c>
       <c r="J24" t="n">
-        <v>26.46</v>
+        <v>28.24</v>
       </c>
       <c r="K24" t="n">
         <v>1.78</v>
       </c>
       <c r="L24" t="n">
-        <v>7.21</v>
+        <v>6.73</v>
       </c>
       <c r="M24" t="n">
-        <v>28.24</v>
+        <v>28.86</v>
       </c>
       <c r="N24" t="n">
-        <v>1.78</v>
+        <v>0.62</v>
       </c>
       <c r="O24" t="n">
-        <v>6.73</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>28.86</v>
+        <v>29.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.46</v>
+        <v>30.82</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.52</v>
+        <v>0.36</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.68</v>
+        <v>1.18</v>
       </c>
       <c r="G25" t="n">
-        <v>30.82</v>
+        <v>31.12</v>
       </c>
       <c r="H25" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="J25" t="n">
-        <v>31.12</v>
+        <v>31.68</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.97</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="O25" t="n">
-        <v>1.8</v>
+        <v>0.06</v>
       </c>
       <c r="P25" t="n">
-        <v>31.7</v>
+        <v>31.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="R25" t="n">
-        <v>0.06</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.49</v>
+        <v>8.51</v>
       </c>
       <c r="G26" t="n">
-        <v>51</v>
+        <v>58.55</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>7.55</v>
       </c>
       <c r="I26" t="n">
-        <v>8.51</v>
+        <v>14.8</v>
       </c>
       <c r="J26" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="K26" t="n">
-        <v>7.55</v>
+        <v>-1.9</v>
       </c>
       <c r="L26" t="n">
-        <v>14.8</v>
+        <v>-3.25</v>
       </c>
       <c r="M26" t="n">
-        <v>56.65</v>
+        <v>56.6</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.9</v>
+        <v>-0.05</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.25</v>
+        <v>-0.09</v>
       </c>
       <c r="P26" t="n">
-        <v>56.6</v>
+        <v>55.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.05</v>
+        <v>-1.45</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.09</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>472.2</v>
+        <v>463</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.17</v>
+        <v>-1.95</v>
       </c>
       <c r="G27" t="n">
-        <v>463</v>
+        <v>477.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.95</v>
+        <v>3.11</v>
       </c>
       <c r="J27" t="n">
-        <v>477.4</v>
+        <v>471.4</v>
       </c>
       <c r="K27" t="n">
-        <v>14.4</v>
+        <v>-6</v>
       </c>
       <c r="L27" t="n">
-        <v>3.11</v>
+        <v>-1.26</v>
       </c>
       <c r="M27" t="n">
-        <v>471.4</v>
+        <v>464.4</v>
       </c>
       <c r="N27" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.26</v>
+        <v>-1.48</v>
       </c>
       <c r="P27" t="n">
-        <v>464.4</v>
+        <v>457.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.48</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>131.2</v>
+        <v>134.2</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.38</v>
+        <v>2.29</v>
       </c>
       <c r="G28" t="n">
-        <v>134.2</v>
+        <v>140.9</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2.29</v>
+        <v>4.99</v>
       </c>
       <c r="J28" t="n">
-        <v>140.9</v>
+        <v>139</v>
       </c>
       <c r="K28" t="n">
-        <v>6.7</v>
+        <v>-1.9</v>
       </c>
       <c r="L28" t="n">
-        <v>4.99</v>
+        <v>-1.35</v>
       </c>
       <c r="M28" t="n">
-        <v>139</v>
+        <v>133.9</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.9</v>
+        <v>-5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.35</v>
+        <v>-3.67</v>
       </c>
       <c r="P28" t="n">
-        <v>133.9</v>
+        <v>133.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="R28" t="n">
-        <v>-3.67</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>116.2</v>
+        <v>116.4</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.51</v>
+        <v>0.17</v>
       </c>
       <c r="G29" t="n">
-        <v>116.4</v>
+        <v>119</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="I29" t="n">
-        <v>0.17</v>
+        <v>2.23</v>
       </c>
       <c r="J29" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>-0.5</v>
       </c>
       <c r="L29" t="n">
-        <v>2.23</v>
+        <v>-0.42</v>
       </c>
       <c r="M29" t="n">
         <v>118.5</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>118.5</v>
+        <v>118.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>83.55</v>
+        <v>82.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.9</v>
+        <v>-1.05</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.07</v>
+        <v>-1.26</v>
       </c>
       <c r="G30" t="n">
-        <v>82.5</v>
+        <v>84.25</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.05</v>
+        <v>1.75</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.26</v>
+        <v>2.12</v>
       </c>
       <c r="J30" t="n">
-        <v>84.25</v>
+        <v>84.05</v>
       </c>
       <c r="K30" t="n">
-        <v>1.75</v>
+        <v>-0.2</v>
       </c>
       <c r="L30" t="n">
-        <v>2.12</v>
+        <v>-0.24</v>
       </c>
       <c r="M30" t="n">
-        <v>84.05</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="N30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P30" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="Q30" t="n">
         <v>-0.2</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
         <v>-0.24</v>
-      </c>
-      <c r="P30" t="n">
-        <v>84.34999999999999</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.36</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>125.4</v>
+        <v>131.6</v>
       </c>
       <c r="E31" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="F31" t="n">
-        <v>2.12</v>
+        <v>4.94</v>
       </c>
       <c r="G31" t="n">
-        <v>131.6</v>
+        <v>137.3</v>
       </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I31" t="n">
-        <v>4.94</v>
+        <v>4.33</v>
       </c>
       <c r="J31" t="n">
-        <v>137.3</v>
+        <v>145.2</v>
       </c>
       <c r="K31" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="L31" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="M31" t="n">
-        <v>145.2</v>
+        <v>140.9</v>
       </c>
       <c r="N31" t="n">
-        <v>7.9</v>
+        <v>-4.3</v>
       </c>
       <c r="O31" t="n">
-        <v>5.75</v>
+        <v>-2.96</v>
       </c>
       <c r="P31" t="n">
-        <v>140.9</v>
+        <v>139.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>-4.3</v>
+        <v>-1.2</v>
       </c>
       <c r="R31" t="n">
-        <v>-2.96</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>70.8</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.35</v>
+        <v>4.05</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.87</v>
+        <v>5.72</v>
       </c>
       <c r="G32" t="n">
-        <v>74.84999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="H32" t="n">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="I32" t="n">
-        <v>5.72</v>
+        <v>2.54</v>
       </c>
       <c r="J32" t="n">
-        <v>76.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="L32" t="n">
-        <v>2.54</v>
+        <v>-4.43</v>
       </c>
       <c r="M32" t="n">
-        <v>73.34999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>-3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>-4.43</v>
+        <v>4.43</v>
       </c>
       <c r="P32" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>101</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.94</v>
+        <v>-2.08</v>
       </c>
       <c r="G33" t="n">
-        <v>98.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.1</v>
+        <v>1.8</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.08</v>
+        <v>1.82</v>
       </c>
       <c r="J33" t="n">
-        <v>100.7</v>
+        <v>99.75</v>
       </c>
       <c r="K33" t="n">
-        <v>1.8</v>
+        <v>-0.95</v>
       </c>
       <c r="L33" t="n">
-        <v>1.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>99.75</v>
+        <v>101.7</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.95</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
-        <v>101.7</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.95</v>
+        <v>-1.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.95</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>44.18</v>
+        <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.28</v>
+        <v>0.82</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.63</v>
+        <v>1.86</v>
       </c>
       <c r="G34" t="n">
-        <v>45</v>
+        <v>48.4</v>
       </c>
       <c r="H34" t="n">
-        <v>0.82</v>
+        <v>3.4</v>
       </c>
       <c r="I34" t="n">
-        <v>1.86</v>
+        <v>7.56</v>
       </c>
       <c r="J34" t="n">
-        <v>48.4</v>
+        <v>52.95</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="L34" t="n">
-        <v>7.56</v>
+        <v>9.4</v>
       </c>
       <c r="M34" t="n">
-        <v>52.95</v>
+        <v>51.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4.55</v>
+        <v>-1.35</v>
       </c>
       <c r="O34" t="n">
-        <v>9.4</v>
+        <v>-2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>51.6</v>
+        <v>52.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1.35</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.55</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>4.87</v>
+        <v>5.01</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I35" t="n">
-        <v>1.04</v>
+        <v>2.87</v>
       </c>
       <c r="J35" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="L35" t="n">
-        <v>2.87</v>
+        <v>-0.2</v>
       </c>
       <c r="M35" t="n">
         <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.33</v>
+        <v>10.42</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.13</v>
+        <v>0.09</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.24</v>
+        <v>0.87</v>
       </c>
       <c r="G36" t="n">
-        <v>10.42</v>
+        <v>10.76</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="I36" t="n">
-        <v>0.87</v>
+        <v>3.26</v>
       </c>
       <c r="J36" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="K36" t="n">
-        <v>0.34</v>
+        <v>-0.03</v>
       </c>
       <c r="L36" t="n">
-        <v>3.26</v>
+        <v>-0.28</v>
       </c>
       <c r="M36" t="n">
         <v>10.73</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>10.73</v>
+        <v>10.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>418.2</v>
+        <v>421.2</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="G37" t="n">
-        <v>421.2</v>
+        <v>427</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="I37" t="n">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
       <c r="J37" t="n">
-        <v>427</v>
+        <v>424.2</v>
       </c>
       <c r="K37" t="n">
-        <v>5.8</v>
+        <v>-2.8</v>
       </c>
       <c r="L37" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="M37" t="n">
-        <v>424.2</v>
+        <v>425.4</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.66</v>
+        <v>0.28</v>
       </c>
       <c r="P37" t="n">
-        <v>425.4</v>
+        <v>423.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.92</v>
+        <v>16.24</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.03</v>
+        <v>0.32</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.19</v>
+        <v>2.01</v>
       </c>
       <c r="G38" t="n">
-        <v>16.24</v>
+        <v>16.39</v>
       </c>
       <c r="H38" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="I38" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
       <c r="J38" t="n">
-        <v>16.39</v>
+        <v>16.42</v>
       </c>
       <c r="K38" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="L38" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
       <c r="M38" t="n">
-        <v>16.42</v>
+        <v>16.08</v>
       </c>
       <c r="N38" t="n">
-        <v>0.03</v>
+        <v>-0.34</v>
       </c>
       <c r="O38" t="n">
-        <v>0.18</v>
+        <v>-2.07</v>
       </c>
       <c r="P38" t="n">
-        <v>16.08</v>
+        <v>16.14</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.34</v>
+        <v>0.06</v>
       </c>
       <c r="R38" t="n">
-        <v>-2.07</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="E39" t="n">
-        <v>23.5</v>
+        <v>14</v>
       </c>
       <c r="F39" t="n">
-        <v>3.72</v>
+        <v>2.14</v>
       </c>
       <c r="G39" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="H39" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="I39" t="n">
-        <v>2.14</v>
+        <v>-0.6</v>
       </c>
       <c r="J39" t="n">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="K39" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.6</v>
+        <v>-2.11</v>
       </c>
       <c r="M39" t="n">
-        <v>651</v>
+        <v>657.5</v>
       </c>
       <c r="N39" t="n">
-        <v>-14</v>
+        <v>6.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.11</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>657.5</v>
+        <v>651.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.5</v>
+        <v>-6</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.75</v>
+        <v>60.25</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2</v>
+        <v>-2.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.32</v>
+        <v>-3.98</v>
       </c>
       <c r="G40" t="n">
-        <v>60.25</v>
+        <v>62.25</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.5</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.98</v>
+        <v>3.32</v>
       </c>
       <c r="J40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>-0.95</v>
       </c>
       <c r="L40" t="n">
-        <v>3.32</v>
+        <v>-1.53</v>
       </c>
       <c r="M40" t="n">
-        <v>61.3</v>
+        <v>62.5</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.95</v>
+        <v>1.2</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.53</v>
+        <v>1.96</v>
       </c>
       <c r="P40" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.96</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.04</v>
+        <v>0.17</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.18</v>
+        <v>0.78</v>
       </c>
       <c r="G41" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="H41" t="n">
-        <v>0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="I41" t="n">
-        <v>0.78</v>
+        <v>-0.55</v>
       </c>
       <c r="J41" t="n">
-        <v>21.88</v>
+        <v>21.92</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.55</v>
+        <v>0.18</v>
       </c>
       <c r="M41" t="n">
-        <v>21.92</v>
+        <v>22.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="O41" t="n">
-        <v>0.18</v>
+        <v>2.65</v>
       </c>
       <c r="P41" t="n">
-        <v>22.5</v>
+        <v>22.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.58</v>
+        <v>-0.17</v>
       </c>
       <c r="R41" t="n">
-        <v>2.65</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.55</v>
+        <v>58.85</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.09</v>
+        <v>0.51</v>
       </c>
       <c r="G42" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="I42" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="J42" t="n">
-        <v>58.86</v>
+        <v>58.68</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02</v>
+        <v>-0.31</v>
       </c>
       <c r="M42" t="n">
-        <v>58.68</v>
+        <v>58.77</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.18</v>
+        <v>0.09</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.31</v>
+        <v>0.15</v>
       </c>
       <c r="P42" t="n">
-        <v>58.77</v>
+        <v>59.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="R42" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36.28</v>
+        <v>36.65</v>
       </c>
       <c r="E43" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="G43" t="n">
-        <v>36.65</v>
+        <v>36.7</v>
       </c>
       <c r="H43" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="I43" t="n">
-        <v>1.02</v>
+        <v>0.14</v>
       </c>
       <c r="J43" t="n">
-        <v>36.7</v>
+        <v>36.56</v>
       </c>
       <c r="K43" t="n">
-        <v>0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="L43" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="M43" t="n">
-        <v>36.56</v>
+        <v>36.99</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.38</v>
+        <v>1.18</v>
       </c>
       <c r="P43" t="n">
-        <v>36.99</v>
+        <v>37.11</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.43</v>
+        <v>0.12</v>
       </c>
       <c r="R43" t="n">
-        <v>1.18</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.69</v>
+        <v>6.56</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01</v>
+        <v>-0.13</v>
       </c>
       <c r="F44" t="n">
-        <v>0.15</v>
+        <v>-1.94</v>
       </c>
       <c r="G44" t="n">
-        <v>6.56</v>
+        <v>6.41</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.94</v>
+        <v>-2.29</v>
       </c>
       <c r="J44" t="n">
-        <v>6.41</v>
+        <v>6.35</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="L44" t="n">
-        <v>-2.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.06</v>
+        <v>-0.17</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.68</v>
       </c>
       <c r="P44" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.17</v>
+        <v>0.04</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.68</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>1.28</v>
+        <v>-0.42</v>
       </c>
       <c r="G45" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="J45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="P45" t="n">
         <v>2.35</v>
       </c>
-      <c r="K45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="R45" t="n">
-        <v>-3.04</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G46" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="H46" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q46" t="n">
         <v>0.03</v>
       </c>
-      <c r="I46" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O46" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="P46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="R46" t="n">
-        <v>-2.69</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.79</v>
+        <v>10.92</v>
       </c>
       <c r="E47" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="G47" t="n">
-        <v>10.92</v>
+        <v>10.74</v>
       </c>
       <c r="H47" t="n">
-        <v>0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>-1.65</v>
       </c>
       <c r="J47" t="n">
-        <v>10.74</v>
+        <v>10.66</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.65</v>
+        <v>-0.74</v>
       </c>
       <c r="M47" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.74</v>
+        <v>-0.28</v>
       </c>
       <c r="P47" t="n">
-        <v>10.63</v>
+        <v>10.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.28</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.375</v>
       </c>
-      <c r="E48" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.38</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
         <v>1.33</v>
       </c>
-      <c r="J48" t="n">
+      <c r="M48" t="n">
         <v>0.375</v>
       </c>
-      <c r="K48" t="n">
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="M48" t="n">
+      <c r="P48" t="n">
         <v>0.38</v>
       </c>
-      <c r="N48" t="n">
+      <c r="Q48" t="n">
         <v>0.005</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>1.33</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="R48" t="n">
-        <v>-1.32</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.68</v>
+        <v>4.59</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="F49" t="n">
-        <v>0.21</v>
+        <v>-1.92</v>
       </c>
       <c r="G49" t="n">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.92</v>
+        <v>1.09</v>
       </c>
       <c r="J49" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="K49" t="n">
         <v>0.05</v>
       </c>
       <c r="L49" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="M49" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O49" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="P49" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="R49" t="n">
-        <v>1.28</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="50">
@@ -3491,22 +3491,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.86</v>
+        <v>-0.98</v>
       </c>
       <c r="G50" t="n">
         <v>1.01</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>1.01</v>
@@ -3527,13 +3527,13 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.59</v>
+        <v>-4.17</v>
       </c>
       <c r="G51" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="I51" t="n">
-        <v>-4.17</v>
+        <v>-0.97</v>
       </c>
       <c r="J51" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.97</v>
+        <v>-2.44</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.44</v>
+        <v>-2.25</v>
       </c>
       <c r="P51" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.25</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="F52" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="G52" t="n">
-        <v>10.96</v>
+        <v>11.14</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.09</v>
+        <v>1.64</v>
       </c>
       <c r="J52" t="n">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
       <c r="K52" t="n">
-        <v>0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="L52" t="n">
-        <v>1.64</v>
+        <v>-1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>10.94</v>
+        <v>10.91</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.8</v>
+        <v>-0.27</v>
       </c>
       <c r="P52" t="n">
-        <v>10.91</v>
+        <v>10.78</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.27</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.18</v>
+        <v>8.25</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.61</v>
+        <v>0.86</v>
       </c>
       <c r="G53" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="H53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="J53" t="n">
-        <v>8.33</v>
+        <v>8.26</v>
       </c>
       <c r="K53" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>0.97</v>
+        <v>-0.84</v>
       </c>
       <c r="M53" t="n">
-        <v>8.26</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.84</v>
+        <v>-1.82</v>
       </c>
       <c r="P53" t="n">
-        <v>8.109999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.15</v>
+        <v>0.02</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.82</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="54">
@@ -3742,46 +3742,46 @@
         <v>0.425</v>
       </c>
       <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F54" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.425</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.42</v>
-      </c>
       <c r="K54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M54" t="n">
         <v>0.425</v>
       </c>
       <c r="N54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="K55" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F55" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.005</v>
-      </c>
       <c r="L55" t="n">
-        <v>0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="N55" t="n">
         <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="P55" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.73</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.495</v>
+        <v>0.49</v>
       </c>
       <c r="E56" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>2.06</v>
+        <v>-1.01</v>
       </c>
       <c r="G56" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J56" t="n">
         <v>0.49</v>
       </c>
-      <c r="H56" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.505</v>
-      </c>
       <c r="K56" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="L56" t="n">
-        <v>3.06</v>
+        <v>-2.97</v>
       </c>
       <c r="M56" t="n">
         <v>0.49</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-2.97</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="E57" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F57" t="n">
-        <v>1.34</v>
+        <v>-0.53</v>
       </c>
       <c r="G57" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.53</v>
+        <v>-0.8</v>
       </c>
       <c r="J57" t="n">
         <v>3.72</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="P57" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.61</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.079</v>
       </c>
-      <c r="E58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.08</v>
       </c>
-      <c r="H58" t="n">
+      <c r="K58" t="n">
         <v>0.001</v>
       </c>
-      <c r="I58" t="n">
+      <c r="L58" t="n">
         <v>1.27</v>
       </c>
-      <c r="J58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="K58" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-1.25</v>
-      </c>
       <c r="M58" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="N58" t="n">
         <v>0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P58" t="n">
         <v>0.081</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.17</v>
+        <v>21.39</v>
       </c>
       <c r="E59" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G59" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="J59" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L59" t="n">
         <v>-0.19</v>
       </c>
-      <c r="F59" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="G59" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J59" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K59" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-2.06</v>
-      </c>
       <c r="M59" t="n">
-        <v>20.91</v>
+        <v>20.96</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
       <c r="P59" t="n">
-        <v>20.96</v>
+        <v>21.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="R59" t="n">
-        <v>0.24</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3</v>
+        <v>-2.42</v>
       </c>
       <c r="G60" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="H60" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N60" t="n">
         <v>-0.08</v>
       </c>
-      <c r="I60" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="O60" t="n">
-        <v>-0.31</v>
+        <v>-2.45</v>
       </c>
       <c r="P60" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="R60" t="n">
-        <v>-2.45</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J61" t="n">
         <v>1.51</v>
       </c>
-      <c r="E61" t="n">
+      <c r="K61" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N61" t="n">
         <v>0.04</v>
       </c>
-      <c r="F61" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L61" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="N61" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="O61" t="n">
-        <v>-3.21</v>
+        <v>2.65</v>
       </c>
       <c r="P61" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="R61" t="n">
-        <v>2.65</v>
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-06 Close</t>
+          <t>2026-05-07 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change</t>
+          <t>2026-05-07 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-06 Change %</t>
+          <t>2026-05-07 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-07 Close</t>
+          <t>2026-05-08 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change</t>
+          <t>2026-05-08 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change %</t>
+          <t>2026-05-08 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-08 Close</t>
+          <t>2026-05-11 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change</t>
+          <t>2026-05-11 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change %</t>
+          <t>2026-05-11 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-11 Close</t>
+          <t>2026-05-12 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change</t>
+          <t>2026-05-12 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change %</t>
+          <t>2026-05-12 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-12 Close</t>
+          <t>2026-05-13 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change</t>
+          <t>2026-05-13 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change %</t>
+          <t>2026-05-13 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>140.5</v>
+        <v>143.1</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>143.1</v>
+        <v>138.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6</v>
+        <v>-4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>-3.07</v>
       </c>
       <c r="J3" t="n">
-        <v>138.7</v>
+        <v>141.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.4</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.07</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>141.2</v>
+        <v>138.6</v>
       </c>
       <c r="N3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="P3" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.5</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>138.6</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-1.84</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>201.6</v>
+        <v>203.6</v>
       </c>
       <c r="E4" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>4.89</v>
+        <v>0.99</v>
       </c>
       <c r="G4" t="n">
-        <v>203.6</v>
+        <v>199</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>-4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.99</v>
+        <v>-2.26</v>
       </c>
       <c r="J4" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.6</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.26</v>
+        <v>2.01</v>
       </c>
       <c r="M4" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.01</v>
+        <v>-4.43</v>
       </c>
       <c r="P4" t="n">
-        <v>194</v>
+        <v>198.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9</v>
+        <v>4.1</v>
       </c>
       <c r="R4" t="n">
-        <v>-4.43</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G5" t="n">
         <v>5.94</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.96</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="J5" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.34</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="N5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.06</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.95</v>
+        <v>6.99</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="G6" t="n">
-        <v>6.99</v>
+        <v>6.92</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.58</v>
+        <v>-1</v>
       </c>
       <c r="J6" t="n">
-        <v>6.92</v>
+        <v>6.98</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L6" t="n">
-        <v>-1</v>
+        <v>0.87</v>
       </c>
       <c r="M6" t="n">
-        <v>6.98</v>
+        <v>7.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>1.98</v>
+        <v>-0.19</v>
       </c>
       <c r="G7" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.19</v>
+        <v>-0.58</v>
       </c>
       <c r="J7" t="n">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
       <c r="M7" t="n">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="J8" t="n">
-        <v>8.76</v>
+        <v>8.84</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.35</v>
+        <v>0.91</v>
       </c>
       <c r="M8" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O8" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="P8" t="n">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.68</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="9">
@@ -949,34 +949,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="G9" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="J9" t="n">
         <v>7.27</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7.23</v>
-      </c>
       <c r="K9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.55</v>
+        <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>7.27</v>
+        <v>7.31</v>
       </c>
       <c r="N9" t="n">
         <v>0.04</v>
@@ -985,13 +985,13 @@
         <v>0.55</v>
       </c>
       <c r="P9" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R9" t="n">
-        <v>0.55</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.04</v>
+        <v>47.82</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.06</v>
+        <v>0.78</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.13</v>
+        <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>47.82</v>
+        <v>47.24</v>
       </c>
       <c r="H10" t="n">
-        <v>0.78</v>
+        <v>-0.58</v>
       </c>
       <c r="I10" t="n">
-        <v>1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="J10" t="n">
-        <v>47.24</v>
+        <v>47.46</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.21</v>
+        <v>0.47</v>
       </c>
       <c r="M10" t="n">
-        <v>47.46</v>
+        <v>47.52</v>
       </c>
       <c r="N10" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="P10" t="n">
-        <v>47.52</v>
+        <v>47.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0.13</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.71</v>
+        <v>4.65</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" t="n">
-        <v>2.39</v>
+        <v>-1.27</v>
       </c>
       <c r="G11" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="P11" t="n">
         <v>4.65</v>
       </c>
-      <c r="H11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.62</v>
-      </c>
       <c r="Q11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R11" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.68</v>
+        <v>10.69</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-8.48</v>
       </c>
       <c r="G12" t="n">
-        <v>10.69</v>
+        <v>10.59</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.99</v>
+        <v>-0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>10.59</v>
+        <v>10.64</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="M12" t="n">
-        <v>10.64</v>
+        <v>11.06</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="O12" t="n">
-        <v>0.47</v>
+        <v>3.95</v>
       </c>
       <c r="P12" t="n">
         <v>11.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.04</v>
+        <v>26.42</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.52</v>
+        <v>-1.62</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.82</v>
+        <v>-5.78</v>
       </c>
       <c r="G13" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.62</v>
+        <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.78</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>26.44</v>
+        <v>26.6</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
       <c r="M13" t="n">
-        <v>26.6</v>
+        <v>26.92</v>
       </c>
       <c r="N13" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="O13" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>26.92</v>
+        <v>26.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.89</v>
+        <v>-0.37</v>
       </c>
       <c r="G14" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.37</v>
+        <v>-1.11</v>
       </c>
       <c r="J14" t="n">
         <v>2.68</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.75</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>1.75</v>
+        <v>-1.15</v>
       </c>
       <c r="J15" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.15</v>
+        <v>0.58</v>
       </c>
       <c r="M15" t="n">
-        <v>5.21</v>
+        <v>5.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="O15" t="n">
-        <v>0.58</v>
+        <v>4.61</v>
       </c>
       <c r="P15" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="R15" t="n">
-        <v>4.61</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G16" t="n">
         <v>5.24</v>
       </c>
-      <c r="E16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.27</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="I16" t="n">
-        <v>0.57</v>
+        <v>-0.57</v>
       </c>
       <c r="J16" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.57</v>
+        <v>-0.76</v>
       </c>
       <c r="M16" t="n">
         <v>5.2</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P17" t="n">
         <v>3.87</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.85</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="18">
@@ -1510,46 +1510,46 @@
         <v>3.54</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.04</v>
       </c>
-      <c r="F18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="J18" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="L18" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="P18" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.28</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64.2</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>66</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8</v>
+        <v>-0.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>-0.61</v>
       </c>
       <c r="J19" t="n">
-        <v>65.59999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.61</v>
+        <v>-0.84</v>
       </c>
       <c r="M19" t="n">
-        <v>65.05</v>
+        <v>65</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.84</v>
+        <v>-0.08</v>
       </c>
       <c r="P19" t="n">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.08</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.9</v>
+        <v>31.18</v>
       </c>
       <c r="E20" t="n">
-        <v>0.78</v>
+        <v>1.28</v>
       </c>
       <c r="F20" t="n">
-        <v>2.68</v>
+        <v>4.28</v>
       </c>
       <c r="G20" t="n">
-        <v>31.18</v>
+        <v>31.26</v>
       </c>
       <c r="H20" t="n">
-        <v>1.28</v>
+        <v>0.08</v>
       </c>
       <c r="I20" t="n">
-        <v>4.28</v>
+        <v>0.26</v>
       </c>
       <c r="J20" t="n">
-        <v>31.26</v>
+        <v>31.38</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="L20" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="M20" t="n">
-        <v>31.38</v>
+        <v>30.58</v>
       </c>
       <c r="N20" t="n">
-        <v>0.12</v>
+        <v>-0.8</v>
       </c>
       <c r="O20" t="n">
-        <v>0.38</v>
+        <v>-2.55</v>
       </c>
       <c r="P20" t="n">
-        <v>30.58</v>
+        <v>29.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.8</v>
+        <v>-0.62</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.55</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.19</v>
+        <v>5.35</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="F21" t="n">
-        <v>1.17</v>
+        <v>3.08</v>
       </c>
       <c r="G21" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="H21" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>3.08</v>
+        <v>1.31</v>
       </c>
       <c r="J21" t="n">
-        <v>5.42</v>
+        <v>5.49</v>
       </c>
       <c r="K21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="O21" t="n">
-        <v>1.29</v>
+        <v>-0.55</v>
       </c>
       <c r="P21" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.55</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>84.7</v>
+        <v>85.3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="G22" t="n">
-        <v>85.3</v>
+        <v>85.45</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.71</v>
+        <v>0.18</v>
       </c>
       <c r="J22" t="n">
-        <v>85.45</v>
+        <v>86.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="L22" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
       <c r="M22" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="P22" t="n">
-        <v>86.5</v>
+        <v>86.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.35</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G23" t="n">
         <v>27.4</v>
       </c>
-      <c r="E23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="G23" t="n">
-        <v>27.52</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.12</v>
+        <v>-0.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="J23" t="n">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>27.38</v>
+        <v>26.38</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.02</v>
+        <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.65</v>
       </c>
       <c r="P23" t="n">
-        <v>26.38</v>
+        <v>26.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>-3.65</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.68</v>
+        <v>26.46</v>
       </c>
       <c r="E24" t="n">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="F24" t="n">
-        <v>1.56</v>
+        <v>7.21</v>
       </c>
       <c r="G24" t="n">
-        <v>26.46</v>
+        <v>28.24</v>
       </c>
       <c r="H24" t="n">
         <v>1.78</v>
       </c>
       <c r="I24" t="n">
-        <v>7.21</v>
+        <v>6.73</v>
       </c>
       <c r="J24" t="n">
-        <v>28.24</v>
+        <v>28.86</v>
       </c>
       <c r="K24" t="n">
-        <v>1.78</v>
+        <v>0.62</v>
       </c>
       <c r="L24" t="n">
-        <v>6.73</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>28.86</v>
+        <v>29.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="O24" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>29.2</v>
+        <v>29.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.82</v>
+        <v>31.12</v>
       </c>
       <c r="E25" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="F25" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="G25" t="n">
-        <v>31.12</v>
+        <v>31.68</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.97</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>0.06</v>
       </c>
       <c r="M25" t="n">
-        <v>31.7</v>
+        <v>31.46</v>
       </c>
       <c r="N25" t="n">
-        <v>0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06</v>
+        <v>-0.76</v>
       </c>
       <c r="P25" t="n">
-        <v>31.46</v>
+        <v>31.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.24</v>
+        <v>0.34</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.76</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>58.55</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>7.55</v>
       </c>
       <c r="F26" t="n">
-        <v>8.51</v>
+        <v>14.8</v>
       </c>
       <c r="G26" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="H26" t="n">
-        <v>7.55</v>
+        <v>-1.9</v>
       </c>
       <c r="I26" t="n">
-        <v>14.8</v>
+        <v>-3.25</v>
       </c>
       <c r="J26" t="n">
-        <v>56.65</v>
+        <v>56.6</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.9</v>
+        <v>-0.05</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.25</v>
+        <v>-0.09</v>
       </c>
       <c r="M26" t="n">
-        <v>56.6</v>
+        <v>55.15</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.05</v>
+        <v>-1.45</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.09</v>
+        <v>-2.56</v>
       </c>
       <c r="P26" t="n">
-        <v>55.15</v>
+        <v>55.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.45</v>
+        <v>0.1</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.56</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>463</v>
+        <v>477.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.95</v>
+        <v>3.11</v>
       </c>
       <c r="G27" t="n">
-        <v>477.4</v>
+        <v>471.4</v>
       </c>
       <c r="H27" t="n">
-        <v>14.4</v>
+        <v>-6</v>
       </c>
       <c r="I27" t="n">
-        <v>3.11</v>
+        <v>-1.26</v>
       </c>
       <c r="J27" t="n">
-        <v>471.4</v>
+        <v>464.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.26</v>
+        <v>-1.48</v>
       </c>
       <c r="M27" t="n">
-        <v>464.4</v>
+        <v>457.2</v>
       </c>
       <c r="N27" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.48</v>
+        <v>-1.55</v>
       </c>
       <c r="P27" t="n">
-        <v>457.2</v>
+        <v>462.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.2</v>
+        <v>5.4</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.55</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>134.2</v>
+        <v>140.9</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="F28" t="n">
-        <v>2.29</v>
+        <v>4.99</v>
       </c>
       <c r="G28" t="n">
-        <v>140.9</v>
+        <v>139</v>
       </c>
       <c r="H28" t="n">
-        <v>6.7</v>
+        <v>-1.9</v>
       </c>
       <c r="I28" t="n">
-        <v>4.99</v>
+        <v>-1.35</v>
       </c>
       <c r="J28" t="n">
-        <v>139</v>
+        <v>133.9</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.9</v>
+        <v>-5.1</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.35</v>
+        <v>-3.67</v>
       </c>
       <c r="M28" t="n">
-        <v>133.9</v>
+        <v>133.3</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.67</v>
+        <v>-0.45</v>
       </c>
       <c r="P28" t="n">
-        <v>133.3</v>
+        <v>132.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>116.4</v>
+        <v>119</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="F29" t="n">
-        <v>0.17</v>
+        <v>2.23</v>
       </c>
       <c r="G29" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6</v>
+        <v>-0.5</v>
       </c>
       <c r="I29" t="n">
-        <v>2.23</v>
+        <v>-0.42</v>
       </c>
       <c r="J29" t="n">
         <v>118.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>118.5</v>
+        <v>118.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="P29" t="n">
-        <v>118.4</v>
+        <v>128.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.08</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82.5</v>
+        <v>84.25</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.05</v>
+        <v>1.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.26</v>
+        <v>2.12</v>
       </c>
       <c r="G30" t="n">
-        <v>84.25</v>
+        <v>84.05</v>
       </c>
       <c r="H30" t="n">
-        <v>1.75</v>
+        <v>-0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>2.12</v>
+        <v>-0.24</v>
       </c>
       <c r="J30" t="n">
-        <v>84.05</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="N30" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L30" t="n">
+      <c r="O30" t="n">
         <v>-0.24</v>
       </c>
-      <c r="M30" t="n">
-        <v>84.34999999999999</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0.36</v>
-      </c>
       <c r="P30" t="n">
-        <v>84.15000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.2</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.24</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>131.6</v>
+        <v>137.3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="F31" t="n">
-        <v>4.94</v>
+        <v>4.33</v>
       </c>
       <c r="G31" t="n">
-        <v>137.3</v>
+        <v>145.2</v>
       </c>
       <c r="H31" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="I31" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="J31" t="n">
-        <v>145.2</v>
+        <v>140.9</v>
       </c>
       <c r="K31" t="n">
-        <v>7.9</v>
+        <v>-4.3</v>
       </c>
       <c r="L31" t="n">
-        <v>5.75</v>
+        <v>-2.96</v>
       </c>
       <c r="M31" t="n">
-        <v>140.9</v>
+        <v>139.7</v>
       </c>
       <c r="N31" t="n">
-        <v>-4.3</v>
+        <v>-1.2</v>
       </c>
       <c r="O31" t="n">
-        <v>-2.96</v>
+        <v>-0.85</v>
       </c>
       <c r="P31" t="n">
-        <v>139.7</v>
+        <v>137.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.2</v>
+        <v>-2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.85</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>74.84999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="E32" t="n">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="F32" t="n">
-        <v>5.72</v>
+        <v>2.54</v>
       </c>
       <c r="G32" t="n">
-        <v>76.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="I32" t="n">
-        <v>2.54</v>
+        <v>-4.43</v>
       </c>
       <c r="J32" t="n">
-        <v>73.34999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L32" t="n">
-        <v>-4.43</v>
+        <v>4.43</v>
       </c>
       <c r="M32" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>76.59999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>98.90000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.08</v>
+        <v>1.82</v>
       </c>
       <c r="G33" t="n">
-        <v>100.7</v>
+        <v>99.75</v>
       </c>
       <c r="H33" t="n">
-        <v>1.8</v>
+        <v>-0.95</v>
       </c>
       <c r="I33" t="n">
-        <v>1.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>99.75</v>
+        <v>101.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.95</v>
+        <v>1.95</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>101.7</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>1.95</v>
+        <v>-1.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.95</v>
+        <v>-1.82</v>
       </c>
       <c r="P33" t="n">
-        <v>99.84999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.85</v>
+        <v>-1.7</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.82</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45</v>
+        <v>48.4</v>
       </c>
       <c r="E34" t="n">
-        <v>0.82</v>
+        <v>3.4</v>
       </c>
       <c r="F34" t="n">
-        <v>1.86</v>
+        <v>7.56</v>
       </c>
       <c r="G34" t="n">
-        <v>48.4</v>
+        <v>52.95</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="I34" t="n">
-        <v>7.56</v>
+        <v>9.4</v>
       </c>
       <c r="J34" t="n">
-        <v>52.95</v>
+        <v>51.6</v>
       </c>
       <c r="K34" t="n">
-        <v>4.55</v>
+        <v>-1.35</v>
       </c>
       <c r="L34" t="n">
-        <v>9.4</v>
+        <v>-2.55</v>
       </c>
       <c r="M34" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P34" t="n">
         <v>51.6</v>
       </c>
-      <c r="N34" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="P34" t="n">
-        <v>52.6</v>
-      </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.94</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.87</v>
+        <v>5.01</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>2.87</v>
       </c>
       <c r="G35" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="I35" t="n">
-        <v>2.87</v>
+        <v>-0.2</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="P35" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.42</v>
+        <v>10.76</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="F36" t="n">
-        <v>0.87</v>
+        <v>3.26</v>
       </c>
       <c r="G36" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="H36" t="n">
-        <v>0.34</v>
+        <v>-0.03</v>
       </c>
       <c r="I36" t="n">
-        <v>3.26</v>
+        <v>-0.28</v>
       </c>
       <c r="J36" t="n">
         <v>10.73</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>10.73</v>
+        <v>10.66</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="P36" t="n">
-        <v>10.66</v>
+        <v>10.72</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.65</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>421.2</v>
+        <v>427</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="F37" t="n">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
       <c r="G37" t="n">
-        <v>427</v>
+        <v>424.2</v>
       </c>
       <c r="H37" t="n">
-        <v>5.8</v>
+        <v>-2.8</v>
       </c>
       <c r="I37" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="J37" t="n">
-        <v>424.2</v>
+        <v>425.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.66</v>
+        <v>0.28</v>
       </c>
       <c r="M37" t="n">
-        <v>425.4</v>
+        <v>423.8</v>
       </c>
       <c r="N37" t="n">
-        <v>1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="O37" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="P37" t="n">
         <v>423.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.24</v>
+        <v>16.39</v>
       </c>
       <c r="E38" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="F38" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
       <c r="G38" t="n">
-        <v>16.39</v>
+        <v>16.42</v>
       </c>
       <c r="H38" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="I38" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
       <c r="J38" t="n">
-        <v>16.42</v>
+        <v>16.08</v>
       </c>
       <c r="K38" t="n">
-        <v>0.03</v>
+        <v>-0.34</v>
       </c>
       <c r="L38" t="n">
-        <v>0.18</v>
+        <v>-2.07</v>
       </c>
       <c r="M38" t="n">
-        <v>16.08</v>
+        <v>16.14</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.34</v>
+        <v>0.06</v>
       </c>
       <c r="O38" t="n">
-        <v>-2.07</v>
+        <v>0.37</v>
       </c>
       <c r="P38" t="n">
-        <v>16.14</v>
+        <v>16.03</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="R38" t="n">
-        <v>0.37</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E39" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="F39" t="n">
-        <v>2.14</v>
+        <v>-0.6</v>
       </c>
       <c r="G39" t="n">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="H39" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6</v>
+        <v>-2.11</v>
       </c>
       <c r="J39" t="n">
-        <v>651</v>
+        <v>657.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-14</v>
+        <v>6.5</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.11</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>657.5</v>
+        <v>651.5</v>
       </c>
       <c r="N39" t="n">
-        <v>6.5</v>
+        <v>-6</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>-0.91</v>
       </c>
       <c r="P39" t="n">
-        <v>651.5</v>
+        <v>673</v>
       </c>
       <c r="Q39" t="n">
-        <v>-6</v>
+        <v>21.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.91</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>60.25</v>
+        <v>62.25</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.5</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.98</v>
+        <v>3.32</v>
       </c>
       <c r="G40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>-0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>3.32</v>
+        <v>-1.53</v>
       </c>
       <c r="J40" t="n">
-        <v>61.3</v>
+        <v>62.5</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.95</v>
+        <v>1.2</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.53</v>
+        <v>1.96</v>
       </c>
       <c r="M40" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="N40" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.96</v>
+        <v>0.16</v>
       </c>
       <c r="P40" t="n">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="R40" t="n">
-        <v>0.16</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="E41" t="n">
-        <v>0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="F41" t="n">
-        <v>0.78</v>
+        <v>-0.55</v>
       </c>
       <c r="G41" t="n">
-        <v>21.88</v>
+        <v>21.92</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.55</v>
+        <v>0.18</v>
       </c>
       <c r="J41" t="n">
-        <v>21.92</v>
+        <v>22.5</v>
       </c>
       <c r="K41" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="L41" t="n">
-        <v>0.18</v>
+        <v>2.65</v>
       </c>
       <c r="M41" t="n">
-        <v>22.5</v>
+        <v>22.33</v>
       </c>
       <c r="N41" t="n">
-        <v>0.58</v>
+        <v>-0.17</v>
       </c>
       <c r="O41" t="n">
-        <v>2.65</v>
+        <v>-0.76</v>
       </c>
       <c r="P41" t="n">
-        <v>22.33</v>
+        <v>22.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.76</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="F42" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="G42" t="n">
-        <v>58.86</v>
+        <v>58.68</v>
       </c>
       <c r="H42" t="n">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.02</v>
+        <v>-0.31</v>
       </c>
       <c r="J42" t="n">
-        <v>58.68</v>
+        <v>58.77</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.18</v>
+        <v>0.09</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.31</v>
+        <v>0.15</v>
       </c>
       <c r="M42" t="n">
-        <v>58.77</v>
+        <v>59.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="O42" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>59.1</v>
+        <v>59.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="R42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36.65</v>
+        <v>36.7</v>
       </c>
       <c r="E43" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="F43" t="n">
-        <v>1.02</v>
+        <v>0.14</v>
       </c>
       <c r="G43" t="n">
-        <v>36.7</v>
+        <v>36.56</v>
       </c>
       <c r="H43" t="n">
-        <v>0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="I43" t="n">
-        <v>0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="J43" t="n">
-        <v>36.56</v>
+        <v>36.99</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.38</v>
+        <v>1.18</v>
       </c>
       <c r="M43" t="n">
-        <v>36.99</v>
+        <v>37.11</v>
       </c>
       <c r="N43" t="n">
-        <v>0.43</v>
+        <v>0.12</v>
       </c>
       <c r="O43" t="n">
-        <v>1.18</v>
+        <v>0.32</v>
       </c>
       <c r="P43" t="n">
-        <v>37.11</v>
+        <v>37.35</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="R43" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.56</v>
+        <v>6.41</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.94</v>
+        <v>-2.29</v>
       </c>
       <c r="G44" t="n">
-        <v>6.41</v>
+        <v>6.35</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.06</v>
+        <v>-0.17</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.68</v>
       </c>
       <c r="M44" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.17</v>
+        <v>0.04</v>
       </c>
       <c r="O44" t="n">
-        <v>-2.68</v>
+        <v>0.65</v>
       </c>
       <c r="P44" t="n">
-        <v>6.22</v>
+        <v>6.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R44" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="G45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="M45" t="n">
         <v>2.35</v>
       </c>
-      <c r="H45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K45" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.23</v>
-      </c>
       <c r="N45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="O45" t="n">
-        <v>-3.04</v>
+        <v>5.38</v>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="R45" t="n">
-        <v>5.38</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="E46" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N46" t="n">
         <v>0.03</v>
       </c>
-      <c r="F46" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="O46" t="n">
-        <v>-2.69</v>
+        <v>0.92</v>
       </c>
       <c r="P46" t="n">
         <v>3.28</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.92</v>
+        <v>10.74</v>
       </c>
       <c r="E47" t="n">
-        <v>0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="F47" t="n">
-        <v>1.2</v>
+        <v>-1.65</v>
       </c>
       <c r="G47" t="n">
-        <v>10.74</v>
+        <v>10.66</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.65</v>
+        <v>-0.74</v>
       </c>
       <c r="J47" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.74</v>
+        <v>-0.28</v>
       </c>
       <c r="M47" t="n">
-        <v>10.63</v>
+        <v>10.64</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.28</v>
+        <v>0.09</v>
       </c>
       <c r="P47" t="n">
-        <v>10.64</v>
+        <v>10.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="R47" t="n">
-        <v>0.09</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.38</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>1.33</v>
       </c>
-      <c r="G48" t="n">
+      <c r="J48" t="n">
         <v>0.375</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="J48" t="n">
+      <c r="M48" t="n">
         <v>0.38</v>
       </c>
-      <c r="K48" t="n">
+      <c r="N48" t="n">
         <v>0.005</v>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>1.33</v>
       </c>
-      <c r="M48" t="n">
+      <c r="P48" t="n">
         <v>0.375</v>
       </c>
-      <c r="N48" t="n">
+      <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>-1.32</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.33</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.92</v>
+        <v>1.09</v>
       </c>
       <c r="G49" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="H49" t="n">
         <v>0.05</v>
       </c>
       <c r="I49" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="J49" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="K49" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L49" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="M49" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="N49" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="O49" t="n">
-        <v>1.28</v>
+        <v>-0.63</v>
       </c>
       <c r="P49" t="n">
-        <v>4.72</v>
+        <v>4.82</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.63</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="50">
@@ -3494,10 +3494,10 @@
         <v>1.01</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>1.01</v>
@@ -3518,22 +3518,22 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="P50" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R50" t="n">
-        <v>0.99</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="F51" t="n">
-        <v>-4.17</v>
+        <v>-0.97</v>
       </c>
       <c r="G51" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.97</v>
+        <v>-2.44</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.44</v>
+        <v>-2.25</v>
       </c>
       <c r="M51" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.25</v>
+        <v>1.02</v>
       </c>
       <c r="P51" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R51" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.96</v>
+        <v>11.14</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.09</v>
+        <v>1.64</v>
       </c>
       <c r="G52" t="n">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
       <c r="H52" t="n">
-        <v>0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="I52" t="n">
-        <v>1.64</v>
+        <v>-1.8</v>
       </c>
       <c r="J52" t="n">
-        <v>10.94</v>
+        <v>10.91</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.8</v>
+        <v>-0.27</v>
       </c>
       <c r="M52" t="n">
-        <v>10.91</v>
+        <v>10.78</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.27</v>
+        <v>-1.19</v>
       </c>
       <c r="P52" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.13</v>
+        <v>0.11</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.19</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="E53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F53" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="G53" t="n">
-        <v>8.33</v>
+        <v>8.26</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>0.97</v>
+        <v>-0.84</v>
       </c>
       <c r="J53" t="n">
-        <v>8.26</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.84</v>
+        <v>-1.82</v>
       </c>
       <c r="M53" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P53" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="N53" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="P53" t="n">
-        <v>8.130000000000001</v>
-      </c>
       <c r="Q53" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="R53" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.425</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.42</v>
-      </c>
       <c r="H54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="J54" t="n">
         <v>0.425</v>
       </c>
       <c r="K54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="P54" t="n">
         <v>0.42</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="E55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="H55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="K55" t="n">
         <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="M55" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.73</v>
+        <v>1.47</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R55" t="n">
-        <v>1.47</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="56">
@@ -3863,40 +3863,40 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.49</v>
       </c>
-      <c r="E56" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.505</v>
-      </c>
       <c r="H56" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="I56" t="n">
-        <v>3.06</v>
+        <v>-2.97</v>
       </c>
       <c r="J56" t="n">
         <v>0.49</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.97</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="P56" t="n">
         <v>0.48</v>
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.53</v>
+        <v>-0.8</v>
       </c>
       <c r="G57" t="n">
         <v>3.72</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="M57" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.61</v>
+        <v>0.27</v>
       </c>
       <c r="P57" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="R57" t="n">
-        <v>0.27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3987,40 +3987,40 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.08</v>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
         <v>0.001</v>
       </c>
-      <c r="F58" t="n">
+      <c r="I58" t="n">
         <v>1.27</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-1.25</v>
-      </c>
       <c r="J58" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="K58" t="n">
         <v>0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M58" t="n">
         <v>0.081</v>
       </c>
       <c r="N58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0.081</v>
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.39</v>
+        <v>20.95</v>
       </c>
       <c r="E59" t="n">
-        <v>0.22</v>
+        <v>-0.44</v>
       </c>
       <c r="F59" t="n">
-        <v>1.04</v>
+        <v>-2.06</v>
       </c>
       <c r="G59" t="n">
-        <v>20.95</v>
+        <v>20.91</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.44</v>
+        <v>-0.04</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.06</v>
+        <v>-0.19</v>
       </c>
       <c r="J59" t="n">
-        <v>20.91</v>
+        <v>20.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
       <c r="M59" t="n">
-        <v>20.96</v>
+        <v>21.1</v>
       </c>
       <c r="N59" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="O59" t="n">
-        <v>0.24</v>
+        <v>0.67</v>
       </c>
       <c r="P59" t="n">
-        <v>21.1</v>
+        <v>21.58</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="R59" t="n">
-        <v>0.67</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="E60" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K60" t="n">
         <v>-0.08</v>
       </c>
-      <c r="F60" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="K60" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="L60" t="n">
-        <v>-0.31</v>
+        <v>-2.45</v>
       </c>
       <c r="M60" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="O60" t="n">
-        <v>-2.45</v>
+        <v>3.14</v>
       </c>
       <c r="P60" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="R60" t="n">
-        <v>3.14</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F61" t="n">
-        <v>0.66</v>
+        <v>2.63</v>
       </c>
       <c r="G61" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="H61" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="K61" t="n">
         <v>0.04</v>
       </c>
-      <c r="I61" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="K61" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="L61" t="n">
-        <v>-3.21</v>
+        <v>2.65</v>
       </c>
       <c r="M61" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="N61" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O61" t="n">
-        <v>2.65</v>
+        <v>1.29</v>
       </c>
       <c r="P61" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R61" t="n">
-        <v>1.29</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-07 Close</t>
+          <t>2026-05-08 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change</t>
+          <t>2026-05-08 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-07 Change %</t>
+          <t>2026-05-08 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-08 Close</t>
+          <t>2026-05-11 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change</t>
+          <t>2026-05-11 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change %</t>
+          <t>2026-05-11 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-11 Close</t>
+          <t>2026-05-12 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change</t>
+          <t>2026-05-12 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change %</t>
+          <t>2026-05-12 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-12 Close</t>
+          <t>2026-05-13 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change</t>
+          <t>2026-05-13 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change %</t>
+          <t>2026-05-13 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-13 Close</t>
+          <t>2026-05-14 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change</t>
+          <t>2026-05-14 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change %</t>
+          <t>2026-05-14 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>143.1</v>
+        <v>138.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6</v>
+        <v>-4.4</v>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>-3.07</v>
       </c>
       <c r="G3" t="n">
-        <v>138.7</v>
+        <v>141.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.4</v>
+        <v>2.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.07</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
-        <v>141.2</v>
+        <v>138.6</v>
       </c>
       <c r="K3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="M3" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>1.8</v>
       </c>
-      <c r="M3" t="n">
-        <v>138.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-1.84</v>
-      </c>
       <c r="P3" t="n">
-        <v>141.1</v>
+        <v>140.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>-0.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>203.6</v>
+        <v>199</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>-4.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.99</v>
+        <v>-2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.26</v>
+        <v>2.01</v>
       </c>
       <c r="J4" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="L4" t="n">
-        <v>2.01</v>
+        <v>-4.43</v>
       </c>
       <c r="M4" t="n">
-        <v>194</v>
+        <v>198.1</v>
       </c>
       <c r="N4" t="n">
-        <v>-9</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.43</v>
+        <v>2.11</v>
       </c>
       <c r="P4" t="n">
-        <v>198.1</v>
+        <v>199.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.11</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.96</v>
+        <v>5.94</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="G5" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.34</v>
+        <v>1.01</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="K5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="O5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>6.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.99</v>
+        <v>6.92</v>
       </c>
       <c r="E6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.04</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="R6" t="n">
-        <v>-0.71</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.19</v>
+        <v>-0.58</v>
       </c>
       <c r="G7" t="n">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J7" t="n">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="N7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="R7" t="n">
-        <v>-0.38</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="G8" t="n">
-        <v>8.76</v>
+        <v>8.84</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.35</v>
+        <v>0.91</v>
       </c>
       <c r="J8" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="M8" t="n">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0.68</v>
+        <v>-0.34</v>
       </c>
       <c r="P8" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -949,25 +949,25 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="G9" t="n">
         <v>7.27</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.23</v>
-      </c>
       <c r="H9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.55</v>
+        <v>0.55</v>
       </c>
       <c r="J9" t="n">
-        <v>7.27</v>
+        <v>7.31</v>
       </c>
       <c r="K9" t="n">
         <v>0.04</v>
@@ -976,22 +976,22 @@
         <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O9" t="n">
-        <v>0.55</v>
+        <v>-0.14</v>
       </c>
       <c r="P9" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.14</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.82</v>
+        <v>47.24</v>
       </c>
       <c r="E10" t="n">
-        <v>0.78</v>
+        <v>-0.58</v>
       </c>
       <c r="F10" t="n">
-        <v>1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G10" t="n">
-        <v>47.24</v>
+        <v>47.46</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.21</v>
+        <v>0.47</v>
       </c>
       <c r="J10" t="n">
-        <v>47.46</v>
+        <v>47.52</v>
       </c>
       <c r="K10" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="M10" t="n">
-        <v>47.52</v>
+        <v>47.22</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="P10" t="n">
-        <v>47.22</v>
+        <v>47.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3</v>
+        <v>0.26</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.63</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M11" t="n">
         <v>4.65</v>
       </c>
-      <c r="E11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.62</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="O11" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="R11" t="n">
-        <v>0.65</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.69</v>
+        <v>10.59</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.99</v>
+        <v>-0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>10.59</v>
+        <v>10.64</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="J12" t="n">
-        <v>10.64</v>
+        <v>11.06</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="L12" t="n">
-        <v>0.47</v>
+        <v>3.95</v>
       </c>
       <c r="M12" t="n">
         <v>11.06</v>
       </c>
       <c r="N12" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>11.06</v>
+        <v>10.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.62</v>
+        <v>0.02</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.78</v>
+        <v>0.08</v>
       </c>
       <c r="G13" t="n">
-        <v>26.44</v>
+        <v>26.6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
       <c r="J13" t="n">
-        <v>26.6</v>
+        <v>26.92</v>
       </c>
       <c r="K13" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="L13" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
-        <v>26.92</v>
+        <v>26.62</v>
       </c>
       <c r="N13" t="n">
-        <v>0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>-1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>26.62</v>
+        <v>26.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.11</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.37</v>
+        <v>-1.11</v>
       </c>
       <c r="G14" t="n">
         <v>2.68</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.11</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.75</v>
+        <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>-1.15</v>
       </c>
       <c r="G15" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="H15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.06</v>
       </c>
-      <c r="I15" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="R15" t="n">
-        <v>-0.37</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.27</v>
+        <v>5.24</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="F16" t="n">
-        <v>0.57</v>
+        <v>-0.57</v>
       </c>
       <c r="G16" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.57</v>
+        <v>-0.76</v>
       </c>
       <c r="J16" t="n">
         <v>5.2</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="P16" t="n">
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.38</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.87</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.85</v>
-      </c>
       <c r="N17" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O17" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="P17" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="R17" t="n">
-        <v>0.52</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="G18" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I18" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="M18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="P18" t="n">
         <v>3.59</v>
       </c>
-      <c r="N18" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.56</v>
-      </c>
       <c r="Q18" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.84</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8</v>
+        <v>-0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>-0.61</v>
       </c>
       <c r="G19" t="n">
-        <v>65.59999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.61</v>
+        <v>-0.84</v>
       </c>
       <c r="J19" t="n">
-        <v>65.05</v>
+        <v>65</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.84</v>
+        <v>-0.08</v>
       </c>
       <c r="M19" t="n">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.08</v>
+        <v>-1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.38</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.18</v>
+        <v>31.26</v>
       </c>
       <c r="E20" t="n">
-        <v>1.28</v>
+        <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>4.28</v>
+        <v>0.26</v>
       </c>
       <c r="G20" t="n">
-        <v>31.26</v>
+        <v>31.38</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="J20" t="n">
-        <v>31.38</v>
+        <v>30.58</v>
       </c>
       <c r="K20" t="n">
-        <v>0.12</v>
+        <v>-0.8</v>
       </c>
       <c r="L20" t="n">
-        <v>0.38</v>
+        <v>-2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>30.58</v>
+        <v>29.96</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8</v>
+        <v>-0.62</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.55</v>
+        <v>-2.03</v>
       </c>
       <c r="P20" t="n">
-        <v>29.96</v>
+        <v>29.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.03</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="E21" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>3.08</v>
+        <v>1.31</v>
       </c>
       <c r="G21" t="n">
-        <v>5.42</v>
+        <v>5.49</v>
       </c>
       <c r="H21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="J21" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="K21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>-0.55</v>
       </c>
       <c r="M21" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.55</v>
+        <v>-0.18</v>
       </c>
       <c r="P21" t="n">
-        <v>5.45</v>
+        <v>5.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.18</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.3</v>
+        <v>85.45</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F22" t="n">
-        <v>0.71</v>
+        <v>0.18</v>
       </c>
       <c r="G22" t="n">
-        <v>85.45</v>
+        <v>86.2</v>
       </c>
       <c r="H22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J22" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P22" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0.15</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M22" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="P22" t="n">
-        <v>86.55</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.05</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.52</v>
+        <v>27.4</v>
       </c>
       <c r="E23" t="n">
-        <v>0.12</v>
+        <v>-0.12</v>
       </c>
       <c r="F23" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="G23" t="n">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>27.38</v>
+        <v>26.38</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.02</v>
+        <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.65</v>
       </c>
       <c r="M23" t="n">
-        <v>26.38</v>
+        <v>26.88</v>
       </c>
       <c r="N23" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.65</v>
+        <v>1.9</v>
       </c>
       <c r="P23" t="n">
-        <v>26.88</v>
+        <v>26.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26.46</v>
+        <v>28.24</v>
       </c>
       <c r="E24" t="n">
         <v>1.78</v>
       </c>
       <c r="F24" t="n">
-        <v>7.21</v>
+        <v>6.73</v>
       </c>
       <c r="G24" t="n">
-        <v>28.24</v>
+        <v>28.86</v>
       </c>
       <c r="H24" t="n">
-        <v>1.78</v>
+        <v>0.62</v>
       </c>
       <c r="I24" t="n">
-        <v>6.73</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
-        <v>28.86</v>
+        <v>29.2</v>
       </c>
       <c r="K24" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="M24" t="n">
-        <v>29.2</v>
+        <v>29.66</v>
       </c>
       <c r="N24" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="O24" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="P24" t="n">
-        <v>29.66</v>
+        <v>29.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.12</v>
+        <v>31.68</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.97</v>
+        <v>1.8</v>
       </c>
       <c r="G25" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>0.06</v>
       </c>
       <c r="J25" t="n">
-        <v>31.7</v>
+        <v>31.46</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06</v>
+        <v>-0.76</v>
       </c>
       <c r="M25" t="n">
-        <v>31.46</v>
+        <v>31.8</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.24</v>
+        <v>0.34</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.76</v>
+        <v>1.08</v>
       </c>
       <c r="P25" t="n">
-        <v>31.8</v>
+        <v>31.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="R25" t="n">
-        <v>1.08</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="E26" t="n">
-        <v>7.55</v>
+        <v>-1.9</v>
       </c>
       <c r="F26" t="n">
-        <v>14.8</v>
+        <v>-3.25</v>
       </c>
       <c r="G26" t="n">
-        <v>56.65</v>
+        <v>56.6</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.9</v>
+        <v>-0.05</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.25</v>
+        <v>-0.09</v>
       </c>
       <c r="J26" t="n">
-        <v>56.6</v>
+        <v>55.15</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.05</v>
+        <v>-1.45</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.09</v>
+        <v>-2.56</v>
       </c>
       <c r="M26" t="n">
-        <v>55.15</v>
+        <v>55.25</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.45</v>
+        <v>0.1</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.56</v>
+        <v>0.18</v>
       </c>
       <c r="P26" t="n">
-        <v>55.25</v>
+        <v>51.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1</v>
+        <v>-3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>0.18</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>477.4</v>
+        <v>471.4</v>
       </c>
       <c r="E27" t="n">
-        <v>14.4</v>
+        <v>-6</v>
       </c>
       <c r="F27" t="n">
-        <v>3.11</v>
+        <v>-1.26</v>
       </c>
       <c r="G27" t="n">
-        <v>471.4</v>
+        <v>464.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.26</v>
+        <v>-1.48</v>
       </c>
       <c r="J27" t="n">
-        <v>464.4</v>
+        <v>457.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.48</v>
+        <v>-1.55</v>
       </c>
       <c r="M27" t="n">
-        <v>457.2</v>
+        <v>462.6</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.2</v>
+        <v>5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.55</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>462.6</v>
+        <v>460.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.4</v>
+        <v>-2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>140.9</v>
+        <v>139</v>
       </c>
       <c r="E28" t="n">
-        <v>6.7</v>
+        <v>-1.9</v>
       </c>
       <c r="F28" t="n">
-        <v>4.99</v>
+        <v>-1.35</v>
       </c>
       <c r="G28" t="n">
-        <v>139</v>
+        <v>133.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.9</v>
+        <v>-5.1</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.35</v>
+        <v>-3.67</v>
       </c>
       <c r="J28" t="n">
-        <v>133.9</v>
+        <v>133.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="L28" t="n">
-        <v>-3.67</v>
+        <v>-0.45</v>
       </c>
       <c r="M28" t="n">
-        <v>133.3</v>
+        <v>132.8</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
       <c r="P28" t="n">
-        <v>132.8</v>
+        <v>137.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.5</v>
+        <v>5.1</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.38</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="E29" t="n">
-        <v>2.6</v>
+        <v>-0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.23</v>
+        <v>-0.42</v>
       </c>
       <c r="G29" t="n">
         <v>118.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>118.5</v>
+        <v>118.4</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="M29" t="n">
-        <v>118.4</v>
+        <v>128.2</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>128.2</v>
+        <v>130.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="R29" t="n">
-        <v>8.279999999999999</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>84.25</v>
+        <v>84.05</v>
       </c>
       <c r="E30" t="n">
-        <v>1.75</v>
+        <v>-0.2</v>
       </c>
       <c r="F30" t="n">
-        <v>2.12</v>
+        <v>-0.24</v>
       </c>
       <c r="G30" t="n">
-        <v>84.05</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="H30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="K30" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="L30" t="n">
         <v>-0.24</v>
       </c>
-      <c r="J30" t="n">
-        <v>84.34999999999999</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.36</v>
-      </c>
       <c r="M30" t="n">
-        <v>84.15000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.2</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.24</v>
+        <v>4.1</v>
       </c>
       <c r="P30" t="n">
-        <v>87.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>-1.9</v>
       </c>
       <c r="R30" t="n">
-        <v>4.1</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>137.3</v>
+        <v>145.2</v>
       </c>
       <c r="E31" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="F31" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="G31" t="n">
-        <v>145.2</v>
+        <v>140.9</v>
       </c>
       <c r="H31" t="n">
-        <v>7.9</v>
+        <v>-4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>5.75</v>
+        <v>-2.96</v>
       </c>
       <c r="J31" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="M31" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="P31" t="n">
         <v>140.9</v>
       </c>
-      <c r="K31" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="M31" t="n">
-        <v>139.7</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="P31" t="n">
-        <v>137.5</v>
-      </c>
       <c r="Q31" t="n">
-        <v>-2.2</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.57</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>76.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>1.9</v>
+        <v>-3.4</v>
       </c>
       <c r="F32" t="n">
-        <v>2.54</v>
+        <v>-4.43</v>
       </c>
       <c r="G32" t="n">
-        <v>73.34999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I32" t="n">
-        <v>-4.43</v>
+        <v>4.43</v>
       </c>
       <c r="J32" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>76.59999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="P32" t="n">
-        <v>74.15000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2.45</v>
+        <v>-2.65</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.2</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>100.7</v>
+        <v>99.75</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8</v>
+        <v>-0.95</v>
       </c>
       <c r="F33" t="n">
-        <v>1.82</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>99.75</v>
+        <v>101.7</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.95</v>
+        <v>1.95</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="J33" t="n">
-        <v>101.7</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>1.95</v>
+        <v>-1.85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>-1.82</v>
       </c>
       <c r="M33" t="n">
-        <v>99.84999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.85</v>
+        <v>-1.7</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.82</v>
+        <v>-1.7</v>
       </c>
       <c r="P33" t="n">
         <v>98.15000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>48.4</v>
+        <v>52.95</v>
       </c>
       <c r="E34" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="F34" t="n">
-        <v>7.56</v>
+        <v>9.4</v>
       </c>
       <c r="G34" t="n">
-        <v>52.95</v>
+        <v>51.6</v>
       </c>
       <c r="H34" t="n">
-        <v>4.55</v>
+        <v>-1.35</v>
       </c>
       <c r="I34" t="n">
-        <v>9.4</v>
+        <v>-2.55</v>
       </c>
       <c r="J34" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M34" t="n">
         <v>51.6</v>
       </c>
-      <c r="K34" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="M34" t="n">
-        <v>52.6</v>
-      </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.94</v>
+        <v>-1.9</v>
       </c>
       <c r="P34" t="n">
-        <v>51.6</v>
+        <v>50.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.9</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="F35" t="n">
-        <v>2.87</v>
+        <v>-0.2</v>
       </c>
       <c r="G35" t="n">
         <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="M35" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="N35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q35" t="n">
         <v>-0.03</v>
       </c>
-      <c r="O35" t="n">
+      <c r="R35" t="n">
         <v>-0.6</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.4</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.76</v>
+        <v>10.73</v>
       </c>
       <c r="E36" t="n">
-        <v>0.34</v>
+        <v>-0.03</v>
       </c>
       <c r="F36" t="n">
-        <v>3.26</v>
+        <v>-0.28</v>
       </c>
       <c r="G36" t="n">
         <v>10.73</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>10.73</v>
+        <v>10.66</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="M36" t="n">
-        <v>10.66</v>
+        <v>10.72</v>
       </c>
       <c r="N36" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="Q36" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="O36" t="n">
+      <c r="R36" t="n">
         <v>-0.65</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>427</v>
+        <v>424.2</v>
       </c>
       <c r="E37" t="n">
-        <v>5.8</v>
+        <v>-2.8</v>
       </c>
       <c r="F37" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G37" t="n">
-        <v>424.2</v>
+        <v>425.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.66</v>
+        <v>0.28</v>
       </c>
       <c r="J37" t="n">
-        <v>425.4</v>
+        <v>423.8</v>
       </c>
       <c r="K37" t="n">
-        <v>1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="L37" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="M37" t="n">
         <v>423.8</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>423.8</v>
+        <v>423.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.39</v>
+        <v>16.42</v>
       </c>
       <c r="E38" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="F38" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
       <c r="G38" t="n">
-        <v>16.42</v>
+        <v>16.08</v>
       </c>
       <c r="H38" t="n">
-        <v>0.03</v>
+        <v>-0.34</v>
       </c>
       <c r="I38" t="n">
-        <v>0.18</v>
+        <v>-2.07</v>
       </c>
       <c r="J38" t="n">
-        <v>16.08</v>
+        <v>16.14</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.34</v>
+        <v>0.06</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.07</v>
+        <v>0.37</v>
       </c>
       <c r="M38" t="n">
-        <v>16.14</v>
+        <v>16.03</v>
       </c>
       <c r="N38" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="O38" t="n">
-        <v>0.37</v>
+        <v>-0.68</v>
       </c>
       <c r="P38" t="n">
-        <v>16.03</v>
+        <v>16.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.11</v>
+        <v>0.02</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.68</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="E39" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6</v>
+        <v>-2.11</v>
       </c>
       <c r="G39" t="n">
-        <v>651</v>
+        <v>657.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-14</v>
+        <v>6.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.11</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>657.5</v>
+        <v>651.5</v>
       </c>
       <c r="K39" t="n">
-        <v>6.5</v>
+        <v>-6</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>-0.91</v>
       </c>
       <c r="M39" t="n">
-        <v>651.5</v>
+        <v>673</v>
       </c>
       <c r="N39" t="n">
-        <v>-6</v>
+        <v>21.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.91</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="Q39" t="n">
-        <v>21.5</v>
+        <v>13</v>
       </c>
       <c r="R39" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="G40" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J40" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M40" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="P40" t="n">
         <v>62.25</v>
       </c>
-      <c r="E40" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="G40" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="I40" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="J40" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="M40" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P40" t="n">
-        <v>62.4</v>
-      </c>
       <c r="Q40" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.88</v>
+        <v>21.92</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.55</v>
+        <v>0.18</v>
       </c>
       <c r="G41" t="n">
-        <v>21.92</v>
+        <v>22.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="I41" t="n">
-        <v>0.18</v>
+        <v>2.65</v>
       </c>
       <c r="J41" t="n">
-        <v>22.5</v>
+        <v>22.33</v>
       </c>
       <c r="K41" t="n">
-        <v>0.58</v>
+        <v>-0.17</v>
       </c>
       <c r="L41" t="n">
-        <v>2.65</v>
+        <v>-0.76</v>
       </c>
       <c r="M41" t="n">
-        <v>22.33</v>
+        <v>22.89</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.76</v>
+        <v>2.51</v>
       </c>
       <c r="P41" t="n">
-        <v>22.89</v>
+        <v>22.95</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="R41" t="n">
-        <v>2.51</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.86</v>
+        <v>58.68</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02</v>
+        <v>-0.31</v>
       </c>
       <c r="G42" t="n">
-        <v>58.68</v>
+        <v>58.77</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.18</v>
+        <v>0.09</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.31</v>
+        <v>0.15</v>
       </c>
       <c r="J42" t="n">
-        <v>58.77</v>
+        <v>59.1</v>
       </c>
       <c r="K42" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="L42" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>59.1</v>
+        <v>59.9</v>
       </c>
       <c r="N42" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="P42" t="n">
-        <v>59.9</v>
+        <v>60.13</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.8</v>
+        <v>0.23</v>
       </c>
       <c r="R42" t="n">
-        <v>1.35</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36.7</v>
+        <v>36.56</v>
       </c>
       <c r="E43" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="G43" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J43" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M43" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P43" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R43" t="n">
         <v>0.05</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G43" t="n">
-        <v>36.56</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="J43" t="n">
-        <v>36.99</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M43" t="n">
-        <v>37.11</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="P43" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.65</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.41</v>
+        <v>6.35</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="H44" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P44" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="Q44" t="n">
         <v>-0.06</v>
       </c>
-      <c r="I44" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="P44" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R44" t="n">
-        <v>0.48</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="J45" t="n">
         <v>2.35</v>
       </c>
-      <c r="E45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.23</v>
-      </c>
       <c r="K45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="L45" t="n">
-        <v>-3.04</v>
+        <v>5.38</v>
       </c>
       <c r="M45" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="N45" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="O45" t="n">
-        <v>5.38</v>
+        <v>-1.28</v>
       </c>
       <c r="P45" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="Q45" t="n">
         <v>-0.03</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="E46" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F46" t="n">
-        <v>1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G46" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6</v>
+        <v>-2.69</v>
       </c>
       <c r="J46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="L46" t="n">
-        <v>-2.69</v>
+        <v>0.92</v>
       </c>
       <c r="M46" t="n">
         <v>3.28</v>
       </c>
       <c r="N46" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.74</v>
+        <v>10.66</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.65</v>
+        <v>-0.74</v>
       </c>
       <c r="G47" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.74</v>
+        <v>-0.28</v>
       </c>
       <c r="J47" t="n">
-        <v>10.63</v>
+        <v>10.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.28</v>
+        <v>0.09</v>
       </c>
       <c r="M47" t="n">
-        <v>10.64</v>
+        <v>10.78</v>
       </c>
       <c r="N47" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="O47" t="n">
-        <v>0.09</v>
+        <v>1.32</v>
       </c>
       <c r="P47" t="n">
-        <v>10.78</v>
+        <v>10.52</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.14</v>
+        <v>-0.26</v>
       </c>
       <c r="R47" t="n">
-        <v>1.32</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.375</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="G48" t="n">
+      <c r="J48" t="n">
         <v>0.38</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
         <v>1.33</v>
       </c>
-      <c r="J48" t="n">
+      <c r="M48" t="n">
         <v>0.375</v>
       </c>
-      <c r="K48" t="n">
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="M48" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1.33</v>
-      </c>
       <c r="P48" t="n">
-        <v>0.375</v>
+        <v>0.355</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.32</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="E49" t="n">
         <v>0.05</v>
       </c>
       <c r="F49" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G49" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="H49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P49" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="Q49" t="n">
         <v>0.05</v>
       </c>
-      <c r="I49" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O49" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="P49" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0.1</v>
-      </c>
       <c r="R49" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="50">
@@ -3509,31 +3509,31 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="P50" t="n">
         <v>1.01</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N50" t="n">
+      <c r="Q50" t="n">
         <v>0.01</v>
       </c>
-      <c r="O50" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="R50" t="n">
-        <v>-1.96</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Q51" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P51" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="R51" t="n">
-        <v>1.77</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
       <c r="E52" t="n">
-        <v>0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="F52" t="n">
-        <v>1.64</v>
+        <v>-1.8</v>
       </c>
       <c r="G52" t="n">
-        <v>10.94</v>
+        <v>10.91</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.8</v>
+        <v>-0.27</v>
       </c>
       <c r="J52" t="n">
-        <v>10.91</v>
+        <v>10.78</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.27</v>
+        <v>-1.19</v>
       </c>
       <c r="M52" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.13</v>
+        <v>0.11</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.19</v>
+        <v>1.02</v>
       </c>
       <c r="P52" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="R52" t="n">
-        <v>1.02</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.33</v>
+        <v>8.26</v>
       </c>
       <c r="E53" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>0.97</v>
+        <v>-0.84</v>
       </c>
       <c r="G53" t="n">
-        <v>8.26</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.84</v>
+        <v>-1.82</v>
       </c>
       <c r="J53" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M53" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="K53" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="M53" t="n">
-        <v>8.130000000000001</v>
-      </c>
       <c r="N53" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="O53" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="P53" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.25</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="54">
@@ -3739,40 +3739,40 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.42</v>
+        <v>0.425</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G54" t="n">
         <v>0.425</v>
       </c>
       <c r="H54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="M54" t="n">
         <v>0.42</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0.42</v>
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H55" t="n">
         <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="J55" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.73</v>
+        <v>1.47</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="N55" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>1.47</v>
+        <v>-10.14</v>
       </c>
       <c r="P55" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="R55" t="n">
-        <v>-10.14</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.505</v>
+        <v>0.49</v>
       </c>
       <c r="E56" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="F56" t="n">
-        <v>3.06</v>
+        <v>-2.97</v>
       </c>
       <c r="G56" t="n">
         <v>0.49</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.97</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="M56" t="n">
         <v>0.48</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.48</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3928,46 +3928,46 @@
         <v>3.72</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="J57" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.61</v>
+        <v>0.27</v>
       </c>
       <c r="M57" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="N57" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="O57" t="n">
-        <v>0.27</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="R57" t="n">
-        <v>3</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="58">
@@ -3987,31 +3987,31 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.079</v>
+        <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="H58" t="n">
         <v>0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="J58" t="n">
         <v>0.081</v>
       </c>
       <c r="K58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0.081</v>
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.95</v>
+        <v>20.91</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.44</v>
+        <v>-0.04</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.06</v>
+        <v>-0.19</v>
       </c>
       <c r="G59" t="n">
-        <v>20.91</v>
+        <v>20.96</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
       <c r="J59" t="n">
-        <v>20.96</v>
+        <v>21.1</v>
       </c>
       <c r="K59" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="L59" t="n">
-        <v>0.24</v>
+        <v>0.67</v>
       </c>
       <c r="M59" t="n">
-        <v>21.1</v>
+        <v>21.58</v>
       </c>
       <c r="N59" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="O59" t="n">
-        <v>0.67</v>
+        <v>2.27</v>
       </c>
       <c r="P59" t="n">
-        <v>21.58</v>
+        <v>21.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="R59" t="n">
-        <v>2.27</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="E60" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>1.24</v>
+        <v>-0.31</v>
       </c>
       <c r="G60" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.31</v>
+        <v>-2.45</v>
       </c>
       <c r="J60" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="K60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Q60" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L60" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="R60" t="n">
-        <v>-1.22</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="E61" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H61" t="n">
         <v>0.04</v>
       </c>
-      <c r="F61" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="I61" t="n">
-        <v>-3.21</v>
+        <v>2.65</v>
       </c>
       <c r="J61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="P61" t="n">
         <v>1.55</v>
       </c>
-      <c r="K61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L61" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.64</v>
-      </c>
       <c r="Q61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="R61" t="n">
-        <v>4.46</v>
+        <v>-5.49</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-08 Close</t>
+          <t>2026-05-11 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change</t>
+          <t>2026-05-11 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-08 Change %</t>
+          <t>2026-05-11 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-11 Close</t>
+          <t>2026-05-12 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change</t>
+          <t>2026-05-12 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change %</t>
+          <t>2026-05-12 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-12 Close</t>
+          <t>2026-05-13 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change</t>
+          <t>2026-05-13 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change %</t>
+          <t>2026-05-13 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-13 Close</t>
+          <t>2026-05-14 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change</t>
+          <t>2026-05-14 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change %</t>
+          <t>2026-05-14 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-14 Close</t>
+          <t>2026-05-15 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change</t>
+          <t>2026-05-15 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change %</t>
+          <t>2026-05-15 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>138.7</v>
+        <v>141.2</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.4</v>
+        <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.07</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>141.2</v>
+        <v>138.6</v>
       </c>
       <c r="H3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="J3" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="K3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>1.8</v>
       </c>
-      <c r="J3" t="n">
-        <v>138.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-1.84</v>
-      </c>
       <c r="M3" t="n">
-        <v>141.1</v>
+        <v>140.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>-0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8</v>
+        <v>-0.43</v>
       </c>
       <c r="P3" t="n">
-        <v>140.5</v>
+        <v>139.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.43</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.26</v>
+        <v>2.01</v>
       </c>
       <c r="G4" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="I4" t="n">
-        <v>2.01</v>
+        <v>-4.43</v>
       </c>
       <c r="J4" t="n">
-        <v>194</v>
+        <v>198.1</v>
       </c>
       <c r="K4" t="n">
-        <v>-9</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.43</v>
+        <v>2.11</v>
       </c>
       <c r="M4" t="n">
-        <v>198.1</v>
+        <v>199.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.11</v>
+        <v>0.66</v>
       </c>
       <c r="P4" t="n">
-        <v>199.4</v>
+        <v>198</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.66</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.34</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="H5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.06</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>6.09</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.92</v>
+        <v>6.98</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>-1</v>
+        <v>0.87</v>
       </c>
       <c r="G6" t="n">
-        <v>6.98</v>
+        <v>7.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>-0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>7.04</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.71</v>
+        <v>0.57</v>
       </c>
       <c r="P6" t="n">
-        <v>7.04</v>
+        <v>6.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0.57</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="J7" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="K7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P7" t="n">
         <v>5.22</v>
       </c>
-      <c r="N7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.29</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.76</v>
+        <v>8.84</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.35</v>
+        <v>0.91</v>
       </c>
       <c r="G8" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="J8" t="n">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="L8" t="n">
-        <v>0.68</v>
+        <v>-0.34</v>
       </c>
       <c r="M8" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="9">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.23</v>
+        <v>7.27</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.55</v>
+        <v>0.55</v>
       </c>
       <c r="G9" t="n">
-        <v>7.27</v>
+        <v>7.31</v>
       </c>
       <c r="H9" t="n">
         <v>0.04</v>
@@ -967,31 +967,31 @@
         <v>0.55</v>
       </c>
       <c r="J9" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>0.55</v>
+        <v>-0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.14</v>
+        <v>0.82</v>
       </c>
       <c r="P9" t="n">
-        <v>7.36</v>
+        <v>7.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0.82</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.24</v>
+        <v>47.46</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.21</v>
+        <v>0.47</v>
       </c>
       <c r="G10" t="n">
-        <v>47.46</v>
+        <v>47.52</v>
       </c>
       <c r="H10" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="J10" t="n">
-        <v>47.52</v>
+        <v>47.22</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="M10" t="n">
-        <v>47.22</v>
+        <v>47.48</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3</v>
+        <v>0.26</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.63</v>
+        <v>0.55</v>
       </c>
       <c r="P10" t="n">
-        <v>47.48</v>
+        <v>46.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.26</v>
+        <v>-0.54</v>
       </c>
       <c r="R10" t="n">
-        <v>0.55</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.86</v>
+        <v>-0.22</v>
       </c>
       <c r="G11" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.22</v>
+        <v>0.43</v>
       </c>
       <c r="J11" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L11" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="M11" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="O11" t="n">
-        <v>0.65</v>
+        <v>-1.72</v>
       </c>
       <c r="P11" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.08</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.59</v>
+        <v>10.64</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="G12" t="n">
-        <v>10.64</v>
+        <v>11.06</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="I12" t="n">
-        <v>0.47</v>
+        <v>3.95</v>
       </c>
       <c r="J12" t="n">
         <v>11.06</v>
       </c>
       <c r="K12" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>11.06</v>
+        <v>10.92</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.27</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.44</v>
+        <v>26.6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
       <c r="G13" t="n">
-        <v>26.6</v>
+        <v>26.92</v>
       </c>
       <c r="H13" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>26.92</v>
+        <v>26.62</v>
       </c>
       <c r="K13" t="n">
-        <v>0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>-1.11</v>
       </c>
       <c r="M13" t="n">
-        <v>26.62</v>
+        <v>26.36</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.11</v>
+        <v>-0.98</v>
       </c>
       <c r="P13" t="n">
-        <v>26.36</v>
+        <v>26.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.26</v>
+        <v>0.06</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.98</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="14">
@@ -1262,46 +1262,46 @@
         <v>2.68</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.11</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="J14" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.75</v>
+        <v>1.13</v>
       </c>
       <c r="M14" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="O14" t="n">
-        <v>1.13</v>
+        <v>-2.97</v>
       </c>
       <c r="P14" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.97</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="E15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="N15" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F15" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="O15" t="n">
-        <v>-0.37</v>
+        <v>-1.1</v>
       </c>
       <c r="P15" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.1</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.57</v>
+        <v>-0.76</v>
       </c>
       <c r="G16" t="n">
         <v>5.2</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I16" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="R16" t="n">
-        <v>-0.58</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="E17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H17" t="n">
         <v>0.01</v>
       </c>
-      <c r="F17" t="n">
+      <c r="I17" t="n">
         <v>0.26</v>
       </c>
-      <c r="G17" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-1.03</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L17" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="M17" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="O17" t="n">
-        <v>0.52</v>
+        <v>-1.55</v>
       </c>
       <c r="P17" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.55</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F18" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="J18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.59</v>
       </c>
-      <c r="K18" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.56</v>
-      </c>
       <c r="N18" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.84</v>
+        <v>0.84</v>
       </c>
       <c r="P18" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="R18" t="n">
-        <v>0.84</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65.59999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.61</v>
+        <v>-0.84</v>
       </c>
       <c r="G19" t="n">
-        <v>65.05</v>
+        <v>65</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.84</v>
+        <v>-0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.08</v>
+        <v>-1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.38</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>63.5</v>
+        <v>62.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.6</v>
+        <v>-1.05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.26</v>
+        <v>31.38</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="F20" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="G20" t="n">
-        <v>31.38</v>
+        <v>30.58</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12</v>
+        <v>-0.8</v>
       </c>
       <c r="I20" t="n">
-        <v>0.38</v>
+        <v>-2.55</v>
       </c>
       <c r="J20" t="n">
-        <v>30.58</v>
+        <v>29.96</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8</v>
+        <v>-0.62</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.55</v>
+        <v>-2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>29.96</v>
+        <v>29.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.03</v>
+        <v>-0.27</v>
       </c>
       <c r="P20" t="n">
         <v>29.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.42</v>
+        <v>5.49</v>
       </c>
       <c r="E21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="G21" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="I21" t="n">
-        <v>1.29</v>
+        <v>-0.55</v>
       </c>
       <c r="J21" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.55</v>
+        <v>-0.18</v>
       </c>
       <c r="M21" t="n">
-        <v>5.45</v>
+        <v>5.51</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.18</v>
+        <v>1.1</v>
       </c>
       <c r="P21" t="n">
-        <v>5.51</v>
+        <v>5.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.45</v>
+        <v>86.2</v>
       </c>
       <c r="E22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G22" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J22" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M22" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.15</v>
       </c>
-      <c r="F22" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="O22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P22" t="n">
         <v>86.2</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M22" t="n">
-        <v>86.55</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="P22" t="n">
-        <v>86.7</v>
-      </c>
       <c r="Q22" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0.17</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>27.38</v>
+        <v>26.38</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>-1</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.65</v>
       </c>
       <c r="J23" t="n">
-        <v>26.38</v>
+        <v>26.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.65</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>26.88</v>
+        <v>26.14</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>-2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>26.14</v>
+        <v>25.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="R23" t="n">
-        <v>-2.75</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.24</v>
+        <v>28.86</v>
       </c>
       <c r="E24" t="n">
-        <v>1.78</v>
+        <v>0.62</v>
       </c>
       <c r="F24" t="n">
-        <v>6.73</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>28.86</v>
+        <v>29.2</v>
       </c>
       <c r="H24" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="J24" t="n">
-        <v>29.2</v>
+        <v>29.66</v>
       </c>
       <c r="K24" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="L24" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>29.66</v>
+        <v>29.88</v>
       </c>
       <c r="N24" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="O24" t="n">
-        <v>1.58</v>
+        <v>0.74</v>
       </c>
       <c r="P24" t="n">
-        <v>29.88</v>
+        <v>29.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="R24" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.68</v>
+        <v>31.7</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8</v>
+        <v>0.06</v>
       </c>
       <c r="G25" t="n">
-        <v>31.7</v>
+        <v>31.46</v>
       </c>
       <c r="H25" t="n">
-        <v>0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="I25" t="n">
-        <v>0.06</v>
+        <v>-0.76</v>
       </c>
       <c r="J25" t="n">
-        <v>31.46</v>
+        <v>31.8</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.24</v>
+        <v>0.34</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.76</v>
+        <v>1.08</v>
       </c>
       <c r="M25" t="n">
-        <v>31.8</v>
+        <v>31.72</v>
       </c>
       <c r="N25" t="n">
-        <v>0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="O25" t="n">
-        <v>1.08</v>
+        <v>-0.25</v>
       </c>
       <c r="P25" t="n">
-        <v>31.72</v>
+        <v>30.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.25</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>56.65</v>
+        <v>56.6</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9</v>
+        <v>-0.05</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.25</v>
+        <v>-0.09</v>
       </c>
       <c r="G26" t="n">
-        <v>56.6</v>
+        <v>55.15</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.05</v>
+        <v>-1.45</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.09</v>
+        <v>-2.56</v>
       </c>
       <c r="J26" t="n">
-        <v>55.15</v>
+        <v>55.25</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.45</v>
+        <v>0.1</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.56</v>
+        <v>0.18</v>
       </c>
       <c r="M26" t="n">
-        <v>55.25</v>
+        <v>51.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1</v>
+        <v>-3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>0.18</v>
+        <v>-6.24</v>
       </c>
       <c r="P26" t="n">
-        <v>51.8</v>
+        <v>47.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.45</v>
+        <v>-3.96</v>
       </c>
       <c r="R26" t="n">
-        <v>-6.24</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>471.4</v>
+        <v>464.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.26</v>
+        <v>-1.48</v>
       </c>
       <c r="G27" t="n">
-        <v>464.4</v>
+        <v>457.2</v>
       </c>
       <c r="H27" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.48</v>
+        <v>-1.55</v>
       </c>
       <c r="J27" t="n">
-        <v>457.2</v>
+        <v>462.6</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.2</v>
+        <v>5.4</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.55</v>
+        <v>1.18</v>
       </c>
       <c r="M27" t="n">
-        <v>462.6</v>
+        <v>460.2</v>
       </c>
       <c r="N27" t="n">
-        <v>5.4</v>
+        <v>-2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>-0.52</v>
       </c>
       <c r="P27" t="n">
-        <v>460.2</v>
+        <v>456.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.4</v>
+        <v>-3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.52</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>139</v>
+        <v>133.9</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.9</v>
+        <v>-5.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.35</v>
+        <v>-3.67</v>
       </c>
       <c r="G28" t="n">
-        <v>133.9</v>
+        <v>133.3</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.67</v>
+        <v>-0.45</v>
       </c>
       <c r="J28" t="n">
-        <v>133.3</v>
+        <v>132.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
       <c r="M28" t="n">
-        <v>132.8</v>
+        <v>137.9</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.5</v>
+        <v>5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.38</v>
+        <v>3.84</v>
       </c>
       <c r="P28" t="n">
-        <v>137.9</v>
+        <v>132.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="R28" t="n">
-        <v>3.84</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="29">
@@ -2192,46 +2192,46 @@
         <v>118.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>118.5</v>
+        <v>118.4</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="J29" t="n">
-        <v>118.4</v>
+        <v>128.2</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>128.2</v>
+        <v>130.1</v>
       </c>
       <c r="N29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
-        <v>8.279999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="P29" t="n">
-        <v>130.1</v>
+        <v>127.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>84.05</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G30" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="H30" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F30" t="n">
+      <c r="I30" t="n">
         <v>-0.24</v>
       </c>
-      <c r="G30" t="n">
-        <v>84.34999999999999</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.36</v>
-      </c>
       <c r="J30" t="n">
-        <v>84.15000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.2</v>
+        <v>3.45</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.24</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>87.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>-1.9</v>
       </c>
       <c r="O30" t="n">
-        <v>4.1</v>
+        <v>-2.17</v>
       </c>
       <c r="P30" t="n">
-        <v>85.7</v>
+        <v>82.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.9</v>
+        <v>-3</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.17</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>145.2</v>
+        <v>140.9</v>
       </c>
       <c r="E31" t="n">
-        <v>7.9</v>
+        <v>-4.3</v>
       </c>
       <c r="F31" t="n">
-        <v>5.75</v>
+        <v>-2.96</v>
       </c>
       <c r="G31" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="J31" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="M31" t="n">
         <v>140.9</v>
       </c>
-      <c r="H31" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="J31" t="n">
-        <v>139.7</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="M31" t="n">
-        <v>137.5</v>
-      </c>
       <c r="N31" t="n">
-        <v>-2.2</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.57</v>
+        <v>2.47</v>
       </c>
       <c r="P31" t="n">
-        <v>140.9</v>
+        <v>135.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="R31" t="n">
-        <v>2.47</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>73.34999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.4</v>
+        <v>3.25</v>
       </c>
       <c r="F32" t="n">
-        <v>-4.43</v>
+        <v>4.43</v>
       </c>
       <c r="G32" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>76.59999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>74.15000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.45</v>
+        <v>-2.65</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.2</v>
+        <v>-3.57</v>
       </c>
       <c r="P32" t="n">
-        <v>71.5</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2.65</v>
+        <v>-0.35</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.57</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>99.75</v>
+        <v>101.7</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.95</v>
+        <v>1.95</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="G33" t="n">
-        <v>101.7</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>1.95</v>
+        <v>-1.85</v>
       </c>
       <c r="I33" t="n">
-        <v>1.95</v>
+        <v>-1.82</v>
       </c>
       <c r="J33" t="n">
-        <v>99.84999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.85</v>
+        <v>-1.7</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.82</v>
+        <v>-1.7</v>
       </c>
       <c r="M33" t="n">
         <v>98.15000000000001</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="Q33" t="n">
         <v>-1.7</v>
       </c>
-      <c r="O33" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="P33" t="n">
-        <v>98.15000000000001</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>52.95</v>
+        <v>51.6</v>
       </c>
       <c r="E34" t="n">
-        <v>4.55</v>
+        <v>-1.35</v>
       </c>
       <c r="F34" t="n">
-        <v>9.4</v>
+        <v>-2.55</v>
       </c>
       <c r="G34" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J34" t="n">
         <v>51.6</v>
       </c>
-      <c r="H34" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="J34" t="n">
-        <v>52.6</v>
-      </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.94</v>
+        <v>-1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>51.6</v>
+        <v>50.85</v>
       </c>
       <c r="N34" t="n">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.9</v>
+        <v>-1.45</v>
       </c>
       <c r="P34" t="n">
-        <v>50.85</v>
+        <v>49.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.75</v>
+        <v>-1.51</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.45</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="35">
@@ -2564,46 +2564,46 @@
         <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="K35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="N35" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L35" t="n">
+      <c r="O35" t="n">
         <v>-0.6</v>
       </c>
-      <c r="M35" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.4</v>
-      </c>
       <c r="P35" t="n">
-        <v>4.96</v>
+        <v>4.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.6</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="36">
@@ -2626,46 +2626,46 @@
         <v>10.73</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="Q36" t="n">
         <v>-0.28</v>
       </c>
-      <c r="G36" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="M36" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
       <c r="R36" t="n">
-        <v>-0.65</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>424.2</v>
+        <v>425.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.66</v>
+        <v>0.28</v>
       </c>
       <c r="G37" t="n">
-        <v>425.4</v>
+        <v>423.8</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="I37" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="J37" t="n">
         <v>423.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>423.8</v>
+        <v>423.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="P37" t="n">
-        <v>423.6</v>
+        <v>416.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.2</v>
+        <v>-7.2</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.05</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.42</v>
+        <v>16.08</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03</v>
+        <v>-0.34</v>
       </c>
       <c r="F38" t="n">
-        <v>0.18</v>
+        <v>-2.07</v>
       </c>
       <c r="G38" t="n">
-        <v>16.08</v>
+        <v>16.14</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.34</v>
+        <v>0.06</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.07</v>
+        <v>0.37</v>
       </c>
       <c r="J38" t="n">
-        <v>16.14</v>
+        <v>16.03</v>
       </c>
       <c r="K38" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="L38" t="n">
-        <v>0.37</v>
+        <v>-0.68</v>
       </c>
       <c r="M38" t="n">
-        <v>16.03</v>
+        <v>16.05</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.11</v>
+        <v>0.02</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.68</v>
+        <v>0.12</v>
       </c>
       <c r="P38" t="n">
-        <v>16.05</v>
+        <v>15.96</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="R38" t="n">
-        <v>0.12</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>651</v>
+        <v>657.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-14</v>
+        <v>6.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.11</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>657.5</v>
+        <v>651.5</v>
       </c>
       <c r="H39" t="n">
-        <v>6.5</v>
+        <v>-6</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>-0.91</v>
       </c>
       <c r="J39" t="n">
-        <v>651.5</v>
+        <v>673</v>
       </c>
       <c r="K39" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M39" t="n">
+        <v>686</v>
+      </c>
+      <c r="N39" t="n">
+        <v>13</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P39" t="n">
+        <v>680</v>
+      </c>
+      <c r="Q39" t="n">
         <v>-6</v>
       </c>
-      <c r="L39" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="M39" t="n">
-        <v>673</v>
-      </c>
-      <c r="N39" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P39" t="n">
-        <v>686</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>13</v>
-      </c>
       <c r="R39" t="n">
-        <v>1.93</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G40" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J40" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M40" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="P40" t="n">
         <v>61.3</v>
       </c>
-      <c r="E40" t="n">
+      <c r="Q40" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F40" t="n">
+      <c r="R40" t="n">
         <v>-1.53</v>
-      </c>
-      <c r="G40" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="J40" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="M40" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="P40" t="n">
-        <v>62.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="R40" t="n">
-        <v>-0.24</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.92</v>
+        <v>22.5</v>
       </c>
       <c r="E41" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="F41" t="n">
-        <v>0.18</v>
+        <v>2.65</v>
       </c>
       <c r="G41" t="n">
-        <v>22.5</v>
+        <v>22.33</v>
       </c>
       <c r="H41" t="n">
-        <v>0.58</v>
+        <v>-0.17</v>
       </c>
       <c r="I41" t="n">
-        <v>2.65</v>
+        <v>-0.76</v>
       </c>
       <c r="J41" t="n">
-        <v>22.33</v>
+        <v>22.89</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.76</v>
+        <v>2.51</v>
       </c>
       <c r="M41" t="n">
-        <v>22.89</v>
+        <v>22.95</v>
       </c>
       <c r="N41" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="O41" t="n">
-        <v>2.51</v>
+        <v>0.26</v>
       </c>
       <c r="P41" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R41" t="n">
-        <v>0.26</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.68</v>
+        <v>58.77</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.18</v>
+        <v>0.09</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.31</v>
+        <v>0.15</v>
       </c>
       <c r="G42" t="n">
-        <v>58.77</v>
+        <v>59.1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>59.1</v>
+        <v>59.9</v>
       </c>
       <c r="K42" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>59.9</v>
+        <v>60.13</v>
       </c>
       <c r="N42" t="n">
-        <v>0.8</v>
+        <v>0.23</v>
       </c>
       <c r="O42" t="n">
-        <v>1.35</v>
+        <v>0.38</v>
       </c>
       <c r="P42" t="n">
-        <v>60.13</v>
+        <v>60.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R42" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36.56</v>
+        <v>36.99</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.38</v>
+        <v>1.18</v>
       </c>
       <c r="G43" t="n">
-        <v>36.99</v>
+        <v>37.11</v>
       </c>
       <c r="H43" t="n">
-        <v>0.43</v>
+        <v>0.12</v>
       </c>
       <c r="I43" t="n">
-        <v>1.18</v>
+        <v>0.32</v>
       </c>
       <c r="J43" t="n">
-        <v>37.11</v>
+        <v>37.35</v>
       </c>
       <c r="K43" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="L43" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="M43" t="n">
-        <v>37.35</v>
+        <v>37.37</v>
       </c>
       <c r="N43" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="O43" t="n">
-        <v>0.65</v>
+        <v>0.05</v>
       </c>
       <c r="P43" t="n">
-        <v>37.37</v>
+        <v>37.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R43" t="n">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="E44" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N44" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F44" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="G44" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="I44" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.03</v>
-      </c>
       <c r="O44" t="n">
-        <v>0.48</v>
+        <v>-0.96</v>
       </c>
       <c r="P44" t="n">
-        <v>6.19</v>
+        <v>6.13</v>
       </c>
       <c r="Q44" t="n">
         <v>-0.06</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.13</v>
+        <v>-3.04</v>
       </c>
       <c r="G45" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="I45" t="n">
-        <v>-3.04</v>
+        <v>5.38</v>
       </c>
       <c r="J45" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="K45" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="L45" t="n">
-        <v>5.38</v>
+        <v>-1.28</v>
       </c>
       <c r="M45" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="N45" t="n">
         <v>-0.03</v>
       </c>
       <c r="O45" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="P45" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.29</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6</v>
+        <v>-2.69</v>
       </c>
       <c r="G46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.69</v>
+        <v>0.92</v>
       </c>
       <c r="J46" t="n">
         <v>3.28</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>-1.52</v>
       </c>
       <c r="P46" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.52</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.74</v>
+        <v>-0.28</v>
       </c>
       <c r="G47" t="n">
-        <v>10.63</v>
+        <v>10.64</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.28</v>
+        <v>0.09</v>
       </c>
       <c r="J47" t="n">
-        <v>10.64</v>
+        <v>10.78</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="L47" t="n">
-        <v>0.09</v>
+        <v>1.32</v>
       </c>
       <c r="M47" t="n">
-        <v>10.78</v>
+        <v>10.52</v>
       </c>
       <c r="N47" t="n">
-        <v>0.14</v>
+        <v>-0.26</v>
       </c>
       <c r="O47" t="n">
-        <v>1.32</v>
+        <v>-2.41</v>
       </c>
       <c r="P47" t="n">
-        <v>10.52</v>
+        <v>10.37</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.41</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.38</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>1.33</v>
       </c>
-      <c r="G48" t="n">
+      <c r="J48" t="n">
         <v>0.375</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1.33</v>
-      </c>
       <c r="M48" t="n">
-        <v>0.375</v>
+        <v>0.355</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.32</v>
+        <v>-5.33</v>
       </c>
       <c r="P48" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
       <c r="Q48" t="n">
         <v>-0.02</v>
       </c>
       <c r="R48" t="n">
-        <v>-5.33</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="E49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="N49" t="n">
         <v>0.05</v>
       </c>
-      <c r="F49" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="K49" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P49" t="n">
         <v>4.82</v>
       </c>
-      <c r="N49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P49" t="n">
-        <v>4.87</v>
-      </c>
       <c r="Q49" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="R49" t="n">
-        <v>1.04</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="50">
@@ -3500,40 +3500,40 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="M50" t="n">
         <v>1.01</v>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K50" t="n">
+      <c r="N50" t="n">
         <v>0.01</v>
       </c>
-      <c r="L50" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="N50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O50" t="n">
-        <v>-1.96</v>
-      </c>
       <c r="P50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.44</v>
+        <v>-2.25</v>
       </c>
       <c r="G51" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="I51" t="n">
-        <v>-2.25</v>
+        <v>1.02</v>
       </c>
       <c r="J51" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="K51" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="M51" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="N51" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="O51" t="n">
-        <v>1.77</v>
+        <v>-1</v>
       </c>
       <c r="P51" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R51" t="n">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.94</v>
+        <v>10.91</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.8</v>
+        <v>-0.27</v>
       </c>
       <c r="G52" t="n">
-        <v>10.91</v>
+        <v>10.78</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.27</v>
+        <v>-1.19</v>
       </c>
       <c r="J52" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.13</v>
+        <v>0.11</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.19</v>
+        <v>1.02</v>
       </c>
       <c r="M52" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="N52" t="n">
-        <v>0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="O52" t="n">
-        <v>1.02</v>
+        <v>-1.74</v>
       </c>
       <c r="P52" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.74</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.26</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.84</v>
+        <v>-1.82</v>
       </c>
       <c r="G53" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J53" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="H53" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="J53" t="n">
-        <v>8.130000000000001</v>
-      </c>
       <c r="K53" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="L53" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="M53" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.25</v>
+        <v>-3.08</v>
       </c>
       <c r="P53" t="n">
         <v>7.86</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>-3.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3742,28 +3742,28 @@
         <v>0.425</v>
       </c>
       <c r="E54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="J54" t="n">
         <v>0.42</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0.42</v>
@@ -3775,13 +3775,13 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="E55" t="n">
         <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="G55" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-10.14</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="Q55" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I55" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="O55" t="n">
-        <v>-10.14</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="R55" t="n">
-        <v>-3.23</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="56">
@@ -3866,28 +3866,28 @@
         <v>0.49</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.97</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="J56" t="n">
         <v>0.48</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0.48</v>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="G57" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.61</v>
+        <v>0.27</v>
       </c>
       <c r="J57" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="K57" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="L57" t="n">
-        <v>0.27</v>
+        <v>3</v>
       </c>
       <c r="M57" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>0.53</v>
       </c>
       <c r="P57" t="n">
         <v>3.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3987,22 +3987,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="E58" t="n">
         <v>0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G58" t="n">
         <v>0.081</v>
       </c>
       <c r="H58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0.081</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.91</v>
+        <v>20.96</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
       <c r="G59" t="n">
-        <v>20.96</v>
+        <v>21.1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I59" t="n">
-        <v>0.24</v>
+        <v>0.67</v>
       </c>
       <c r="J59" t="n">
-        <v>21.1</v>
+        <v>21.58</v>
       </c>
       <c r="K59" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="L59" t="n">
-        <v>0.67</v>
+        <v>2.27</v>
       </c>
       <c r="M59" t="n">
-        <v>21.58</v>
+        <v>21.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="O59" t="n">
-        <v>2.27</v>
+        <v>-1.3</v>
       </c>
       <c r="P59" t="n">
-        <v>21.3</v>
+        <v>21.13</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="R59" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="E60" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F60" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O60" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="R60" t="n">
-        <v>-2.47</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.21</v>
+        <v>2.65</v>
       </c>
       <c r="G61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M61" t="n">
         <v>1.55</v>
       </c>
-      <c r="H61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.64</v>
-      </c>
       <c r="N61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="O61" t="n">
-        <v>4.46</v>
+        <v>-5.49</v>
       </c>
       <c r="P61" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="R61" t="n">
-        <v>-5.49</v>
+        <v>-10.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-11 Close</t>
+          <t>2026-05-12 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change</t>
+          <t>2026-05-12 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-11 Change %</t>
+          <t>2026-05-12 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-12 Close</t>
+          <t>2026-05-13 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change</t>
+          <t>2026-05-13 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change %</t>
+          <t>2026-05-13 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-13 Close</t>
+          <t>2026-05-14 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change</t>
+          <t>2026-05-14 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change %</t>
+          <t>2026-05-14 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-14 Close</t>
+          <t>2026-05-15 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change</t>
+          <t>2026-05-15 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change %</t>
+          <t>2026-05-15 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-15 Close</t>
+          <t>2026-05-18 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change</t>
+          <t>2026-05-18 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change %</t>
+          <t>2026-05-18 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141.2</v>
+        <v>138.6</v>
       </c>
       <c r="E3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="G3" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="H3" t="n">
         <v>2.5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>1.8</v>
       </c>
-      <c r="G3" t="n">
-        <v>138.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-1.84</v>
-      </c>
       <c r="J3" t="n">
-        <v>141.1</v>
+        <v>140.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>-0.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>-0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>140.5</v>
+        <v>139.4</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.43</v>
+        <v>-0.78</v>
       </c>
       <c r="P3" t="n">
-        <v>139.4</v>
+        <v>138.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="F4" t="n">
-        <v>2.01</v>
+        <v>-4.43</v>
       </c>
       <c r="G4" t="n">
-        <v>194</v>
+        <v>198.1</v>
       </c>
       <c r="H4" t="n">
-        <v>-9</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.43</v>
+        <v>2.11</v>
       </c>
       <c r="J4" t="n">
-        <v>198.1</v>
+        <v>199.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="L4" t="n">
-        <v>2.11</v>
+        <v>0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>199.4</v>
+        <v>198</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0.66</v>
+        <v>-0.7</v>
       </c>
       <c r="P4" t="n">
-        <v>198</v>
+        <v>196.6</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="E5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.06</v>
       </c>
-      <c r="F5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>6.09</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="P5" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R5" t="n">
-        <v>0.16</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.98</v>
+        <v>7.05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>-0.71</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>7.04</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.71</v>
+        <v>0.57</v>
       </c>
       <c r="M6" t="n">
-        <v>7.04</v>
+        <v>6.89</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="O6" t="n">
-        <v>0.57</v>
+        <v>-2.13</v>
       </c>
       <c r="P6" t="n">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.13</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="H7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M7" t="n">
         <v>5.22</v>
       </c>
-      <c r="K7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5.29</v>
-      </c>
       <c r="N7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>-1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.32</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="G8" t="n">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.68</v>
+        <v>-0.34</v>
       </c>
       <c r="J8" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.01</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.27</v>
+        <v>7.31</v>
       </c>
       <c r="E9" t="n">
         <v>0.04</v>
@@ -958,40 +958,40 @@
         <v>0.55</v>
       </c>
       <c r="G9" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.55</v>
+        <v>-0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.14</v>
+        <v>0.82</v>
       </c>
       <c r="M9" t="n">
-        <v>7.36</v>
+        <v>7.29</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.82</v>
+        <v>-0.95</v>
       </c>
       <c r="P9" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.95</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.46</v>
+        <v>47.52</v>
       </c>
       <c r="E10" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="G10" t="n">
-        <v>47.52</v>
+        <v>47.22</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="I10" t="n">
-        <v>0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="J10" t="n">
-        <v>47.22</v>
+        <v>47.48</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3</v>
+        <v>0.26</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.63</v>
+        <v>0.55</v>
       </c>
       <c r="M10" t="n">
-        <v>47.48</v>
+        <v>46.94</v>
       </c>
       <c r="N10" t="n">
-        <v>0.26</v>
+        <v>-0.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0.55</v>
+        <v>-1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>46.94</v>
+        <v>46.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.14</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.22</v>
+        <v>0.43</v>
       </c>
       <c r="G11" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I11" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="J11" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="L11" t="n">
-        <v>0.65</v>
+        <v>-1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="N11" t="n">
         <v>-0.08</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="P11" t="n">
         <v>4.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.64</v>
+        <v>11.06</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="F12" t="n">
-        <v>0.47</v>
+        <v>3.95</v>
       </c>
       <c r="G12" t="n">
         <v>11.06</v>
       </c>
       <c r="H12" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11.06</v>
+        <v>10.92</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.27</v>
+        <v>-0.27</v>
       </c>
       <c r="P12" t="n">
-        <v>10.89</v>
+        <v>10.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.27</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.6</v>
+        <v>26.92</v>
       </c>
       <c r="E13" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="F13" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>26.92</v>
+        <v>26.62</v>
       </c>
       <c r="H13" t="n">
-        <v>0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>-1.11</v>
       </c>
       <c r="J13" t="n">
-        <v>26.62</v>
+        <v>26.36</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.11</v>
+        <v>-0.98</v>
       </c>
       <c r="M13" t="n">
-        <v>26.36</v>
+        <v>26.42</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.26</v>
+        <v>0.06</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.98</v>
+        <v>0.23</v>
       </c>
       <c r="P13" t="n">
-        <v>26.42</v>
+        <v>26.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="R13" t="n">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.75</v>
+        <v>1.13</v>
       </c>
       <c r="J14" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="L14" t="n">
-        <v>1.13</v>
+        <v>-2.97</v>
       </c>
       <c r="M14" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.97</v>
+        <v>-1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.92</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.21</v>
+        <v>5.45</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="F15" t="n">
-        <v>0.58</v>
+        <v>4.61</v>
       </c>
       <c r="G15" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="H15" t="n">
-        <v>0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="I15" t="n">
-        <v>4.61</v>
+        <v>-0.37</v>
       </c>
       <c r="J15" t="n">
-        <v>5.43</v>
+        <v>5.37</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.37</v>
+        <v>-1.1</v>
       </c>
       <c r="M15" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1</v>
+        <v>-0.93</v>
       </c>
       <c r="P15" t="n">
-        <v>5.32</v>
+        <v>5.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.93</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="16">
@@ -1386,46 +1386,46 @@
         <v>5.2</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="N16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F16" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="O16" t="n">
-        <v>-0.58</v>
+        <v>-0.78</v>
       </c>
       <c r="P16" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.78</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.03</v>
+        <v>0.26</v>
       </c>
       <c r="G17" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="J17" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.52</v>
+        <v>-1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.55</v>
+        <v>-2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="R17" t="n">
-        <v>-2.1</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="G18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.59</v>
       </c>
-      <c r="H18" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.56</v>
-      </c>
       <c r="K18" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.84</v>
+        <v>0.84</v>
       </c>
       <c r="M18" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="N18" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="O18" t="n">
-        <v>0.84</v>
+        <v>-1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.67</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65.05</v>
+        <v>65</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.84</v>
+        <v>-0.08</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.08</v>
+        <v>-1.38</v>
       </c>
       <c r="J19" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.38</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>63.5</v>
+        <v>62.45</v>
       </c>
       <c r="N19" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="P19" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O19" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="P19" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1.05</v>
-      </c>
       <c r="R19" t="n">
-        <v>-1.65</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.38</v>
+        <v>30.58</v>
       </c>
       <c r="E20" t="n">
-        <v>0.12</v>
+        <v>-0.8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.38</v>
+        <v>-2.55</v>
       </c>
       <c r="G20" t="n">
-        <v>30.58</v>
+        <v>29.96</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8</v>
+        <v>-0.62</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.55</v>
+        <v>-2.03</v>
       </c>
       <c r="J20" t="n">
-        <v>29.96</v>
+        <v>29.88</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.03</v>
+        <v>-0.27</v>
       </c>
       <c r="M20" t="n">
         <v>29.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>29.88</v>
+        <v>29.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F21" t="n">
-        <v>1.29</v>
+        <v>-0.55</v>
       </c>
       <c r="G21" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.55</v>
+        <v>-0.18</v>
       </c>
       <c r="J21" t="n">
-        <v>5.45</v>
+        <v>5.51</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.18</v>
+        <v>1.1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.51</v>
+        <v>5.32</v>
       </c>
       <c r="N21" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1</v>
+        <v>-3.45</v>
       </c>
       <c r="P21" t="n">
-        <v>5.32</v>
+        <v>5.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.19</v>
+        <v>0.32</v>
       </c>
       <c r="R21" t="n">
-        <v>-3.45</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G22" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J22" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M22" t="n">
         <v>86.2</v>
       </c>
-      <c r="E22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G22" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86.55</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M22" t="n">
-        <v>86.7</v>
-      </c>
       <c r="N22" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0.17</v>
+        <v>-0.58</v>
       </c>
       <c r="P22" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.58</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.38</v>
+        <v>26.38</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.02</v>
+        <v>-1</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.65</v>
       </c>
       <c r="G23" t="n">
-        <v>26.38</v>
+        <v>26.88</v>
       </c>
       <c r="H23" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.65</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>26.88</v>
+        <v>26.14</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9</v>
+        <v>-2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>26.14</v>
+        <v>25.22</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.75</v>
+        <v>-3.52</v>
       </c>
       <c r="P23" t="n">
-        <v>25.22</v>
+        <v>25.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.92</v>
+        <v>-0.1</v>
       </c>
       <c r="R23" t="n">
-        <v>-3.52</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.86</v>
+        <v>29.2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="G24" t="n">
-        <v>29.2</v>
+        <v>29.66</v>
       </c>
       <c r="H24" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="I24" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="J24" t="n">
-        <v>29.66</v>
+        <v>29.88</v>
       </c>
       <c r="K24" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>0.74</v>
       </c>
       <c r="M24" t="n">
-        <v>29.88</v>
+        <v>29.96</v>
       </c>
       <c r="N24" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="O24" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="P24" t="n">
-        <v>29.96</v>
+        <v>29.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="R24" t="n">
-        <v>0.27</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.7</v>
+        <v>31.46</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02</v>
+        <v>-0.24</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06</v>
+        <v>-0.76</v>
       </c>
       <c r="G25" t="n">
-        <v>31.46</v>
+        <v>31.8</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.24</v>
+        <v>0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.76</v>
+        <v>1.08</v>
       </c>
       <c r="J25" t="n">
-        <v>31.8</v>
+        <v>31.72</v>
       </c>
       <c r="K25" t="n">
-        <v>0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="L25" t="n">
-        <v>1.08</v>
+        <v>-0.25</v>
       </c>
       <c r="M25" t="n">
-        <v>31.72</v>
+        <v>30.7</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.25</v>
+        <v>-3.22</v>
       </c>
       <c r="P25" t="n">
-        <v>30.7</v>
+        <v>30.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.02</v>
+        <v>-0.04</v>
       </c>
       <c r="R25" t="n">
-        <v>-3.22</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>56.6</v>
+        <v>55.15</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.05</v>
+        <v>-1.45</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.09</v>
+        <v>-2.56</v>
       </c>
       <c r="G26" t="n">
-        <v>55.15</v>
+        <v>55.25</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.45</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.56</v>
+        <v>0.18</v>
       </c>
       <c r="J26" t="n">
-        <v>55.25</v>
+        <v>51.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1</v>
+        <v>-3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>0.18</v>
+        <v>-6.24</v>
       </c>
       <c r="M26" t="n">
-        <v>51.8</v>
+        <v>47.84</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.45</v>
+        <v>-3.96</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.24</v>
+        <v>-7.64</v>
       </c>
       <c r="P26" t="n">
-        <v>47.84</v>
+        <v>47.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.96</v>
+        <v>-0.42</v>
       </c>
       <c r="R26" t="n">
-        <v>-7.64</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>464.4</v>
+        <v>457.2</v>
       </c>
       <c r="E27" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.48</v>
+        <v>-1.55</v>
       </c>
       <c r="G27" t="n">
-        <v>457.2</v>
+        <v>462.6</v>
       </c>
       <c r="H27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J27" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="M27" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="P27" t="n">
+        <v>449.2</v>
+      </c>
+      <c r="Q27" t="n">
         <v>-7.2</v>
       </c>
-      <c r="I27" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="J27" t="n">
-        <v>462.6</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M27" t="n">
-        <v>460.2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="P27" t="n">
-        <v>456.4</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-3.8</v>
-      </c>
       <c r="R27" t="n">
-        <v>-0.83</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>133.9</v>
+        <v>133.3</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.67</v>
+        <v>-0.45</v>
       </c>
       <c r="G28" t="n">
-        <v>133.3</v>
+        <v>132.8</v>
       </c>
       <c r="H28" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J28" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="M28" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="P28" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="Q28" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I28" t="n">
+      <c r="R28" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="J28" t="n">
-        <v>132.8</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="M28" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="P28" t="n">
-        <v>132.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-4.06</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>118.5</v>
+        <v>118.4</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="G29" t="n">
-        <v>118.4</v>
+        <v>128.2</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>128.2</v>
+        <v>130.1</v>
       </c>
       <c r="K29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="L29" t="n">
-        <v>8.279999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>130.1</v>
+        <v>127.9</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.48</v>
+        <v>-1.69</v>
       </c>
       <c r="P29" t="n">
-        <v>127.9</v>
+        <v>126.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.69</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>84.34999999999999</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="F30" t="n">
-        <v>0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="G30" t="n">
-        <v>84.15000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2</v>
+        <v>3.45</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.24</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>87.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3.45</v>
+        <v>-1.9</v>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>-2.17</v>
       </c>
       <c r="M30" t="n">
-        <v>85.7</v>
+        <v>82.7</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.9</v>
+        <v>-3</v>
       </c>
       <c r="O30" t="n">
-        <v>-2.17</v>
+        <v>-3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>82.7</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>-3</v>
+        <v>-0.55</v>
       </c>
       <c r="R30" t="n">
-        <v>-3.5</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="G31" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="J31" t="n">
         <v>140.9</v>
       </c>
-      <c r="E31" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="G31" t="n">
-        <v>139.7</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J31" t="n">
-        <v>137.5</v>
-      </c>
       <c r="K31" t="n">
-        <v>-2.2</v>
+        <v>3.4</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.57</v>
+        <v>2.47</v>
       </c>
       <c r="M31" t="n">
-        <v>140.9</v>
+        <v>135.8</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.47</v>
+        <v>-3.62</v>
       </c>
       <c r="P31" t="n">
-        <v>135.8</v>
+        <v>134.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>-5.1</v>
+        <v>-1.1</v>
       </c>
       <c r="R31" t="n">
-        <v>-3.62</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2378,46 +2378,46 @@
         <v>76.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>76.59999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="J32" t="n">
-        <v>74.15000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K32" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="M32" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="P32" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="Q32" t="n">
         <v>-2.45</v>
       </c>
-      <c r="L32" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-3.57</v>
-      </c>
-      <c r="P32" t="n">
-        <v>71.15000000000001</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>-0.35</v>
-      </c>
       <c r="R32" t="n">
-        <v>-0.49</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>101.7</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>1.95</v>
+        <v>-1.85</v>
       </c>
       <c r="F33" t="n">
-        <v>1.95</v>
+        <v>-1.82</v>
       </c>
       <c r="G33" t="n">
-        <v>99.84999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.85</v>
+        <v>-1.7</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.82</v>
+        <v>-1.7</v>
       </c>
       <c r="J33" t="n">
         <v>98.15000000000001</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="N33" t="n">
         <v>-1.7</v>
       </c>
-      <c r="L33" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="M33" t="n">
-        <v>98.15000000000001</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
       <c r="P33" t="n">
-        <v>96.45</v>
+        <v>93.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.7</v>
+        <v>-2.65</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.73</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G34" t="n">
         <v>51.6</v>
       </c>
-      <c r="E34" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="G34" t="n">
-        <v>52.6</v>
-      </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I34" t="n">
-        <v>1.94</v>
+        <v>-1.9</v>
       </c>
       <c r="J34" t="n">
-        <v>51.6</v>
+        <v>50.85</v>
       </c>
       <c r="K34" t="n">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.9</v>
+        <v>-1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>50.85</v>
+        <v>49.34</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.75</v>
+        <v>-1.51</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.45</v>
+        <v>-2.97</v>
       </c>
       <c r="P34" t="n">
-        <v>49.34</v>
+        <v>48.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.97</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="G35" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="H35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="K35" t="n">
         <v>-0.03</v>
       </c>
-      <c r="I35" t="n">
+      <c r="L35" t="n">
         <v>-0.6</v>
       </c>
-      <c r="J35" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.4</v>
-      </c>
       <c r="M35" t="n">
-        <v>4.96</v>
+        <v>4.83</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.6</v>
+        <v>-2.62</v>
       </c>
       <c r="P35" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="R35" t="n">
-        <v>-2.62</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.73</v>
+        <v>10.66</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="G36" t="n">
-        <v>10.66</v>
+        <v>10.72</v>
       </c>
       <c r="H36" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="K36" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="I36" t="n">
+      <c r="L36" t="n">
         <v>-0.65</v>
       </c>
-      <c r="J36" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="M36" t="n">
-        <v>10.65</v>
+        <v>10.37</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.65</v>
+        <v>-2.63</v>
       </c>
       <c r="P36" t="n">
-        <v>10.37</v>
+        <v>10.17</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.28</v>
+        <v>-0.2</v>
       </c>
       <c r="R36" t="n">
-        <v>-2.63</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>425.4</v>
+        <v>423.8</v>
       </c>
       <c r="E37" t="n">
-        <v>1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="G37" t="n">
         <v>423.8</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>423.8</v>
+        <v>423.6</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="M37" t="n">
-        <v>423.6</v>
+        <v>416.4</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.2</v>
+        <v>-7.2</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.05</v>
+        <v>-1.7</v>
       </c>
       <c r="P37" t="n">
-        <v>416.4</v>
+        <v>410</v>
       </c>
       <c r="Q37" t="n">
-        <v>-7.2</v>
+        <v>-6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.7</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.08</v>
+        <v>16.14</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.34</v>
+        <v>0.06</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.07</v>
+        <v>0.37</v>
       </c>
       <c r="G38" t="n">
-        <v>16.14</v>
+        <v>16.03</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="I38" t="n">
-        <v>0.37</v>
+        <v>-0.68</v>
       </c>
       <c r="J38" t="n">
-        <v>16.03</v>
+        <v>16.05</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.11</v>
+        <v>0.02</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.68</v>
+        <v>0.12</v>
       </c>
       <c r="M38" t="n">
-        <v>16.05</v>
+        <v>15.96</v>
       </c>
       <c r="N38" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="O38" t="n">
-        <v>0.12</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P38" t="n">
-        <v>15.96</v>
+        <v>15.72</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.09</v>
+        <v>-0.24</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>657.5</v>
+        <v>651.5</v>
       </c>
       <c r="E39" t="n">
-        <v>6.5</v>
+        <v>-6</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>-0.91</v>
       </c>
       <c r="G39" t="n">
-        <v>651.5</v>
+        <v>673</v>
       </c>
       <c r="H39" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>686</v>
+      </c>
+      <c r="K39" t="n">
+        <v>13</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M39" t="n">
+        <v>680</v>
+      </c>
+      <c r="N39" t="n">
         <v>-6</v>
       </c>
-      <c r="I39" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="J39" t="n">
-        <v>673</v>
-      </c>
-      <c r="K39" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>686</v>
-      </c>
-      <c r="N39" t="n">
-        <v>13</v>
-      </c>
       <c r="O39" t="n">
-        <v>1.93</v>
+        <v>-0.87</v>
       </c>
       <c r="P39" t="n">
-        <v>680</v>
+        <v>674.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.87</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="F40" t="n">
-        <v>1.96</v>
+        <v>0.16</v>
       </c>
       <c r="G40" t="n">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="I40" t="n">
-        <v>0.16</v>
+        <v>-0.32</v>
       </c>
       <c r="J40" t="n">
-        <v>62.4</v>
+        <v>62.25</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
       <c r="M40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.15</v>
+        <v>-0.95</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.24</v>
+        <v>-1.53</v>
       </c>
       <c r="P40" t="n">
-        <v>61.3</v>
+        <v>60.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.95</v>
+        <v>-0.65</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.53</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>22.5</v>
+        <v>22.33</v>
       </c>
       <c r="E41" t="n">
-        <v>0.58</v>
+        <v>-0.17</v>
       </c>
       <c r="F41" t="n">
-        <v>2.65</v>
+        <v>-0.76</v>
       </c>
       <c r="G41" t="n">
-        <v>22.33</v>
+        <v>22.89</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.76</v>
+        <v>2.51</v>
       </c>
       <c r="J41" t="n">
-        <v>22.89</v>
+        <v>22.95</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L41" t="n">
-        <v>2.51</v>
+        <v>0.26</v>
       </c>
       <c r="M41" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="N41" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="O41" t="n">
-        <v>0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="P41" t="n">
-        <v>22.93</v>
+        <v>23.04</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.09</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.77</v>
+        <v>59.1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="F42" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>59.1</v>
+        <v>59.9</v>
       </c>
       <c r="H42" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="I42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M42" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P42" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="J42" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M42" t="n">
-        <v>60.13</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="P42" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="R42" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36.99</v>
+        <v>37.11</v>
       </c>
       <c r="E43" t="n">
-        <v>0.43</v>
+        <v>0.12</v>
       </c>
       <c r="F43" t="n">
-        <v>1.18</v>
+        <v>0.32</v>
       </c>
       <c r="G43" t="n">
-        <v>37.11</v>
+        <v>37.35</v>
       </c>
       <c r="H43" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="I43" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="J43" t="n">
-        <v>37.35</v>
+        <v>37.37</v>
       </c>
       <c r="K43" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="L43" t="n">
-        <v>0.65</v>
+        <v>0.05</v>
       </c>
       <c r="M43" t="n">
-        <v>37.37</v>
+        <v>37.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="P43" t="n">
-        <v>37.3</v>
+        <v>37.29</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.17</v>
+        <v>0.04</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.68</v>
+        <v>0.65</v>
       </c>
       <c r="G44" t="n">
-        <v>6.22</v>
+        <v>6.25</v>
       </c>
       <c r="H44" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="J44" t="n">
-        <v>6.25</v>
+        <v>6.19</v>
       </c>
       <c r="K44" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="L44" t="n">
-        <v>0.48</v>
+        <v>-0.96</v>
       </c>
       <c r="M44" t="n">
-        <v>6.19</v>
+        <v>6.13</v>
       </c>
       <c r="N44" t="n">
         <v>-0.06</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="P44" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.97</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.04</v>
+        <v>5.38</v>
       </c>
       <c r="G45" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="H45" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="I45" t="n">
-        <v>5.38</v>
+        <v>-1.28</v>
       </c>
       <c r="J45" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="K45" t="n">
         <v>-0.03</v>
       </c>
       <c r="L45" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="M45" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O45" t="n">
-        <v>-1.29</v>
+        <v>-1.75</v>
       </c>
       <c r="P45" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.75</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.69</v>
+        <v>0.92</v>
       </c>
       <c r="G46" t="n">
         <v>3.28</v>
       </c>
       <c r="H46" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-1.52</v>
       </c>
       <c r="M46" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.52</v>
+        <v>0.62</v>
       </c>
       <c r="P46" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>0.62</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.63</v>
+        <v>10.64</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.28</v>
+        <v>0.09</v>
       </c>
       <c r="G47" t="n">
-        <v>10.64</v>
+        <v>10.78</v>
       </c>
       <c r="H47" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09</v>
+        <v>1.32</v>
       </c>
       <c r="J47" t="n">
-        <v>10.78</v>
+        <v>10.52</v>
       </c>
       <c r="K47" t="n">
-        <v>0.14</v>
+        <v>-0.26</v>
       </c>
       <c r="L47" t="n">
-        <v>1.32</v>
+        <v>-2.41</v>
       </c>
       <c r="M47" t="n">
-        <v>10.52</v>
+        <v>10.37</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.41</v>
+        <v>-1.43</v>
       </c>
       <c r="P47" t="n">
-        <v>10.37</v>
+        <v>10.79</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.43</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.375</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>-1.32</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1.33</v>
-      </c>
       <c r="J48" t="n">
-        <v>0.375</v>
+        <v>0.355</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.32</v>
+        <v>-5.33</v>
       </c>
       <c r="M48" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
       <c r="N48" t="n">
         <v>-0.02</v>
       </c>
       <c r="O48" t="n">
-        <v>-5.33</v>
+        <v>-5.63</v>
       </c>
       <c r="P48" t="n">
         <v>0.335</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-5.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="E49" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="F49" t="n">
-        <v>1.28</v>
+        <v>-0.63</v>
       </c>
       <c r="G49" t="n">
-        <v>4.72</v>
+        <v>4.82</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.63</v>
+        <v>2.12</v>
       </c>
       <c r="J49" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.82</v>
       </c>
-      <c r="K49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="P49" t="n">
         <v>4.87</v>
       </c>
-      <c r="N49" t="n">
+      <c r="Q49" t="n">
         <v>0.05</v>
       </c>
-      <c r="O49" t="n">
+      <c r="R49" t="n">
         <v>1.04</v>
-      </c>
-      <c r="P49" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="R49" t="n">
-        <v>-1.03</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="J50" t="n">
         <v>1.01</v>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="K50" t="n">
         <v>0.01</v>
       </c>
-      <c r="I50" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-1.96</v>
-      </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>-0.99</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.25</v>
+        <v>1.02</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="H51" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="J51" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="K51" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="L51" t="n">
-        <v>1.77</v>
+        <v>-1</v>
       </c>
       <c r="M51" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O51" t="n">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
       <c r="P51" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.25</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.91</v>
+        <v>10.78</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.27</v>
+        <v>-1.19</v>
       </c>
       <c r="G52" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.19</v>
+        <v>1.02</v>
       </c>
       <c r="J52" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="K52" t="n">
-        <v>0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="L52" t="n">
-        <v>1.02</v>
+        <v>-1.74</v>
       </c>
       <c r="M52" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.74</v>
+        <v>-0.93</v>
       </c>
       <c r="P52" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.93</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G53" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="E53" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="G53" t="n">
-        <v>8.130000000000001</v>
-      </c>
       <c r="H53" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="J53" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.25</v>
+        <v>-3.08</v>
       </c>
       <c r="M53" t="n">
         <v>7.86</v>
       </c>
       <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="R53" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="P53" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3739,22 +3739,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="G54" t="n">
         <v>0.42</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0.42</v>
@@ -3766,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P54" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="R54" t="n">
-        <v>2.38</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-10.14</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="N55" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F55" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="K55" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L55" t="n">
-        <v>-10.14</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="O55" t="n">
-        <v>-3.23</v>
+        <v>-0.83</v>
       </c>
       <c r="P55" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="Q55" t="n">
         <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="56">
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="G56" t="n">
         <v>0.48</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0.48</v>
@@ -3890,22 +3890,22 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="P56" t="n">
         <v>0.485</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.61</v>
+        <v>0.27</v>
       </c>
       <c r="G57" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="H57" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="I57" t="n">
-        <v>0.27</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="K57" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
+        <v>0.53</v>
       </c>
       <c r="M57" t="n">
         <v>3.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="58">
@@ -3990,10 +3990,10 @@
         <v>0.081</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0.081</v>
@@ -4014,22 +4014,22 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="P58" t="n">
         <v>0.081</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.08</v>
-      </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.23</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.96</v>
+        <v>21.1</v>
       </c>
       <c r="E59" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G59" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J59" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P59" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R59" t="n">
         <v>0.05</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G59" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J59" t="n">
-        <v>21.58</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L59" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="M59" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="O59" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="P59" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="R59" t="n">
-        <v>-0.8</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="E60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K60" t="n">
         <v>-0.08</v>
       </c>
-      <c r="F60" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Q60" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L60" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="O60" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="R60" t="n">
-        <v>-0.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="J61" t="n">
         <v>1.55</v>
       </c>
-      <c r="E61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F61" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.64</v>
-      </c>
       <c r="K61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="L61" t="n">
-        <v>4.46</v>
+        <v>-5.49</v>
       </c>
       <c r="M61" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="O61" t="n">
-        <v>-5.49</v>
+        <v>-10.32</v>
       </c>
       <c r="P61" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="R61" t="n">
-        <v>-10.32</v>
+        <v>-1.44</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-12 Close</t>
+          <t>2026-05-13 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change</t>
+          <t>2026-05-13 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-12 Change %</t>
+          <t>2026-05-13 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-13 Close</t>
+          <t>2026-05-14 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change</t>
+          <t>2026-05-14 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change %</t>
+          <t>2026-05-14 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-14 Close</t>
+          <t>2026-05-15 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change</t>
+          <t>2026-05-15 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change %</t>
+          <t>2026-05-15 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-15 Close</t>
+          <t>2026-05-18 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change</t>
+          <t>2026-05-18 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change %</t>
+          <t>2026-05-18 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-18 Close</t>
+          <t>2026-05-19 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change</t>
+          <t>2026-05-19 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change %</t>
+          <t>2026-05-19 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>138.6</v>
+        <v>141.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>141.1</v>
+        <v>140.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>-0.43</v>
       </c>
       <c r="J3" t="n">
-        <v>140.5</v>
+        <v>139.4</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.43</v>
+        <v>-0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>139.4</v>
+        <v>138.1</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="P3" t="n">
-        <v>138.1</v>
+        <v>140.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.93</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>194</v>
+        <v>198.1</v>
       </c>
       <c r="E4" t="n">
-        <v>-9</v>
+        <v>4.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.43</v>
+        <v>2.11</v>
       </c>
       <c r="G4" t="n">
-        <v>198.1</v>
+        <v>199.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.11</v>
+        <v>0.66</v>
       </c>
       <c r="J4" t="n">
-        <v>199.4</v>
+        <v>198</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.66</v>
+        <v>-0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>198</v>
+        <v>196.6</v>
       </c>
       <c r="N4" t="n">
         <v>-1.4</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="P4" t="n">
-        <v>196.6</v>
+        <v>201.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.71</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.03</v>
+        <v>6.09</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>6.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>0.16</v>
+        <v>-0.49</v>
       </c>
       <c r="P5" t="n">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.49</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-0.71</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>7.04</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.71</v>
+        <v>0.57</v>
       </c>
       <c r="J6" t="n">
-        <v>7.04</v>
+        <v>6.89</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.57</v>
+        <v>-2.13</v>
       </c>
       <c r="M6" t="n">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.13</v>
+        <v>-0.58</v>
       </c>
       <c r="P6" t="n">
-        <v>6.85</v>
+        <v>6.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="E7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J7" t="n">
         <v>5.22</v>
       </c>
-      <c r="H7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.29</v>
-      </c>
       <c r="K7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>-1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.32</v>
+        <v>-0.19</v>
       </c>
       <c r="P7" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.19</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="F8" t="n">
-        <v>0.68</v>
+        <v>-0.34</v>
       </c>
       <c r="G8" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.01</v>
+        <v>-0.23</v>
       </c>
       <c r="P8" t="n">
-        <v>8.76</v>
+        <v>8.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.23</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F9" t="n">
-        <v>0.55</v>
+        <v>-0.14</v>
       </c>
       <c r="G9" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.14</v>
+        <v>0.82</v>
       </c>
       <c r="J9" t="n">
-        <v>7.36</v>
+        <v>7.29</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.82</v>
+        <v>-0.95</v>
       </c>
       <c r="M9" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.95</v>
+        <v>-0.55</v>
       </c>
       <c r="P9" t="n">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.55</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.52</v>
+        <v>47.22</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="G10" t="n">
-        <v>47.22</v>
+        <v>47.48</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3</v>
+        <v>0.26</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.63</v>
+        <v>0.55</v>
       </c>
       <c r="J10" t="n">
-        <v>47.48</v>
+        <v>46.94</v>
       </c>
       <c r="K10" t="n">
-        <v>0.26</v>
+        <v>-0.54</v>
       </c>
       <c r="L10" t="n">
-        <v>0.55</v>
+        <v>-1.14</v>
       </c>
       <c r="M10" t="n">
-        <v>46.94</v>
+        <v>46.58</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.14</v>
+        <v>-0.77</v>
       </c>
       <c r="P10" t="n">
-        <v>46.58</v>
+        <v>46.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.77</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F11" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="G11" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="I11" t="n">
-        <v>0.65</v>
+        <v>-1.72</v>
       </c>
       <c r="J11" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="K11" t="n">
         <v>-0.08</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="M11" t="n">
         <v>4.49</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="12">
@@ -1138,46 +1138,46 @@
         <v>11.06</v>
       </c>
       <c r="E12" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>11.06</v>
+        <v>10.92</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="J12" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.27</v>
+        <v>-0.27</v>
       </c>
       <c r="M12" t="n">
-        <v>10.89</v>
+        <v>10.99</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.27</v>
+        <v>0.92</v>
       </c>
       <c r="P12" t="n">
-        <v>10.99</v>
+        <v>11.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.92</v>
+        <v>26.62</v>
       </c>
       <c r="E13" t="n">
-        <v>0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>-1.11</v>
       </c>
       <c r="G13" t="n">
-        <v>26.62</v>
+        <v>26.36</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.11</v>
+        <v>-0.98</v>
       </c>
       <c r="J13" t="n">
-        <v>26.36</v>
+        <v>26.42</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.26</v>
+        <v>0.06</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.98</v>
+        <v>0.23</v>
       </c>
       <c r="M13" t="n">
-        <v>26.42</v>
+        <v>26.76</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="O13" t="n">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>26.76</v>
+        <v>27.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.75</v>
+        <v>1.13</v>
       </c>
       <c r="G14" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="I14" t="n">
-        <v>1.13</v>
+        <v>-2.97</v>
       </c>
       <c r="J14" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.97</v>
+        <v>-1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.92</v>
+        <v>-1.56</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.04</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="E15" t="n">
-        <v>0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>4.61</v>
+        <v>-0.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.43</v>
+        <v>5.37</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.37</v>
+        <v>-1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1</v>
+        <v>-0.93</v>
       </c>
       <c r="M15" t="n">
-        <v>5.32</v>
+        <v>5.17</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.93</v>
+        <v>-2.82</v>
       </c>
       <c r="P15" t="n">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.15</v>
+        <v>0.13</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.82</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="G16" t="n">
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.38</v>
+        <v>-0.58</v>
       </c>
       <c r="J16" t="n">
-        <v>5.15</v>
+        <v>5.11</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.58</v>
+        <v>-0.78</v>
       </c>
       <c r="M16" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="N16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>-0.78</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.39</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F17" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="G17" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="I17" t="n">
-        <v>0.52</v>
+        <v>-1.55</v>
       </c>
       <c r="J17" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.55</v>
+        <v>-2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1</v>
+        <v>-2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="R17" t="n">
-        <v>-2.95</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="G18" t="n">
         <v>3.59</v>
       </c>
-      <c r="E18" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.56</v>
-      </c>
       <c r="H18" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.84</v>
+        <v>0.84</v>
       </c>
       <c r="J18" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.84</v>
+        <v>-1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.67</v>
+        <v>-1.13</v>
       </c>
       <c r="P18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.13</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.08</v>
+        <v>-1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.38</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>63.5</v>
+        <v>62.45</v>
       </c>
       <c r="K19" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="M19" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="N19" t="n">
         <v>-0.6</v>
       </c>
-      <c r="L19" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="M19" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-1.05</v>
-      </c>
       <c r="O19" t="n">
-        <v>-1.65</v>
+        <v>-0.96</v>
       </c>
       <c r="P19" t="n">
-        <v>61.85</v>
+        <v>61.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.96</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.58</v>
+        <v>29.96</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8</v>
+        <v>-0.62</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.55</v>
+        <v>-2.03</v>
       </c>
       <c r="G20" t="n">
-        <v>29.96</v>
+        <v>29.88</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.03</v>
+        <v>-0.27</v>
       </c>
       <c r="J20" t="n">
         <v>29.88</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>29.88</v>
+        <v>29.76</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="P20" t="n">
-        <v>29.76</v>
+        <v>29.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.4</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.55</v>
+        <v>-0.18</v>
       </c>
       <c r="G21" t="n">
-        <v>5.45</v>
+        <v>5.51</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.18</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
-        <v>5.51</v>
+        <v>5.32</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1</v>
+        <v>-3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>5.32</v>
+        <v>5.64</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.19</v>
+        <v>0.32</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.45</v>
+        <v>6.02</v>
       </c>
       <c r="P21" t="n">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
       <c r="R21" t="n">
-        <v>6.02</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.5</v>
+        <v>86.55</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.35</v>
+        <v>0.06</v>
       </c>
       <c r="G22" t="n">
-        <v>86.55</v>
+        <v>86.7</v>
       </c>
       <c r="H22" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="J22" t="n">
-        <v>86.7</v>
+        <v>86.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.17</v>
+        <v>-0.58</v>
       </c>
       <c r="M22" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.58</v>
+        <v>0.23</v>
       </c>
       <c r="P22" t="n">
-        <v>86.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.38</v>
+        <v>26.88</v>
       </c>
       <c r="E23" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.65</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>26.88</v>
+        <v>26.14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>-2.75</v>
       </c>
       <c r="J23" t="n">
-        <v>26.14</v>
+        <v>25.22</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.75</v>
+        <v>-3.52</v>
       </c>
       <c r="M23" t="n">
-        <v>25.22</v>
+        <v>25.12</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.92</v>
+        <v>-0.1</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.52</v>
+        <v>-0.4</v>
       </c>
       <c r="P23" t="n">
-        <v>25.12</v>
+        <v>24.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.4</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.2</v>
+        <v>29.66</v>
       </c>
       <c r="E24" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>29.66</v>
+        <v>29.88</v>
       </c>
       <c r="H24" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="I24" t="n">
-        <v>1.58</v>
+        <v>0.74</v>
       </c>
       <c r="J24" t="n">
-        <v>29.88</v>
+        <v>29.96</v>
       </c>
       <c r="K24" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="L24" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="M24" t="n">
-        <v>29.96</v>
+        <v>29.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="O24" t="n">
-        <v>0.27</v>
+        <v>-0.87</v>
       </c>
       <c r="P24" t="n">
-        <v>29.7</v>
+        <v>28.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.26</v>
+        <v>-0.74</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.87</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.46</v>
+        <v>31.8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.24</v>
+        <v>0.34</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.76</v>
+        <v>1.08</v>
       </c>
       <c r="G25" t="n">
-        <v>31.8</v>
+        <v>31.72</v>
       </c>
       <c r="H25" t="n">
-        <v>0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="I25" t="n">
-        <v>1.08</v>
+        <v>-0.25</v>
       </c>
       <c r="J25" t="n">
-        <v>31.72</v>
+        <v>30.7</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.25</v>
+        <v>-3.22</v>
       </c>
       <c r="M25" t="n">
-        <v>30.7</v>
+        <v>30.66</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.02</v>
+        <v>-0.04</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.22</v>
+        <v>-0.13</v>
       </c>
       <c r="P25" t="n">
-        <v>30.66</v>
+        <v>30.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55.15</v>
+        <v>55.25</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.45</v>
+        <v>0.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.56</v>
+        <v>0.18</v>
       </c>
       <c r="G26" t="n">
-        <v>55.25</v>
+        <v>51.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>-3.45</v>
       </c>
       <c r="I26" t="n">
-        <v>0.18</v>
+        <v>-6.24</v>
       </c>
       <c r="J26" t="n">
-        <v>51.8</v>
+        <v>47.84</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.45</v>
+        <v>-3.96</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.24</v>
+        <v>-7.64</v>
       </c>
       <c r="M26" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="P26" t="n">
         <v>47.84</v>
       </c>
-      <c r="N26" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="P26" t="n">
-        <v>47.42</v>
-      </c>
       <c r="Q26" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.88</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>457.2</v>
+        <v>462.6</v>
       </c>
       <c r="E27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G27" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J27" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M27" t="n">
+        <v>449.2</v>
+      </c>
+      <c r="N27" t="n">
         <v>-7.2</v>
       </c>
-      <c r="F27" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="G27" t="n">
-        <v>462.6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="J27" t="n">
-        <v>460.2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="M27" t="n">
-        <v>456.4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-3.8</v>
-      </c>
       <c r="O27" t="n">
-        <v>-0.83</v>
+        <v>-1.58</v>
       </c>
       <c r="P27" t="n">
-        <v>449.2</v>
+        <v>460</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.2</v>
+        <v>10.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.58</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="G28" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="J28" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="M28" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="P28" t="n">
         <v>133.3</v>
       </c>
-      <c r="E28" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="G28" t="n">
-        <v>132.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="J28" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="M28" t="n">
-        <v>132.3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="P28" t="n">
-        <v>131.7</v>
-      </c>
       <c r="Q28" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.45</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>118.4</v>
+        <v>128.2</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>128.2</v>
+        <v>130.1</v>
       </c>
       <c r="H29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I29" t="n">
-        <v>8.279999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="J29" t="n">
-        <v>130.1</v>
+        <v>127.9</v>
       </c>
       <c r="K29" t="n">
-        <v>1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>-1.69</v>
       </c>
       <c r="M29" t="n">
-        <v>127.9</v>
+        <v>126.5</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.69</v>
+        <v>-1.09</v>
       </c>
       <c r="P29" t="n">
-        <v>126.5</v>
+        <v>125.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.09</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>84.15000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2</v>
+        <v>3.45</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.24</v>
+        <v>4.1</v>
       </c>
       <c r="G30" t="n">
-        <v>87.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H30" t="n">
-        <v>3.45</v>
+        <v>-1.9</v>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>-2.17</v>
       </c>
       <c r="J30" t="n">
-        <v>85.7</v>
+        <v>82.7</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.9</v>
+        <v>-3</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.17</v>
+        <v>-3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>82.7</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>-3</v>
+        <v>-0.55</v>
       </c>
       <c r="O30" t="n">
-        <v>-3.5</v>
+        <v>-0.67</v>
       </c>
       <c r="P30" t="n">
-        <v>82.15000000000001</v>
+        <v>83.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.55</v>
+        <v>0.9</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.67</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>139.7</v>
+        <v>137.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.2</v>
+        <v>-2.2</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.85</v>
+        <v>-1.57</v>
       </c>
       <c r="G31" t="n">
-        <v>137.5</v>
+        <v>140.9</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.2</v>
+        <v>3.4</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.57</v>
+        <v>2.47</v>
       </c>
       <c r="J31" t="n">
-        <v>140.9</v>
+        <v>135.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="L31" t="n">
-        <v>2.47</v>
+        <v>-3.62</v>
       </c>
       <c r="M31" t="n">
-        <v>135.8</v>
+        <v>134.7</v>
       </c>
       <c r="N31" t="n">
-        <v>-5.1</v>
+        <v>-1.1</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>134.7</v>
+        <v>136.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.1</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>76.59999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="G32" t="n">
-        <v>74.15000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="H32" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="J32" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M32" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N32" t="n">
         <v>-2.45</v>
       </c>
-      <c r="I32" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="L32" t="n">
-        <v>-3.57</v>
-      </c>
-      <c r="M32" t="n">
-        <v>71.15000000000001</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-0.35</v>
-      </c>
       <c r="O32" t="n">
-        <v>-0.49</v>
+        <v>-3.44</v>
       </c>
       <c r="P32" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2.45</v>
+        <v>-0.2</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.44</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>99.84999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.85</v>
+        <v>-1.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.82</v>
+        <v>-1.7</v>
       </c>
       <c r="G33" t="n">
         <v>98.15000000000001</v>
       </c>
       <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="K33" t="n">
         <v>-1.7</v>
       </c>
-      <c r="I33" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J33" t="n">
-        <v>98.15000000000001</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
       <c r="M33" t="n">
-        <v>96.45</v>
+        <v>93.8</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.7</v>
+        <v>-2.65</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.73</v>
+        <v>-2.75</v>
       </c>
       <c r="P33" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2.65</v>
+        <v>0.1</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.75</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>52.6</v>
+        <v>51.6</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F34" t="n">
-        <v>1.94</v>
+        <v>-1.9</v>
       </c>
       <c r="G34" t="n">
-        <v>51.6</v>
+        <v>50.85</v>
       </c>
       <c r="H34" t="n">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.9</v>
+        <v>-1.45</v>
       </c>
       <c r="J34" t="n">
-        <v>50.85</v>
+        <v>49.34</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.75</v>
+        <v>-1.51</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.45</v>
+        <v>-2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>49.34</v>
+        <v>48.68</v>
       </c>
       <c r="N34" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="O34" t="n">
-        <v>-2.97</v>
+        <v>-1.34</v>
       </c>
       <c r="P34" t="n">
-        <v>48.68</v>
+        <v>48.88</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.66</v>
+        <v>0.2</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.34</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="E35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H35" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F35" t="n">
+      <c r="I35" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G35" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Q35" t="n">
         <v>0.02</v>
       </c>
-      <c r="I35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L35" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="O35" t="n">
-        <v>-2.62</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="R35" t="n">
-        <v>-1.86</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.66</v>
+        <v>10.72</v>
       </c>
       <c r="E36" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="H36" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F36" t="n">
+      <c r="I36" t="n">
         <v>-0.65</v>
       </c>
-      <c r="G36" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="Q36" t="n">
         <v>0.06</v>
       </c>
-      <c r="I36" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J36" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="M36" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="O36" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="R36" t="n">
-        <v>-1.93</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="37">
@@ -2688,46 +2688,46 @@
         <v>423.8</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>423.8</v>
+        <v>423.6</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="J37" t="n">
-        <v>423.6</v>
+        <v>416.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.2</v>
+        <v>-7.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.05</v>
+        <v>-1.7</v>
       </c>
       <c r="M37" t="n">
-        <v>416.4</v>
+        <v>410</v>
       </c>
       <c r="N37" t="n">
-        <v>-7.2</v>
+        <v>-6.4</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.7</v>
+        <v>-1.54</v>
       </c>
       <c r="P37" t="n">
         <v>410</v>
       </c>
       <c r="Q37" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.14</v>
+        <v>16.03</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="F38" t="n">
-        <v>0.37</v>
+        <v>-0.68</v>
       </c>
       <c r="G38" t="n">
-        <v>16.03</v>
+        <v>16.05</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.11</v>
+        <v>0.02</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.68</v>
+        <v>0.12</v>
       </c>
       <c r="J38" t="n">
-        <v>16.05</v>
+        <v>15.96</v>
       </c>
       <c r="K38" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M38" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="Q38" t="n">
         <v>0.02</v>
       </c>
-      <c r="L38" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M38" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="P38" t="n">
-        <v>15.72</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>-0.24</v>
-      </c>
       <c r="R38" t="n">
-        <v>-1.5</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>651.5</v>
+        <v>673</v>
       </c>
       <c r="E39" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>686</v>
+      </c>
+      <c r="H39" t="n">
+        <v>13</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J39" t="n">
+        <v>680</v>
+      </c>
+      <c r="K39" t="n">
         <v>-6</v>
       </c>
-      <c r="F39" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="G39" t="n">
-        <v>673</v>
-      </c>
-      <c r="H39" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J39" t="n">
-        <v>686</v>
-      </c>
-      <c r="K39" t="n">
-        <v>13</v>
-      </c>
       <c r="L39" t="n">
-        <v>1.93</v>
+        <v>-0.87</v>
       </c>
       <c r="M39" t="n">
-        <v>680</v>
+        <v>674.5</v>
       </c>
       <c r="N39" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.87</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P39" t="n">
-        <v>674.5</v>
+        <v>660</v>
       </c>
       <c r="Q39" t="n">
-        <v>-5.5</v>
+        <v>-14.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F40" t="n">
-        <v>0.16</v>
+        <v>-0.32</v>
       </c>
       <c r="G40" t="n">
-        <v>62.4</v>
+        <v>62.25</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
       <c r="J40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.15</v>
+        <v>-0.95</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.24</v>
+        <v>-1.53</v>
       </c>
       <c r="M40" t="n">
-        <v>61.3</v>
+        <v>60.65</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.95</v>
+        <v>-0.65</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.53</v>
+        <v>-1.06</v>
       </c>
       <c r="P40" t="n">
-        <v>60.65</v>
+        <v>58.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.65</v>
+        <v>-2.15</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.06</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>22.33</v>
+        <v>22.89</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.76</v>
+        <v>2.51</v>
       </c>
       <c r="G41" t="n">
-        <v>22.89</v>
+        <v>22.95</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I41" t="n">
-        <v>2.51</v>
+        <v>0.26</v>
       </c>
       <c r="J41" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="K41" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="L41" t="n">
-        <v>0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="M41" t="n">
-        <v>22.93</v>
+        <v>23.04</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.09</v>
+        <v>0.48</v>
       </c>
       <c r="P41" t="n">
-        <v>23.04</v>
+        <v>23.43</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="R41" t="n">
-        <v>0.48</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>59.1</v>
+        <v>59.9</v>
       </c>
       <c r="E42" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="F42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G42" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J42" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M42" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="N42" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G42" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="J42" t="n">
-        <v>60.13</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M42" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="O42" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="P42" t="n">
-        <v>60.76</v>
+        <v>62</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="R42" t="n">
-        <v>0.93</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.11</v>
+        <v>37.35</v>
       </c>
       <c r="E43" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="F43" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="G43" t="n">
-        <v>37.35</v>
+        <v>37.37</v>
       </c>
       <c r="H43" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="I43" t="n">
-        <v>0.65</v>
+        <v>0.05</v>
       </c>
       <c r="J43" t="n">
-        <v>37.37</v>
+        <v>37.3</v>
       </c>
       <c r="K43" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="M43" t="n">
-        <v>37.3</v>
+        <v>37.29</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="P43" t="n">
-        <v>37.29</v>
+        <v>37.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.01</v>
+        <v>0.46</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.03</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.22</v>
+        <v>6.25</v>
       </c>
       <c r="E44" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F44" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="G44" t="n">
-        <v>6.25</v>
+        <v>6.19</v>
       </c>
       <c r="H44" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.48</v>
+        <v>-0.96</v>
       </c>
       <c r="J44" t="n">
-        <v>6.19</v>
+        <v>6.13</v>
       </c>
       <c r="K44" t="n">
         <v>-0.06</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="M44" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.97</v>
+        <v>-0.33</v>
       </c>
       <c r="P44" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.33</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="E45" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="F45" t="n">
-        <v>5.38</v>
+        <v>-1.28</v>
       </c>
       <c r="G45" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="H45" t="n">
         <v>-0.03</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="J45" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L45" t="n">
-        <v>-1.29</v>
+        <v>-1.75</v>
       </c>
       <c r="M45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="P45" t="n">
         <v>2.25</v>
       </c>
-      <c r="N45" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.24</v>
-      </c>
       <c r="Q45" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="46">
@@ -3246,46 +3246,46 @@
         <v>3.28</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>-1.52</v>
       </c>
       <c r="J46" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.52</v>
+        <v>0.62</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N46" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="O46" t="n">
-        <v>0.62</v>
+        <v>-1.23</v>
       </c>
       <c r="P46" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.23</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.64</v>
+        <v>10.78</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09</v>
+        <v>1.32</v>
       </c>
       <c r="G47" t="n">
-        <v>10.78</v>
+        <v>10.52</v>
       </c>
       <c r="H47" t="n">
-        <v>0.14</v>
+        <v>-0.26</v>
       </c>
       <c r="I47" t="n">
-        <v>1.32</v>
+        <v>-2.41</v>
       </c>
       <c r="J47" t="n">
-        <v>10.52</v>
+        <v>10.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.41</v>
+        <v>-1.43</v>
       </c>
       <c r="M47" t="n">
-        <v>10.37</v>
+        <v>10.79</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="O47" t="n">
-        <v>-1.43</v>
+        <v>4.05</v>
       </c>
       <c r="P47" t="n">
-        <v>10.79</v>
+        <v>11.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="R47" t="n">
-        <v>4.05</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="G48" t="n">
-        <v>0.375</v>
+        <v>0.355</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.32</v>
+        <v>-5.33</v>
       </c>
       <c r="J48" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
       <c r="K48" t="n">
         <v>-0.02</v>
       </c>
       <c r="L48" t="n">
-        <v>-5.33</v>
+        <v>-5.63</v>
       </c>
       <c r="M48" t="n">
         <v>0.335</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-5.63</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.335</v>
+        <v>0.34</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.72</v>
+        <v>4.82</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.63</v>
+        <v>2.12</v>
       </c>
       <c r="G49" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J49" t="n">
         <v>4.82</v>
       </c>
-      <c r="H49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.87</v>
       </c>
-      <c r="K49" t="n">
+      <c r="N49" t="n">
         <v>0.05</v>
       </c>
-      <c r="L49" t="n">
+      <c r="O49" t="n">
         <v>1.04</v>
       </c>
-      <c r="M49" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O49" t="n">
-        <v>-1.03</v>
-      </c>
       <c r="P49" t="n">
-        <v>4.87</v>
+        <v>4.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="R49" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H50" t="n">
         <v>0.01</v>
       </c>
-      <c r="F50" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
         <v>1</v>
       </c>
-      <c r="H50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-1.96</v>
-      </c>
       <c r="J50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>-0.99</v>
       </c>
       <c r="M50" t="n">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.99</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="E51" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="G51" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="H51" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="I51" t="n">
-        <v>1.77</v>
+        <v>-1</v>
       </c>
       <c r="J51" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L51" t="n">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
       <c r="M51" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.25</v>
+        <v>-1.26</v>
       </c>
       <c r="P51" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="R51" t="n">
-        <v>-1.26</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.13</v>
+        <v>0.11</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.19</v>
+        <v>1.02</v>
       </c>
       <c r="G52" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="H52" t="n">
-        <v>0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="I52" t="n">
-        <v>1.02</v>
+        <v>-1.74</v>
       </c>
       <c r="J52" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.74</v>
+        <v>-0.93</v>
       </c>
       <c r="M52" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.93</v>
+        <v>-2.08</v>
       </c>
       <c r="P52" t="n">
-        <v>10.38</v>
+        <v>10.23</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.08</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.130000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F53" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="G53" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.25</v>
+        <v>-3.08</v>
       </c>
       <c r="J53" t="n">
         <v>7.86</v>
       </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O53" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L53" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="M53" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
       <c r="P53" t="n">
-        <v>7.84</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.25</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="54">
@@ -3742,10 +3742,10 @@
         <v>0.42</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0.42</v>
@@ -3757,31 +3757,31 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M54" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="N54" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="O54" t="n">
-        <v>2.38</v>
+        <v>3.49</v>
       </c>
       <c r="P54" t="n">
-        <v>0.445</v>
+        <v>0.465</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="R54" t="n">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>1.47</v>
+        <v>-10.14</v>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="I55" t="n">
-        <v>-10.14</v>
+        <v>-3.23</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-3.23</v>
+        <v>-0.83</v>
       </c>
       <c r="M55" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="N55" t="n">
         <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="P55" t="n">
-        <v>0.59</v>
+        <v>0.585</v>
       </c>
       <c r="Q55" t="n">
         <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="56">
@@ -3866,10 +3866,10 @@
         <v>0.48</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0.48</v>
@@ -3881,22 +3881,22 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M56" t="n">
         <v>0.485</v>
       </c>
       <c r="N56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.485</v>
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="F57" t="n">
-        <v>0.27</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="H57" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>0.53</v>
       </c>
       <c r="J57" t="n">
         <v>3.8</v>
       </c>
       <c r="K57" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
       <c r="P57" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="R57" t="n">
-        <v>-2.37</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="58">
@@ -4005,31 +4005,31 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.081</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P58" t="n">
         <v>0.08</v>
       </c>
-      <c r="N58" t="n">
+      <c r="Q58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="O58" t="n">
+      <c r="R58" t="n">
         <v>-1.23</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.1</v>
+        <v>21.58</v>
       </c>
       <c r="E59" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="F59" t="n">
-        <v>0.67</v>
+        <v>2.27</v>
       </c>
       <c r="G59" t="n">
-        <v>21.58</v>
+        <v>21.3</v>
       </c>
       <c r="H59" t="n">
-        <v>0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="I59" t="n">
-        <v>2.27</v>
+        <v>-1.3</v>
       </c>
       <c r="J59" t="n">
-        <v>21.3</v>
+        <v>21.13</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="M59" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.17</v>
+        <v>0.01</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.8</v>
+        <v>0.05</v>
       </c>
       <c r="P59" t="n">
-        <v>21.14</v>
+        <v>21.67</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.01</v>
+        <v>0.53</v>
       </c>
       <c r="R59" t="n">
-        <v>0.05</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="F60" t="n">
-        <v>3.14</v>
+        <v>-1.22</v>
       </c>
       <c r="G60" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="H60" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N60" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I60" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="O60" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="P60" t="n">
         <v>3.16</v>
       </c>
-      <c r="K60" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L60" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O60" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.11</v>
-      </c>
       <c r="Q60" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="R60" t="n">
-        <v>-1.27</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>1.29</v>
+        <v>4.46</v>
       </c>
       <c r="G61" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="H61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="I61" t="n">
-        <v>4.46</v>
+        <v>-5.49</v>
       </c>
       <c r="J61" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="L61" t="n">
-        <v>-5.49</v>
+        <v>-10.32</v>
       </c>
       <c r="M61" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="O61" t="n">
-        <v>-10.32</v>
+        <v>-1.44</v>
       </c>
       <c r="P61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.44</v>
+        <v>-2.19</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-13 Close</t>
+          <t>2026-05-14 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change</t>
+          <t>2026-05-14 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-13 Change %</t>
+          <t>2026-05-14 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-14 Close</t>
+          <t>2026-05-15 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change</t>
+          <t>2026-05-15 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change %</t>
+          <t>2026-05-15 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-15 Close</t>
+          <t>2026-05-18 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change</t>
+          <t>2026-05-18 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change %</t>
+          <t>2026-05-18 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-18 Close</t>
+          <t>2026-05-19 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change</t>
+          <t>2026-05-19 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change %</t>
+          <t>2026-05-19 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-19 Close</t>
+          <t>2026-05-20 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change</t>
+          <t>2026-05-20 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change %</t>
+          <t>2026-05-20 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141.1</v>
+        <v>140.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>-0.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8</v>
+        <v>-0.43</v>
       </c>
       <c r="G3" t="n">
-        <v>140.5</v>
+        <v>139.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.43</v>
+        <v>-0.78</v>
       </c>
       <c r="J3" t="n">
-        <v>139.4</v>
+        <v>138.1</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="M3" t="n">
-        <v>138.1</v>
+        <v>140.3</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.93</v>
+        <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>140.3</v>
+        <v>138.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>-1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>198.1</v>
+        <v>199.4</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="F4" t="n">
-        <v>2.11</v>
+        <v>0.66</v>
       </c>
       <c r="G4" t="n">
-        <v>199.4</v>
+        <v>198</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>-0.7</v>
       </c>
       <c r="J4" t="n">
-        <v>198</v>
+        <v>196.6</v>
       </c>
       <c r="K4" t="n">
         <v>-1.4</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>196.6</v>
+        <v>201.2</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.71</v>
+        <v>2.34</v>
       </c>
       <c r="P4" t="n">
-        <v>201.2</v>
+        <v>198</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>-3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="5">
@@ -704,46 +704,46 @@
         <v>6.09</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="J5" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="K5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.01</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="R5" t="n">
-        <v>-0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>7.04</v>
       </c>
       <c r="E6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F6" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.08</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G7" t="n">
         <v>5.22</v>
       </c>
-      <c r="E7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.34</v>
+        <v>-1.32</v>
       </c>
       <c r="J7" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.32</v>
+        <v>-0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.19</v>
+        <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="8">
@@ -890,46 +890,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="J8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.01</v>
+        <v>-0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>8.76</v>
+        <v>8.85</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.23</v>
+        <v>1.03</v>
       </c>
       <c r="P8" t="n">
-        <v>8.85</v>
+        <v>8.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.03</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.14</v>
+        <v>0.82</v>
       </c>
       <c r="G9" t="n">
-        <v>7.36</v>
+        <v>7.29</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.82</v>
+        <v>-0.95</v>
       </c>
       <c r="J9" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.95</v>
+        <v>-0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.55</v>
+        <v>0.41</v>
       </c>
       <c r="P9" t="n">
-        <v>7.28</v>
+        <v>7.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="R9" t="n">
-        <v>0.41</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="10">
@@ -1011,43 +1011,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.22</v>
+        <v>47.48</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3</v>
+        <v>0.26</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.63</v>
+        <v>0.55</v>
       </c>
       <c r="G10" t="n">
-        <v>47.48</v>
+        <v>46.94</v>
       </c>
       <c r="H10" t="n">
-        <v>0.26</v>
+        <v>-0.54</v>
       </c>
       <c r="I10" t="n">
-        <v>0.55</v>
+        <v>-1.14</v>
       </c>
       <c r="J10" t="n">
-        <v>46.94</v>
+        <v>46.58</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.14</v>
+        <v>-0.77</v>
       </c>
       <c r="M10" t="n">
-        <v>46.58</v>
+        <v>46.34</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.77</v>
+        <v>-0.52</v>
       </c>
       <c r="P10" t="n">
-        <v>46.34</v>
+        <v>46.1</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.24</v>
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>0.65</v>
+        <v>-1.72</v>
       </c>
       <c r="G11" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="H11" t="n">
         <v>-0.08</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="J11" t="n">
         <v>4.49</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P11" t="n">
         <v>4.49</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Q11" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R11" t="n">
-        <v>0.22</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.06</v>
+        <v>10.92</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="G12" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.27</v>
+        <v>-0.27</v>
       </c>
       <c r="J12" t="n">
-        <v>10.89</v>
+        <v>10.99</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.27</v>
+        <v>0.92</v>
       </c>
       <c r="M12" t="n">
-        <v>10.99</v>
+        <v>11.12</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="O12" t="n">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>11.12</v>
+        <v>11.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.62</v>
+        <v>26.36</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.11</v>
+        <v>-0.98</v>
       </c>
       <c r="G13" t="n">
-        <v>26.36</v>
+        <v>26.42</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.26</v>
+        <v>0.06</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.98</v>
+        <v>0.23</v>
       </c>
       <c r="J13" t="n">
-        <v>26.42</v>
+        <v>26.76</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="L13" t="n">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
-        <v>26.76</v>
+        <v>27.56</v>
       </c>
       <c r="N13" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>2.99</v>
       </c>
       <c r="P13" t="n">
-        <v>27.56</v>
+        <v>27.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="R13" t="n">
-        <v>2.99</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="F14" t="n">
-        <v>1.13</v>
+        <v>-2.97</v>
       </c>
       <c r="G14" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.97</v>
+        <v>-1.92</v>
       </c>
       <c r="J14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.92</v>
+        <v>-1.56</v>
       </c>
       <c r="M14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="N14" t="n">
         <v>-0.04</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="P14" t="n">
         <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.43</v>
+        <v>5.37</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.37</v>
+        <v>-1.1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1</v>
+        <v>-0.93</v>
       </c>
       <c r="J15" t="n">
-        <v>5.32</v>
+        <v>5.17</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.93</v>
+        <v>-2.82</v>
       </c>
       <c r="M15" t="n">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.15</v>
+        <v>0.13</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.82</v>
+        <v>2.51</v>
       </c>
       <c r="P15" t="n">
-        <v>5.3</v>
+        <v>5.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="R15" t="n">
-        <v>2.51</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.38</v>
+        <v>-0.58</v>
       </c>
       <c r="G16" t="n">
-        <v>5.15</v>
+        <v>5.11</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.58</v>
+        <v>-0.78</v>
       </c>
       <c r="J16" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="K16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="N16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>-0.78</v>
       </c>
-      <c r="M16" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.39</v>
-      </c>
       <c r="P16" t="n">
-        <v>5.09</v>
+        <v>4.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.78</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.52</v>
+        <v>-1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.55</v>
+        <v>-2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.1</v>
+        <v>-2.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.95</v>
+        <v>-1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.1</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="E18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F18" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.38</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>63.5</v>
+        <v>62.45</v>
       </c>
       <c r="H19" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="K19" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I19" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="J19" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-1.05</v>
-      </c>
       <c r="L19" t="n">
-        <v>-1.65</v>
+        <v>-0.96</v>
       </c>
       <c r="M19" t="n">
-        <v>61.85</v>
+        <v>61.4</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.96</v>
+        <v>-0.73</v>
       </c>
       <c r="P19" t="n">
-        <v>61.4</v>
+        <v>61.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.45</v>
+        <v>-0.25</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.73</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.96</v>
+        <v>29.88</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.03</v>
+        <v>-0.27</v>
       </c>
       <c r="G20" t="n">
         <v>29.88</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>29.88</v>
+        <v>29.76</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="M20" t="n">
-        <v>29.76</v>
+        <v>29.62</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4</v>
+        <v>-0.47</v>
       </c>
       <c r="P20" t="n">
-        <v>29.62</v>
+        <v>29.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.47</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.45</v>
+        <v>5.51</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.18</v>
+        <v>1.1</v>
       </c>
       <c r="G21" t="n">
-        <v>5.51</v>
+        <v>5.32</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>-3.45</v>
       </c>
       <c r="J21" t="n">
-        <v>5.32</v>
+        <v>5.64</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.19</v>
+        <v>0.32</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.45</v>
+        <v>6.02</v>
       </c>
       <c r="M21" t="n">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="N21" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
       <c r="O21" t="n">
-        <v>6.02</v>
+        <v>0.71</v>
       </c>
       <c r="P21" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="R21" t="n">
-        <v>0.71</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G22" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="J22" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M22" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P22" t="n">
         <v>86.55</v>
       </c>
-      <c r="E22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G22" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="M22" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P22" t="n">
-        <v>86.8</v>
-      </c>
       <c r="Q22" t="n">
-        <v>0.4</v>
+        <v>-0.25</v>
       </c>
       <c r="R22" t="n">
-        <v>0.46</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.88</v>
+        <v>26.14</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>-2.75</v>
       </c>
       <c r="G23" t="n">
-        <v>26.14</v>
+        <v>25.22</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.75</v>
+        <v>-3.52</v>
       </c>
       <c r="J23" t="n">
-        <v>25.22</v>
+        <v>25.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.92</v>
+        <v>-0.1</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.52</v>
+        <v>-0.4</v>
       </c>
       <c r="M23" t="n">
-        <v>25.12</v>
+        <v>24.72</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4</v>
+        <v>-1.59</v>
       </c>
       <c r="P23" t="n">
-        <v>24.72</v>
+        <v>24.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4</v>
+        <v>-0.12</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.59</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.66</v>
+        <v>29.88</v>
       </c>
       <c r="E24" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>0.74</v>
       </c>
       <c r="G24" t="n">
-        <v>29.88</v>
+        <v>29.96</v>
       </c>
       <c r="H24" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="J24" t="n">
-        <v>29.96</v>
+        <v>29.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="L24" t="n">
-        <v>0.27</v>
+        <v>-0.87</v>
       </c>
       <c r="M24" t="n">
-        <v>29.7</v>
+        <v>28.96</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.26</v>
+        <v>-0.74</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.87</v>
+        <v>-2.49</v>
       </c>
       <c r="P24" t="n">
-        <v>28.96</v>
+        <v>28.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.74</v>
+        <v>-0.36</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.49</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.8</v>
+        <v>31.72</v>
       </c>
       <c r="E25" t="n">
-        <v>0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="F25" t="n">
-        <v>1.08</v>
+        <v>-0.25</v>
       </c>
       <c r="G25" t="n">
-        <v>31.72</v>
+        <v>30.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.25</v>
+        <v>-3.22</v>
       </c>
       <c r="J25" t="n">
-        <v>30.7</v>
+        <v>30.66</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.02</v>
+        <v>-0.04</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.22</v>
+        <v>-0.13</v>
       </c>
       <c r="M25" t="n">
-        <v>30.66</v>
+        <v>30.64</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>30.64</v>
+        <v>30.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.02</v>
+        <v>-0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55.25</v>
+        <v>51.8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1</v>
+        <v>-3.45</v>
       </c>
       <c r="F26" t="n">
-        <v>0.18</v>
+        <v>-6.24</v>
       </c>
       <c r="G26" t="n">
-        <v>51.8</v>
+        <v>47.84</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.45</v>
+        <v>-3.96</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.24</v>
+        <v>-7.64</v>
       </c>
       <c r="J26" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="M26" t="n">
         <v>47.84</v>
       </c>
-      <c r="K26" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="M26" t="n">
-        <v>47.42</v>
-      </c>
       <c r="N26" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.88</v>
+        <v>0.89</v>
       </c>
       <c r="P26" t="n">
-        <v>47.84</v>
+        <v>50.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.42</v>
+        <v>2.86</v>
       </c>
       <c r="R26" t="n">
-        <v>0.89</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>462.6</v>
+        <v>460.2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.4</v>
+        <v>-2.4</v>
       </c>
       <c r="F27" t="n">
-        <v>1.18</v>
+        <v>-0.52</v>
       </c>
       <c r="G27" t="n">
-        <v>460.2</v>
+        <v>456.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.4</v>
+        <v>-3.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.52</v>
+        <v>-0.83</v>
       </c>
       <c r="J27" t="n">
-        <v>456.4</v>
+        <v>449.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.8</v>
+        <v>-7.2</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.83</v>
+        <v>-1.58</v>
       </c>
       <c r="M27" t="n">
-        <v>449.2</v>
+        <v>460</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.2</v>
+        <v>10.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.58</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>460</v>
+        <v>455.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>10.8</v>
+        <v>-4.8</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>132.8</v>
+        <v>137.9</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5</v>
+        <v>5.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.38</v>
+        <v>3.84</v>
       </c>
       <c r="G28" t="n">
-        <v>137.9</v>
+        <v>132.3</v>
       </c>
       <c r="H28" t="n">
-        <v>5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>3.84</v>
+        <v>-4.06</v>
       </c>
       <c r="J28" t="n">
-        <v>132.3</v>
+        <v>131.7</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.6</v>
+        <v>-0.6</v>
       </c>
       <c r="L28" t="n">
-        <v>-4.06</v>
+        <v>-0.45</v>
       </c>
       <c r="M28" t="n">
-        <v>131.7</v>
+        <v>133.3</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.45</v>
+        <v>1.21</v>
       </c>
       <c r="P28" t="n">
-        <v>133.3</v>
+        <v>131.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>128.2</v>
+        <v>130.1</v>
       </c>
       <c r="E29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="F29" t="n">
-        <v>8.279999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="G29" t="n">
-        <v>130.1</v>
+        <v>127.9</v>
       </c>
       <c r="H29" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="J29" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="M29" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="P29" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1.9</v>
       </c>
-      <c r="I29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J29" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="M29" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="P29" t="n">
-        <v>125.9</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="R29" t="n">
-        <v>-0.47</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>87.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="E30" t="n">
-        <v>3.45</v>
+        <v>-1.9</v>
       </c>
       <c r="F30" t="n">
-        <v>4.1</v>
+        <v>-2.17</v>
       </c>
       <c r="G30" t="n">
-        <v>85.7</v>
+        <v>82.7</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.9</v>
+        <v>-3</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.17</v>
+        <v>-3.5</v>
       </c>
       <c r="J30" t="n">
-        <v>82.7</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-3</v>
+        <v>-0.55</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.5</v>
+        <v>-0.67</v>
       </c>
       <c r="M30" t="n">
-        <v>82.15000000000001</v>
+        <v>83.05</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.55</v>
+        <v>0.9</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.67</v>
+        <v>1.1</v>
       </c>
       <c r="P30" t="n">
-        <v>83.05</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.1</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>137.5</v>
+        <v>140.9</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.2</v>
+        <v>3.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.57</v>
+        <v>2.47</v>
       </c>
       <c r="G31" t="n">
-        <v>140.9</v>
+        <v>135.8</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="I31" t="n">
-        <v>2.47</v>
+        <v>-3.62</v>
       </c>
       <c r="J31" t="n">
-        <v>135.8</v>
+        <v>134.7</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.1</v>
+        <v>-1.1</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>134.7</v>
+        <v>136.7</v>
       </c>
       <c r="N31" t="n">
-        <v>-1.1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="P31" t="n">
-        <v>136.7</v>
+        <v>134.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.48</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>74.15000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="E32" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="G32" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="J32" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="K32" t="n">
         <v>-2.45</v>
       </c>
-      <c r="F32" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="G32" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-3.57</v>
-      </c>
-      <c r="J32" t="n">
-        <v>71.15000000000001</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-0.35</v>
-      </c>
       <c r="L32" t="n">
-        <v>-0.49</v>
+        <v>-3.44</v>
       </c>
       <c r="M32" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.45</v>
+        <v>-0.2</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.44</v>
+        <v>-0.29</v>
       </c>
       <c r="P32" t="n">
-        <v>68.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.2</v>
+        <v>6.65</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.29</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2440,46 +2440,46 @@
         <v>98.15000000000001</v>
       </c>
       <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="H33" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F33" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="G33" t="n">
-        <v>98.15000000000001</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
       <c r="J33" t="n">
-        <v>96.45</v>
+        <v>93.8</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.7</v>
+        <v>-2.65</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.73</v>
+        <v>-2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.65</v>
+        <v>0.1</v>
       </c>
       <c r="O33" t="n">
-        <v>-2.75</v>
+        <v>0.11</v>
       </c>
       <c r="P33" t="n">
-        <v>93.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1</v>
+        <v>-3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>0.11</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>51.6</v>
+        <v>50.85</v>
       </c>
       <c r="E34" t="n">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.9</v>
+        <v>-1.45</v>
       </c>
       <c r="G34" t="n">
-        <v>50.85</v>
+        <v>49.34</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.75</v>
+        <v>-1.51</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.45</v>
+        <v>-2.97</v>
       </c>
       <c r="J34" t="n">
-        <v>49.34</v>
+        <v>48.68</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.97</v>
+        <v>-1.34</v>
       </c>
       <c r="M34" t="n">
-        <v>48.68</v>
+        <v>48.88</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.66</v>
+        <v>0.2</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.34</v>
+        <v>0.41</v>
       </c>
       <c r="P34" t="n">
-        <v>48.88</v>
+        <v>47.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0.41</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="N35" t="n">
         <v>0.02</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I35" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="L35" t="n">
-        <v>-2.62</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="O35" t="n">
-        <v>-1.86</v>
+        <v>0.42</v>
       </c>
       <c r="P35" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R35" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.72</v>
+        <v>10.65</v>
       </c>
       <c r="E36" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="N36" t="n">
         <v>0.06</v>
       </c>
-      <c r="F36" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G36" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="J36" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="M36" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="O36" t="n">
-        <v>-1.93</v>
+        <v>0.59</v>
       </c>
       <c r="P36" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="R36" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>423.8</v>
+        <v>423.6</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G37" t="n">
-        <v>423.6</v>
+        <v>416.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2</v>
+        <v>-7.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.05</v>
+        <v>-1.7</v>
       </c>
       <c r="J37" t="n">
-        <v>416.4</v>
+        <v>410</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.2</v>
+        <v>-6.4</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.7</v>
+        <v>-1.54</v>
       </c>
       <c r="M37" t="n">
         <v>410</v>
       </c>
       <c r="N37" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>410</v>
+        <v>411.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.03</v>
+        <v>16.05</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.11</v>
+        <v>0.02</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.68</v>
+        <v>0.12</v>
       </c>
       <c r="G38" t="n">
-        <v>16.05</v>
+        <v>15.96</v>
       </c>
       <c r="H38" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.02</v>
       </c>
-      <c r="I38" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J38" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="L38" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="M38" t="n">
-        <v>15.72</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-0.24</v>
-      </c>
       <c r="O38" t="n">
-        <v>-1.5</v>
+        <v>0.13</v>
       </c>
       <c r="P38" t="n">
-        <v>15.74</v>
+        <v>15.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.02</v>
+        <v>-0.49</v>
       </c>
       <c r="R38" t="n">
-        <v>0.13</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="E39" t="n">
-        <v>21.5</v>
+        <v>13</v>
       </c>
       <c r="F39" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="G39" t="n">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="H39" t="n">
-        <v>13</v>
+        <v>-6</v>
       </c>
       <c r="I39" t="n">
-        <v>1.93</v>
+        <v>-0.87</v>
       </c>
       <c r="J39" t="n">
-        <v>680</v>
+        <v>674.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.87</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>674.5</v>
+        <v>660</v>
       </c>
       <c r="N39" t="n">
-        <v>-5.5</v>
+        <v>-14.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="P39" t="n">
-        <v>660</v>
+        <v>662.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>-14.5</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-2.15</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.4</v>
+        <v>62.25</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
       <c r="G40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.15</v>
+        <v>-0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.24</v>
+        <v>-1.53</v>
       </c>
       <c r="J40" t="n">
-        <v>61.3</v>
+        <v>60.65</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.95</v>
+        <v>-0.65</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.53</v>
+        <v>-1.06</v>
       </c>
       <c r="M40" t="n">
-        <v>60.65</v>
+        <v>58.5</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.65</v>
+        <v>-2.15</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.06</v>
+        <v>-3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>58.5</v>
+        <v>57.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>-2.15</v>
+        <v>-0.55</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.54</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>22.89</v>
+        <v>22.95</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F41" t="n">
-        <v>2.51</v>
+        <v>0.26</v>
       </c>
       <c r="G41" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="I41" t="n">
-        <v>0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="J41" t="n">
-        <v>22.93</v>
+        <v>23.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.09</v>
+        <v>0.48</v>
       </c>
       <c r="M41" t="n">
-        <v>23.04</v>
+        <v>23.43</v>
       </c>
       <c r="N41" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="O41" t="n">
-        <v>0.48</v>
+        <v>1.69</v>
       </c>
       <c r="P41" t="n">
-        <v>23.43</v>
+        <v>23.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="R41" t="n">
-        <v>1.69</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>59.9</v>
+        <v>60.13</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8</v>
+        <v>0.23</v>
       </c>
       <c r="F42" t="n">
-        <v>1.35</v>
+        <v>0.38</v>
       </c>
       <c r="G42" t="n">
-        <v>60.13</v>
+        <v>60.2</v>
       </c>
       <c r="H42" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="J42" t="n">
-        <v>60.2</v>
+        <v>60.76</v>
       </c>
       <c r="K42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="M42" t="n">
-        <v>60.76</v>
+        <v>62</v>
       </c>
       <c r="N42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="O42" t="n">
-        <v>0.93</v>
+        <v>2.04</v>
       </c>
       <c r="P42" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.24</v>
+        <v>-0.7</v>
       </c>
       <c r="R42" t="n">
-        <v>2.04</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.35</v>
+        <v>37.37</v>
       </c>
       <c r="E43" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="F43" t="n">
-        <v>0.65</v>
+        <v>0.05</v>
       </c>
       <c r="G43" t="n">
-        <v>37.37</v>
+        <v>37.3</v>
       </c>
       <c r="H43" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="J43" t="n">
-        <v>37.3</v>
+        <v>37.29</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="M43" t="n">
-        <v>37.29</v>
+        <v>37.75</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.01</v>
+        <v>0.46</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.03</v>
+        <v>1.23</v>
       </c>
       <c r="P43" t="n">
-        <v>37.75</v>
+        <v>37.59</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.46</v>
+        <v>-0.16</v>
       </c>
       <c r="R43" t="n">
-        <v>1.23</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.25</v>
+        <v>6.19</v>
       </c>
       <c r="E44" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="F44" t="n">
-        <v>0.48</v>
+        <v>-0.96</v>
       </c>
       <c r="G44" t="n">
-        <v>6.19</v>
+        <v>6.13</v>
       </c>
       <c r="H44" t="n">
         <v>-0.06</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="J44" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.97</v>
+        <v>-0.33</v>
       </c>
       <c r="M44" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.33</v>
+        <v>0.16</v>
       </c>
       <c r="P44" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="R44" t="n">
-        <v>0.16</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="E45" t="n">
         <v>-0.03</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="G45" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.29</v>
+        <v>-1.75</v>
       </c>
       <c r="J45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M45" t="n">
         <v>2.25</v>
       </c>
-      <c r="K45" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.24</v>
-      </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.44</v>
+        <v>0.45</v>
       </c>
       <c r="P45" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R45" t="n">
-        <v>0.45</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-1.52</v>
       </c>
       <c r="G46" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.52</v>
+        <v>0.62</v>
       </c>
       <c r="J46" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="K46" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="L46" t="n">
-        <v>0.62</v>
+        <v>-1.23</v>
       </c>
       <c r="M46" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.23</v>
+        <v>1.56</v>
       </c>
       <c r="P46" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="R46" t="n">
-        <v>1.56</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.78</v>
+        <v>10.52</v>
       </c>
       <c r="E47" t="n">
-        <v>0.14</v>
+        <v>-0.26</v>
       </c>
       <c r="F47" t="n">
-        <v>1.32</v>
+        <v>-2.41</v>
       </c>
       <c r="G47" t="n">
-        <v>10.52</v>
+        <v>10.37</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.41</v>
+        <v>-1.43</v>
       </c>
       <c r="J47" t="n">
-        <v>10.37</v>
+        <v>10.79</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.43</v>
+        <v>4.05</v>
       </c>
       <c r="M47" t="n">
-        <v>10.79</v>
+        <v>11.02</v>
       </c>
       <c r="N47" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="O47" t="n">
-        <v>4.05</v>
+        <v>2.13</v>
       </c>
       <c r="P47" t="n">
-        <v>11.02</v>
+        <v>11.06</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="R47" t="n">
-        <v>2.13</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.375</v>
+        <v>0.355</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.32</v>
+        <v>-5.33</v>
       </c>
       <c r="G48" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
       <c r="H48" t="n">
         <v>-0.02</v>
       </c>
       <c r="I48" t="n">
-        <v>-5.33</v>
+        <v>-5.63</v>
       </c>
       <c r="J48" t="n">
         <v>0.335</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>-5.63</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P48" t="n">
         <v>0.335</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.34</v>
-      </c>
       <c r="Q48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>1.49</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.82</v>
       </c>
-      <c r="E49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="J49" t="n">
         <v>4.87</v>
       </c>
-      <c r="H49" t="n">
+      <c r="K49" t="n">
         <v>0.05</v>
       </c>
-      <c r="I49" t="n">
+      <c r="L49" t="n">
         <v>1.04</v>
       </c>
-      <c r="J49" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="K49" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-1.03</v>
-      </c>
       <c r="M49" t="n">
-        <v>4.87</v>
+        <v>4.98</v>
       </c>
       <c r="N49" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="O49" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="P49" t="n">
-        <v>4.98</v>
+        <v>5.02</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="R49" t="n">
-        <v>2.26</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-1.96</v>
-      </c>
       <c r="G50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>-0.99</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
       </c>
       <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L50" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R50" t="n">
-        <v>3</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="E51" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F51" t="n">
-        <v>1.77</v>
+        <v>-1</v>
       </c>
       <c r="G51" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I51" t="n">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
       <c r="J51" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.25</v>
+        <v>-1.26</v>
       </c>
       <c r="M51" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.26</v>
+        <v>0.51</v>
       </c>
       <c r="P51" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="R51" t="n">
-        <v>0.51</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="E52" t="n">
-        <v>0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="F52" t="n">
-        <v>1.02</v>
+        <v>-1.74</v>
       </c>
       <c r="G52" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.74</v>
+        <v>-0.93</v>
       </c>
       <c r="J52" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.93</v>
+        <v>-2.08</v>
       </c>
       <c r="M52" t="n">
-        <v>10.38</v>
+        <v>10.23</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="O52" t="n">
-        <v>-2.08</v>
+        <v>-1.45</v>
       </c>
       <c r="P52" t="n">
-        <v>10.23</v>
+        <v>10.32</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.15</v>
+        <v>0.09</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.45</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.25</v>
+        <v>-3.08</v>
       </c>
       <c r="G53" t="n">
         <v>7.86</v>
       </c>
       <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L53" t="n">
         <v>-0.25</v>
       </c>
-      <c r="I53" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="J53" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
       <c r="M53" t="n">
-        <v>7.84</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.25</v>
+        <v>4.85</v>
       </c>
       <c r="P53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>4.85</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="54">
@@ -3748,40 +3748,40 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="J54" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L54" t="n">
-        <v>2.38</v>
+        <v>3.49</v>
       </c>
       <c r="M54" t="n">
-        <v>0.445</v>
+        <v>0.465</v>
       </c>
       <c r="N54" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="O54" t="n">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
       <c r="P54" t="n">
-        <v>0.465</v>
+        <v>0.46</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>4.49</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="F55" t="n">
-        <v>-10.14</v>
+        <v>-3.23</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-3.23</v>
+        <v>-0.83</v>
       </c>
       <c r="J55" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="K55" t="n">
         <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="M55" t="n">
-        <v>0.59</v>
+        <v>0.585</v>
       </c>
       <c r="N55" t="n">
         <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="P55" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="56">
@@ -3872,22 +3872,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="J56" t="n">
         <v>0.485</v>
       </c>
       <c r="K56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0.485</v>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="E57" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>0.53</v>
       </c>
       <c r="G57" t="n">
         <v>3.8</v>
       </c>
       <c r="H57" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
       <c r="M57" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="O57" t="n">
-        <v>-2.37</v>
+        <v>-1.62</v>
       </c>
       <c r="P57" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.62</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="58">
@@ -3996,40 +3996,40 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.081</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.08</v>
       </c>
-      <c r="K58" t="n">
+      <c r="N58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="L58" t="n">
+      <c r="O58" t="n">
         <v>-1.23</v>
       </c>
-      <c r="M58" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P58" t="n">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.23</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.58</v>
+        <v>21.3</v>
       </c>
       <c r="E59" t="n">
-        <v>0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="F59" t="n">
-        <v>2.27</v>
+        <v>-1.3</v>
       </c>
       <c r="G59" t="n">
-        <v>21.3</v>
+        <v>21.13</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="J59" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.17</v>
+        <v>0.01</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.8</v>
+        <v>0.05</v>
       </c>
       <c r="M59" t="n">
-        <v>21.14</v>
+        <v>21.67</v>
       </c>
       <c r="N59" t="n">
-        <v>0.01</v>
+        <v>0.53</v>
       </c>
       <c r="O59" t="n">
-        <v>0.05</v>
+        <v>2.51</v>
       </c>
       <c r="P59" t="n">
-        <v>21.67</v>
+        <v>21.86</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="R59" t="n">
-        <v>2.51</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="E60" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K60" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F60" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="L60" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="M60" t="n">
         <v>3.16</v>
       </c>
-      <c r="H60" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="N60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P60" t="n">
         <v>3.15</v>
       </c>
-      <c r="K60" t="n">
+      <c r="Q60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L60" t="n">
+      <c r="R60" t="n">
         <v>-0.32</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O60" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.61</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="E61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="F61" t="n">
-        <v>4.46</v>
+        <v>-5.49</v>
       </c>
       <c r="G61" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="I61" t="n">
-        <v>-5.49</v>
+        <v>-10.32</v>
       </c>
       <c r="J61" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="L61" t="n">
-        <v>-10.32</v>
+        <v>-1.44</v>
       </c>
       <c r="M61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O61" t="n">
-        <v>-1.44</v>
+        <v>-2.19</v>
       </c>
       <c r="P61" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R61" t="n">
-        <v>-2.19</v>
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-14 Close</t>
+          <t>2026-05-15 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change</t>
+          <t>2026-05-15 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-14 Change %</t>
+          <t>2026-05-15 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-15 Close</t>
+          <t>2026-05-18 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change</t>
+          <t>2026-05-18 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change %</t>
+          <t>2026-05-18 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-18 Close</t>
+          <t>2026-05-19 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change</t>
+          <t>2026-05-19 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change %</t>
+          <t>2026-05-19 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-19 Close</t>
+          <t>2026-05-20 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change</t>
+          <t>2026-05-20 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change %</t>
+          <t>2026-05-20 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-20 Close</t>
+          <t>2026-05-21 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change</t>
+          <t>2026-05-21 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change %</t>
+          <t>2026-05-21 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>140.5</v>
+        <v>139.4</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.43</v>
+        <v>-0.78</v>
       </c>
       <c r="G3" t="n">
-        <v>139.4</v>
+        <v>138.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="J3" t="n">
-        <v>138.1</v>
+        <v>140.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3</v>
+        <v>2.2</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.93</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>140.3</v>
+        <v>138.7</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>-1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59</v>
+        <v>-1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>138.7</v>
+        <v>141.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.6</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.14</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>199.4</v>
+        <v>198</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.66</v>
+        <v>-0.7</v>
       </c>
       <c r="G4" t="n">
-        <v>198</v>
+        <v>196.6</v>
       </c>
       <c r="H4" t="n">
         <v>-1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="J4" t="n">
-        <v>196.6</v>
+        <v>201.2</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.71</v>
+        <v>2.34</v>
       </c>
       <c r="M4" t="n">
-        <v>201.2</v>
+        <v>198</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>-3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>-1.59</v>
       </c>
       <c r="P4" t="n">
-        <v>198</v>
+        <v>200.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.59</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="H5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.01</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="O5" t="n">
-        <v>-0.16</v>
+        <v>0.17</v>
       </c>
       <c r="P5" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01</v>
+        <v>-0.19</v>
       </c>
       <c r="R5" t="n">
-        <v>0.17</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.04</v>
+        <v>6.89</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="F6" t="n">
-        <v>0.57</v>
+        <v>-2.13</v>
       </c>
       <c r="G6" t="n">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.13</v>
+        <v>-0.58</v>
       </c>
       <c r="J6" t="n">
-        <v>6.85</v>
+        <v>6.93</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
       <c r="M6" t="n">
-        <v>6.93</v>
+        <v>6.88</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>-0.72</v>
       </c>
       <c r="P6" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.72</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.34</v>
+        <v>-1.32</v>
       </c>
       <c r="G7" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.32</v>
+        <v>-0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.19</v>
+        <v>1.15</v>
       </c>
       <c r="M7" t="n">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>-0.76</v>
       </c>
       <c r="P7" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.76</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.01</v>
+        <v>-0.23</v>
       </c>
       <c r="J8" t="n">
-        <v>8.76</v>
+        <v>8.85</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.23</v>
+        <v>1.03</v>
       </c>
       <c r="M8" t="n">
-        <v>8.85</v>
+        <v>8.73</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="O8" t="n">
-        <v>1.03</v>
+        <v>-1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>8.73</v>
+        <v>8.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.36</v>
+        <v>7.29</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.82</v>
+        <v>-0.95</v>
       </c>
       <c r="G9" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.95</v>
+        <v>-0.55</v>
       </c>
       <c r="J9" t="n">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.55</v>
+        <v>0.41</v>
       </c>
       <c r="M9" t="n">
-        <v>7.28</v>
+        <v>7.19</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="O9" t="n">
-        <v>0.41</v>
+        <v>-1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.24</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="10">
@@ -1011,34 +1011,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.48</v>
+        <v>46.94</v>
       </c>
       <c r="E10" t="n">
-        <v>0.26</v>
+        <v>-0.54</v>
       </c>
       <c r="F10" t="n">
-        <v>0.55</v>
+        <v>-1.14</v>
       </c>
       <c r="G10" t="n">
-        <v>46.94</v>
+        <v>46.58</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.14</v>
+        <v>-0.77</v>
       </c>
       <c r="J10" t="n">
-        <v>46.58</v>
+        <v>46.34</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.77</v>
+        <v>-0.52</v>
       </c>
       <c r="M10" t="n">
-        <v>46.34</v>
+        <v>46.1</v>
       </c>
       <c r="N10" t="n">
         <v>-0.24</v>
@@ -1047,13 +1047,13 @@
         <v>-0.52</v>
       </c>
       <c r="P10" t="n">
-        <v>46.1</v>
+        <v>46.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.24</v>
+        <v>0.04</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.52</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="E11" t="n">
         <v>-0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="G11" t="n">
         <v>4.49</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M11" t="n">
         <v>4.49</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="O11" t="n">
-        <v>0.22</v>
+        <v>-0.22</v>
       </c>
       <c r="P11" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.22</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.27</v>
+        <v>-0.27</v>
       </c>
       <c r="G12" t="n">
-        <v>10.89</v>
+        <v>10.99</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.27</v>
+        <v>0.92</v>
       </c>
       <c r="J12" t="n">
-        <v>10.99</v>
+        <v>11.12</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="L12" t="n">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
       <c r="M12" t="n">
-        <v>11.12</v>
+        <v>11.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
       <c r="P12" t="n">
-        <v>11.2</v>
+        <v>10.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="R12" t="n">
-        <v>0.72</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.36</v>
+        <v>26.42</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.26</v>
+        <v>0.06</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.98</v>
+        <v>0.23</v>
       </c>
       <c r="G13" t="n">
-        <v>26.42</v>
+        <v>26.76</v>
       </c>
       <c r="H13" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="I13" t="n">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
       <c r="J13" t="n">
-        <v>26.76</v>
+        <v>27.56</v>
       </c>
       <c r="K13" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.29</v>
+        <v>2.99</v>
       </c>
       <c r="M13" t="n">
-        <v>27.56</v>
+        <v>27.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="O13" t="n">
-        <v>2.99</v>
+        <v>0.87</v>
       </c>
       <c r="P13" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.24</v>
+        <v>-0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0.87</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.97</v>
+        <v>-1.92</v>
       </c>
       <c r="G14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.92</v>
+        <v>-1.56</v>
       </c>
       <c r="J14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="K14" t="n">
         <v>-0.04</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="M14" t="n">
         <v>2.48</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1</v>
+        <v>-0.93</v>
       </c>
       <c r="G15" t="n">
-        <v>5.32</v>
+        <v>5.17</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.93</v>
+        <v>-2.82</v>
       </c>
       <c r="J15" t="n">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.15</v>
+        <v>0.13</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.82</v>
+        <v>2.51</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3</v>
+        <v>5.22</v>
       </c>
       <c r="N15" t="n">
-        <v>0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="O15" t="n">
-        <v>2.51</v>
+        <v>-1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>5.22</v>
+        <v>5.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.51</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.15</v>
+        <v>5.11</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.58</v>
+        <v>-0.78</v>
       </c>
       <c r="G16" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="H16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="K16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>-0.78</v>
       </c>
-      <c r="J16" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.39</v>
-      </c>
       <c r="M16" t="n">
-        <v>5.09</v>
+        <v>4.99</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.78</v>
+        <v>-1.96</v>
       </c>
       <c r="P16" t="n">
-        <v>4.99</v>
+        <v>4.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.96</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="E17" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F17" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="R17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.84</v>
+        <v>-1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.67</v>
+        <v>-1.13</v>
       </c>
       <c r="J18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.13</v>
+        <v>0.29</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="P18" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.86</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63.5</v>
+        <v>62.45</v>
       </c>
       <c r="E19" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="G19" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="H19" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F19" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="G19" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-1.05</v>
-      </c>
       <c r="I19" t="n">
-        <v>-1.65</v>
+        <v>-0.96</v>
       </c>
       <c r="J19" t="n">
-        <v>61.85</v>
+        <v>61.4</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.96</v>
+        <v>-0.73</v>
       </c>
       <c r="M19" t="n">
-        <v>61.4</v>
+        <v>61.15</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.45</v>
+        <v>-0.25</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.73</v>
+        <v>-0.41</v>
       </c>
       <c r="P19" t="n">
-        <v>61.15</v>
+        <v>60.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.41</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="20">
@@ -1634,46 +1634,46 @@
         <v>29.88</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>29.88</v>
+        <v>29.76</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="J20" t="n">
-        <v>29.76</v>
+        <v>29.62</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="L20" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="M20" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="P20" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-0.4</v>
       </c>
-      <c r="M20" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="P20" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="R20" t="n">
-        <v>-1.69</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.51</v>
+        <v>5.32</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1</v>
+        <v>-3.45</v>
       </c>
       <c r="G21" t="n">
-        <v>5.32</v>
+        <v>5.64</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.19</v>
+        <v>0.32</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.45</v>
+        <v>6.02</v>
       </c>
       <c r="J21" t="n">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="K21" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
       <c r="L21" t="n">
-        <v>6.02</v>
+        <v>0.71</v>
       </c>
       <c r="M21" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="N21" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="O21" t="n">
-        <v>0.71</v>
+        <v>-2.11</v>
       </c>
       <c r="P21" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.11</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.7</v>
+        <v>86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.17</v>
+        <v>-0.58</v>
       </c>
       <c r="G22" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J22" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M22" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="R22" t="n">
         <v>-0.58</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="M22" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P22" t="n">
-        <v>86.55</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-0.29</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.14</v>
+        <v>25.22</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.75</v>
+        <v>-3.52</v>
       </c>
       <c r="G23" t="n">
-        <v>25.22</v>
+        <v>25.12</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.92</v>
+        <v>-0.1</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.52</v>
+        <v>-0.4</v>
       </c>
       <c r="J23" t="n">
-        <v>25.12</v>
+        <v>24.72</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4</v>
+        <v>-1.59</v>
       </c>
       <c r="M23" t="n">
-        <v>24.72</v>
+        <v>24.6</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4</v>
+        <v>-0.12</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.59</v>
+        <v>-0.49</v>
       </c>
       <c r="P23" t="n">
-        <v>24.6</v>
+        <v>23.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.12</v>
+        <v>-0.82</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.49</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.88</v>
+        <v>29.96</v>
       </c>
       <c r="E24" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="F24" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="G24" t="n">
-        <v>29.96</v>
+        <v>29.7</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.27</v>
+        <v>-0.87</v>
       </c>
       <c r="J24" t="n">
-        <v>29.7</v>
+        <v>28.96</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.26</v>
+        <v>-0.74</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.87</v>
+        <v>-2.49</v>
       </c>
       <c r="M24" t="n">
-        <v>28.96</v>
+        <v>28.6</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.74</v>
+        <v>-0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.49</v>
+        <v>-1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>28.6</v>
+        <v>27.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.24</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31.72</v>
+        <v>30.7</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.25</v>
+        <v>-3.22</v>
       </c>
       <c r="G25" t="n">
-        <v>30.7</v>
+        <v>30.66</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.02</v>
+        <v>-0.04</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.22</v>
+        <v>-0.13</v>
       </c>
       <c r="J25" t="n">
-        <v>30.66</v>
+        <v>30.64</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>30.64</v>
+        <v>30.14</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.02</v>
+        <v>-0.5</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.63</v>
       </c>
       <c r="P25" t="n">
-        <v>30.14</v>
+        <v>29.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51.8</v>
+        <v>47.84</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.45</v>
+        <v>-3.96</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.24</v>
+        <v>-7.64</v>
       </c>
       <c r="G26" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J26" t="n">
         <v>47.84</v>
       </c>
-      <c r="H26" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="J26" t="n">
-        <v>47.42</v>
-      </c>
       <c r="K26" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M26" t="n">
-        <v>47.84</v>
+        <v>50.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.42</v>
+        <v>2.86</v>
       </c>
       <c r="O26" t="n">
-        <v>0.89</v>
+        <v>5.98</v>
       </c>
       <c r="P26" t="n">
-        <v>50.7</v>
+        <v>46.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.86</v>
+        <v>-3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>5.98</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>460.2</v>
+        <v>456.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.4</v>
+        <v>-3.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.52</v>
+        <v>-0.83</v>
       </c>
       <c r="G27" t="n">
-        <v>456.4</v>
+        <v>449.2</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.8</v>
+        <v>-7.2</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.83</v>
+        <v>-1.58</v>
       </c>
       <c r="J27" t="n">
-        <v>449.2</v>
+        <v>460</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.2</v>
+        <v>10.8</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.58</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>460</v>
+        <v>455.2</v>
       </c>
       <c r="N27" t="n">
-        <v>10.8</v>
+        <v>-4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>-1.04</v>
       </c>
       <c r="P27" t="n">
-        <v>455.2</v>
+        <v>439</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.8</v>
+        <v>-16.2</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.04</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>137.9</v>
+        <v>132.3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="F28" t="n">
-        <v>3.84</v>
+        <v>-4.06</v>
       </c>
       <c r="G28" t="n">
-        <v>132.3</v>
+        <v>131.7</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.6</v>
+        <v>-0.6</v>
       </c>
       <c r="I28" t="n">
-        <v>-4.06</v>
+        <v>-0.45</v>
       </c>
       <c r="J28" t="n">
-        <v>131.7</v>
+        <v>133.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.45</v>
+        <v>1.21</v>
       </c>
       <c r="M28" t="n">
-        <v>133.3</v>
+        <v>131.9</v>
       </c>
       <c r="N28" t="n">
-        <v>1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
       <c r="P28" t="n">
-        <v>131.9</v>
+        <v>126</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.4</v>
+        <v>-5.9</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.05</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>130.1</v>
+        <v>127.9</v>
       </c>
       <c r="E29" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="G29" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="J29" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="M29" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="N29" t="n">
         <v>1.9</v>
       </c>
-      <c r="F29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="G29" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="J29" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="M29" t="n">
-        <v>125.9</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="O29" t="n">
-        <v>-0.47</v>
+        <v>1.51</v>
       </c>
       <c r="P29" t="n">
-        <v>127.8</v>
+        <v>123.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.9</v>
+        <v>-4.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.51</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>85.7</v>
+        <v>82.7</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.9</v>
+        <v>-3</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.17</v>
+        <v>-3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>82.7</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-3</v>
+        <v>-0.55</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.5</v>
+        <v>-0.67</v>
       </c>
       <c r="J30" t="n">
-        <v>82.15000000000001</v>
+        <v>83.05</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.55</v>
+        <v>0.9</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.67</v>
+        <v>1.1</v>
       </c>
       <c r="M30" t="n">
-        <v>83.05</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.1</v>
+        <v>-0.24</v>
       </c>
       <c r="P30" t="n">
-        <v>82.84999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>140.9</v>
+        <v>135.8</v>
       </c>
       <c r="E31" t="n">
-        <v>3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="F31" t="n">
-        <v>2.47</v>
+        <v>-3.62</v>
       </c>
       <c r="G31" t="n">
-        <v>135.8</v>
+        <v>134.7</v>
       </c>
       <c r="H31" t="n">
-        <v>-5.1</v>
+        <v>-1.1</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>134.7</v>
+        <v>136.7</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.1</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>136.7</v>
+        <v>134.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.48</v>
+        <v>-1.83</v>
       </c>
       <c r="P31" t="n">
-        <v>134.2</v>
+        <v>126.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>-2.5</v>
+        <v>-7.7</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.83</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>71.5</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.65</v>
+        <v>-0.35</v>
       </c>
       <c r="F32" t="n">
-        <v>-3.57</v>
+        <v>-0.49</v>
       </c>
       <c r="G32" t="n">
-        <v>71.15000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.35</v>
+        <v>-2.45</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.49</v>
+        <v>-3.44</v>
       </c>
       <c r="J32" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.45</v>
+        <v>-0.2</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.44</v>
+        <v>-0.29</v>
       </c>
       <c r="M32" t="n">
-        <v>68.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.2</v>
+        <v>6.65</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.29</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="P32" t="n">
-        <v>75.15000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.65</v>
+        <v>-0.95</v>
       </c>
       <c r="R32" t="n">
-        <v>9.710000000000001</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>98.15000000000001</v>
+        <v>96.45</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
       <c r="G33" t="n">
-        <v>96.45</v>
+        <v>93.8</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.7</v>
+        <v>-2.65</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.73</v>
+        <v>-2.75</v>
       </c>
       <c r="J33" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.65</v>
+        <v>0.1</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.75</v>
+        <v>0.11</v>
       </c>
       <c r="M33" t="n">
-        <v>93.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1</v>
+        <v>-3.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0.11</v>
+        <v>-3.94</v>
       </c>
       <c r="P33" t="n">
-        <v>90.2</v>
+        <v>90.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>-3.7</v>
+        <v>0.35</v>
       </c>
       <c r="R33" t="n">
-        <v>-3.94</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>50.85</v>
+        <v>49.34</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.75</v>
+        <v>-1.51</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.45</v>
+        <v>-2.97</v>
       </c>
       <c r="G34" t="n">
-        <v>49.34</v>
+        <v>48.68</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.97</v>
+        <v>-1.34</v>
       </c>
       <c r="J34" t="n">
-        <v>48.68</v>
+        <v>48.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.66</v>
+        <v>0.2</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.34</v>
+        <v>0.41</v>
       </c>
       <c r="M34" t="n">
-        <v>48.88</v>
+        <v>47.68</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="O34" t="n">
-        <v>0.41</v>
+        <v>-2.45</v>
       </c>
       <c r="P34" t="n">
-        <v>47.68</v>
+        <v>44.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.45</v>
+        <v>-5.66</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.96</v>
+        <v>4.83</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6</v>
+        <v>-2.62</v>
       </c>
       <c r="G35" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.62</v>
+        <v>-1.86</v>
       </c>
       <c r="J35" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.86</v>
+        <v>0.42</v>
       </c>
       <c r="M35" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="N35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O35" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="P35" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0.21</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.65</v>
+        <v>10.37</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.65</v>
+        <v>-2.63</v>
       </c>
       <c r="G36" t="n">
-        <v>10.37</v>
+        <v>10.17</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.28</v>
+        <v>-0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.63</v>
+        <v>-1.93</v>
       </c>
       <c r="J36" t="n">
-        <v>10.17</v>
+        <v>10.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.93</v>
+        <v>0.59</v>
       </c>
       <c r="M36" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="N36" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="O36" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="P36" t="n">
-        <v>10.24</v>
+        <v>10.03</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>423.6</v>
+        <v>416.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.2</v>
+        <v>-7.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.05</v>
+        <v>-1.7</v>
       </c>
       <c r="G37" t="n">
-        <v>416.4</v>
+        <v>410</v>
       </c>
       <c r="H37" t="n">
-        <v>-7.2</v>
+        <v>-6.4</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.7</v>
+        <v>-1.54</v>
       </c>
       <c r="J37" t="n">
         <v>410</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>410</v>
+        <v>411.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="P37" t="n">
-        <v>411.2</v>
+        <v>407.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0.29</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.05</v>
+        <v>15.96</v>
       </c>
       <c r="E38" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="K38" t="n">
         <v>0.02</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G38" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="J38" t="n">
-        <v>15.72</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-0.24</v>
-      </c>
       <c r="L38" t="n">
-        <v>-1.5</v>
+        <v>0.13</v>
       </c>
       <c r="M38" t="n">
-        <v>15.74</v>
+        <v>15.25</v>
       </c>
       <c r="N38" t="n">
-        <v>0.02</v>
+        <v>-0.49</v>
       </c>
       <c r="O38" t="n">
-        <v>0.13</v>
+        <v>-3.11</v>
       </c>
       <c r="P38" t="n">
-        <v>15.25</v>
+        <v>15.21</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.49</v>
+        <v>-0.04</v>
       </c>
       <c r="R38" t="n">
-        <v>-3.11</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>-6</v>
       </c>
       <c r="F39" t="n">
-        <v>1.93</v>
+        <v>-0.87</v>
       </c>
       <c r="G39" t="n">
-        <v>680</v>
+        <v>674.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.87</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>674.5</v>
+        <v>660</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.5</v>
+        <v>-14.5</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>660</v>
+        <v>662.5</v>
       </c>
       <c r="N39" t="n">
-        <v>-14.5</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.15</v>
+        <v>0.38</v>
       </c>
       <c r="P39" t="n">
-        <v>662.5</v>
+        <v>673.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="R39" t="n">
-        <v>0.38</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.25</v>
+        <v>61.3</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.15</v>
+        <v>-0.95</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.24</v>
+        <v>-1.53</v>
       </c>
       <c r="G40" t="n">
-        <v>61.3</v>
+        <v>60.65</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.95</v>
+        <v>-0.65</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.53</v>
+        <v>-1.06</v>
       </c>
       <c r="J40" t="n">
-        <v>60.65</v>
+        <v>58.5</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.65</v>
+        <v>-2.15</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.06</v>
+        <v>-3.54</v>
       </c>
       <c r="M40" t="n">
-        <v>58.5</v>
+        <v>57.95</v>
       </c>
       <c r="N40" t="n">
-        <v>-2.15</v>
+        <v>-0.55</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.54</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P40" t="n">
-        <v>57.95</v>
+        <v>60.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.55</v>
+        <v>2.65</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.9399999999999999</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>22.95</v>
+        <v>22.93</v>
       </c>
       <c r="E41" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F41" t="n">
-        <v>0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="G41" t="n">
-        <v>22.93</v>
+        <v>23.04</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.09</v>
+        <v>0.48</v>
       </c>
       <c r="J41" t="n">
-        <v>23.04</v>
+        <v>23.43</v>
       </c>
       <c r="K41" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="L41" t="n">
-        <v>0.48</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>23.43</v>
+        <v>23.24</v>
       </c>
       <c r="N41" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="P41" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R41" t="n">
         <v>0.39</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="P41" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="R41" t="n">
-        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>60.13</v>
+        <v>60.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="G42" t="n">
-        <v>60.2</v>
+        <v>60.76</v>
       </c>
       <c r="H42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="J42" t="n">
-        <v>60.76</v>
+        <v>62</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="L42" t="n">
-        <v>0.93</v>
+        <v>2.04</v>
       </c>
       <c r="M42" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="N42" t="n">
-        <v>1.24</v>
+        <v>-0.7</v>
       </c>
       <c r="O42" t="n">
-        <v>2.04</v>
+        <v>-1.13</v>
       </c>
       <c r="P42" t="n">
-        <v>61.3</v>
+        <v>61.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.7</v>
+        <v>0.45</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.13</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.37</v>
+        <v>37.3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="G43" t="n">
-        <v>37.3</v>
+        <v>37.29</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="J43" t="n">
-        <v>37.29</v>
+        <v>37.75</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.01</v>
+        <v>0.46</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.03</v>
+        <v>1.23</v>
       </c>
       <c r="M43" t="n">
-        <v>37.75</v>
+        <v>37.59</v>
       </c>
       <c r="N43" t="n">
-        <v>0.46</v>
+        <v>-0.16</v>
       </c>
       <c r="O43" t="n">
-        <v>1.23</v>
+        <v>-0.42</v>
       </c>
       <c r="P43" t="n">
-        <v>37.59</v>
+        <v>37.69</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.42</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.19</v>
+        <v>6.13</v>
       </c>
       <c r="E44" t="n">
         <v>-0.06</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="G44" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.97</v>
+        <v>-0.33</v>
       </c>
       <c r="J44" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.33</v>
+        <v>0.16</v>
       </c>
       <c r="M44" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="N44" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O44" t="n">
-        <v>0.16</v>
+        <v>0.98</v>
       </c>
       <c r="P44" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="R44" t="n">
-        <v>0.98</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.29</v>
+        <v>-1.75</v>
       </c>
       <c r="G45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="J45" t="n">
         <v>2.25</v>
       </c>
-      <c r="H45" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.24</v>
-      </c>
       <c r="K45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L45" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="R45" t="n">
-        <v>-0.89</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.52</v>
+        <v>0.62</v>
       </c>
       <c r="G46" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="P46" t="n">
         <v>3.25</v>
       </c>
-      <c r="H46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P46" t="n">
-        <v>3.24</v>
-      </c>
       <c r="Q46" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.61</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.52</v>
+        <v>10.37</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.41</v>
+        <v>-1.43</v>
       </c>
       <c r="G47" t="n">
-        <v>10.37</v>
+        <v>10.79</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.43</v>
+        <v>4.05</v>
       </c>
       <c r="J47" t="n">
-        <v>10.79</v>
+        <v>11.02</v>
       </c>
       <c r="K47" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="L47" t="n">
-        <v>4.05</v>
+        <v>2.13</v>
       </c>
       <c r="M47" t="n">
-        <v>11.02</v>
+        <v>11.06</v>
       </c>
       <c r="N47" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="O47" t="n">
-        <v>2.13</v>
+        <v>0.36</v>
       </c>
       <c r="P47" t="n">
-        <v>11.06</v>
+        <v>11.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="R47" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
       <c r="E48" t="n">
         <v>-0.02</v>
       </c>
       <c r="F48" t="n">
-        <v>-5.33</v>
+        <v>-5.63</v>
       </c>
       <c r="G48" t="n">
         <v>0.335</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>-5.63</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M48" t="n">
         <v>0.335</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="P48" t="n">
         <v>0.34</v>
       </c>
-      <c r="N48" t="n">
+      <c r="Q48" t="n">
         <v>0.005</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>1.49</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="R48" t="n">
-        <v>-1.47</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.87</v>
       </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
         <v>0.05</v>
       </c>
-      <c r="F49" t="n">
+      <c r="I49" t="n">
         <v>1.04</v>
       </c>
-      <c r="G49" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-1.03</v>
-      </c>
       <c r="J49" t="n">
-        <v>4.87</v>
+        <v>4.98</v>
       </c>
       <c r="K49" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="L49" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="M49" t="n">
-        <v>4.98</v>
+        <v>5.02</v>
       </c>
       <c r="N49" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="O49" t="n">
-        <v>2.26</v>
+        <v>0.8</v>
       </c>
       <c r="P49" t="n">
-        <v>5.02</v>
+        <v>4.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="R49" t="n">
-        <v>0.8</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>-0.99</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I50" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.03</v>
-      </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>-0.97</v>
       </c>
       <c r="P50" t="n">
         <v>1.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F51" t="n">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
       <c r="G51" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.25</v>
+        <v>-1.26</v>
       </c>
       <c r="J51" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.26</v>
+        <v>0.51</v>
       </c>
       <c r="M51" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="N51" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="O51" t="n">
-        <v>0.51</v>
+        <v>-3.3</v>
       </c>
       <c r="P51" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="R51" t="n">
-        <v>-3.3</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.74</v>
+        <v>-0.93</v>
       </c>
       <c r="G52" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.93</v>
+        <v>-2.08</v>
       </c>
       <c r="J52" t="n">
-        <v>10.38</v>
+        <v>10.23</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.08</v>
+        <v>-1.45</v>
       </c>
       <c r="M52" t="n">
-        <v>10.23</v>
+        <v>10.32</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.15</v>
+        <v>0.09</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.45</v>
+        <v>0.88</v>
       </c>
       <c r="P52" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="R52" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="53">
@@ -3680,46 +3680,46 @@
         <v>7.86</v>
       </c>
       <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I53" t="n">
         <v>-0.25</v>
       </c>
-      <c r="F53" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="G53" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
       <c r="J53" t="n">
-        <v>7.84</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.25</v>
+        <v>4.85</v>
       </c>
       <c r="M53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="N53" t="n">
-        <v>0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="O53" t="n">
-        <v>4.85</v>
+        <v>-1.82</v>
       </c>
       <c r="P53" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.82</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="G54" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="H54" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="I54" t="n">
-        <v>2.38</v>
+        <v>3.49</v>
       </c>
       <c r="J54" t="n">
-        <v>0.445</v>
+        <v>0.465</v>
       </c>
       <c r="K54" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="L54" t="n">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
       <c r="M54" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="P54" t="n">
         <v>0.465</v>
       </c>
-      <c r="N54" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O54" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.46</v>
-      </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.08</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.23</v>
+        <v>-0.83</v>
       </c>
       <c r="G55" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="H55" t="n">
         <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="J55" t="n">
-        <v>0.59</v>
+        <v>0.585</v>
       </c>
       <c r="K55" t="n">
         <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="M55" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="P55" t="n">
         <v>0.59</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G56" t="n">
         <v>0.485</v>
       </c>
       <c r="H56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0.485</v>
@@ -3890,22 +3890,22 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="P56" t="n">
         <v>0.475</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3928,46 +3928,46 @@
         <v>3.8</v>
       </c>
       <c r="E57" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
       <c r="J57" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.37</v>
+        <v>-1.62</v>
       </c>
       <c r="M57" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.62</v>
+        <v>2.19</v>
       </c>
       <c r="P57" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="R57" t="n">
-        <v>2.19</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.081</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.08</v>
       </c>
-      <c r="H58" t="n">
+      <c r="K58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="I58" t="n">
+      <c r="L58" t="n">
         <v>-1.23</v>
       </c>
-      <c r="J58" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1.25</v>
-      </c>
       <c r="M58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="P58" t="n">
         <v>0.08</v>
       </c>
-      <c r="N58" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="O58" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.078</v>
-      </c>
       <c r="Q58" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.3</v>
+        <v>21.13</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.17</v>
+        <v>0.01</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.8</v>
+        <v>0.05</v>
       </c>
       <c r="J59" t="n">
-        <v>21.14</v>
+        <v>21.67</v>
       </c>
       <c r="K59" t="n">
-        <v>0.01</v>
+        <v>0.53</v>
       </c>
       <c r="L59" t="n">
-        <v>0.05</v>
+        <v>2.51</v>
       </c>
       <c r="M59" t="n">
-        <v>21.67</v>
+        <v>21.86</v>
       </c>
       <c r="N59" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="O59" t="n">
-        <v>2.51</v>
+        <v>0.88</v>
       </c>
       <c r="P59" t="n">
-        <v>21.86</v>
+        <v>22.38</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="R59" t="n">
-        <v>0.88</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="J60" t="n">
         <v>3.16</v>
       </c>
-      <c r="E60" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="K60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M60" t="n">
         <v>3.15</v>
       </c>
-      <c r="H60" t="n">
+      <c r="N60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I60" t="n">
+      <c r="O60" t="n">
         <v>-0.32</v>
       </c>
-      <c r="J60" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="K60" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L60" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="M60" t="n">
+      <c r="P60" t="n">
         <v>3.16</v>
       </c>
-      <c r="N60" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Q60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="F61" t="n">
-        <v>-5.49</v>
+        <v>-10.32</v>
       </c>
       <c r="G61" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="I61" t="n">
-        <v>-10.32</v>
+        <v>-1.44</v>
       </c>
       <c r="J61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.44</v>
+        <v>-2.19</v>
       </c>
       <c r="M61" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.19</v>
+        <v>1.49</v>
       </c>
       <c r="P61" t="n">
         <v>1.36</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-15 Close</t>
+          <t>2026-05-18 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change</t>
+          <t>2026-05-18 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-15 Change %</t>
+          <t>2026-05-18 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-18 Close</t>
+          <t>2026-05-19 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change</t>
+          <t>2026-05-19 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change %</t>
+          <t>2026-05-19 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-19 Close</t>
+          <t>2026-05-20 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change</t>
+          <t>2026-05-20 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change %</t>
+          <t>2026-05-20 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-20 Close</t>
+          <t>2026-05-21 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change</t>
+          <t>2026-05-21 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change %</t>
+          <t>2026-05-21 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-21 Close</t>
+          <t>2026-05-22 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change</t>
+          <t>2026-05-22 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change %</t>
+          <t>2026-05-22 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>139.4</v>
+        <v>138.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="G3" t="n">
-        <v>138.1</v>
+        <v>140.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.93</v>
+        <v>1.59</v>
       </c>
       <c r="J3" t="n">
-        <v>140.3</v>
+        <v>138.7</v>
       </c>
       <c r="K3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.2</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M3" t="n">
-        <v>138.7</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="P3" t="n">
-        <v>141.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
       <c r="R3" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>198</v>
+        <v>196.6</v>
       </c>
       <c r="E4" t="n">
         <v>-1.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="G4" t="n">
-        <v>196.6</v>
+        <v>201.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.71</v>
+        <v>2.34</v>
       </c>
       <c r="J4" t="n">
-        <v>201.2</v>
+        <v>198</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>-3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>2.34</v>
+        <v>-1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>198</v>
+        <v>200.6</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.59</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>200.6</v>
+        <v>204</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="E5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.01</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="L5" t="n">
-        <v>-0.16</v>
+        <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01</v>
+        <v>-0.19</v>
       </c>
       <c r="O5" t="n">
-        <v>0.17</v>
+        <v>-3.13</v>
       </c>
       <c r="P5" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="R5" t="n">
-        <v>-3.13</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.13</v>
+        <v>-0.58</v>
       </c>
       <c r="G6" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="P6" t="n">
         <v>6.85</v>
       </c>
-      <c r="H6" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="Q6" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.16</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.32</v>
+        <v>-0.19</v>
       </c>
       <c r="G7" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.19</v>
+        <v>1.15</v>
       </c>
       <c r="J7" t="n">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="L7" t="n">
-        <v>1.15</v>
+        <v>-0.76</v>
       </c>
       <c r="M7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="P7" t="n">
         <v>5.23</v>
       </c>
-      <c r="N7" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="Q7" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.57</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.01</v>
+        <v>-0.23</v>
       </c>
       <c r="G8" t="n">
-        <v>8.76</v>
+        <v>8.85</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.23</v>
+        <v>1.03</v>
       </c>
       <c r="J8" t="n">
-        <v>8.85</v>
+        <v>8.73</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="L8" t="n">
-        <v>1.03</v>
+        <v>-1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>8.73</v>
+        <v>8.69</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="P8" t="n">
-        <v>8.69</v>
+        <v>8.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.46</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="9">
@@ -949,43 +949,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.95</v>
+        <v>-0.55</v>
       </c>
       <c r="G9" t="n">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.55</v>
+        <v>0.41</v>
       </c>
       <c r="J9" t="n">
-        <v>7.28</v>
+        <v>7.19</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="L9" t="n">
-        <v>0.41</v>
+        <v>-1.24</v>
       </c>
       <c r="M9" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.24</v>
+        <v>-0.14</v>
       </c>
       <c r="P9" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.01</v>
@@ -1011,25 +1011,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.94</v>
+        <v>46.58</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.14</v>
+        <v>-0.77</v>
       </c>
       <c r="G10" t="n">
-        <v>46.58</v>
+        <v>46.34</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.77</v>
+        <v>-0.52</v>
       </c>
       <c r="J10" t="n">
-        <v>46.34</v>
+        <v>46.1</v>
       </c>
       <c r="K10" t="n">
         <v>-0.24</v>
@@ -1038,22 +1038,22 @@
         <v>-0.52</v>
       </c>
       <c r="M10" t="n">
-        <v>46.1</v>
+        <v>46.14</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.24</v>
+        <v>0.04</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.52</v>
+        <v>0.09</v>
       </c>
       <c r="P10" t="n">
-        <v>46.14</v>
+        <v>46.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="R10" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="11">
@@ -1076,46 +1076,46 @@
         <v>4.49</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J11" t="n">
         <v>4.49</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K11" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="L11" t="n">
-        <v>0.22</v>
+        <v>-0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="N11" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="O11" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="R11" t="n">
-        <v>-1.11</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.89</v>
+        <v>10.99</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.27</v>
+        <v>0.92</v>
       </c>
       <c r="G12" t="n">
-        <v>10.99</v>
+        <v>11.12</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
       <c r="J12" t="n">
-        <v>11.12</v>
+        <v>11.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="L12" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
       <c r="M12" t="n">
-        <v>11.2</v>
+        <v>10.94</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="O12" t="n">
-        <v>0.72</v>
+        <v>-2.32</v>
       </c>
       <c r="P12" t="n">
-        <v>10.94</v>
+        <v>10.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.26</v>
+        <v>-0.11</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.32</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.42</v>
+        <v>26.76</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="F13" t="n">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
       <c r="G13" t="n">
-        <v>26.76</v>
+        <v>27.56</v>
       </c>
       <c r="H13" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.29</v>
+        <v>2.99</v>
       </c>
       <c r="J13" t="n">
-        <v>27.56</v>
+        <v>27.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="L13" t="n">
-        <v>2.99</v>
+        <v>0.87</v>
       </c>
       <c r="M13" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.24</v>
+        <v>-0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0.87</v>
+        <v>-1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>27.3</v>
+        <v>27.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.8</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="14">
@@ -1259,43 +1259,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.92</v>
+        <v>-1.56</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H14" t="n">
         <v>-0.04</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="J14" t="n">
         <v>2.48</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.01</v>
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.32</v>
+        <v>5.17</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.93</v>
+        <v>-2.82</v>
       </c>
       <c r="G15" t="n">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.15</v>
+        <v>0.13</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.82</v>
+        <v>2.51</v>
       </c>
       <c r="J15" t="n">
-        <v>5.3</v>
+        <v>5.22</v>
       </c>
       <c r="K15" t="n">
-        <v>0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="L15" t="n">
-        <v>2.51</v>
+        <v>-1.51</v>
       </c>
       <c r="M15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="P15" t="n">
         <v>5.22</v>
       </c>
-      <c r="N15" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.15</v>
-      </c>
       <c r="Q15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.34</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="E16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="H16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F16" t="n">
+      <c r="I16" t="n">
         <v>-0.78</v>
       </c>
-      <c r="G16" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.39</v>
-      </c>
       <c r="J16" t="n">
-        <v>5.09</v>
+        <v>4.99</v>
       </c>
       <c r="K16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L16" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="R16" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1</v>
+        <v>-2.95</v>
       </c>
       <c r="G17" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.95</v>
+        <v>-1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="P17" t="n">
         <v>3.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.67</v>
+        <v>-1.13</v>
       </c>
       <c r="G18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.13</v>
+        <v>0.29</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L18" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.86</v>
+        <v>-2.31</v>
       </c>
       <c r="P18" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="R18" t="n">
-        <v>-2.31</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62.45</v>
+        <v>61.85</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.05</v>
+        <v>-0.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.65</v>
+        <v>-0.96</v>
       </c>
       <c r="G19" t="n">
-        <v>61.85</v>
+        <v>61.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.96</v>
+        <v>-0.73</v>
       </c>
       <c r="J19" t="n">
-        <v>61.4</v>
+        <v>61.15</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.45</v>
+        <v>-0.25</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.73</v>
+        <v>-0.41</v>
       </c>
       <c r="M19" t="n">
-        <v>61.15</v>
+        <v>60.8</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.41</v>
+        <v>-0.57</v>
       </c>
       <c r="P19" t="n">
-        <v>60.8</v>
+        <v>60.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.35</v>
+        <v>0.05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.57</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.88</v>
+        <v>29.76</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G20" t="n">
-        <v>29.76</v>
+        <v>29.62</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="I20" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="J20" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="M20" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="N20" t="n">
         <v>-0.4</v>
       </c>
-      <c r="J20" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="M20" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="O20" t="n">
-        <v>-1.69</v>
+        <v>-1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>28.72</v>
+        <v>28.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.37</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.32</v>
+        <v>5.64</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.19</v>
+        <v>0.32</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.45</v>
+        <v>6.02</v>
       </c>
       <c r="G21" t="n">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>6.02</v>
+        <v>0.71</v>
       </c>
       <c r="J21" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="K21" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="L21" t="n">
-        <v>0.71</v>
+        <v>-2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.11</v>
+        <v>-1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.62</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G22" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J22" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M22" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="N22" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F22" t="n">
+      <c r="O22" t="n">
         <v>-0.58</v>
       </c>
-      <c r="G22" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M22" t="n">
-        <v>86.55</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="P22" t="n">
-        <v>86.05</v>
+        <v>85.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.5</v>
+        <v>-0.55</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.58</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.22</v>
+        <v>25.12</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.92</v>
+        <v>-0.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.52</v>
+        <v>-0.4</v>
       </c>
       <c r="G23" t="n">
-        <v>25.12</v>
+        <v>24.72</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4</v>
+        <v>-1.59</v>
       </c>
       <c r="J23" t="n">
-        <v>24.72</v>
+        <v>24.6</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4</v>
+        <v>-0.12</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.59</v>
+        <v>-0.49</v>
       </c>
       <c r="M23" t="n">
-        <v>24.6</v>
+        <v>23.78</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.12</v>
+        <v>-0.82</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.49</v>
+        <v>-3.33</v>
       </c>
       <c r="P23" t="n">
-        <v>23.78</v>
+        <v>24.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.82</v>
+        <v>0.7</v>
       </c>
       <c r="R23" t="n">
-        <v>-3.33</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.96</v>
+        <v>29.7</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="F24" t="n">
-        <v>0.27</v>
+        <v>-0.87</v>
       </c>
       <c r="G24" t="n">
-        <v>29.7</v>
+        <v>28.96</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.26</v>
+        <v>-0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.87</v>
+        <v>-2.49</v>
       </c>
       <c r="J24" t="n">
-        <v>28.96</v>
+        <v>28.6</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.74</v>
+        <v>-0.36</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.49</v>
+        <v>-1.24</v>
       </c>
       <c r="M24" t="n">
-        <v>28.6</v>
+        <v>27.52</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.24</v>
+        <v>-3.78</v>
       </c>
       <c r="P24" t="n">
-        <v>27.52</v>
+        <v>28.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.08</v>
+        <v>0.78</v>
       </c>
       <c r="R24" t="n">
-        <v>-3.78</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.7</v>
+        <v>30.66</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.02</v>
+        <v>-0.04</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.22</v>
+        <v>-0.13</v>
       </c>
       <c r="G25" t="n">
-        <v>30.66</v>
+        <v>30.64</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>30.64</v>
+        <v>30.14</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.02</v>
+        <v>-0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.63</v>
       </c>
       <c r="M25" t="n">
-        <v>30.14</v>
+        <v>29.66</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="P25" t="n">
-        <v>29.66</v>
+        <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.48</v>
+        <v>0.34</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.59</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="G26" t="n">
         <v>47.84</v>
       </c>
-      <c r="E26" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="G26" t="n">
-        <v>47.42</v>
-      </c>
       <c r="H26" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.88</v>
+        <v>0.89</v>
       </c>
       <c r="J26" t="n">
-        <v>47.84</v>
+        <v>50.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.42</v>
+        <v>2.86</v>
       </c>
       <c r="L26" t="n">
-        <v>0.89</v>
+        <v>5.98</v>
       </c>
       <c r="M26" t="n">
-        <v>50.7</v>
+        <v>46.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.86</v>
+        <v>-3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>5.98</v>
+        <v>-7.69</v>
       </c>
       <c r="P26" t="n">
-        <v>46.8</v>
+        <v>48.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.9</v>
+        <v>2.08</v>
       </c>
       <c r="R26" t="n">
-        <v>-7.69</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>456.4</v>
+        <v>449.2</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.8</v>
+        <v>-7.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.83</v>
+        <v>-1.58</v>
       </c>
       <c r="G27" t="n">
-        <v>449.2</v>
+        <v>460</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.2</v>
+        <v>10.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.58</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
-        <v>460</v>
+        <v>455.2</v>
       </c>
       <c r="K27" t="n">
-        <v>10.8</v>
+        <v>-4.8</v>
       </c>
       <c r="L27" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="M27" t="n">
+        <v>439</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="P27" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2.4</v>
       </c>
-      <c r="M27" t="n">
-        <v>455.2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="P27" t="n">
-        <v>439</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-16.2</v>
-      </c>
       <c r="R27" t="n">
-        <v>-3.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>132.3</v>
+        <v>131.7</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.6</v>
+        <v>-0.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.06</v>
+        <v>-0.45</v>
       </c>
       <c r="G28" t="n">
-        <v>131.7</v>
+        <v>133.3</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.45</v>
+        <v>1.21</v>
       </c>
       <c r="J28" t="n">
-        <v>133.3</v>
+        <v>131.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
       <c r="M28" t="n">
-        <v>131.9</v>
+        <v>126</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.4</v>
+        <v>-5.9</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.05</v>
+        <v>-4.47</v>
       </c>
       <c r="P28" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5.9</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>-4.47</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>127.9</v>
+        <v>126.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.69</v>
+        <v>-1.09</v>
       </c>
       <c r="G29" t="n">
-        <v>126.5</v>
+        <v>125.9</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.09</v>
+        <v>-0.47</v>
       </c>
       <c r="J29" t="n">
-        <v>125.9</v>
+        <v>127.8</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.6</v>
+        <v>1.9</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.47</v>
+        <v>1.51</v>
       </c>
       <c r="M29" t="n">
-        <v>127.8</v>
+        <v>123.5</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>-4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.51</v>
+        <v>-3.36</v>
       </c>
       <c r="P29" t="n">
-        <v>123.5</v>
+        <v>121.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>-4.3</v>
+        <v>-1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>-3.36</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="30">
@@ -2251,43 +2251,43 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82.7</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-3</v>
+        <v>-0.55</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.5</v>
+        <v>-0.67</v>
       </c>
       <c r="G30" t="n">
-        <v>82.15000000000001</v>
+        <v>83.05</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.55</v>
+        <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.67</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
-        <v>83.05</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.1</v>
+        <v>-0.24</v>
       </c>
       <c r="M30" t="n">
-        <v>82.84999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
       <c r="P30" t="n">
-        <v>82.09999999999999</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>-0.75</v>
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>135.8</v>
+        <v>134.7</v>
       </c>
       <c r="E31" t="n">
-        <v>-5.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>134.7</v>
+        <v>136.7</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="J31" t="n">
-        <v>136.7</v>
+        <v>134.2</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>-1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>134.2</v>
+        <v>126.5</v>
       </c>
       <c r="N31" t="n">
-        <v>-2.5</v>
+        <v>-7.7</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.83</v>
+        <v>-5.74</v>
       </c>
       <c r="P31" t="n">
-        <v>126.5</v>
+        <v>128.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>-7.7</v>
+        <v>1.7</v>
       </c>
       <c r="R31" t="n">
-        <v>-5.74</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>71.15000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.35</v>
+        <v>-2.45</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.49</v>
+        <v>-3.44</v>
       </c>
       <c r="G32" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.45</v>
+        <v>-0.2</v>
       </c>
       <c r="I32" t="n">
-        <v>-3.44</v>
+        <v>-0.29</v>
       </c>
       <c r="J32" t="n">
-        <v>68.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.2</v>
+        <v>6.65</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.29</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>75.15000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="N32" t="n">
-        <v>6.65</v>
+        <v>-0.95</v>
       </c>
       <c r="O32" t="n">
-        <v>9.710000000000001</v>
+        <v>-1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>74.2</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.95</v>
+        <v>5.65</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.26</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>96.45</v>
+        <v>93.8</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.7</v>
+        <v>-2.65</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.73</v>
+        <v>-2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.65</v>
+        <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.75</v>
+        <v>0.11</v>
       </c>
       <c r="J33" t="n">
-        <v>93.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1</v>
+        <v>-3.7</v>
       </c>
       <c r="L33" t="n">
-        <v>0.11</v>
+        <v>-3.94</v>
       </c>
       <c r="M33" t="n">
-        <v>90.2</v>
+        <v>90.55</v>
       </c>
       <c r="N33" t="n">
-        <v>-3.7</v>
+        <v>0.35</v>
       </c>
       <c r="O33" t="n">
-        <v>-3.94</v>
+        <v>0.39</v>
       </c>
       <c r="P33" t="n">
-        <v>90.55</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.39</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>49.34</v>
+        <v>48.68</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.97</v>
+        <v>-1.34</v>
       </c>
       <c r="G34" t="n">
-        <v>48.68</v>
+        <v>48.88</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.66</v>
+        <v>0.2</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.34</v>
+        <v>0.41</v>
       </c>
       <c r="J34" t="n">
-        <v>48.88</v>
+        <v>47.68</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="L34" t="n">
-        <v>0.41</v>
+        <v>-2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>47.68</v>
+        <v>44.98</v>
       </c>
       <c r="N34" t="n">
-        <v>-1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="O34" t="n">
-        <v>-2.45</v>
+        <v>-5.66</v>
       </c>
       <c r="P34" t="n">
-        <v>44.98</v>
+        <v>45.64</v>
       </c>
       <c r="Q34" t="n">
-        <v>-2.7</v>
+        <v>0.66</v>
       </c>
       <c r="R34" t="n">
-        <v>-5.66</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.62</v>
+        <v>-1.86</v>
       </c>
       <c r="G35" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.86</v>
+        <v>0.42</v>
       </c>
       <c r="J35" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="P35" t="n">
         <v>4.76</v>
       </c>
-      <c r="K35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4.67</v>
-      </c>
       <c r="Q35" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="R35" t="n">
-        <v>-2.1</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.37</v>
+        <v>10.17</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.28</v>
+        <v>-0.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.63</v>
+        <v>-1.93</v>
       </c>
       <c r="G36" t="n">
-        <v>10.17</v>
+        <v>10.23</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.93</v>
+        <v>0.59</v>
       </c>
       <c r="J36" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="K36" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="L36" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="M36" t="n">
-        <v>10.24</v>
+        <v>10.03</v>
       </c>
       <c r="N36" t="n">
-        <v>0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1</v>
+        <v>-2.05</v>
       </c>
       <c r="P36" t="n">
-        <v>10.03</v>
+        <v>10.22</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.21</v>
+        <v>0.19</v>
       </c>
       <c r="R36" t="n">
-        <v>-2.05</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>416.4</v>
+        <v>410</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.2</v>
+        <v>-6.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.7</v>
+        <v>-1.54</v>
       </c>
       <c r="G37" t="n">
         <v>410</v>
       </c>
       <c r="H37" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>410</v>
+        <v>411.2</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="M37" t="n">
-        <v>411.2</v>
+        <v>407.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0.29</v>
+        <v>-0.92</v>
       </c>
       <c r="P37" t="n">
-        <v>407.4</v>
+        <v>409.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.8</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.92</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.96</v>
+        <v>15.72</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.09</v>
+        <v>-0.24</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="G38" t="n">
-        <v>15.72</v>
+        <v>15.74</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.24</v>
+        <v>0.02</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5</v>
+        <v>0.13</v>
       </c>
       <c r="J38" t="n">
-        <v>15.74</v>
+        <v>15.25</v>
       </c>
       <c r="K38" t="n">
-        <v>0.02</v>
+        <v>-0.49</v>
       </c>
       <c r="L38" t="n">
-        <v>0.13</v>
+        <v>-3.11</v>
       </c>
       <c r="M38" t="n">
-        <v>15.25</v>
+        <v>15.21</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.49</v>
+        <v>-0.04</v>
       </c>
       <c r="O38" t="n">
-        <v>-3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="P38" t="n">
-        <v>15.21</v>
+        <v>15.14</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>680</v>
+        <v>674.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.87</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>674.5</v>
+        <v>660</v>
       </c>
       <c r="H39" t="n">
-        <v>-5.5</v>
+        <v>-14.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="J39" t="n">
-        <v>660</v>
+        <v>662.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-14.5</v>
+        <v>2.5</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.15</v>
+        <v>0.38</v>
       </c>
       <c r="M39" t="n">
-        <v>662.5</v>
+        <v>673.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="O39" t="n">
-        <v>0.38</v>
+        <v>1.66</v>
       </c>
       <c r="P39" t="n">
-        <v>673.5</v>
+        <v>686</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>61.3</v>
+        <v>60.65</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.95</v>
+        <v>-0.65</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.53</v>
+        <v>-1.06</v>
       </c>
       <c r="G40" t="n">
-        <v>60.65</v>
+        <v>58.5</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.65</v>
+        <v>-2.15</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.06</v>
+        <v>-3.54</v>
       </c>
       <c r="J40" t="n">
-        <v>58.5</v>
+        <v>57.95</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.15</v>
+        <v>-0.55</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.54</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>57.95</v>
+        <v>60.6</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.55</v>
+        <v>2.65</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.9399999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="P40" t="n">
-        <v>60.6</v>
+        <v>62.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>4.57</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>22.93</v>
+        <v>23.04</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.09</v>
+        <v>0.48</v>
       </c>
       <c r="G41" t="n">
-        <v>23.04</v>
+        <v>23.43</v>
       </c>
       <c r="H41" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="I41" t="n">
-        <v>0.48</v>
+        <v>1.69</v>
       </c>
       <c r="J41" t="n">
-        <v>23.43</v>
+        <v>23.24</v>
       </c>
       <c r="K41" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M41" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O41" t="n">
         <v>0.39</v>
       </c>
-      <c r="L41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M41" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="P41" t="n">
-        <v>23.33</v>
+        <v>23.53</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="R41" t="n">
-        <v>0.39</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>60.2</v>
+        <v>60.76</v>
       </c>
       <c r="E42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="G42" t="n">
-        <v>60.76</v>
+        <v>62</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.93</v>
+        <v>2.04</v>
       </c>
       <c r="J42" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="K42" t="n">
-        <v>1.24</v>
+        <v>-0.7</v>
       </c>
       <c r="L42" t="n">
-        <v>2.04</v>
+        <v>-1.13</v>
       </c>
       <c r="M42" t="n">
-        <v>61.3</v>
+        <v>61.75</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.7</v>
+        <v>0.45</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.13</v>
+        <v>0.73</v>
       </c>
       <c r="P42" t="n">
-        <v>61.75</v>
+        <v>62.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="R42" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.3</v>
+        <v>37.29</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="G43" t="n">
-        <v>37.29</v>
+        <v>37.75</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.01</v>
+        <v>0.46</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.03</v>
+        <v>1.23</v>
       </c>
       <c r="J43" t="n">
-        <v>37.75</v>
+        <v>37.59</v>
       </c>
       <c r="K43" t="n">
-        <v>0.46</v>
+        <v>-0.16</v>
       </c>
       <c r="L43" t="n">
-        <v>1.23</v>
+        <v>-0.42</v>
       </c>
       <c r="M43" t="n">
-        <v>37.59</v>
+        <v>37.69</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.42</v>
+        <v>0.27</v>
       </c>
       <c r="P43" t="n">
-        <v>37.69</v>
+        <v>37.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="R43" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.97</v>
+        <v>-0.33</v>
       </c>
       <c r="G44" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.33</v>
+        <v>0.16</v>
       </c>
       <c r="J44" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L44" t="n">
-        <v>0.16</v>
+        <v>0.98</v>
       </c>
       <c r="M44" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="N44" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="O44" t="n">
-        <v>0.98</v>
+        <v>-0.16</v>
       </c>
       <c r="P44" t="n">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.16</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="G45" t="n">
         <v>2.25</v>
       </c>
-      <c r="E45" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.24</v>
-      </c>
       <c r="H45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I45" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K45" t="n">
+      <c r="O45" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.01</v>
       </c>
-      <c r="L45" t="n">
+      <c r="R45" t="n">
         <v>0.45</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="R45" t="n">
-        <v>-0.45</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="M46" t="n">
         <v>3.25</v>
       </c>
-      <c r="E46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.24</v>
-      </c>
       <c r="N46" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.61</v>
+        <v>0.31</v>
       </c>
       <c r="P46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="R46" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.37</v>
+        <v>10.79</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.43</v>
+        <v>4.05</v>
       </c>
       <c r="G47" t="n">
-        <v>10.79</v>
+        <v>11.02</v>
       </c>
       <c r="H47" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="I47" t="n">
-        <v>4.05</v>
+        <v>2.13</v>
       </c>
       <c r="J47" t="n">
-        <v>11.02</v>
+        <v>11.06</v>
       </c>
       <c r="K47" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="L47" t="n">
-        <v>2.13</v>
+        <v>0.36</v>
       </c>
       <c r="M47" t="n">
-        <v>11.06</v>
+        <v>11.11</v>
       </c>
       <c r="N47" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O47" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="P47" t="n">
-        <v>11.11</v>
+        <v>11.27</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="R47" t="n">
-        <v>0.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="48">
@@ -3370,46 +3370,46 @@
         <v>0.335</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>-5.63</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.335</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="M48" t="n">
         <v>0.34</v>
       </c>
-      <c r="K48" t="n">
+      <c r="N48" t="n">
         <v>0.005</v>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>1.49</v>
       </c>
-      <c r="M48" t="n">
+      <c r="P48" t="n">
         <v>0.335</v>
       </c>
-      <c r="N48" t="n">
+      <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="O48" t="n">
+      <c r="R48" t="n">
         <v>-1.47</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.49</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
-        <v>4.87</v>
+        <v>4.98</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="I49" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="J49" t="n">
-        <v>4.98</v>
+        <v>5.02</v>
       </c>
       <c r="K49" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="L49" t="n">
-        <v>2.26</v>
+        <v>0.8</v>
       </c>
       <c r="M49" t="n">
-        <v>5.02</v>
+        <v>4.7</v>
       </c>
       <c r="N49" t="n">
-        <v>0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8</v>
+        <v>-6.37</v>
       </c>
       <c r="P49" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.32</v>
+        <v>-0.11</v>
       </c>
       <c r="R49" t="n">
-        <v>-6.37</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="50">
@@ -3494,37 +3494,37 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F50" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.03</v>
-      </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>-0.97</v>
       </c>
       <c r="M50" t="n">
         <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.02</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.25</v>
+        <v>-1.26</v>
       </c>
       <c r="G51" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.26</v>
+        <v>0.51</v>
       </c>
       <c r="J51" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="K51" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="L51" t="n">
-        <v>0.51</v>
+        <v>-3.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="O51" t="n">
-        <v>-3.3</v>
+        <v>-2.89</v>
       </c>
       <c r="P51" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.89</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.93</v>
+        <v>-2.08</v>
       </c>
       <c r="G52" t="n">
-        <v>10.38</v>
+        <v>10.23</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.08</v>
+        <v>-1.45</v>
       </c>
       <c r="J52" t="n">
-        <v>10.23</v>
+        <v>10.32</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.15</v>
+        <v>0.09</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.45</v>
+        <v>0.88</v>
       </c>
       <c r="M52" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="N52" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="P52" t="n">
-        <v>10.42</v>
+        <v>10.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="R52" t="n">
-        <v>0.97</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="G53" t="n">
-        <v>7.84</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.25</v>
+        <v>4.85</v>
       </c>
       <c r="J53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="K53" t="n">
-        <v>0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="L53" t="n">
-        <v>4.85</v>
+        <v>-1.82</v>
       </c>
       <c r="M53" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.82</v>
+        <v>0.99</v>
       </c>
       <c r="P53" t="n">
-        <v>8.15</v>
+        <v>8.17</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="R53" t="n">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="F54" t="n">
-        <v>2.38</v>
+        <v>3.49</v>
       </c>
       <c r="G54" t="n">
-        <v>0.445</v>
+        <v>0.465</v>
       </c>
       <c r="H54" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="I54" t="n">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
       <c r="J54" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="M54" t="n">
         <v>0.465</v>
       </c>
-      <c r="K54" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L54" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P54" t="n">
         <v>0.46</v>
       </c>
-      <c r="N54" t="n">
+      <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="O54" t="n">
+      <c r="R54" t="n">
         <v>-1.08</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.09</v>
       </c>
     </row>
     <row r="55">
@@ -3801,40 +3801,40 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="E55" t="n">
         <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="G55" t="n">
-        <v>0.59</v>
+        <v>0.585</v>
       </c>
       <c r="H55" t="n">
         <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="J55" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="M55" t="n">
         <v>0.59</v>
       </c>
       <c r="N55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0.59</v>
@@ -3866,10 +3866,10 @@
         <v>0.485</v>
       </c>
       <c r="E56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0.485</v>
@@ -3881,22 +3881,22 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="M56" t="n">
         <v>0.475</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-2.06</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.475</v>
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
       <c r="G57" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="I57" t="n">
-        <v>-2.37</v>
+        <v>-1.62</v>
       </c>
       <c r="J57" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.62</v>
+        <v>2.19</v>
       </c>
       <c r="M57" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="N57" t="n">
-        <v>0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="O57" t="n">
-        <v>2.19</v>
+        <v>-3.22</v>
       </c>
       <c r="P57" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.22</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.08</v>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="F58" t="n">
+      <c r="I58" t="n">
         <v>-1.23</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1.25</v>
-      </c>
       <c r="J58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.08</v>
       </c>
-      <c r="K58" t="n">
+      <c r="N58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="Q58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="L58" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="O58" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.002</v>
-      </c>
       <c r="R58" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.17</v>
+        <v>0.01</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.8</v>
+        <v>0.05</v>
       </c>
       <c r="G59" t="n">
-        <v>21.14</v>
+        <v>21.67</v>
       </c>
       <c r="H59" t="n">
-        <v>0.01</v>
+        <v>0.53</v>
       </c>
       <c r="I59" t="n">
-        <v>0.05</v>
+        <v>2.51</v>
       </c>
       <c r="J59" t="n">
-        <v>21.67</v>
+        <v>21.86</v>
       </c>
       <c r="K59" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="L59" t="n">
-        <v>2.51</v>
+        <v>0.88</v>
       </c>
       <c r="M59" t="n">
-        <v>21.86</v>
+        <v>22.38</v>
       </c>
       <c r="N59" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="O59" t="n">
-        <v>0.88</v>
+        <v>2.38</v>
       </c>
       <c r="P59" t="n">
-        <v>22.38</v>
+        <v>22.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="R59" t="n">
-        <v>2.38</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="60">
@@ -4111,43 +4111,43 @@
         </is>
       </c>
       <c r="D60" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J60" t="n">
         <v>3.15</v>
       </c>
-      <c r="E60" t="n">
+      <c r="K60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F60" t="n">
+      <c r="L60" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G60" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="M60" t="n">
         <v>3.16</v>
       </c>
-      <c r="K60" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="P60" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="Q60" t="n">
         <v>0.01</v>
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-10.32</v>
+        <v>-1.44</v>
       </c>
       <c r="G61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.44</v>
+        <v>-2.19</v>
       </c>
       <c r="J61" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.19</v>
+        <v>1.49</v>
       </c>
       <c r="M61" t="n">
         <v>1.36</v>
       </c>
       <c r="N61" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-18 Close</t>
+          <t>2026-05-19 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change</t>
+          <t>2026-05-19 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-18 Change %</t>
+          <t>2026-05-19 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-19 Close</t>
+          <t>2026-05-20 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change</t>
+          <t>2026-05-20 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change %</t>
+          <t>2026-05-20 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-20 Close</t>
+          <t>2026-05-21 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change</t>
+          <t>2026-05-21 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change %</t>
+          <t>2026-05-21 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-21 Close</t>
+          <t>2026-05-22 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change</t>
+          <t>2026-05-22 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change %</t>
+          <t>2026-05-22 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-22 Close</t>
+          <t>2026-05-25 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change</t>
+          <t>2026-05-25 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change %</t>
+          <t>2026-05-25 Change %</t>
         </is>
       </c>
     </row>
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>138.1</v>
+        <v>140.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3</v>
+        <v>2.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.93</v>
+        <v>1.59</v>
       </c>
       <c r="G3" t="n">
-        <v>140.3</v>
+        <v>138.7</v>
       </c>
       <c r="H3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="J3" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.2</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="J3" t="n">
-        <v>138.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="M3" t="n">
-        <v>141.7</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
       <c r="O3" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="P3" t="n">
         <v>143.9</v>
@@ -639,40 +639,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>196.6</v>
+        <v>201.2</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.71</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>201.2</v>
+        <v>198</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>-3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.34</v>
+        <v>-1.59</v>
       </c>
       <c r="J4" t="n">
-        <v>198</v>
+        <v>200.6</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.2</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.59</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>200.6</v>
+        <v>204</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="P4" t="n">
         <v>204</v>
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G5" t="n">
         <v>6.07</v>
       </c>
-      <c r="E5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.06</v>
-      </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.16</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01</v>
+        <v>-0.19</v>
       </c>
       <c r="L5" t="n">
-        <v>0.17</v>
+        <v>-3.13</v>
       </c>
       <c r="M5" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.13</v>
+        <v>0.68</v>
       </c>
       <c r="P5" t="n">
         <v>5.92</v>
@@ -763,40 +763,40 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M6" t="n">
         <v>6.85</v>
       </c>
-      <c r="E6" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="N6" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.16</v>
+        <v>0.74</v>
       </c>
       <c r="P6" t="n">
         <v>6.85</v>
@@ -825,40 +825,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.19</v>
+        <v>1.15</v>
       </c>
       <c r="G7" t="n">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1.15</v>
+        <v>-0.76</v>
       </c>
       <c r="J7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="M7" t="n">
         <v>5.23</v>
       </c>
-      <c r="K7" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="N7" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.57</v>
+        <v>0.58</v>
       </c>
       <c r="P7" t="n">
         <v>5.23</v>
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.76</v>
+        <v>8.85</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.23</v>
+        <v>1.03</v>
       </c>
       <c r="G8" t="n">
-        <v>8.85</v>
+        <v>8.73</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="I8" t="n">
-        <v>1.03</v>
+        <v>-1.36</v>
       </c>
       <c r="J8" t="n">
-        <v>8.73</v>
+        <v>8.69</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>8.69</v>
+        <v>8.77</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.46</v>
+        <v>0.92</v>
       </c>
       <c r="P8" t="n">
         <v>8.77</v>
@@ -949,34 +949,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.55</v>
+        <v>0.41</v>
       </c>
       <c r="G9" t="n">
-        <v>7.28</v>
+        <v>7.19</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.41</v>
+        <v>-1.24</v>
       </c>
       <c r="J9" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.24</v>
+        <v>-0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="N9" t="n">
         <v>-0.01</v>
@@ -1011,16 +1011,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.58</v>
+        <v>46.34</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.77</v>
+        <v>-0.52</v>
       </c>
       <c r="G10" t="n">
-        <v>46.34</v>
+        <v>46.1</v>
       </c>
       <c r="H10" t="n">
         <v>-0.24</v>
@@ -1029,22 +1029,22 @@
         <v>-0.52</v>
       </c>
       <c r="J10" t="n">
-        <v>46.1</v>
+        <v>46.14</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.24</v>
+        <v>0.04</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.52</v>
+        <v>0.09</v>
       </c>
       <c r="M10" t="n">
-        <v>46.14</v>
+        <v>46.26</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="O10" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="P10" t="n">
         <v>46.26</v>
@@ -1073,40 +1073,40 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G11" t="n">
         <v>4.49</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.22</v>
+        <v>-0.22</v>
       </c>
       <c r="J11" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="K11" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="N11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L11" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="O11" t="n">
-        <v>-1.11</v>
+        <v>-0.23</v>
       </c>
       <c r="P11" t="n">
         <v>4.43</v>
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.99</v>
+        <v>11.12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
       <c r="G12" t="n">
-        <v>11.12</v>
+        <v>11.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
       <c r="J12" t="n">
-        <v>11.2</v>
+        <v>10.94</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="L12" t="n">
-        <v>0.72</v>
+        <v>-2.32</v>
       </c>
       <c r="M12" t="n">
-        <v>10.94</v>
+        <v>10.83</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.26</v>
+        <v>-0.11</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.32</v>
+        <v>-1.01</v>
       </c>
       <c r="P12" t="n">
         <v>10.83</v>
@@ -1197,40 +1197,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.76</v>
+        <v>27.56</v>
       </c>
       <c r="E13" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1.29</v>
+        <v>2.99</v>
       </c>
       <c r="G13" t="n">
-        <v>27.56</v>
+        <v>27.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="I13" t="n">
-        <v>2.99</v>
+        <v>0.87</v>
       </c>
       <c r="J13" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.24</v>
+        <v>-0.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.87</v>
+        <v>-1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>27.3</v>
+        <v>27.44</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8</v>
+        <v>0.51</v>
       </c>
       <c r="P13" t="n">
         <v>27.44</v>
@@ -1259,34 +1259,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="E14" t="n">
         <v>-0.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="G14" t="n">
         <v>2.48</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="N14" t="n">
         <v>-0.01</v>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.82</v>
+        <v>2.51</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3</v>
+        <v>5.22</v>
       </c>
       <c r="H15" t="n">
-        <v>0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.51</v>
+        <v>-1.51</v>
       </c>
       <c r="J15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="M15" t="n">
         <v>5.22</v>
       </c>
-      <c r="K15" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.15</v>
-      </c>
       <c r="N15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
         <v>5.22</v>
@@ -1383,40 +1383,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="F16" t="n">
-        <v>0.39</v>
+        <v>-0.78</v>
       </c>
       <c r="G16" t="n">
-        <v>5.09</v>
+        <v>4.99</v>
       </c>
       <c r="H16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="N16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I16" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="O16" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P16" t="n">
         <v>4.89</v>
@@ -1445,40 +1445,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.95</v>
+        <v>-1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>3.5</v>
@@ -1507,40 +1507,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.13</v>
+        <v>0.29</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="J18" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.86</v>
+        <v>-2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.31</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
         <v>3.43</v>
@@ -1569,40 +1569,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61.85</v>
+        <v>61.4</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.96</v>
+        <v>-0.73</v>
       </c>
       <c r="G19" t="n">
-        <v>61.4</v>
+        <v>61.15</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.45</v>
+        <v>-0.25</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.73</v>
+        <v>-0.41</v>
       </c>
       <c r="J19" t="n">
-        <v>61.15</v>
+        <v>60.8</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.41</v>
+        <v>-0.57</v>
       </c>
       <c r="M19" t="n">
-        <v>60.8</v>
+        <v>60.85</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.35</v>
+        <v>0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.57</v>
+        <v>0.08</v>
       </c>
       <c r="P19" t="n">
         <v>60.85</v>
@@ -1631,40 +1631,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.76</v>
+        <v>29.62</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="F20" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="G20" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="K20" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G20" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="J20" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="L20" t="n">
-        <v>-1.69</v>
+        <v>-1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>28.72</v>
+        <v>28.92</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.37</v>
+        <v>0.7</v>
       </c>
       <c r="P20" t="n">
         <v>28.92</v>
@@ -1693,40 +1693,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="E21" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
       <c r="F21" t="n">
-        <v>6.02</v>
+        <v>0.71</v>
       </c>
       <c r="G21" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="H21" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.71</v>
+        <v>-2.11</v>
       </c>
       <c r="J21" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.11</v>
+        <v>-1.62</v>
       </c>
       <c r="M21" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.62</v>
+        <v>-1.46</v>
       </c>
       <c r="P21" t="n">
         <v>5.39</v>
@@ -1755,40 +1755,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="G22" t="n">
-        <v>86.8</v>
+        <v>86.55</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4</v>
+        <v>-0.25</v>
       </c>
       <c r="I22" t="n">
-        <v>0.46</v>
+        <v>-0.29</v>
       </c>
       <c r="J22" t="n">
-        <v>86.55</v>
+        <v>86.05</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.29</v>
+        <v>-0.58</v>
       </c>
       <c r="M22" t="n">
-        <v>86.05</v>
+        <v>85.5</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5</v>
+        <v>-0.55</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.58</v>
+        <v>-0.64</v>
       </c>
       <c r="P22" t="n">
         <v>85.5</v>
@@ -1817,40 +1817,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.12</v>
+        <v>24.72</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4</v>
+        <v>-1.59</v>
       </c>
       <c r="G23" t="n">
-        <v>24.72</v>
+        <v>24.6</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4</v>
+        <v>-0.12</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.59</v>
+        <v>-0.49</v>
       </c>
       <c r="J23" t="n">
-        <v>24.6</v>
+        <v>23.78</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.12</v>
+        <v>-0.82</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.49</v>
+        <v>-3.33</v>
       </c>
       <c r="M23" t="n">
-        <v>23.78</v>
+        <v>24.48</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.82</v>
+        <v>0.7</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.33</v>
+        <v>2.94</v>
       </c>
       <c r="P23" t="n">
         <v>24.48</v>
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.7</v>
+        <v>28.96</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.26</v>
+        <v>-0.74</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.87</v>
+        <v>-2.49</v>
       </c>
       <c r="G24" t="n">
-        <v>28.96</v>
+        <v>28.6</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.74</v>
+        <v>-0.36</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.49</v>
+        <v>-1.24</v>
       </c>
       <c r="J24" t="n">
-        <v>28.6</v>
+        <v>27.52</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.24</v>
+        <v>-3.78</v>
       </c>
       <c r="M24" t="n">
-        <v>27.52</v>
+        <v>28.3</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.08</v>
+        <v>0.78</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.78</v>
+        <v>2.83</v>
       </c>
       <c r="P24" t="n">
         <v>28.3</v>
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.66</v>
+        <v>30.64</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>30.64</v>
+        <v>30.14</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.02</v>
+        <v>-0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.63</v>
       </c>
       <c r="J25" t="n">
-        <v>30.14</v>
+        <v>29.66</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="M25" t="n">
-        <v>29.66</v>
+        <v>30</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.48</v>
+        <v>0.34</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.59</v>
+        <v>1.15</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47.42</v>
+        <v>47.84</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G26" t="n">
-        <v>47.84</v>
+        <v>50.7</v>
       </c>
       <c r="H26" t="n">
-        <v>0.42</v>
+        <v>2.86</v>
       </c>
       <c r="I26" t="n">
-        <v>0.89</v>
+        <v>5.98</v>
       </c>
       <c r="J26" t="n">
-        <v>50.7</v>
+        <v>46.8</v>
       </c>
       <c r="K26" t="n">
-        <v>2.86</v>
+        <v>-3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>5.98</v>
+        <v>-7.69</v>
       </c>
       <c r="M26" t="n">
-        <v>46.8</v>
+        <v>48.88</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.9</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.69</v>
+        <v>4.44</v>
       </c>
       <c r="P26" t="n">
         <v>48.88</v>
@@ -2065,40 +2065,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>449.2</v>
+        <v>460</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.2</v>
+        <v>10.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.58</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>460</v>
+        <v>455.2</v>
       </c>
       <c r="H27" t="n">
-        <v>10.8</v>
+        <v>-4.8</v>
       </c>
       <c r="I27" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="J27" t="n">
+        <v>439</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="M27" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="N27" t="n">
         <v>2.4</v>
       </c>
-      <c r="J27" t="n">
-        <v>455.2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="M27" t="n">
-        <v>439</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-16.2</v>
-      </c>
       <c r="O27" t="n">
-        <v>-3.56</v>
+        <v>0.55</v>
       </c>
       <c r="P27" t="n">
         <v>441.4</v>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>131.7</v>
+        <v>133.3</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.45</v>
+        <v>1.21</v>
       </c>
       <c r="G28" t="n">
-        <v>133.3</v>
+        <v>131.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
       <c r="J28" t="n">
-        <v>131.9</v>
+        <v>126</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.4</v>
+        <v>-5.9</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.05</v>
+        <v>-4.47</v>
       </c>
       <c r="M28" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.9</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>-4.47</v>
+        <v>0.79</v>
       </c>
       <c r="P28" t="n">
         <v>127</v>
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>126.5</v>
+        <v>125.9</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.09</v>
+        <v>-0.47</v>
       </c>
       <c r="G29" t="n">
-        <v>125.9</v>
+        <v>127.8</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6</v>
+        <v>1.9</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.47</v>
+        <v>1.51</v>
       </c>
       <c r="J29" t="n">
-        <v>127.8</v>
+        <v>123.5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.9</v>
+        <v>-4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.51</v>
+        <v>-3.36</v>
       </c>
       <c r="M29" t="n">
-        <v>123.5</v>
+        <v>121.7</v>
       </c>
       <c r="N29" t="n">
-        <v>-4.3</v>
+        <v>-1.8</v>
       </c>
       <c r="O29" t="n">
-        <v>-3.36</v>
+        <v>-1.46</v>
       </c>
       <c r="P29" t="n">
         <v>121.7</v>
@@ -2251,34 +2251,34 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82.15000000000001</v>
+        <v>83.05</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.55</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.67</v>
+        <v>1.1</v>
       </c>
       <c r="G30" t="n">
-        <v>83.05</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>-0.24</v>
       </c>
       <c r="J30" t="n">
-        <v>82.84999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
       <c r="M30" t="n">
-        <v>82.09999999999999</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>-0.75</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>134.7</v>
+        <v>136.7</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G31" t="n">
-        <v>136.7</v>
+        <v>134.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>1.48</v>
+        <v>-1.83</v>
       </c>
       <c r="J31" t="n">
-        <v>134.2</v>
+        <v>126.5</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.5</v>
+        <v>-7.7</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.83</v>
+        <v>-5.74</v>
       </c>
       <c r="M31" t="n">
-        <v>126.5</v>
+        <v>128.2</v>
       </c>
       <c r="N31" t="n">
-        <v>-7.7</v>
+        <v>1.7</v>
       </c>
       <c r="O31" t="n">
-        <v>-5.74</v>
+        <v>1.34</v>
       </c>
       <c r="P31" t="n">
         <v>128.2</v>
@@ -2375,40 +2375,40 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.45</v>
+        <v>-0.2</v>
       </c>
       <c r="F32" t="n">
-        <v>-3.44</v>
+        <v>-0.29</v>
       </c>
       <c r="G32" t="n">
-        <v>68.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2</v>
+        <v>6.65</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.29</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>75.15000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K32" t="n">
-        <v>6.65</v>
+        <v>-0.95</v>
       </c>
       <c r="L32" t="n">
-        <v>9.710000000000001</v>
+        <v>-1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>74.2</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.95</v>
+        <v>5.65</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.26</v>
+        <v>7.61</v>
       </c>
       <c r="P32" t="n">
         <v>79.84999999999999</v>
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.65</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.75</v>
+        <v>0.11</v>
       </c>
       <c r="G33" t="n">
-        <v>93.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>-3.7</v>
       </c>
       <c r="I33" t="n">
-        <v>0.11</v>
+        <v>-3.94</v>
       </c>
       <c r="J33" t="n">
-        <v>90.2</v>
+        <v>90.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.7</v>
+        <v>0.35</v>
       </c>
       <c r="L33" t="n">
-        <v>-3.94</v>
+        <v>0.39</v>
       </c>
       <c r="M33" t="n">
-        <v>90.55</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="O33" t="n">
-        <v>0.39</v>
+        <v>1.16</v>
       </c>
       <c r="P33" t="n">
         <v>91.59999999999999</v>
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>48.68</v>
+        <v>48.88</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.66</v>
+        <v>0.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.34</v>
+        <v>0.41</v>
       </c>
       <c r="G34" t="n">
-        <v>48.88</v>
+        <v>47.68</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.41</v>
+        <v>-2.45</v>
       </c>
       <c r="J34" t="n">
-        <v>47.68</v>
+        <v>44.98</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.45</v>
+        <v>-5.66</v>
       </c>
       <c r="M34" t="n">
-        <v>44.98</v>
+        <v>45.64</v>
       </c>
       <c r="N34" t="n">
-        <v>-2.7</v>
+        <v>0.66</v>
       </c>
       <c r="O34" t="n">
-        <v>-5.66</v>
+        <v>1.47</v>
       </c>
       <c r="P34" t="n">
         <v>45.64</v>
@@ -2561,40 +2561,40 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.86</v>
+        <v>0.42</v>
       </c>
       <c r="G35" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="M35" t="n">
         <v>4.76</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.67</v>
-      </c>
       <c r="N35" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O35" t="n">
-        <v>-2.1</v>
+        <v>1.93</v>
       </c>
       <c r="P35" t="n">
         <v>4.76</v>
@@ -2623,40 +2623,40 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.17</v>
+        <v>10.23</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.93</v>
+        <v>0.59</v>
       </c>
       <c r="G36" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="H36" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I36" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
-        <v>10.24</v>
+        <v>10.03</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1</v>
+        <v>-2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>10.03</v>
+        <v>10.22</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.21</v>
+        <v>0.19</v>
       </c>
       <c r="O36" t="n">
-        <v>-2.05</v>
+        <v>1.89</v>
       </c>
       <c r="P36" t="n">
         <v>10.22</v>
@@ -2688,37 +2688,37 @@
         <v>410</v>
       </c>
       <c r="E37" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>410</v>
+        <v>411.2</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="J37" t="n">
-        <v>411.2</v>
+        <v>407.4</v>
       </c>
       <c r="K37" t="n">
-        <v>1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="L37" t="n">
-        <v>0.29</v>
+        <v>-0.92</v>
       </c>
       <c r="M37" t="n">
-        <v>407.4</v>
+        <v>409.2</v>
       </c>
       <c r="N37" t="n">
-        <v>-3.8</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.92</v>
+        <v>0.44</v>
       </c>
       <c r="P37" t="n">
         <v>409.2</v>
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.72</v>
+        <v>15.74</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.24</v>
+        <v>0.02</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5</v>
+        <v>0.13</v>
       </c>
       <c r="G38" t="n">
-        <v>15.74</v>
+        <v>15.25</v>
       </c>
       <c r="H38" t="n">
-        <v>0.02</v>
+        <v>-0.49</v>
       </c>
       <c r="I38" t="n">
-        <v>0.13</v>
+        <v>-3.11</v>
       </c>
       <c r="J38" t="n">
-        <v>15.25</v>
+        <v>15.21</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.49</v>
+        <v>-0.04</v>
       </c>
       <c r="L38" t="n">
-        <v>-3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="M38" t="n">
-        <v>15.21</v>
+        <v>15.14</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
       <c r="P38" t="n">
         <v>15.14</v>
@@ -2809,40 +2809,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>674.5</v>
+        <v>660</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.5</v>
+        <v>-14.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="G39" t="n">
-        <v>660</v>
+        <v>662.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-14.5</v>
+        <v>2.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.15</v>
+        <v>0.38</v>
       </c>
       <c r="J39" t="n">
-        <v>662.5</v>
+        <v>673.5</v>
       </c>
       <c r="K39" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="L39" t="n">
-        <v>0.38</v>
+        <v>1.66</v>
       </c>
       <c r="M39" t="n">
-        <v>673.5</v>
+        <v>686</v>
       </c>
       <c r="N39" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="P39" t="n">
         <v>686</v>
@@ -2871,40 +2871,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>60.65</v>
+        <v>58.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.65</v>
+        <v>-2.15</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.06</v>
+        <v>-3.54</v>
       </c>
       <c r="G40" t="n">
-        <v>58.5</v>
+        <v>57.95</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.15</v>
+        <v>-0.55</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.54</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>57.95</v>
+        <v>60.6</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.55</v>
+        <v>2.65</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.9399999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="M40" t="n">
-        <v>60.6</v>
+        <v>62.6</v>
       </c>
       <c r="N40" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>4.57</v>
+        <v>3.3</v>
       </c>
       <c r="P40" t="n">
         <v>62.6</v>
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.04</v>
+        <v>23.43</v>
       </c>
       <c r="E41" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="F41" t="n">
-        <v>0.48</v>
+        <v>1.69</v>
       </c>
       <c r="G41" t="n">
-        <v>23.43</v>
+        <v>23.24</v>
       </c>
       <c r="H41" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="J41" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L41" t="n">
         <v>0.39</v>
       </c>
-      <c r="I41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J41" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="K41" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="L41" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="M41" t="n">
-        <v>23.33</v>
+        <v>23.53</v>
       </c>
       <c r="N41" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="O41" t="n">
-        <v>0.39</v>
+        <v>0.86</v>
       </c>
       <c r="P41" t="n">
-        <v>23.53</v>
+        <v>23.51</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="R41" t="n">
-        <v>0.86</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>60.76</v>
+        <v>62</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="F42" t="n">
-        <v>0.93</v>
+        <v>2.04</v>
       </c>
       <c r="G42" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="H42" t="n">
-        <v>1.24</v>
+        <v>-0.7</v>
       </c>
       <c r="I42" t="n">
-        <v>2.04</v>
+        <v>-1.13</v>
       </c>
       <c r="J42" t="n">
-        <v>61.3</v>
+        <v>61.75</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.7</v>
+        <v>0.45</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.13</v>
+        <v>0.73</v>
       </c>
       <c r="M42" t="n">
-        <v>61.75</v>
+        <v>62.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="O42" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="P42" t="n">
-        <v>62.1</v>
+        <v>62.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="R42" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.29</v>
+        <v>37.75</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.01</v>
+        <v>0.46</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.03</v>
+        <v>1.23</v>
       </c>
       <c r="G43" t="n">
-        <v>37.75</v>
+        <v>37.59</v>
       </c>
       <c r="H43" t="n">
-        <v>0.46</v>
+        <v>-0.16</v>
       </c>
       <c r="I43" t="n">
-        <v>1.23</v>
+        <v>-0.42</v>
       </c>
       <c r="J43" t="n">
-        <v>37.59</v>
+        <v>37.69</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.42</v>
+        <v>0.27</v>
       </c>
       <c r="M43" t="n">
-        <v>37.69</v>
+        <v>37.7</v>
       </c>
       <c r="N43" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="O43" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="P43" t="n">
-        <v>37.7</v>
+        <v>37.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="R43" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.33</v>
+        <v>0.16</v>
       </c>
       <c r="G44" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="H44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="Q44" t="n">
         <v>0.01</v>
       </c>
-      <c r="I44" t="n">
+      <c r="R44" t="n">
         <v>0.16</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O44" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="P44" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.65</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="E45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="L45" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N45" t="n">
         <v>0.01</v>
       </c>
-      <c r="I45" t="n">
+      <c r="O45" t="n">
         <v>0.45</v>
       </c>
-      <c r="J45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="K45" t="n">
+      <c r="P45" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q45" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L45" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R45" t="n">
-        <v>0.45</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.23</v>
+        <v>1.56</v>
       </c>
       <c r="G46" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="I46" t="n">
-        <v>1.56</v>
+        <v>-0.61</v>
       </c>
       <c r="J46" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.61</v>
+        <v>0.31</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="O46" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="P46" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="R46" t="n">
-        <v>0.92</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.79</v>
+        <v>11.02</v>
       </c>
       <c r="E47" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="F47" t="n">
-        <v>4.05</v>
+        <v>2.13</v>
       </c>
       <c r="G47" t="n">
-        <v>11.02</v>
+        <v>11.06</v>
       </c>
       <c r="H47" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="I47" t="n">
-        <v>2.13</v>
+        <v>0.36</v>
       </c>
       <c r="J47" t="n">
-        <v>11.06</v>
+        <v>11.11</v>
       </c>
       <c r="K47" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L47" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="M47" t="n">
-        <v>11.11</v>
+        <v>11.27</v>
       </c>
       <c r="N47" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="O47" t="n">
-        <v>0.45</v>
+        <v>1.44</v>
       </c>
       <c r="P47" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.335</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.34</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
         <v>1.49</v>
       </c>
-      <c r="J48" t="n">
+      <c r="M48" t="n">
         <v>0.335</v>
       </c>
-      <c r="K48" t="n">
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>-1.47</v>
       </c>
-      <c r="M48" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1.49</v>
-      </c>
       <c r="P48" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.87</v>
+        <v>4.98</v>
       </c>
       <c r="E49" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G49" t="n">
-        <v>4.98</v>
+        <v>5.02</v>
       </c>
       <c r="H49" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="I49" t="n">
-        <v>2.26</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
-        <v>5.02</v>
+        <v>4.7</v>
       </c>
       <c r="K49" t="n">
-        <v>0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="L49" t="n">
-        <v>0.8</v>
+        <v>-6.37</v>
       </c>
       <c r="M49" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.32</v>
+        <v>-0.11</v>
       </c>
       <c r="O49" t="n">
-        <v>-6.37</v>
+        <v>-2.34</v>
       </c>
       <c r="P49" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="R49" t="n">
-        <v>-2.34</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="50">
@@ -3491,31 +3491,31 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H50" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>-0.97</v>
       </c>
       <c r="J50" t="n">
         <v>1.02</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>1.02</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.26</v>
+        <v>0.51</v>
       </c>
       <c r="G51" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="I51" t="n">
-        <v>0.51</v>
+        <v>-3.3</v>
       </c>
       <c r="J51" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="L51" t="n">
-        <v>-3.3</v>
+        <v>-2.89</v>
       </c>
       <c r="M51" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.89</v>
+        <v>2.16</v>
       </c>
       <c r="P51" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="R51" t="n">
-        <v>2.16</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.38</v>
+        <v>10.23</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.08</v>
+        <v>-1.45</v>
       </c>
       <c r="G52" t="n">
-        <v>10.23</v>
+        <v>10.32</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.15</v>
+        <v>0.09</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.45</v>
+        <v>0.88</v>
       </c>
       <c r="J52" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="K52" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="M52" t="n">
-        <v>10.42</v>
+        <v>10.91</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="O52" t="n">
-        <v>0.97</v>
+        <v>4.7</v>
       </c>
       <c r="P52" t="n">
-        <v>10.91</v>
+        <v>11.07</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="R52" t="n">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.84</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.25</v>
+        <v>4.85</v>
       </c>
       <c r="G53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="H53" t="n">
-        <v>0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="I53" t="n">
-        <v>4.85</v>
+        <v>-1.82</v>
       </c>
       <c r="J53" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.82</v>
+        <v>0.99</v>
       </c>
       <c r="M53" t="n">
-        <v>8.15</v>
+        <v>8.17</v>
       </c>
       <c r="N53" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="O53" t="n">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
       <c r="P53" t="n">
-        <v>8.17</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="R53" t="n">
-        <v>0.25</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.445</v>
+        <v>0.465</v>
       </c>
       <c r="E54" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="F54" t="n">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
       <c r="G54" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.465</v>
       </c>
-      <c r="H54" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M54" t="n">
         <v>0.46</v>
       </c>
-      <c r="K54" t="n">
+      <c r="N54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L54" t="n">
+      <c r="O54" t="n">
         <v>-1.08</v>
       </c>
-      <c r="M54" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.09</v>
-      </c>
       <c r="P54" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="55">
@@ -3801,31 +3801,31 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.59</v>
+        <v>0.585</v>
       </c>
       <c r="E55" t="n">
         <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="G55" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="J55" t="n">
         <v>0.59</v>
       </c>
       <c r="K55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.59</v>
@@ -3872,22 +3872,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="J56" t="n">
         <v>0.475</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.06</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0.475</v>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.37</v>
+        <v>-1.62</v>
       </c>
       <c r="G57" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.62</v>
+        <v>2.19</v>
       </c>
       <c r="J57" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="K57" t="n">
-        <v>0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="L57" t="n">
-        <v>2.19</v>
+        <v>-3.22</v>
       </c>
       <c r="M57" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="O57" t="n">
-        <v>-3.22</v>
+        <v>-0.55</v>
       </c>
       <c r="P57" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.55</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>1.25</v>
+        <v>-1.23</v>
       </c>
       <c r="G58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.08</v>
       </c>
-      <c r="H58" t="n">
+      <c r="K58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="N58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="I58" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="K58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.002</v>
-      </c>
       <c r="O58" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
       <c r="P58" t="n">
         <v>0.079</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.14</v>
+        <v>21.67</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01</v>
+        <v>0.53</v>
       </c>
       <c r="F59" t="n">
-        <v>0.05</v>
+        <v>2.51</v>
       </c>
       <c r="G59" t="n">
-        <v>21.67</v>
+        <v>21.86</v>
       </c>
       <c r="H59" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="I59" t="n">
-        <v>2.51</v>
+        <v>0.88</v>
       </c>
       <c r="J59" t="n">
-        <v>21.86</v>
+        <v>22.38</v>
       </c>
       <c r="K59" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="L59" t="n">
-        <v>0.88</v>
+        <v>2.38</v>
       </c>
       <c r="M59" t="n">
-        <v>22.38</v>
+        <v>22.4</v>
       </c>
       <c r="N59" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="O59" t="n">
-        <v>2.38</v>
+        <v>0.09</v>
       </c>
       <c r="P59" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="R59" t="n">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="60">
@@ -4111,34 +4111,34 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.27</v>
+        <v>1.61</v>
       </c>
       <c r="G60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="J60" t="n">
         <v>3.16</v>
       </c>
-      <c r="H60" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="M60" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="N60" t="n">
         <v>0.01</v>
@@ -4147,13 +4147,13 @@
         <v>0.32</v>
       </c>
       <c r="P60" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="R60" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.44</v>
+        <v>-2.19</v>
       </c>
       <c r="G61" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.19</v>
+        <v>1.49</v>
       </c>
       <c r="J61" t="n">
         <v>1.36</v>
       </c>
       <c r="K61" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="P61" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.74</v>
+        <v>5.19</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-19 Close</t>
+          <t>2026-05-20 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change</t>
+          <t>2026-05-20 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-19 Change %</t>
+          <t>2026-05-20 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-20 Close</t>
+          <t>2026-05-21 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change</t>
+          <t>2026-05-21 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change %</t>
+          <t>2026-05-21 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-21 Close</t>
+          <t>2026-05-22 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change</t>
+          <t>2026-05-22 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change %</t>
+          <t>2026-05-22 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-22 Close</t>
+          <t>2026-05-25 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change</t>
+          <t>2026-05-25 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change %</t>
+          <t>2026-05-25 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-25 Close</t>
+          <t>2026-05-26 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change</t>
+          <t>2026-05-26 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change %</t>
+          <t>2026-05-26 Change %</t>
         </is>
       </c>
     </row>
@@ -577,31 +577,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>140.3</v>
+        <v>138.7</v>
       </c>
       <c r="E3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J3" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="K3" t="n">
         <v>2.2</v>
       </c>
-      <c r="F3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G3" t="n">
-        <v>138.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="J3" t="n">
-        <v>141.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
         <v>143.9</v>
@@ -613,13 +613,13 @@
         <v>1.55</v>
       </c>
       <c r="P3" t="n">
-        <v>143.9</v>
+        <v>145.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="4">
@@ -639,31 +639,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>201.2</v>
+        <v>198</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6</v>
+        <v>-3.2</v>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>-1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>198</v>
+        <v>200.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.2</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.59</v>
+        <v>1.31</v>
       </c>
       <c r="J4" t="n">
-        <v>200.6</v>
+        <v>204</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="M4" t="n">
         <v>204</v>
@@ -675,13 +675,13 @@
         <v>1.69</v>
       </c>
       <c r="P4" t="n">
-        <v>204</v>
+        <v>207.4</v>
       </c>
       <c r="Q4" t="n">
         <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="5">
@@ -701,31 +701,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.06</v>
+        <v>6.07</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.16</v>
+        <v>0.17</v>
       </c>
       <c r="G5" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>-0.19</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>-3.13</v>
       </c>
       <c r="J5" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.13</v>
+        <v>0.68</v>
       </c>
       <c r="M5" t="n">
         <v>5.92</v>
@@ -737,13 +737,13 @@
         <v>0.68</v>
       </c>
       <c r="P5" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0.68</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="6">
@@ -763,31 +763,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.93</v>
+        <v>6.88</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.17</v>
+        <v>-0.72</v>
       </c>
       <c r="G6" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.72</v>
+        <v>-1.16</v>
       </c>
       <c r="J6" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.16</v>
+        <v>0.74</v>
       </c>
       <c r="M6" t="n">
         <v>6.85</v>
@@ -799,13 +799,13 @@
         <v>0.74</v>
       </c>
       <c r="P6" t="n">
-        <v>6.85</v>
+        <v>6.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.74</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="7">
@@ -825,31 +825,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>1.15</v>
+        <v>-0.76</v>
       </c>
       <c r="G7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="J7" t="n">
         <v>5.23</v>
       </c>
-      <c r="H7" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="K7" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.57</v>
+        <v>0.58</v>
       </c>
       <c r="M7" t="n">
         <v>5.23</v>
@@ -861,13 +861,13 @@
         <v>0.58</v>
       </c>
       <c r="P7" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="R7" t="n">
-        <v>0.58</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="8">
@@ -887,31 +887,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.85</v>
+        <v>8.73</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1.03</v>
+        <v>-1.36</v>
       </c>
       <c r="G8" t="n">
-        <v>8.73</v>
+        <v>8.69</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="J8" t="n">
-        <v>8.69</v>
+        <v>8.77</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.46</v>
+        <v>0.92</v>
       </c>
       <c r="M8" t="n">
         <v>8.77</v>
@@ -923,13 +923,13 @@
         <v>0.92</v>
       </c>
       <c r="P8" t="n">
-        <v>8.77</v>
+        <v>8.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="R8" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="9">
@@ -949,25 +949,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.28</v>
+        <v>7.19</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>0.41</v>
+        <v>-1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.24</v>
+        <v>-0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="K9" t="n">
         <v>-0.01</v>
@@ -988,10 +988,10 @@
         <v>7.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.34</v>
+        <v>46.1</v>
       </c>
       <c r="E10" t="n">
         <v>-0.24</v>
@@ -1020,22 +1020,22 @@
         <v>-0.52</v>
       </c>
       <c r="G10" t="n">
-        <v>46.1</v>
+        <v>46.14</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.24</v>
+        <v>0.04</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.52</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>46.14</v>
+        <v>46.26</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="M10" t="n">
         <v>46.26</v>
@@ -1047,13 +1047,13 @@
         <v>0.26</v>
       </c>
       <c r="P10" t="n">
-        <v>46.26</v>
+        <v>45.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.12</v>
+        <v>-0.28</v>
       </c>
       <c r="R10" t="n">
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="11">
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>0.22</v>
+        <v>-0.22</v>
       </c>
       <c r="G11" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="H11" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="K11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I11" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="L11" t="n">
-        <v>-1.11</v>
+        <v>-0.23</v>
       </c>
       <c r="M11" t="n">
         <v>4.43</v>
@@ -1109,7 +1109,7 @@
         <v>-0.23</v>
       </c>
       <c r="P11" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.01</v>
@@ -1135,31 +1135,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.12</v>
+        <v>11.2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2</v>
+        <v>10.94</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.72</v>
+        <v>-2.32</v>
       </c>
       <c r="J12" t="n">
-        <v>10.94</v>
+        <v>10.83</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.26</v>
+        <v>-0.11</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.32</v>
+        <v>-1.01</v>
       </c>
       <c r="M12" t="n">
         <v>10.83</v>
@@ -1171,13 +1171,13 @@
         <v>-1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>10.83</v>
+        <v>10.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.01</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="13">
@@ -1197,31 +1197,31 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.56</v>
+        <v>27.8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="F13" t="n">
-        <v>2.99</v>
+        <v>0.87</v>
       </c>
       <c r="G13" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.24</v>
+        <v>-0.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.87</v>
+        <v>-1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>27.3</v>
+        <v>27.44</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.8</v>
+        <v>0.51</v>
       </c>
       <c r="M13" t="n">
         <v>27.44</v>
@@ -1233,13 +1233,13 @@
         <v>0.51</v>
       </c>
       <c r="P13" t="n">
-        <v>27.44</v>
+        <v>26.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.14</v>
+        <v>-0.52</v>
       </c>
       <c r="R13" t="n">
-        <v>0.51</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="14">
@@ -1262,22 +1262,22 @@
         <v>2.48</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="K14" t="n">
         <v>-0.01</v>
@@ -1295,13 +1295,13 @@
         <v>-0.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.4</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="15">
@@ -1321,31 +1321,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.3</v>
+        <v>5.22</v>
       </c>
       <c r="E15" t="n">
-        <v>0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>2.51</v>
+        <v>-1.51</v>
       </c>
       <c r="G15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="J15" t="n">
         <v>5.22</v>
       </c>
-      <c r="H15" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.15</v>
-      </c>
       <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>5.22</v>
@@ -1357,13 +1357,13 @@
         <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>5.22</v>
+        <v>5.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="16">
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.09</v>
+        <v>4.99</v>
       </c>
       <c r="E16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="K16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F16" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="L16" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>4.89</v>
@@ -1419,13 +1419,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="17">
@@ -1445,31 +1445,31 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
@@ -1481,13 +1481,13 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F18" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="G18" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.86</v>
+        <v>-2.31</v>
       </c>
       <c r="J18" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.31</v>
+        <v>1.18</v>
       </c>
       <c r="M18" t="n">
         <v>3.43</v>
@@ -1546,10 +1546,10 @@
         <v>3.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1569,31 +1569,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61.4</v>
+        <v>61.15</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.45</v>
+        <v>-0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.73</v>
+        <v>-0.41</v>
       </c>
       <c r="G19" t="n">
-        <v>61.15</v>
+        <v>60.8</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.41</v>
+        <v>-0.57</v>
       </c>
       <c r="J19" t="n">
-        <v>60.8</v>
+        <v>60.85</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.35</v>
+        <v>0.05</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.57</v>
+        <v>0.08</v>
       </c>
       <c r="M19" t="n">
         <v>60.85</v>
@@ -1605,13 +1605,13 @@
         <v>0.08</v>
       </c>
       <c r="P19" t="n">
-        <v>60.85</v>
+        <v>60.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0.08</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="20">
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.62</v>
+        <v>29.12</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.47</v>
+        <v>-1.69</v>
       </c>
       <c r="G20" t="n">
-        <v>29.12</v>
+        <v>28.72</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.69</v>
+        <v>-1.37</v>
       </c>
       <c r="J20" t="n">
-        <v>28.72</v>
+        <v>28.92</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.37</v>
+        <v>0.7</v>
       </c>
       <c r="M20" t="n">
         <v>28.92</v>
@@ -1667,13 +1667,13 @@
         <v>0.7</v>
       </c>
       <c r="P20" t="n">
-        <v>28.92</v>
+        <v>29.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="21">
@@ -1693,31 +1693,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="F21" t="n">
-        <v>0.71</v>
+        <v>-2.11</v>
       </c>
       <c r="G21" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.11</v>
+        <v>-1.62</v>
       </c>
       <c r="J21" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.62</v>
+        <v>-1.46</v>
       </c>
       <c r="M21" t="n">
         <v>5.39</v>
@@ -1729,13 +1729,13 @@
         <v>-1.46</v>
       </c>
       <c r="P21" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.46</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="22">
@@ -1755,31 +1755,31 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.8</v>
+        <v>86.55</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4</v>
+        <v>-0.25</v>
       </c>
       <c r="F22" t="n">
-        <v>0.46</v>
+        <v>-0.29</v>
       </c>
       <c r="G22" t="n">
-        <v>86.55</v>
+        <v>86.05</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.29</v>
+        <v>-0.58</v>
       </c>
       <c r="J22" t="n">
-        <v>86.05</v>
+        <v>85.5</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5</v>
+        <v>-0.55</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.58</v>
+        <v>-0.64</v>
       </c>
       <c r="M22" t="n">
         <v>85.5</v>
@@ -1791,13 +1791,13 @@
         <v>-0.64</v>
       </c>
       <c r="P22" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.64</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="23">
@@ -1817,31 +1817,31 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.72</v>
+        <v>24.6</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4</v>
+        <v>-0.12</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.59</v>
+        <v>-0.49</v>
       </c>
       <c r="G23" t="n">
-        <v>24.6</v>
+        <v>23.78</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.12</v>
+        <v>-0.82</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.49</v>
+        <v>-3.33</v>
       </c>
       <c r="J23" t="n">
-        <v>23.78</v>
+        <v>24.48</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.82</v>
+        <v>0.7</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.33</v>
+        <v>2.94</v>
       </c>
       <c r="M23" t="n">
         <v>24.48</v>
@@ -1853,13 +1853,13 @@
         <v>2.94</v>
       </c>
       <c r="P23" t="n">
-        <v>24.48</v>
+        <v>24.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="R23" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24">
@@ -1879,31 +1879,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.96</v>
+        <v>28.6</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.74</v>
+        <v>-0.36</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.49</v>
+        <v>-1.24</v>
       </c>
       <c r="G24" t="n">
-        <v>28.6</v>
+        <v>27.52</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.24</v>
+        <v>-3.78</v>
       </c>
       <c r="J24" t="n">
-        <v>27.52</v>
+        <v>28.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.08</v>
+        <v>0.78</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.78</v>
+        <v>2.83</v>
       </c>
       <c r="M24" t="n">
         <v>28.3</v>
@@ -1915,13 +1915,13 @@
         <v>2.83</v>
       </c>
       <c r="P24" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="25">
@@ -1941,31 +1941,31 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.64</v>
+        <v>30.14</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.02</v>
+        <v>-0.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.63</v>
       </c>
       <c r="G25" t="n">
-        <v>30.14</v>
+        <v>29.66</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="J25" t="n">
-        <v>29.66</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.48</v>
+        <v>0.34</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.59</v>
+        <v>1.15</v>
       </c>
       <c r="M25" t="n">
         <v>30</v>
@@ -1977,13 +1977,13 @@
         <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>30</v>
+        <v>29.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="26">
@@ -2003,31 +2003,31 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>47.84</v>
+        <v>50.7</v>
       </c>
       <c r="E26" t="n">
-        <v>0.42</v>
+        <v>2.86</v>
       </c>
       <c r="F26" t="n">
-        <v>0.89</v>
+        <v>5.98</v>
       </c>
       <c r="G26" t="n">
-        <v>50.7</v>
+        <v>46.8</v>
       </c>
       <c r="H26" t="n">
-        <v>2.86</v>
+        <v>-3.9</v>
       </c>
       <c r="I26" t="n">
-        <v>5.98</v>
+        <v>-7.69</v>
       </c>
       <c r="J26" t="n">
-        <v>46.8</v>
+        <v>48.88</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.9</v>
+        <v>2.08</v>
       </c>
       <c r="L26" t="n">
-        <v>-7.69</v>
+        <v>4.44</v>
       </c>
       <c r="M26" t="n">
         <v>48.88</v>
@@ -2039,13 +2039,13 @@
         <v>4.44</v>
       </c>
       <c r="P26" t="n">
-        <v>48.88</v>
+        <v>51.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="R26" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="27">
@@ -2065,31 +2065,31 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>460</v>
+        <v>455.2</v>
       </c>
       <c r="E27" t="n">
-        <v>10.8</v>
+        <v>-4.8</v>
       </c>
       <c r="F27" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="G27" t="n">
+        <v>439</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="J27" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="K27" t="n">
         <v>2.4</v>
       </c>
-      <c r="G27" t="n">
-        <v>455.2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="J27" t="n">
-        <v>439</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-16.2</v>
-      </c>
       <c r="L27" t="n">
-        <v>-3.56</v>
+        <v>0.55</v>
       </c>
       <c r="M27" t="n">
         <v>441.4</v>
@@ -2101,13 +2101,13 @@
         <v>0.55</v>
       </c>
       <c r="P27" t="n">
-        <v>441.4</v>
+        <v>439</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="28">
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>133.3</v>
+        <v>131.9</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="F28" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
       <c r="G28" t="n">
-        <v>131.9</v>
+        <v>126</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.4</v>
+        <v>-5.9</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.05</v>
+        <v>-4.47</v>
       </c>
       <c r="J28" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.9</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>-4.47</v>
+        <v>0.79</v>
       </c>
       <c r="M28" t="n">
         <v>127</v>
@@ -2163,13 +2163,13 @@
         <v>0.79</v>
       </c>
       <c r="P28" t="n">
-        <v>127</v>
+        <v>127.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="29">
@@ -2189,31 +2189,31 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>125.9</v>
+        <v>127.8</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6</v>
+        <v>1.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.47</v>
+        <v>1.51</v>
       </c>
       <c r="G29" t="n">
-        <v>127.8</v>
+        <v>123.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.9</v>
+        <v>-4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1.51</v>
+        <v>-3.36</v>
       </c>
       <c r="J29" t="n">
-        <v>123.5</v>
+        <v>121.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.3</v>
+        <v>-1.8</v>
       </c>
       <c r="L29" t="n">
-        <v>-3.36</v>
+        <v>-1.46</v>
       </c>
       <c r="M29" t="n">
         <v>121.7</v>
@@ -2225,13 +2225,13 @@
         <v>-1.46</v>
       </c>
       <c r="P29" t="n">
-        <v>121.7</v>
+        <v>118.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.46</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="30">
@@ -2251,25 +2251,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>83.05</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1</v>
+        <v>-0.24</v>
       </c>
       <c r="G30" t="n">
-        <v>82.84999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
       <c r="J30" t="n">
-        <v>82.09999999999999</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>-0.75</v>
@@ -2287,13 +2287,13 @@
         <v>-0.91</v>
       </c>
       <c r="P30" t="n">
-        <v>81.34999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.75</v>
+        <v>-2.55</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.91</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="31">
@@ -2313,31 +2313,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>136.7</v>
+        <v>134.2</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="F31" t="n">
-        <v>1.48</v>
+        <v>-1.83</v>
       </c>
       <c r="G31" t="n">
-        <v>134.2</v>
+        <v>126.5</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.5</v>
+        <v>-7.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.83</v>
+        <v>-5.74</v>
       </c>
       <c r="J31" t="n">
-        <v>126.5</v>
+        <v>128.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.7</v>
+        <v>1.7</v>
       </c>
       <c r="L31" t="n">
-        <v>-5.74</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
         <v>128.2</v>
@@ -2349,13 +2349,13 @@
         <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>128.2</v>
+        <v>128</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.7</v>
+        <v>-0.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="32">
@@ -2375,31 +2375,31 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>68.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2</v>
+        <v>6.65</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.29</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>75.15000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H32" t="n">
-        <v>6.65</v>
+        <v>-0.95</v>
       </c>
       <c r="I32" t="n">
-        <v>9.710000000000001</v>
+        <v>-1.26</v>
       </c>
       <c r="J32" t="n">
-        <v>74.2</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.95</v>
+        <v>5.65</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.26</v>
+        <v>7.61</v>
       </c>
       <c r="M32" t="n">
         <v>79.84999999999999</v>
@@ -2411,13 +2411,13 @@
         <v>7.61</v>
       </c>
       <c r="P32" t="n">
-        <v>79.84999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.65</v>
+        <v>4.55</v>
       </c>
       <c r="R32" t="n">
-        <v>7.61</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="33">
@@ -2437,31 +2437,31 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>93.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1</v>
+        <v>-3.7</v>
       </c>
       <c r="F33" t="n">
-        <v>0.11</v>
+        <v>-3.94</v>
       </c>
       <c r="G33" t="n">
-        <v>90.2</v>
+        <v>90.55</v>
       </c>
       <c r="H33" t="n">
-        <v>-3.7</v>
+        <v>0.35</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.94</v>
+        <v>0.39</v>
       </c>
       <c r="J33" t="n">
-        <v>90.55</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="L33" t="n">
-        <v>0.39</v>
+        <v>1.16</v>
       </c>
       <c r="M33" t="n">
         <v>91.59999999999999</v>
@@ -2473,13 +2473,13 @@
         <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>91.59999999999999</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.05</v>
+        <v>2.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.16</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="34">
@@ -2499,31 +2499,31 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>48.88</v>
+        <v>47.68</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="F34" t="n">
-        <v>0.41</v>
+        <v>-2.45</v>
       </c>
       <c r="G34" t="n">
-        <v>47.68</v>
+        <v>44.98</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.45</v>
+        <v>-5.66</v>
       </c>
       <c r="J34" t="n">
-        <v>44.98</v>
+        <v>45.64</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.7</v>
+        <v>0.66</v>
       </c>
       <c r="L34" t="n">
-        <v>-5.66</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
         <v>45.64</v>
@@ -2535,13 +2535,13 @@
         <v>1.47</v>
       </c>
       <c r="P34" t="n">
-        <v>45.64</v>
+        <v>45.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
       <c r="R34" t="n">
-        <v>1.47</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="35">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="J35" t="n">
         <v>4.76</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.67</v>
-      </c>
       <c r="K35" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.1</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
         <v>4.76</v>
@@ -2597,13 +2597,13 @@
         <v>1.93</v>
       </c>
       <c r="P35" t="n">
-        <v>4.76</v>
+        <v>4.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="R35" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="36">
@@ -2623,31 +2623,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="F36" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="G36" t="n">
-        <v>10.24</v>
+        <v>10.03</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>-2.05</v>
       </c>
       <c r="J36" t="n">
-        <v>10.03</v>
+        <v>10.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.21</v>
+        <v>0.19</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.05</v>
+        <v>1.89</v>
       </c>
       <c r="M36" t="n">
         <v>10.22</v>
@@ -2659,13 +2659,13 @@
         <v>1.89</v>
       </c>
       <c r="P36" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="R36" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="37">
@@ -2685,31 +2685,31 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>410</v>
+        <v>411.2</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="G37" t="n">
-        <v>411.2</v>
+        <v>407.4</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="I37" t="n">
-        <v>0.29</v>
+        <v>-0.92</v>
       </c>
       <c r="J37" t="n">
-        <v>407.4</v>
+        <v>409.2</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.8</v>
+        <v>1.8</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.92</v>
+        <v>0.44</v>
       </c>
       <c r="M37" t="n">
         <v>409.2</v>
@@ -2721,13 +2721,13 @@
         <v>0.44</v>
       </c>
       <c r="P37" t="n">
-        <v>409.2</v>
+        <v>405.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0.44</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="38">
@@ -2747,31 +2747,31 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.74</v>
+        <v>15.25</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02</v>
+        <v>-0.49</v>
       </c>
       <c r="F38" t="n">
-        <v>0.13</v>
+        <v>-3.11</v>
       </c>
       <c r="G38" t="n">
-        <v>15.25</v>
+        <v>15.21</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.49</v>
+        <v>-0.04</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="J38" t="n">
-        <v>15.21</v>
+        <v>15.14</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
       <c r="M38" t="n">
         <v>15.14</v>
@@ -2783,13 +2783,13 @@
         <v>-0.46</v>
       </c>
       <c r="P38" t="n">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.46</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="39">
@@ -2809,31 +2809,31 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>660</v>
+        <v>662.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-14.5</v>
+        <v>2.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.15</v>
+        <v>0.38</v>
       </c>
       <c r="G39" t="n">
-        <v>662.5</v>
+        <v>673.5</v>
       </c>
       <c r="H39" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.38</v>
+        <v>1.66</v>
       </c>
       <c r="J39" t="n">
-        <v>673.5</v>
+        <v>686</v>
       </c>
       <c r="K39" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="M39" t="n">
         <v>686</v>
@@ -2845,13 +2845,13 @@
         <v>1.86</v>
       </c>
       <c r="P39" t="n">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="Q39" t="n">
-        <v>12.5</v>
+        <v>-28</v>
       </c>
       <c r="R39" t="n">
-        <v>1.86</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="40">
@@ -2871,31 +2871,31 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>58.5</v>
+        <v>57.95</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.15</v>
+        <v>-0.55</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.54</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>57.95</v>
+        <v>60.6</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.55</v>
+        <v>2.65</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9399999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="J40" t="n">
-        <v>60.6</v>
+        <v>62.6</v>
       </c>
       <c r="K40" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>4.57</v>
+        <v>3.3</v>
       </c>
       <c r="M40" t="n">
         <v>62.6</v>
@@ -2907,13 +2907,13 @@
         <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="R40" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.43</v>
+        <v>23.24</v>
       </c>
       <c r="E41" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I41" t="n">
         <v>0.39</v>
       </c>
-      <c r="F41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="G41" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="J41" t="n">
-        <v>23.33</v>
+        <v>23.53</v>
       </c>
       <c r="K41" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.39</v>
+        <v>0.86</v>
       </c>
       <c r="M41" t="n">
-        <v>23.53</v>
+        <v>23.51</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="O41" t="n">
-        <v>0.86</v>
+        <v>-0.08</v>
       </c>
       <c r="P41" t="n">
-        <v>23.51</v>
+        <v>23.36</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.08</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="G42" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J42" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M42" t="n">
+        <v>62.18</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P42" t="n">
         <v>62</v>
       </c>
-      <c r="E42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G42" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="I42" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="J42" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="M42" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="P42" t="n">
-        <v>62.18</v>
-      </c>
       <c r="Q42" t="n">
-        <v>0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="R42" t="n">
-        <v>0.13</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.75</v>
+        <v>37.59</v>
       </c>
       <c r="E43" t="n">
-        <v>0.46</v>
+        <v>-0.16</v>
       </c>
       <c r="F43" t="n">
-        <v>1.23</v>
+        <v>-0.42</v>
       </c>
       <c r="G43" t="n">
-        <v>37.59</v>
+        <v>37.69</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.42</v>
+        <v>0.27</v>
       </c>
       <c r="J43" t="n">
-        <v>37.69</v>
+        <v>37.7</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="L43" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="M43" t="n">
-        <v>37.7</v>
+        <v>37.91</v>
       </c>
       <c r="N43" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="O43" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>37.91</v>
+        <v>37.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="R43" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="E44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="N44" t="n">
         <v>0.01</v>
       </c>
-      <c r="F44" t="n">
+      <c r="O44" t="n">
         <v>0.16</v>
       </c>
-      <c r="G44" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="P44" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="Q44" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L44" t="n">
+      <c r="R44" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="P44" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.16</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="E45" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K45" t="n">
         <v>0.01</v>
       </c>
-      <c r="F45" t="n">
+      <c r="L45" t="n">
         <v>0.45</v>
       </c>
-      <c r="G45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="M45" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N45" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I45" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="K45" t="n">
+      <c r="O45" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L45" t="n">
+      <c r="R45" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="R45" t="n">
-        <v>-0.9</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F46" t="n">
-        <v>1.56</v>
+        <v>-0.61</v>
       </c>
       <c r="G46" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.61</v>
+        <v>0.31</v>
       </c>
       <c r="J46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L46" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="M46" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="N46" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="O46" t="n">
-        <v>0.92</v>
+        <v>2.74</v>
       </c>
       <c r="P46" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="R46" t="n">
-        <v>2.74</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.02</v>
+        <v>11.06</v>
       </c>
       <c r="E47" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="F47" t="n">
-        <v>2.13</v>
+        <v>0.36</v>
       </c>
       <c r="G47" t="n">
-        <v>11.06</v>
+        <v>11.11</v>
       </c>
       <c r="H47" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I47" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="J47" t="n">
-        <v>11.11</v>
+        <v>11.27</v>
       </c>
       <c r="K47" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="L47" t="n">
-        <v>0.45</v>
+        <v>1.44</v>
       </c>
       <c r="M47" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="O47" t="n">
-        <v>1.44</v>
+        <v>-0.18</v>
       </c>
       <c r="P47" t="n">
-        <v>11.25</v>
+        <v>11.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.18</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.34</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>1.49</v>
       </c>
-      <c r="G48" t="n">
+      <c r="J48" t="n">
         <v>0.335</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
         <v>-1.47</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1.49</v>
-      </c>
       <c r="M48" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="N48" t="n">
         <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
       <c r="P48" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.49</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.98</v>
+        <v>5.02</v>
       </c>
       <c r="E49" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="F49" t="n">
-        <v>2.26</v>
+        <v>0.8</v>
       </c>
       <c r="G49" t="n">
-        <v>5.02</v>
+        <v>4.7</v>
       </c>
       <c r="H49" t="n">
-        <v>0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>-6.37</v>
       </c>
       <c r="J49" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.32</v>
+        <v>-0.11</v>
       </c>
       <c r="L49" t="n">
-        <v>-6.37</v>
+        <v>-2.34</v>
       </c>
       <c r="M49" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="O49" t="n">
-        <v>-2.34</v>
+        <v>-1.09</v>
       </c>
       <c r="P49" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="R49" t="n">
-        <v>-1.09</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="50">
@@ -3491,22 +3491,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>-0.97</v>
       </c>
       <c r="G50" t="n">
         <v>1.02</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>1.02</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="F51" t="n">
-        <v>0.51</v>
+        <v>-3.3</v>
       </c>
       <c r="G51" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="I51" t="n">
-        <v>-3.3</v>
+        <v>-2.89</v>
       </c>
       <c r="J51" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="P51" t="n">
         <v>3.7</v>
       </c>
-      <c r="K51" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3.75</v>
-      </c>
       <c r="Q51" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.79</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.23</v>
+        <v>10.32</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.15</v>
+        <v>0.09</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.45</v>
+        <v>0.88</v>
       </c>
       <c r="G52" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="H52" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="J52" t="n">
-        <v>10.42</v>
+        <v>10.91</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="L52" t="n">
-        <v>0.97</v>
+        <v>4.7</v>
       </c>
       <c r="M52" t="n">
-        <v>10.91</v>
+        <v>11.07</v>
       </c>
       <c r="N52" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="O52" t="n">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="P52" t="n">
-        <v>11.07</v>
+        <v>10.84</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="R52" t="n">
-        <v>1.47</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="E53" t="n">
-        <v>0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="F53" t="n">
-        <v>4.85</v>
+        <v>-1.82</v>
       </c>
       <c r="G53" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.82</v>
+        <v>0.99</v>
       </c>
       <c r="J53" t="n">
-        <v>8.15</v>
+        <v>8.17</v>
       </c>
       <c r="K53" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="L53" t="n">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
       <c r="M53" t="n">
-        <v>8.17</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="O53" t="n">
-        <v>0.25</v>
+        <v>3.43</v>
       </c>
       <c r="P53" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="R53" t="n">
-        <v>3.43</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.465</v>
       </c>
-      <c r="E54" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F54" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.46</v>
       </c>
-      <c r="H54" t="n">
+      <c r="K54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I54" t="n">
+      <c r="L54" t="n">
         <v>-1.08</v>
       </c>
-      <c r="J54" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.09</v>
-      </c>
       <c r="M54" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="N54" t="n">
         <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
       <c r="P54" t="n">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="55">
@@ -3801,22 +3801,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="G55" t="n">
         <v>0.59</v>
       </c>
       <c r="H55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0.59</v>
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="G56" t="n">
         <v>0.475</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.06</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0.475</v>
@@ -3890,22 +3890,22 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="P56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.11</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="E57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="P57" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="Q57" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F57" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="K57" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="R57" t="n">
-        <v>-0.28</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="58">
@@ -3987,40 +3987,40 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.08</v>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="F58" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.002</v>
-      </c>
       <c r="L58" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
       <c r="M58" t="n">
         <v>0.079</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0.079</v>
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.67</v>
+        <v>21.86</v>
       </c>
       <c r="E59" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="F59" t="n">
-        <v>2.51</v>
+        <v>0.88</v>
       </c>
       <c r="G59" t="n">
-        <v>21.86</v>
+        <v>22.38</v>
       </c>
       <c r="H59" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="I59" t="n">
-        <v>0.88</v>
+        <v>2.38</v>
       </c>
       <c r="J59" t="n">
-        <v>22.38</v>
+        <v>22.4</v>
       </c>
       <c r="K59" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="L59" t="n">
-        <v>2.38</v>
+        <v>0.09</v>
       </c>
       <c r="M59" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="N59" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="O59" t="n">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="P59" t="n">
-        <v>22.29</v>
+        <v>21.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.49</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="60">
@@ -4111,25 +4111,25 @@
         </is>
       </c>
       <c r="D60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="G60" t="n">
         <v>3.16</v>
       </c>
-      <c r="E60" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.15</v>
-      </c>
       <c r="H60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="K60" t="n">
         <v>0.01</v>
@@ -4138,22 +4138,22 @@
         <v>0.32</v>
       </c>
       <c r="M60" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="O60" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="P60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="R60" t="n">
-        <v>0.95</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.19</v>
+        <v>1.49</v>
       </c>
       <c r="G61" t="n">
         <v>1.36</v>
       </c>
       <c r="H61" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="M61" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.74</v>
+        <v>5.19</v>
       </c>
       <c r="P61" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="R61" t="n">
-        <v>5.19</v>
+        <v>-3.52</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-20 Close</t>
+          <t>2026-05-21 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change</t>
+          <t>2026-05-21 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-20 Change %</t>
+          <t>2026-05-21 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-21 Close</t>
+          <t>2026-05-22 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change</t>
+          <t>2026-05-22 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change %</t>
+          <t>2026-05-22 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-22 Close</t>
+          <t>2026-05-25 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change</t>
+          <t>2026-05-25 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change %</t>
+          <t>2026-05-25 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-25 Close</t>
+          <t>2026-05-26 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change</t>
+          <t>2026-05-26 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change %</t>
+          <t>2026-05-26 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-26 Close</t>
+          <t>2026-05-27 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change</t>
+          <t>2026-05-27 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change %</t>
+          <t>2026-05-27 Change %</t>
         </is>
       </c>
     </row>
@@ -577,22 +577,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>138.7</v>
+        <v>141.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.14</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>141.7</v>
+        <v>143.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="J3" t="n">
         <v>143.9</v>
@@ -604,22 +604,22 @@
         <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>143.9</v>
+        <v>145.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="P3" t="n">
-        <v>145.5</v>
+        <v>146.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="4">
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>198</v>
+        <v>200.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.2</v>
+        <v>2.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.59</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
-        <v>200.6</v>
+        <v>204</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="J4" t="n">
         <v>204</v>
@@ -666,22 +666,22 @@
         <v>1.69</v>
       </c>
       <c r="M4" t="n">
-        <v>204</v>
+        <v>207.4</v>
       </c>
       <c r="N4" t="n">
         <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="P4" t="n">
-        <v>207.4</v>
+        <v>209.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="5">
@@ -701,22 +701,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>-0.19</v>
       </c>
       <c r="F5" t="n">
-        <v>0.17</v>
+        <v>-3.13</v>
       </c>
       <c r="G5" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.13</v>
+        <v>0.68</v>
       </c>
       <c r="J5" t="n">
         <v>5.92</v>
@@ -728,22 +728,22 @@
         <v>0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0.68</v>
+        <v>-2.53</v>
       </c>
       <c r="P5" t="n">
-        <v>5.77</v>
+        <v>5.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.53</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="6">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.72</v>
+        <v>-1.16</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.16</v>
+        <v>0.74</v>
       </c>
       <c r="J6" t="n">
         <v>6.85</v>
@@ -790,22 +790,22 @@
         <v>0.74</v>
       </c>
       <c r="M6" t="n">
-        <v>6.85</v>
+        <v>6.78</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.74</v>
+        <v>-1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>6.78</v>
+        <v>6.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.02</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="7">
@@ -825,22 +825,22 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="G7" t="n">
         <v>5.23</v>
       </c>
-      <c r="E7" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="H7" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J7" t="n">
         <v>5.23</v>
@@ -852,22 +852,22 @@
         <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="O7" t="n">
-        <v>0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="P7" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.57</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="8">
@@ -887,22 +887,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.73</v>
+        <v>8.69</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="G8" t="n">
-        <v>8.69</v>
+        <v>8.77</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.46</v>
+        <v>0.92</v>
       </c>
       <c r="J8" t="n">
         <v>8.77</v>
@@ -914,22 +914,22 @@
         <v>0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>8.77</v>
+        <v>8.73</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="O8" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="P8" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.46</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="9">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.24</v>
+        <v>-0.14</v>
       </c>
       <c r="G9" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="H9" t="n">
         <v>-0.01</v>
@@ -979,19 +979,19 @@
         <v>7.17</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7.17</v>
+        <v>7.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1011,22 +1011,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.1</v>
+        <v>46.14</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.52</v>
+        <v>0.09</v>
       </c>
       <c r="G10" t="n">
-        <v>46.14</v>
+        <v>46.26</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="J10" t="n">
         <v>46.26</v>
@@ -1038,22 +1038,22 @@
         <v>0.26</v>
       </c>
       <c r="M10" t="n">
-        <v>46.26</v>
+        <v>45.98</v>
       </c>
       <c r="N10" t="n">
-        <v>0.12</v>
+        <v>-0.28</v>
       </c>
       <c r="O10" t="n">
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
       <c r="P10" t="n">
-        <v>45.98</v>
+        <v>45.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.61</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="11">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="E11" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F11" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="I11" t="n">
-        <v>-1.11</v>
+        <v>-0.23</v>
       </c>
       <c r="J11" t="n">
         <v>4.43</v>
@@ -1100,7 +1100,7 @@
         <v>-0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="N11" t="n">
         <v>-0.01</v>
@@ -1109,13 +1109,13 @@
         <v>-0.23</v>
       </c>
       <c r="P11" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.23</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="12">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.2</v>
+        <v>10.94</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="F12" t="n">
-        <v>0.72</v>
+        <v>-2.32</v>
       </c>
       <c r="G12" t="n">
-        <v>10.94</v>
+        <v>10.83</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.26</v>
+        <v>-0.11</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.32</v>
+        <v>-1.01</v>
       </c>
       <c r="J12" t="n">
         <v>10.83</v>
@@ -1162,22 +1162,22 @@
         <v>-1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>10.83</v>
+        <v>10.91</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.01</v>
+        <v>0.74</v>
       </c>
       <c r="P12" t="n">
-        <v>10.91</v>
+        <v>10.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="R12" t="n">
-        <v>0.74</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="13">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.24</v>
+        <v>-0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>0.87</v>
+        <v>-1.8</v>
       </c>
       <c r="G13" t="n">
-        <v>27.3</v>
+        <v>27.44</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8</v>
+        <v>0.51</v>
       </c>
       <c r="J13" t="n">
         <v>27.44</v>
@@ -1224,22 +1224,22 @@
         <v>0.51</v>
       </c>
       <c r="M13" t="n">
-        <v>27.44</v>
+        <v>26.92</v>
       </c>
       <c r="N13" t="n">
-        <v>0.14</v>
+        <v>-0.52</v>
       </c>
       <c r="O13" t="n">
-        <v>0.51</v>
+        <v>-1.9</v>
       </c>
       <c r="P13" t="n">
-        <v>26.92</v>
+        <v>26.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.52</v>
+        <v>-0.6</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.9</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="14">
@@ -1259,16 +1259,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="H14" t="n">
         <v>-0.01</v>
@@ -1286,22 +1286,22 @@
         <v>-0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4</v>
+        <v>-2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.85</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="15">
@@ -1321,22 +1321,22 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="G15" t="n">
         <v>5.22</v>
       </c>
-      <c r="E15" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.15</v>
-      </c>
       <c r="H15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.34</v>
+        <v>1.36</v>
       </c>
       <c r="J15" t="n">
         <v>5.22</v>
@@ -1348,22 +1348,22 @@
         <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>5.22</v>
+        <v>5.23</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>0.19</v>
       </c>
       <c r="P15" t="n">
-        <v>5.23</v>
+        <v>5.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>0.19</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="16">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.99</v>
+        <v>4.93</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.96</v>
+        <v>-1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>4.93</v>
+        <v>4.89</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>4.89</v>
@@ -1410,22 +1410,22 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.64</v>
       </c>
       <c r="P16" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.64</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="17">
@@ -1445,22 +1445,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="G17" t="n">
         <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -1472,22 +1472,22 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="18">
@@ -1507,22 +1507,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.86</v>
+        <v>-2.31</v>
       </c>
       <c r="G18" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.31</v>
+        <v>1.18</v>
       </c>
       <c r="J18" t="n">
         <v>3.43</v>
@@ -1537,19 +1537,19 @@
         <v>3.43</v>
       </c>
       <c r="N18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="19">
@@ -1569,22 +1569,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61.15</v>
+        <v>60.8</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.41</v>
+        <v>-0.57</v>
       </c>
       <c r="G19" t="n">
-        <v>60.8</v>
+        <v>60.85</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.35</v>
+        <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.57</v>
+        <v>0.08</v>
       </c>
       <c r="J19" t="n">
         <v>60.85</v>
@@ -1596,22 +1596,22 @@
         <v>0.08</v>
       </c>
       <c r="M19" t="n">
-        <v>60.85</v>
+        <v>60.65</v>
       </c>
       <c r="N19" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="P19" t="n">
-        <v>60.65</v>
+        <v>59.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.33</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="20">
@@ -1631,22 +1631,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.12</v>
+        <v>28.72</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.69</v>
+        <v>-1.37</v>
       </c>
       <c r="G20" t="n">
-        <v>28.72</v>
+        <v>28.92</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.37</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>28.92</v>
@@ -1658,22 +1658,22 @@
         <v>0.7</v>
       </c>
       <c r="M20" t="n">
-        <v>28.92</v>
+        <v>29.42</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>29.42</v>
+        <v>28.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5</v>
+        <v>-0.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="21">
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.11</v>
+        <v>-1.62</v>
       </c>
       <c r="G21" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.62</v>
+        <v>-1.46</v>
       </c>
       <c r="J21" t="n">
         <v>5.39</v>
@@ -1720,22 +1720,22 @@
         <v>-1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.46</v>
+        <v>-1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>5.33</v>
+        <v>5.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.11</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.55</v>
+        <v>86.05</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.29</v>
+        <v>-0.58</v>
       </c>
       <c r="G22" t="n">
-        <v>86.05</v>
+        <v>85.5</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5</v>
+        <v>-0.55</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.58</v>
+        <v>-0.64</v>
       </c>
       <c r="J22" t="n">
         <v>85.5</v>
@@ -1782,22 +1782,22 @@
         <v>-0.64</v>
       </c>
       <c r="M22" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.64</v>
+        <v>0.12</v>
       </c>
       <c r="P22" t="n">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0.12</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="23">
@@ -1817,22 +1817,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.6</v>
+        <v>23.78</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.12</v>
+        <v>-0.82</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.49</v>
+        <v>-3.33</v>
       </c>
       <c r="G23" t="n">
-        <v>23.78</v>
+        <v>24.48</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.82</v>
+        <v>0.7</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.33</v>
+        <v>2.94</v>
       </c>
       <c r="J23" t="n">
         <v>24.48</v>
@@ -1844,22 +1844,22 @@
         <v>2.94</v>
       </c>
       <c r="M23" t="n">
-        <v>24.48</v>
+        <v>24.92</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="O23" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="P23" t="n">
-        <v>24.92</v>
+        <v>24.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="24">
@@ -1879,22 +1879,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.6</v>
+        <v>27.52</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.24</v>
+        <v>-3.78</v>
       </c>
       <c r="G24" t="n">
-        <v>27.52</v>
+        <v>28.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.08</v>
+        <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.78</v>
+        <v>2.83</v>
       </c>
       <c r="J24" t="n">
         <v>28.3</v>
@@ -1906,22 +1906,22 @@
         <v>2.83</v>
       </c>
       <c r="M24" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="P24" t="n">
-        <v>28.8</v>
+        <v>28.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5</v>
+        <v>-0.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.77</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="25">
@@ -1941,22 +1941,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.14</v>
+        <v>29.66</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="G25" t="n">
-        <v>29.66</v>
+        <v>30</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.48</v>
+        <v>0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.59</v>
+        <v>1.15</v>
       </c>
       <c r="J25" t="n">
         <v>30</v>
@@ -1968,22 +1968,22 @@
         <v>1.15</v>
       </c>
       <c r="M25" t="n">
-        <v>30</v>
+        <v>29.76</v>
       </c>
       <c r="N25" t="n">
-        <v>0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>-0.8</v>
       </c>
       <c r="P25" t="n">
-        <v>29.76</v>
+        <v>28.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.24</v>
+        <v>-1.36</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.8</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="26">
@@ -2003,22 +2003,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50.7</v>
+        <v>46.8</v>
       </c>
       <c r="E26" t="n">
-        <v>2.86</v>
+        <v>-3.9</v>
       </c>
       <c r="F26" t="n">
-        <v>5.98</v>
+        <v>-7.69</v>
       </c>
       <c r="G26" t="n">
-        <v>46.8</v>
+        <v>48.88</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.9</v>
+        <v>2.08</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.69</v>
+        <v>4.44</v>
       </c>
       <c r="J26" t="n">
         <v>48.88</v>
@@ -2030,22 +2030,22 @@
         <v>4.44</v>
       </c>
       <c r="M26" t="n">
-        <v>48.88</v>
+        <v>51.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="O26" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
       <c r="P26" t="n">
-        <v>51.1</v>
+        <v>52.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="R26" t="n">
-        <v>4.54</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="27">
@@ -2065,22 +2065,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>455.2</v>
+        <v>439</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.8</v>
+        <v>-16.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.04</v>
+        <v>-3.56</v>
       </c>
       <c r="G27" t="n">
-        <v>439</v>
+        <v>441.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-16.2</v>
+        <v>2.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.56</v>
+        <v>0.55</v>
       </c>
       <c r="J27" t="n">
         <v>441.4</v>
@@ -2092,22 +2092,22 @@
         <v>0.55</v>
       </c>
       <c r="M27" t="n">
-        <v>441.4</v>
+        <v>439</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="P27" t="n">
-        <v>439</v>
+        <v>434.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.54</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="28">
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>131.9</v>
+        <v>126</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.4</v>
+        <v>-5.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.05</v>
+        <v>-4.47</v>
       </c>
       <c r="G28" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.9</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>-4.47</v>
+        <v>0.79</v>
       </c>
       <c r="J28" t="n">
         <v>127</v>
@@ -2154,22 +2154,22 @@
         <v>0.79</v>
       </c>
       <c r="M28" t="n">
-        <v>127</v>
+        <v>127.6</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="P28" t="n">
-        <v>127.6</v>
+        <v>124.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.6</v>
+        <v>-3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0.47</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="29">
@@ -2189,22 +2189,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>127.8</v>
+        <v>123.5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9</v>
+        <v>-4.3</v>
       </c>
       <c r="F29" t="n">
-        <v>1.51</v>
+        <v>-3.36</v>
       </c>
       <c r="G29" t="n">
-        <v>123.5</v>
+        <v>121.7</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.3</v>
+        <v>-1.8</v>
       </c>
       <c r="I29" t="n">
-        <v>-3.36</v>
+        <v>-1.46</v>
       </c>
       <c r="J29" t="n">
         <v>121.7</v>
@@ -2216,22 +2216,22 @@
         <v>-1.46</v>
       </c>
       <c r="M29" t="n">
-        <v>121.7</v>
+        <v>118.6</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.46</v>
+        <v>-2.55</v>
       </c>
       <c r="P29" t="n">
-        <v>118.6</v>
+        <v>116.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="R29" t="n">
-        <v>-2.55</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="30">
@@ -2251,16 +2251,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82.84999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
       <c r="G30" t="n">
-        <v>82.09999999999999</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="H30" t="n">
         <v>-0.75</v>
@@ -2278,22 +2278,22 @@
         <v>-0.91</v>
       </c>
       <c r="M30" t="n">
-        <v>81.34999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.75</v>
+        <v>-2.55</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.91</v>
+        <v>-3.13</v>
       </c>
       <c r="P30" t="n">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>-2.55</v>
+        <v>-1.1</v>
       </c>
       <c r="R30" t="n">
-        <v>-3.13</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="31">
@@ -2313,22 +2313,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>134.2</v>
+        <v>126.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.5</v>
+        <v>-7.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.83</v>
+        <v>-5.74</v>
       </c>
       <c r="G31" t="n">
-        <v>126.5</v>
+        <v>128.2</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.7</v>
+        <v>1.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-5.74</v>
+        <v>1.34</v>
       </c>
       <c r="J31" t="n">
         <v>128.2</v>
@@ -2340,22 +2340,22 @@
         <v>1.34</v>
       </c>
       <c r="M31" t="n">
+        <v>128</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="P31" t="n">
         <v>128.2</v>
       </c>
-      <c r="N31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P31" t="n">
-        <v>128</v>
-      </c>
       <c r="Q31" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.16</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="32">
@@ -2375,22 +2375,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>75.15000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="E32" t="n">
-        <v>6.65</v>
+        <v>-0.95</v>
       </c>
       <c r="F32" t="n">
-        <v>9.710000000000001</v>
+        <v>-1.26</v>
       </c>
       <c r="G32" t="n">
-        <v>74.2</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.95</v>
+        <v>5.65</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.26</v>
+        <v>7.61</v>
       </c>
       <c r="J32" t="n">
         <v>79.84999999999999</v>
@@ -2402,22 +2402,22 @@
         <v>7.61</v>
       </c>
       <c r="M32" t="n">
-        <v>79.84999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>5.65</v>
+        <v>4.55</v>
       </c>
       <c r="O32" t="n">
-        <v>7.61</v>
+        <v>5.7</v>
       </c>
       <c r="P32" t="n">
-        <v>84.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.55</v>
+        <v>0.8</v>
       </c>
       <c r="R32" t="n">
-        <v>5.7</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="33">
@@ -2437,22 +2437,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>90.2</v>
+        <v>90.55</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.7</v>
+        <v>0.35</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.94</v>
+        <v>0.39</v>
       </c>
       <c r="G33" t="n">
-        <v>90.55</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="I33" t="n">
-        <v>0.39</v>
+        <v>1.16</v>
       </c>
       <c r="J33" t="n">
         <v>91.59999999999999</v>
@@ -2464,22 +2464,22 @@
         <v>1.16</v>
       </c>
       <c r="M33" t="n">
-        <v>91.59999999999999</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>1.05</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.16</v>
+        <v>2.24</v>
       </c>
       <c r="P33" t="n">
-        <v>93.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.05</v>
+        <v>-2.95</v>
       </c>
       <c r="R33" t="n">
-        <v>2.24</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="34">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>47.68</v>
+        <v>44.98</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.45</v>
+        <v>-5.66</v>
       </c>
       <c r="G34" t="n">
-        <v>44.98</v>
+        <v>45.64</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.7</v>
+        <v>0.66</v>
       </c>
       <c r="I34" t="n">
-        <v>-5.66</v>
+        <v>1.47</v>
       </c>
       <c r="J34" t="n">
         <v>45.64</v>
@@ -2526,22 +2526,22 @@
         <v>1.47</v>
       </c>
       <c r="M34" t="n">
-        <v>45.64</v>
+        <v>45.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
       <c r="O34" t="n">
-        <v>1.47</v>
+        <v>0.35</v>
       </c>
       <c r="P34" t="n">
-        <v>45.8</v>
+        <v>45.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="R34" t="n">
-        <v>0.35</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="35">
@@ -2561,22 +2561,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.21</v>
+        <v>-2.1</v>
       </c>
       <c r="G35" t="n">
-        <v>4.67</v>
+        <v>4.76</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.1</v>
+        <v>1.93</v>
       </c>
       <c r="J35" t="n">
         <v>4.76</v>
@@ -2588,22 +2588,22 @@
         <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>4.76</v>
+        <v>4.84</v>
       </c>
       <c r="N35" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O35" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="P35" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="R35" t="n">
-        <v>1.68</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="36">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.24</v>
+        <v>10.03</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1</v>
+        <v>-2.05</v>
       </c>
       <c r="G36" t="n">
-        <v>10.03</v>
+        <v>10.22</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.21</v>
+        <v>0.19</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.05</v>
+        <v>1.89</v>
       </c>
       <c r="J36" t="n">
         <v>10.22</v>
@@ -2650,22 +2650,22 @@
         <v>1.89</v>
       </c>
       <c r="M36" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="N36" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="O36" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="P36" t="n">
-        <v>10.4</v>
+        <v>10.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="R36" t="n">
-        <v>1.76</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="37">
@@ -2685,22 +2685,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>411.2</v>
+        <v>407.4</v>
       </c>
       <c r="E37" t="n">
-        <v>1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="F37" t="n">
-        <v>0.29</v>
+        <v>-0.92</v>
       </c>
       <c r="G37" t="n">
-        <v>407.4</v>
+        <v>409.2</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.8</v>
+        <v>1.8</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.92</v>
+        <v>0.44</v>
       </c>
       <c r="J37" t="n">
         <v>409.2</v>
@@ -2712,22 +2712,22 @@
         <v>0.44</v>
       </c>
       <c r="M37" t="n">
-        <v>409.2</v>
+        <v>405.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="O37" t="n">
-        <v>0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="P37" t="n">
-        <v>405.6</v>
+        <v>402.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.88</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="38">
@@ -2747,22 +2747,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.25</v>
+        <v>15.21</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.49</v>
+        <v>-0.04</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="G38" t="n">
-        <v>15.21</v>
+        <v>15.14</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
       <c r="J38" t="n">
         <v>15.14</v>
@@ -2774,22 +2774,22 @@
         <v>-0.46</v>
       </c>
       <c r="M38" t="n">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.46</v>
+        <v>-0.26</v>
       </c>
       <c r="P38" t="n">
-        <v>15.1</v>
+        <v>15.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.26</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="39">
@@ -2809,22 +2809,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>662.5</v>
+        <v>673.5</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>0.38</v>
+        <v>1.66</v>
       </c>
       <c r="G39" t="n">
-        <v>673.5</v>
+        <v>686</v>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="J39" t="n">
         <v>686</v>
@@ -2836,22 +2836,22 @@
         <v>1.86</v>
       </c>
       <c r="M39" t="n">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="N39" t="n">
-        <v>12.5</v>
+        <v>-28</v>
       </c>
       <c r="O39" t="n">
-        <v>1.86</v>
+        <v>-4.08</v>
       </c>
       <c r="P39" t="n">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="Q39" t="n">
-        <v>-28</v>
+        <v>42</v>
       </c>
       <c r="R39" t="n">
-        <v>-4.08</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="40">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>57.95</v>
+        <v>60.6</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.55</v>
+        <v>2.65</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9399999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="G40" t="n">
-        <v>60.6</v>
+        <v>62.6</v>
       </c>
       <c r="H40" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>4.57</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>62.6</v>
@@ -2898,22 +2898,22 @@
         <v>3.3</v>
       </c>
       <c r="M40" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P40" t="n">
-        <v>65.2</v>
+        <v>62.85</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.6</v>
+        <v>-2.35</v>
       </c>
       <c r="R40" t="n">
-        <v>4.15</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="41">
@@ -2933,40 +2933,40 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.24</v>
+        <v>23.33</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.19</v>
+        <v>0.09</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="G41" t="n">
-        <v>23.33</v>
+        <v>23.53</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="I41" t="n">
-        <v>0.39</v>
+        <v>0.86</v>
       </c>
       <c r="J41" t="n">
-        <v>23.53</v>
+        <v>23.51</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="L41" t="n">
-        <v>0.86</v>
+        <v>-0.08</v>
       </c>
       <c r="M41" t="n">
-        <v>23.51</v>
+        <v>23.36</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.08</v>
+        <v>-0.64</v>
       </c>
       <c r="P41" t="n">
         <v>23.36</v>
@@ -2995,40 +2995,40 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>61.3</v>
+        <v>61.75</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.7</v>
+        <v>0.45</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.13</v>
+        <v>0.73</v>
       </c>
       <c r="G42" t="n">
-        <v>61.75</v>
+        <v>62.1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="J42" t="n">
-        <v>62.1</v>
+        <v>62.18</v>
       </c>
       <c r="K42" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="L42" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="M42" t="n">
-        <v>62.18</v>
+        <v>62</v>
       </c>
       <c r="N42" t="n">
-        <v>0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="O42" t="n">
-        <v>0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="P42" t="n">
         <v>62</v>
@@ -3057,40 +3057,40 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.59</v>
+        <v>37.69</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.42</v>
+        <v>0.27</v>
       </c>
       <c r="G43" t="n">
-        <v>37.69</v>
+        <v>37.7</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="J43" t="n">
-        <v>37.7</v>
+        <v>37.91</v>
       </c>
       <c r="K43" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="L43" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>37.91</v>
+        <v>37.72</v>
       </c>
       <c r="N43" t="n">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="O43" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="P43" t="n">
         <v>37.72</v>
@@ -3119,40 +3119,40 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="E44" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="F44" t="n">
-        <v>0.98</v>
+        <v>-0.16</v>
       </c>
       <c r="G44" t="n">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="H44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="N44" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I44" t="n">
+      <c r="O44" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.16</v>
       </c>
       <c r="P44" t="n">
         <v>6.21</v>
@@ -3181,40 +3181,40 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="G45" t="n">
         <v>2.23</v>
       </c>
-      <c r="E45" t="n">
+      <c r="H45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="L45" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I45" t="n">
+      <c r="O45" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-0.9</v>
       </c>
       <c r="P45" t="n">
         <v>2.2</v>
@@ -3243,40 +3243,40 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.61</v>
+        <v>0.31</v>
       </c>
       <c r="G46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="H46" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="J46" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="L46" t="n">
-        <v>0.92</v>
+        <v>2.74</v>
       </c>
       <c r="M46" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N46" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="O46" t="n">
-        <v>2.74</v>
+        <v>5.64</v>
       </c>
       <c r="P46" t="n">
         <v>3.56</v>
@@ -3305,40 +3305,40 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.06</v>
+        <v>11.11</v>
       </c>
       <c r="E47" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F47" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="G47" t="n">
-        <v>11.11</v>
+        <v>11.27</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.45</v>
+        <v>1.44</v>
       </c>
       <c r="J47" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="K47" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="L47" t="n">
-        <v>1.44</v>
+        <v>-0.18</v>
       </c>
       <c r="M47" t="n">
-        <v>11.25</v>
+        <v>11.1</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.18</v>
+        <v>-1.33</v>
       </c>
       <c r="P47" t="n">
         <v>11.1</v>
@@ -3367,40 +3367,40 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.335</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>-1.47</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1.49</v>
-      </c>
       <c r="J48" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="K48" t="n">
         <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
       <c r="M48" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="N48" t="n">
         <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.49</v>
+        <v>-1.52</v>
       </c>
       <c r="P48" t="n">
         <v>0.325</v>
@@ -3429,40 +3429,40 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5.02</v>
+        <v>4.7</v>
       </c>
       <c r="E49" t="n">
-        <v>0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8</v>
+        <v>-6.37</v>
       </c>
       <c r="G49" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.32</v>
+        <v>-0.11</v>
       </c>
       <c r="I49" t="n">
-        <v>-6.37</v>
+        <v>-2.34</v>
       </c>
       <c r="J49" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="L49" t="n">
-        <v>-2.34</v>
+        <v>-1.09</v>
       </c>
       <c r="M49" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.09</v>
+        <v>-1.32</v>
       </c>
       <c r="P49" t="n">
         <v>4.48</v>
@@ -3494,10 +3494,10 @@
         <v>1.02</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>1.02</v>
@@ -3553,40 +3553,40 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.3</v>
+        <v>-2.89</v>
       </c>
       <c r="G51" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="M51" t="n">
         <v>3.7</v>
       </c>
-      <c r="H51" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.75</v>
-      </c>
       <c r="N51" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.79</v>
+        <v>-1.33</v>
       </c>
       <c r="P51" t="n">
         <v>3.7</v>
@@ -3615,40 +3615,40 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="E52" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="G52" t="n">
-        <v>10.42</v>
+        <v>10.91</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.97</v>
+        <v>4.7</v>
       </c>
       <c r="J52" t="n">
-        <v>10.91</v>
+        <v>11.07</v>
       </c>
       <c r="K52" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="L52" t="n">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="M52" t="n">
-        <v>11.07</v>
+        <v>10.84</v>
       </c>
       <c r="N52" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="O52" t="n">
-        <v>1.47</v>
+        <v>-2.08</v>
       </c>
       <c r="P52" t="n">
         <v>10.84</v>
@@ -3677,40 +3677,40 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.82</v>
+        <v>0.99</v>
       </c>
       <c r="G53" t="n">
-        <v>8.15</v>
+        <v>8.17</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
       <c r="J53" t="n">
-        <v>8.17</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="L53" t="n">
-        <v>0.25</v>
+        <v>3.43</v>
       </c>
       <c r="M53" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="N53" t="n">
-        <v>0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="O53" t="n">
-        <v>3.43</v>
+        <v>-2.49</v>
       </c>
       <c r="P53" t="n">
         <v>8.24</v>
@@ -3739,40 +3739,40 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.46</v>
       </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F54" t="n">
+      <c r="I54" t="n">
         <v>-1.08</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1.09</v>
-      </c>
       <c r="J54" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="K54" t="n">
         <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
       <c r="M54" t="n">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="N54" t="n">
         <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
       <c r="P54" t="n">
         <v>0.45</v>
@@ -3804,10 +3804,10 @@
         <v>0.59</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0.59</v>
@@ -3866,10 +3866,10 @@
         <v>0.475</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.06</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0.475</v>
@@ -3881,22 +3881,22 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="M56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>-2.11</v>
+        <v>1.08</v>
       </c>
       <c r="P56" t="n">
         <v>0.47</v>
@@ -3925,40 +3925,40 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="E57" t="n">
-        <v>0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="F57" t="n">
-        <v>2.19</v>
+        <v>-3.22</v>
       </c>
       <c r="G57" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="I57" t="n">
-        <v>-3.22</v>
+        <v>-0.55</v>
       </c>
       <c r="J57" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.55</v>
+        <v>-0.28</v>
       </c>
       <c r="M57" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.28</v>
+        <v>-1.68</v>
       </c>
       <c r="P57" t="n">
         <v>3.52</v>
@@ -3987,31 +3987,31 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="H58" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
       <c r="J58" t="n">
         <v>0.079</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0.079</v>
@@ -4049,40 +4049,40 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.86</v>
+        <v>22.38</v>
       </c>
       <c r="E59" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="F59" t="n">
-        <v>0.88</v>
+        <v>2.38</v>
       </c>
       <c r="G59" t="n">
-        <v>22.38</v>
+        <v>22.4</v>
       </c>
       <c r="H59" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="I59" t="n">
-        <v>2.38</v>
+        <v>0.09</v>
       </c>
       <c r="J59" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="K59" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="L59" t="n">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="M59" t="n">
-        <v>22.29</v>
+        <v>21.8</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.49</v>
+        <v>-2.2</v>
       </c>
       <c r="P59" t="n">
         <v>21.8</v>
@@ -4111,16 +4111,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="G60" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="H60" t="n">
         <v>0.01</v>
@@ -4129,22 +4129,22 @@
         <v>0.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L60" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N60" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="O60" t="n">
-        <v>0.95</v>
+        <v>-0.62</v>
       </c>
       <c r="P60" t="n">
         <v>3.18</v>
@@ -4176,37 +4176,37 @@
         <v>1.36</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="J61" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.74</v>
+        <v>5.19</v>
       </c>
       <c r="M61" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="N61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="O61" t="n">
-        <v>5.19</v>
+        <v>-3.52</v>
       </c>
       <c r="P61" t="n">
         <v>1.37</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-21 Close</t>
+          <t>2026-05-22 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change</t>
+          <t>2026-05-22 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-21 Change %</t>
+          <t>2026-05-22 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-22 Close</t>
+          <t>2026-05-25 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change</t>
+          <t>2026-05-25 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change %</t>
+          <t>2026-05-25 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-25 Close</t>
+          <t>2026-05-26 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change</t>
+          <t>2026-05-26 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change %</t>
+          <t>2026-05-26 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-26 Close</t>
+          <t>2026-05-27 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change</t>
+          <t>2026-05-27 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change %</t>
+          <t>2026-05-27 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-27 Close</t>
+          <t>2026-05-28 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change</t>
+          <t>2026-05-28 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change %</t>
+          <t>2026-05-28 Change %</t>
         </is>
       </c>
     </row>
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141.7</v>
+        <v>143.9</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
         <v>143.9</v>
@@ -595,22 +595,22 @@
         <v>1.55</v>
       </c>
       <c r="J3" t="n">
-        <v>143.9</v>
+        <v>145.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="M3" t="n">
-        <v>145.5</v>
+        <v>146.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="P3" t="n">
         <v>146.6</v>
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>200.6</v>
+        <v>204</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
         <v>204</v>
@@ -657,22 +657,22 @@
         <v>1.69</v>
       </c>
       <c r="J4" t="n">
-        <v>204</v>
+        <v>207.4</v>
       </c>
       <c r="K4" t="n">
         <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>207.4</v>
+        <v>209.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.67</v>
+        <v>0.87</v>
       </c>
       <c r="P4" t="n">
         <v>209.2</v>
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.13</v>
+        <v>0.68</v>
       </c>
       <c r="G5" t="n">
         <v>5.92</v>
@@ -719,22 +719,22 @@
         <v>0.68</v>
       </c>
       <c r="J5" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.68</v>
+        <v>-2.53</v>
       </c>
       <c r="M5" t="n">
-        <v>5.77</v>
+        <v>5.82</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.53</v>
+        <v>0.87</v>
       </c>
       <c r="P5" t="n">
         <v>5.82</v>
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.16</v>
+        <v>0.74</v>
       </c>
       <c r="G6" t="n">
         <v>6.85</v>
@@ -781,22 +781,22 @@
         <v>0.74</v>
       </c>
       <c r="J6" t="n">
-        <v>6.85</v>
+        <v>6.78</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.74</v>
+        <v>-1.02</v>
       </c>
       <c r="M6" t="n">
-        <v>6.78</v>
+        <v>6.72</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.02</v>
+        <v>-0.88</v>
       </c>
       <c r="P6" t="n">
         <v>6.72</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.2</v>
+        <v>5.23</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.57</v>
+        <v>0.58</v>
       </c>
       <c r="G7" t="n">
         <v>5.23</v>
@@ -843,22 +843,22 @@
         <v>0.58</v>
       </c>
       <c r="J7" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="P7" t="n">
         <v>5.19</v>
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.69</v>
+        <v>8.77</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.46</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="n">
         <v>8.77</v>
@@ -905,22 +905,22 @@
         <v>0.92</v>
       </c>
       <c r="J8" t="n">
-        <v>8.77</v>
+        <v>8.73</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="L8" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.46</v>
+        <v>-1.72</v>
       </c>
       <c r="P8" t="n">
         <v>8.58</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="E9" t="n">
         <v>-0.01</v>
@@ -970,19 +970,19 @@
         <v>7.17</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.17</v>
+        <v>7.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>7.13</v>
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.14</v>
+        <v>46.26</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="G10" t="n">
         <v>46.26</v>
@@ -1029,22 +1029,22 @@
         <v>0.26</v>
       </c>
       <c r="J10" t="n">
-        <v>46.26</v>
+        <v>45.98</v>
       </c>
       <c r="K10" t="n">
-        <v>0.12</v>
+        <v>-0.28</v>
       </c>
       <c r="L10" t="n">
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
       <c r="M10" t="n">
-        <v>45.98</v>
+        <v>45.82</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.61</v>
+        <v>-0.35</v>
       </c>
       <c r="P10" t="n">
         <v>45.82</v>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.11</v>
+        <v>-0.23</v>
       </c>
       <c r="G11" t="n">
         <v>4.43</v>
@@ -1091,7 +1091,7 @@
         <v>-0.23</v>
       </c>
       <c r="J11" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="K11" t="n">
         <v>-0.01</v>
@@ -1100,13 +1100,13 @@
         <v>-0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.23</v>
+        <v>-1.36</v>
       </c>
       <c r="P11" t="n">
         <v>4.36</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.94</v>
+        <v>10.83</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.26</v>
+        <v>-0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.32</v>
+        <v>-1.01</v>
       </c>
       <c r="G12" t="n">
         <v>10.83</v>
@@ -1153,22 +1153,22 @@
         <v>-1.01</v>
       </c>
       <c r="J12" t="n">
-        <v>10.83</v>
+        <v>10.91</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.01</v>
+        <v>0.74</v>
       </c>
       <c r="M12" t="n">
-        <v>10.91</v>
+        <v>10.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0.74</v>
+        <v>-1.92</v>
       </c>
       <c r="P12" t="n">
         <v>10.7</v>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.3</v>
+        <v>27.44</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8</v>
+        <v>0.51</v>
       </c>
       <c r="G13" t="n">
         <v>27.44</v>
@@ -1215,22 +1215,22 @@
         <v>0.51</v>
       </c>
       <c r="J13" t="n">
-        <v>27.44</v>
+        <v>26.92</v>
       </c>
       <c r="K13" t="n">
-        <v>0.14</v>
+        <v>-0.52</v>
       </c>
       <c r="L13" t="n">
-        <v>0.51</v>
+        <v>-1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>26.92</v>
+        <v>26.32</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.52</v>
+        <v>-0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.9</v>
+        <v>-2.23</v>
       </c>
       <c r="P13" t="n">
         <v>26.32</v>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="E14" t="n">
         <v>-0.01</v>
@@ -1277,22 +1277,22 @@
         <v>-0.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4</v>
+        <v>-2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.85</v>
+        <v>-2.09</v>
       </c>
       <c r="P14" t="n">
         <v>2.34</v>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G15" t="n">
         <v>5.22</v>
@@ -1339,22 +1339,22 @@
         <v>1.36</v>
       </c>
       <c r="J15" t="n">
-        <v>5.22</v>
+        <v>5.23</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>0.19</v>
       </c>
       <c r="M15" t="n">
-        <v>5.23</v>
+        <v>5.16</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.19</v>
+        <v>-1.34</v>
       </c>
       <c r="P15" t="n">
         <v>5.16</v>
@@ -1383,13 +1383,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.93</v>
+        <v>4.89</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>4.89</v>
@@ -1401,22 +1401,22 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.64</v>
       </c>
       <c r="M16" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.64</v>
+        <v>0.21</v>
       </c>
       <c r="P16" t="n">
         <v>4.82</v>
@@ -1448,10 +1448,10 @@
         <v>3.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>3.5</v>
@@ -1463,22 +1463,22 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>-2.24</v>
       </c>
       <c r="P17" t="n">
         <v>3.49</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.31</v>
+        <v>1.18</v>
       </c>
       <c r="G18" t="n">
         <v>3.43</v>
@@ -1528,19 +1528,19 @@
         <v>3.43</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="P18" t="n">
         <v>3.38</v>
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60.8</v>
+        <v>60.85</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.35</v>
+        <v>0.05</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.57</v>
+        <v>0.08</v>
       </c>
       <c r="G19" t="n">
         <v>60.85</v>
@@ -1587,22 +1587,22 @@
         <v>0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>60.85</v>
+        <v>60.65</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="M19" t="n">
-        <v>60.65</v>
+        <v>59.9</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.33</v>
+        <v>-1.24</v>
       </c>
       <c r="P19" t="n">
         <v>59.9</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.72</v>
+        <v>28.92</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.37</v>
+        <v>0.7</v>
       </c>
       <c r="G20" t="n">
         <v>28.92</v>
@@ -1649,22 +1649,22 @@
         <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>28.92</v>
+        <v>29.42</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>29.42</v>
+        <v>28.84</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>-0.58</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>-1.97</v>
       </c>
       <c r="P20" t="n">
         <v>28.84</v>
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.62</v>
+        <v>-1.46</v>
       </c>
       <c r="G21" t="n">
         <v>5.39</v>
@@ -1711,22 +1711,22 @@
         <v>-1.46</v>
       </c>
       <c r="J21" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.46</v>
+        <v>-1.11</v>
       </c>
       <c r="M21" t="n">
-        <v>5.33</v>
+        <v>5.28</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P21" t="n">
         <v>5.28</v>
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86.05</v>
+        <v>85.5</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5</v>
+        <v>-0.55</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.58</v>
+        <v>-0.64</v>
       </c>
       <c r="G22" t="n">
         <v>85.5</v>
@@ -1773,22 +1773,22 @@
         <v>-0.64</v>
       </c>
       <c r="J22" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.64</v>
+        <v>0.12</v>
       </c>
       <c r="M22" t="n">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0.12</v>
+        <v>-0.47</v>
       </c>
       <c r="P22" t="n">
         <v>85.2</v>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.78</v>
+        <v>24.48</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.82</v>
+        <v>0.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.33</v>
+        <v>2.94</v>
       </c>
       <c r="G23" t="n">
         <v>24.48</v>
@@ -1835,22 +1835,22 @@
         <v>2.94</v>
       </c>
       <c r="J23" t="n">
-        <v>24.48</v>
+        <v>24.92</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="L23" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>24.92</v>
+        <v>24.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="O23" t="n">
-        <v>1.8</v>
+        <v>-1.28</v>
       </c>
       <c r="P23" t="n">
         <v>24.6</v>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.52</v>
+        <v>28.3</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.08</v>
+        <v>0.78</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.78</v>
+        <v>2.83</v>
       </c>
       <c r="G24" t="n">
         <v>28.3</v>
@@ -1897,22 +1897,22 @@
         <v>2.83</v>
       </c>
       <c r="J24" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="L24" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="M24" t="n">
-        <v>28.8</v>
+        <v>28.16</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5</v>
+        <v>-0.64</v>
       </c>
       <c r="O24" t="n">
-        <v>1.77</v>
+        <v>-2.22</v>
       </c>
       <c r="P24" t="n">
         <v>28.16</v>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29.66</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.48</v>
+        <v>0.34</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.59</v>
+        <v>1.15</v>
       </c>
       <c r="G25" t="n">
         <v>30</v>
@@ -1959,22 +1959,22 @@
         <v>1.15</v>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>29.76</v>
       </c>
       <c r="K25" t="n">
-        <v>0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="L25" t="n">
-        <v>1.15</v>
+        <v>-0.8</v>
       </c>
       <c r="M25" t="n">
-        <v>29.76</v>
+        <v>28.4</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.24</v>
+        <v>-1.36</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8</v>
+        <v>-4.57</v>
       </c>
       <c r="P25" t="n">
         <v>28.4</v>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46.8</v>
+        <v>48.88</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.9</v>
+        <v>2.08</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.69</v>
+        <v>4.44</v>
       </c>
       <c r="G26" t="n">
         <v>48.88</v>
@@ -2021,22 +2021,22 @@
         <v>4.44</v>
       </c>
       <c r="J26" t="n">
-        <v>48.88</v>
+        <v>51.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="L26" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
       <c r="M26" t="n">
-        <v>51.1</v>
+        <v>52.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="O26" t="n">
-        <v>4.54</v>
+        <v>3.03</v>
       </c>
       <c r="P26" t="n">
         <v>52.65</v>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>439</v>
+        <v>441.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-16.2</v>
+        <v>2.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.56</v>
+        <v>0.55</v>
       </c>
       <c r="G27" t="n">
         <v>441.4</v>
@@ -2083,22 +2083,22 @@
         <v>0.55</v>
       </c>
       <c r="J27" t="n">
-        <v>441.4</v>
+        <v>439</v>
       </c>
       <c r="K27" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="L27" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="M27" t="n">
-        <v>439</v>
+        <v>434.4</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.54</v>
+        <v>-1.05</v>
       </c>
       <c r="P27" t="n">
         <v>434.4</v>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.9</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.47</v>
+        <v>0.79</v>
       </c>
       <c r="G28" t="n">
         <v>127</v>
@@ -2145,22 +2145,22 @@
         <v>0.79</v>
       </c>
       <c r="J28" t="n">
-        <v>127</v>
+        <v>127.6</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="M28" t="n">
-        <v>127.6</v>
+        <v>124.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6</v>
+        <v>-3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0.47</v>
+        <v>-2.59</v>
       </c>
       <c r="P28" t="n">
         <v>124.3</v>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>123.5</v>
+        <v>121.7</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.3</v>
+        <v>-1.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.36</v>
+        <v>-1.46</v>
       </c>
       <c r="G29" t="n">
         <v>121.7</v>
@@ -2207,22 +2207,22 @@
         <v>-1.46</v>
       </c>
       <c r="J29" t="n">
-        <v>121.7</v>
+        <v>118.6</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.46</v>
+        <v>-2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>118.6</v>
+        <v>116.3</v>
       </c>
       <c r="N29" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="O29" t="n">
-        <v>-2.55</v>
+        <v>-1.94</v>
       </c>
       <c r="P29" t="n">
         <v>116.3</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82.09999999999999</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="E30" t="n">
         <v>-0.75</v>
@@ -2269,22 +2269,22 @@
         <v>-0.91</v>
       </c>
       <c r="J30" t="n">
-        <v>81.34999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.75</v>
+        <v>-2.55</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.91</v>
+        <v>-3.13</v>
       </c>
       <c r="M30" t="n">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="N30" t="n">
-        <v>-2.55</v>
+        <v>-1.1</v>
       </c>
       <c r="O30" t="n">
-        <v>-3.13</v>
+        <v>-1.4</v>
       </c>
       <c r="P30" t="n">
         <v>77.7</v>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>126.5</v>
+        <v>128.2</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.7</v>
+        <v>1.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-5.74</v>
+        <v>1.34</v>
       </c>
       <c r="G31" t="n">
         <v>128.2</v>
@@ -2331,22 +2331,22 @@
         <v>1.34</v>
       </c>
       <c r="J31" t="n">
+        <v>128</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M31" t="n">
         <v>128.2</v>
       </c>
-      <c r="K31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M31" t="n">
-        <v>128</v>
-      </c>
       <c r="N31" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.16</v>
+        <v>0.16</v>
       </c>
       <c r="P31" t="n">
         <v>128.2</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>74.2</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.95</v>
+        <v>5.65</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.26</v>
+        <v>7.61</v>
       </c>
       <c r="G32" t="n">
         <v>79.84999999999999</v>
@@ -2393,22 +2393,22 @@
         <v>7.61</v>
       </c>
       <c r="J32" t="n">
-        <v>79.84999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>5.65</v>
+        <v>4.55</v>
       </c>
       <c r="L32" t="n">
-        <v>7.61</v>
+        <v>5.7</v>
       </c>
       <c r="M32" t="n">
-        <v>84.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="N32" t="n">
-        <v>4.55</v>
+        <v>0.8</v>
       </c>
       <c r="O32" t="n">
-        <v>5.7</v>
+        <v>0.95</v>
       </c>
       <c r="P32" t="n">
         <v>85.2</v>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>90.55</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.39</v>
+        <v>1.16</v>
       </c>
       <c r="G33" t="n">
         <v>91.59999999999999</v>
@@ -2455,22 +2455,22 @@
         <v>1.16</v>
       </c>
       <c r="J33" t="n">
-        <v>91.59999999999999</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>1.05</v>
+        <v>2.05</v>
       </c>
       <c r="L33" t="n">
-        <v>1.16</v>
+        <v>2.24</v>
       </c>
       <c r="M33" t="n">
-        <v>93.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>-2.95</v>
       </c>
       <c r="O33" t="n">
-        <v>2.24</v>
+        <v>-3.15</v>
       </c>
       <c r="P33" t="n">
         <v>90.7</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>44.98</v>
+        <v>45.64</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.7</v>
+        <v>0.66</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.66</v>
+        <v>1.47</v>
       </c>
       <c r="G34" t="n">
         <v>45.64</v>
@@ -2517,22 +2517,22 @@
         <v>1.47</v>
       </c>
       <c r="J34" t="n">
-        <v>45.64</v>
+        <v>45.8</v>
       </c>
       <c r="K34" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>0.35</v>
       </c>
       <c r="M34" t="n">
-        <v>45.8</v>
+        <v>45.28</v>
       </c>
       <c r="N34" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="O34" t="n">
-        <v>0.35</v>
+        <v>-1.14</v>
       </c>
       <c r="P34" t="n">
         <v>45.28</v>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.67</v>
+        <v>4.76</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.1</v>
+        <v>1.93</v>
       </c>
       <c r="G35" t="n">
         <v>4.76</v>
@@ -2579,22 +2579,22 @@
         <v>1.93</v>
       </c>
       <c r="J35" t="n">
-        <v>4.76</v>
+        <v>4.84</v>
       </c>
       <c r="K35" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="M35" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="O35" t="n">
-        <v>1.68</v>
+        <v>-0.83</v>
       </c>
       <c r="P35" t="n">
         <v>4.8</v>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.03</v>
+        <v>10.22</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.21</v>
+        <v>0.19</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.05</v>
+        <v>1.89</v>
       </c>
       <c r="G36" t="n">
         <v>10.22</v>
@@ -2641,22 +2641,22 @@
         <v>1.89</v>
       </c>
       <c r="J36" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="K36" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="L36" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="M36" t="n">
-        <v>10.4</v>
+        <v>10.32</v>
       </c>
       <c r="N36" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="O36" t="n">
-        <v>1.76</v>
+        <v>-0.77</v>
       </c>
       <c r="P36" t="n">
         <v>10.32</v>
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>407.4</v>
+        <v>409.2</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.8</v>
+        <v>1.8</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.92</v>
+        <v>0.44</v>
       </c>
       <c r="G37" t="n">
         <v>409.2</v>
@@ -2703,22 +2703,22 @@
         <v>0.44</v>
       </c>
       <c r="J37" t="n">
-        <v>409.2</v>
+        <v>405.6</v>
       </c>
       <c r="K37" t="n">
-        <v>1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="M37" t="n">
-        <v>405.6</v>
+        <v>402.2</v>
       </c>
       <c r="N37" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.88</v>
+        <v>-0.84</v>
       </c>
       <c r="P37" t="n">
         <v>402.2</v>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.21</v>
+        <v>15.14</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
       <c r="G38" t="n">
         <v>15.14</v>
@@ -2765,22 +2765,22 @@
         <v>-0.46</v>
       </c>
       <c r="J38" t="n">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.46</v>
+        <v>-0.26</v>
       </c>
       <c r="M38" t="n">
-        <v>15.1</v>
+        <v>15.04</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.26</v>
+        <v>-0.4</v>
       </c>
       <c r="P38" t="n">
         <v>15.04</v>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>673.5</v>
+        <v>686</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="F39" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="G39" t="n">
         <v>686</v>
@@ -2827,22 +2827,22 @@
         <v>1.86</v>
       </c>
       <c r="J39" t="n">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="K39" t="n">
-        <v>12.5</v>
+        <v>-28</v>
       </c>
       <c r="L39" t="n">
-        <v>1.86</v>
+        <v>-4.08</v>
       </c>
       <c r="M39" t="n">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="N39" t="n">
-        <v>-28</v>
+        <v>42</v>
       </c>
       <c r="O39" t="n">
-        <v>-4.08</v>
+        <v>6.38</v>
       </c>
       <c r="P39" t="n">
         <v>700</v>
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>60.6</v>
+        <v>62.6</v>
       </c>
       <c r="E40" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>4.57</v>
+        <v>3.3</v>
       </c>
       <c r="G40" t="n">
         <v>62.6</v>
@@ -2889,22 +2889,22 @@
         <v>3.3</v>
       </c>
       <c r="J40" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="L40" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="M40" t="n">
-        <v>65.2</v>
+        <v>62.85</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>-2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>4.15</v>
+        <v>-3.6</v>
       </c>
       <c r="P40" t="n">
         <v>62.85</v>
@@ -2933,31 +2933,31 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.33</v>
+        <v>23.53</v>
       </c>
       <c r="E41" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="F41" t="n">
-        <v>0.39</v>
+        <v>0.86</v>
       </c>
       <c r="G41" t="n">
-        <v>23.53</v>
+        <v>23.51</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="I41" t="n">
-        <v>0.86</v>
+        <v>-0.08</v>
       </c>
       <c r="J41" t="n">
-        <v>23.51</v>
+        <v>23.36</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.08</v>
+        <v>-0.64</v>
       </c>
       <c r="M41" t="n">
         <v>23.36</v>
@@ -2995,31 +2995,31 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>61.75</v>
+        <v>62.1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="F42" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="G42" t="n">
-        <v>62.1</v>
+        <v>62.18</v>
       </c>
       <c r="H42" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="J42" t="n">
-        <v>62.18</v>
+        <v>62</v>
       </c>
       <c r="K42" t="n">
-        <v>0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="L42" t="n">
-        <v>0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="M42" t="n">
         <v>62</v>
@@ -3057,31 +3057,31 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.69</v>
+        <v>37.7</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F43" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="G43" t="n">
-        <v>37.7</v>
+        <v>37.91</v>
       </c>
       <c r="H43" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>37.91</v>
+        <v>37.72</v>
       </c>
       <c r="K43" t="n">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="M43" t="n">
         <v>37.72</v>
@@ -3119,31 +3119,31 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="E44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="K44" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F44" t="n">
+      <c r="L44" t="n">
         <v>-0.16</v>
-      </c>
-      <c r="G44" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.16</v>
       </c>
       <c r="M44" t="n">
         <v>6.21</v>
@@ -3181,31 +3181,31 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="E45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F45" t="n">
+      <c r="L45" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="K45" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-0.9</v>
       </c>
       <c r="M45" t="n">
         <v>2.2</v>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F46" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="G46" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="H46" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="I46" t="n">
-        <v>0.92</v>
+        <v>2.74</v>
       </c>
       <c r="J46" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="K46" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="L46" t="n">
-        <v>2.74</v>
+        <v>5.64</v>
       </c>
       <c r="M46" t="n">
         <v>3.56</v>
@@ -3305,31 +3305,31 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.11</v>
+        <v>11.27</v>
       </c>
       <c r="E47" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="F47" t="n">
-        <v>0.45</v>
+        <v>1.44</v>
       </c>
       <c r="G47" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="H47" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="I47" t="n">
-        <v>1.44</v>
+        <v>-0.18</v>
       </c>
       <c r="J47" t="n">
-        <v>11.25</v>
+        <v>11.1</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.18</v>
+        <v>-1.33</v>
       </c>
       <c r="M47" t="n">
         <v>11.1</v>
@@ -3367,31 +3367,31 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>1.49</v>
+        <v>-1.47</v>
       </c>
       <c r="G48" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="H48" t="n">
         <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
       <c r="J48" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="K48" t="n">
         <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.49</v>
+        <v>-1.52</v>
       </c>
       <c r="M48" t="n">
         <v>0.325</v>
@@ -3429,31 +3429,31 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.32</v>
+        <v>-0.11</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.37</v>
+        <v>-2.34</v>
       </c>
       <c r="G49" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="I49" t="n">
-        <v>-2.34</v>
+        <v>-1.09</v>
       </c>
       <c r="J49" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.09</v>
+        <v>-1.32</v>
       </c>
       <c r="M49" t="n">
         <v>4.48</v>
@@ -3553,31 +3553,31 @@
         </is>
       </c>
       <c r="D51" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="J51" t="n">
         <v>3.7</v>
       </c>
-      <c r="E51" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="G51" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K51" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.79</v>
+        <v>-1.33</v>
       </c>
       <c r="M51" t="n">
         <v>3.7</v>
@@ -3615,31 +3615,31 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.42</v>
+        <v>10.91</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="F52" t="n">
-        <v>0.97</v>
+        <v>4.7</v>
       </c>
       <c r="G52" t="n">
-        <v>10.91</v>
+        <v>11.07</v>
       </c>
       <c r="H52" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="I52" t="n">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="J52" t="n">
-        <v>11.07</v>
+        <v>10.84</v>
       </c>
       <c r="K52" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="L52" t="n">
-        <v>1.47</v>
+        <v>-2.08</v>
       </c>
       <c r="M52" t="n">
         <v>10.84</v>
@@ -3677,31 +3677,31 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.15</v>
+        <v>8.17</v>
       </c>
       <c r="E53" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="F53" t="n">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
       <c r="G53" t="n">
-        <v>8.17</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.25</v>
+        <v>3.43</v>
       </c>
       <c r="J53" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="K53" t="n">
-        <v>0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="L53" t="n">
-        <v>3.43</v>
+        <v>-2.49</v>
       </c>
       <c r="M53" t="n">
         <v>8.24</v>
@@ -3739,31 +3739,31 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.465</v>
+        <v>0.46</v>
       </c>
       <c r="E54" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>1.09</v>
+        <v>-1.08</v>
       </c>
       <c r="G54" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="H54" t="n">
         <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
       <c r="J54" t="n">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="K54" t="n">
         <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
       <c r="M54" t="n">
         <v>0.45</v>
@@ -3872,22 +3872,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="J56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.11</v>
+        <v>1.08</v>
       </c>
       <c r="M56" t="n">
         <v>0.47</v>
@@ -3925,31 +3925,31 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.22</v>
+        <v>-0.55</v>
       </c>
       <c r="G57" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.55</v>
+        <v>-0.28</v>
       </c>
       <c r="J57" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.28</v>
+        <v>-1.68</v>
       </c>
       <c r="M57" t="n">
         <v>3.52</v>
@@ -3987,22 +3987,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
       <c r="G58" t="n">
         <v>0.079</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0.079</v>
@@ -4049,31 +4049,31 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.38</v>
+        <v>22.4</v>
       </c>
       <c r="E59" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="F59" t="n">
-        <v>2.38</v>
+        <v>0.09</v>
       </c>
       <c r="G59" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="H59" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="J59" t="n">
-        <v>22.29</v>
+        <v>21.8</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.49</v>
+        <v>-2.2</v>
       </c>
       <c r="M59" t="n">
         <v>21.8</v>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="E60" t="n">
         <v>0.01</v>
@@ -4120,22 +4120,22 @@
         <v>0.32</v>
       </c>
       <c r="G60" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="J60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="K60" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="L60" t="n">
-        <v>0.95</v>
+        <v>-0.62</v>
       </c>
       <c r="M60" t="n">
         <v>3.18</v>
@@ -4173,31 +4173,31 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="G61" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.74</v>
+        <v>5.19</v>
       </c>
       <c r="J61" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="K61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="L61" t="n">
-        <v>5.19</v>
+        <v>-3.52</v>
       </c>
       <c r="M61" t="n">
         <v>1.37</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-22 Close</t>
+          <t>2026-05-25 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change</t>
+          <t>2026-05-25 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-22 Change %</t>
+          <t>2026-05-25 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-25 Close</t>
+          <t>2026-05-26 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change</t>
+          <t>2026-05-26 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change %</t>
+          <t>2026-05-26 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-26 Close</t>
+          <t>2026-05-27 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change</t>
+          <t>2026-05-27 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change %</t>
+          <t>2026-05-27 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-27 Close</t>
+          <t>2026-05-28 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change</t>
+          <t>2026-05-28 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change %</t>
+          <t>2026-05-28 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-28 Close</t>
+          <t>2026-05-29 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change</t>
+          <t>2026-05-29 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change %</t>
+          <t>2026-05-29 Change %</t>
         </is>
       </c>
     </row>
@@ -586,40 +586,40 @@
         <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>143.9</v>
+        <v>145.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="J3" t="n">
-        <v>145.5</v>
+        <v>146.6</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>146.6</v>
+        <v>145.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.76</v>
+        <v>-0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>146.6</v>
+        <v>145.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0.76</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="4">
@@ -648,40 +648,40 @@
         <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>204</v>
+        <v>207.4</v>
       </c>
       <c r="H4" t="n">
         <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J4" t="n">
-        <v>207.4</v>
+        <v>209.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>0.87</v>
       </c>
       <c r="M4" t="n">
-        <v>209.2</v>
+        <v>206.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>0.87</v>
+        <v>-1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>209.2</v>
+        <v>206.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -710,40 +710,40 @@
         <v>0.68</v>
       </c>
       <c r="G5" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.68</v>
+        <v>-2.53</v>
       </c>
       <c r="J5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="P5" t="n">
         <v>5.77</v>
       </c>
-      <c r="K5" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5.82</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="6">
@@ -772,40 +772,40 @@
         <v>0.74</v>
       </c>
       <c r="G6" t="n">
-        <v>6.85</v>
+        <v>6.78</v>
       </c>
       <c r="H6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="R6" t="n">
-        <v>-0.88</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="7">
@@ -834,40 +834,40 @@
         <v>0.58</v>
       </c>
       <c r="G7" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>5.19</v>
+        <v>5.13</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.19</v>
+        <v>-1.16</v>
       </c>
       <c r="P7" t="n">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.19</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="8">
@@ -896,40 +896,40 @@
         <v>0.92</v>
       </c>
       <c r="G8" t="n">
-        <v>8.77</v>
+        <v>8.73</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="J8" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.46</v>
+        <v>-1.72</v>
       </c>
       <c r="M8" t="n">
-        <v>8.58</v>
+        <v>8.48</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.72</v>
+        <v>-1.17</v>
       </c>
       <c r="P8" t="n">
-        <v>8.58</v>
+        <v>8.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.72</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="9">
@@ -961,37 +961,37 @@
         <v>7.17</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>7.17</v>
+        <v>7.13</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>7.13</v>
+        <v>7.07</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.84</v>
       </c>
       <c r="P9" t="n">
-        <v>7.13</v>
+        <v>7.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.04</v>
+        <v>0.23</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="10">
@@ -1020,40 +1020,40 @@
         <v>0.26</v>
       </c>
       <c r="G10" t="n">
-        <v>46.26</v>
+        <v>45.98</v>
       </c>
       <c r="H10" t="n">
-        <v>0.12</v>
+        <v>-0.28</v>
       </c>
       <c r="I10" t="n">
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
       <c r="J10" t="n">
-        <v>45.98</v>
+        <v>45.82</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.61</v>
+        <v>-0.35</v>
       </c>
       <c r="M10" t="n">
-        <v>45.82</v>
+        <v>45.92</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.35</v>
+        <v>0.22</v>
       </c>
       <c r="P10" t="n">
-        <v>45.82</v>
+        <v>47.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.16</v>
+        <v>1.18</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.35</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="11">
@@ -1082,7 +1082,7 @@
         <v>-0.23</v>
       </c>
       <c r="G11" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="H11" t="n">
         <v>-0.01</v>
@@ -1091,31 +1091,31 @@
         <v>-0.23</v>
       </c>
       <c r="J11" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.23</v>
+        <v>-1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="P11" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="12">
@@ -1144,40 +1144,40 @@
         <v>-1.01</v>
       </c>
       <c r="G12" t="n">
-        <v>10.83</v>
+        <v>10.91</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.01</v>
+        <v>0.74</v>
       </c>
       <c r="J12" t="n">
-        <v>10.91</v>
+        <v>10.7</v>
       </c>
       <c r="K12" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.08</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="O12" t="n">
-        <v>-1.92</v>
+        <v>0.75</v>
       </c>
       <c r="P12" t="n">
-        <v>10.7</v>
+        <v>10.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.21</v>
+        <v>0.11</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.92</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="13">
@@ -1206,40 +1206,40 @@
         <v>0.51</v>
       </c>
       <c r="G13" t="n">
-        <v>27.44</v>
+        <v>26.92</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>-0.52</v>
       </c>
       <c r="I13" t="n">
-        <v>0.51</v>
+        <v>-1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>26.92</v>
+        <v>26.32</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.52</v>
+        <v>-0.6</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9</v>
+        <v>-2.23</v>
       </c>
       <c r="M13" t="n">
-        <v>26.32</v>
+        <v>26.16</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6</v>
+        <v>-0.16</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.23</v>
+        <v>-0.61</v>
       </c>
       <c r="P13" t="n">
-        <v>26.32</v>
+        <v>26.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.6</v>
+        <v>0.24</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.23</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="14">
@@ -1268,40 +1268,40 @@
         <v>-0.4</v>
       </c>
       <c r="G14" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="H14" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I14" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="O14" t="n">
-        <v>-2.09</v>
+        <v>-0.43</v>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.09</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="15">
@@ -1330,40 +1330,40 @@
         <v>1.36</v>
       </c>
       <c r="G15" t="n">
-        <v>5.22</v>
+        <v>5.23</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>1.36</v>
+        <v>0.19</v>
       </c>
       <c r="J15" t="n">
-        <v>5.23</v>
+        <v>5.16</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.19</v>
+        <v>-1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>5.16</v>
+        <v>5.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.34</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="16">
@@ -1392,40 +1392,40 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.64</v>
       </c>
       <c r="J16" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.64</v>
+        <v>0.21</v>
       </c>
       <c r="M16" t="n">
-        <v>4.82</v>
+        <v>4.77</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.21</v>
+        <v>-1.04</v>
       </c>
       <c r="P16" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="R16" t="n">
-        <v>0.21</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="17">
@@ -1454,40 +1454,40 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>-2.24</v>
       </c>
       <c r="M17" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.24</v>
+        <v>-1.15</v>
       </c>
       <c r="P17" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.08</v>
+        <v>0.06</v>
       </c>
       <c r="R17" t="n">
-        <v>-2.24</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="18">
@@ -1519,37 +1519,37 @@
         <v>3.43</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="M18" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.46</v>
+        <v>-0.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.46</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="19">
@@ -1578,40 +1578,40 @@
         <v>0.08</v>
       </c>
       <c r="G19" t="n">
-        <v>60.85</v>
+        <v>60.65</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="J19" t="n">
-        <v>60.65</v>
+        <v>59.9</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.33</v>
+        <v>-1.24</v>
       </c>
       <c r="M19" t="n">
-        <v>59.9</v>
+        <v>59.25</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.75</v>
+        <v>-0.65</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.24</v>
+        <v>-1.09</v>
       </c>
       <c r="P19" t="n">
-        <v>59.9</v>
+        <v>60.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.75</v>
+        <v>0.8</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.24</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="20">
@@ -1640,40 +1640,40 @@
         <v>0.7</v>
       </c>
       <c r="G20" t="n">
-        <v>28.92</v>
+        <v>29.42</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.73</v>
       </c>
       <c r="J20" t="n">
-        <v>29.42</v>
+        <v>28.84</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>-0.58</v>
       </c>
       <c r="L20" t="n">
-        <v>1.73</v>
+        <v>-1.97</v>
       </c>
       <c r="M20" t="n">
-        <v>28.84</v>
+        <v>28.56</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.58</v>
+        <v>-0.28</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.97</v>
+        <v>-0.97</v>
       </c>
       <c r="P20" t="n">
-        <v>28.84</v>
+        <v>28.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.58</v>
+        <v>0.32</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.97</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="21">
@@ -1702,40 +1702,40 @@
         <v>-1.46</v>
       </c>
       <c r="G21" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.46</v>
+        <v>-1.11</v>
       </c>
       <c r="J21" t="n">
-        <v>5.33</v>
+        <v>5.28</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="N21" t="n">
         <v>-0.05</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="P21" t="n">
-        <v>5.28</v>
+        <v>5.18</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.05</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="22">
@@ -1764,40 +1764,40 @@
         <v>-0.64</v>
       </c>
       <c r="G22" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.64</v>
+        <v>0.12</v>
       </c>
       <c r="J22" t="n">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L22" t="n">
-        <v>0.12</v>
+        <v>-0.47</v>
       </c>
       <c r="M22" t="n">
-        <v>85.2</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="P22" t="n">
-        <v>85.2</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.47</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="23">
@@ -1826,40 +1826,40 @@
         <v>2.94</v>
       </c>
       <c r="G23" t="n">
-        <v>24.48</v>
+        <v>24.92</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="I23" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
-        <v>24.92</v>
+        <v>24.6</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>-1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>24.6</v>
+        <v>27.82</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.32</v>
+        <v>3.22</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.28</v>
+        <v>13.09</v>
       </c>
       <c r="P23" t="n">
-        <v>24.6</v>
+        <v>26.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.32</v>
+        <v>-1.04</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.28</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="24">
@@ -1888,40 +1888,40 @@
         <v>2.83</v>
       </c>
       <c r="G24" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="H24" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="J24" t="n">
-        <v>28.8</v>
+        <v>28.16</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>-0.64</v>
       </c>
       <c r="L24" t="n">
-        <v>1.77</v>
+        <v>-2.22</v>
       </c>
       <c r="M24" t="n">
-        <v>28.16</v>
+        <v>28.26</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.22</v>
+        <v>0.36</v>
       </c>
       <c r="P24" t="n">
-        <v>28.16</v>
+        <v>30.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.64</v>
+        <v>1.88</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.22</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="25">
@@ -1950,40 +1950,40 @@
         <v>1.15</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>29.76</v>
       </c>
       <c r="H25" t="n">
-        <v>0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="I25" t="n">
-        <v>1.15</v>
+        <v>-0.8</v>
       </c>
       <c r="J25" t="n">
-        <v>29.76</v>
+        <v>28.4</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.24</v>
+        <v>-1.36</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8</v>
+        <v>-4.57</v>
       </c>
       <c r="M25" t="n">
-        <v>28.4</v>
+        <v>28.56</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.36</v>
+        <v>0.16</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>28.4</v>
+        <v>28.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.36</v>
+        <v>-0.52</v>
       </c>
       <c r="R25" t="n">
-        <v>-4.57</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="26">
@@ -2012,40 +2012,40 @@
         <v>4.44</v>
       </c>
       <c r="G26" t="n">
-        <v>48.88</v>
+        <v>51.1</v>
       </c>
       <c r="H26" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="I26" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
       <c r="J26" t="n">
-        <v>51.1</v>
+        <v>52.65</v>
       </c>
       <c r="K26" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="L26" t="n">
-        <v>4.54</v>
+        <v>3.03</v>
       </c>
       <c r="M26" t="n">
-        <v>52.65</v>
+        <v>53.85</v>
       </c>
       <c r="N26" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="O26" t="n">
-        <v>3.03</v>
+        <v>2.28</v>
       </c>
       <c r="P26" t="n">
-        <v>52.65</v>
+        <v>61.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.55</v>
+        <v>7.9</v>
       </c>
       <c r="R26" t="n">
-        <v>3.03</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="27">
@@ -2074,40 +2074,40 @@
         <v>0.55</v>
       </c>
       <c r="G27" t="n">
-        <v>441.4</v>
+        <v>439</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="J27" t="n">
-        <v>439</v>
+        <v>434.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.54</v>
+        <v>-1.05</v>
       </c>
       <c r="M27" t="n">
-        <v>434.4</v>
+        <v>425</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.6</v>
+        <v>-9.4</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.05</v>
+        <v>-2.16</v>
       </c>
       <c r="P27" t="n">
-        <v>434.4</v>
+        <v>427.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.6</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.05</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="28">
@@ -2136,40 +2136,40 @@
         <v>0.79</v>
       </c>
       <c r="G28" t="n">
-        <v>127</v>
+        <v>127.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I28" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="J28" t="n">
-        <v>127.6</v>
+        <v>124.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6</v>
+        <v>-3.3</v>
       </c>
       <c r="L28" t="n">
-        <v>0.47</v>
+        <v>-2.59</v>
       </c>
       <c r="M28" t="n">
-        <v>124.3</v>
+        <v>121.8</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.3</v>
+        <v>-2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>-2.59</v>
+        <v>-2.01</v>
       </c>
       <c r="P28" t="n">
-        <v>124.3</v>
+        <v>120.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.3</v>
+        <v>-0.9</v>
       </c>
       <c r="R28" t="n">
-        <v>-2.59</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="29">
@@ -2198,40 +2198,40 @@
         <v>-1.46</v>
       </c>
       <c r="G29" t="n">
-        <v>121.7</v>
+        <v>118.6</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.46</v>
+        <v>-2.55</v>
       </c>
       <c r="J29" t="n">
-        <v>118.6</v>
+        <v>116.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.55</v>
+        <v>-1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>116.3</v>
+        <v>114.2</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.94</v>
+        <v>-1.81</v>
       </c>
       <c r="P29" t="n">
-        <v>116.3</v>
+        <v>113.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2.3</v>
+        <v>-0.7</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.94</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="30">
@@ -2260,40 +2260,40 @@
         <v>-0.91</v>
       </c>
       <c r="G30" t="n">
-        <v>81.34999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.75</v>
+        <v>-2.55</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.91</v>
+        <v>-3.13</v>
       </c>
       <c r="J30" t="n">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.55</v>
+        <v>-1.1</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.13</v>
+        <v>-1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>77.7</v>
+        <v>73.3</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.1</v>
+        <v>-4.4</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.4</v>
+        <v>-5.66</v>
       </c>
       <c r="P30" t="n">
-        <v>77.7</v>
+        <v>73.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.1</v>
+        <v>0.15</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -2322,40 +2322,40 @@
         <v>1.34</v>
       </c>
       <c r="G31" t="n">
+        <v>128</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J31" t="n">
         <v>128.2</v>
       </c>
-      <c r="H31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J31" t="n">
-        <v>128</v>
-      </c>
       <c r="K31" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.16</v>
+        <v>0.16</v>
       </c>
       <c r="M31" t="n">
-        <v>128.2</v>
+        <v>125.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0.16</v>
+        <v>-2.03</v>
       </c>
       <c r="P31" t="n">
-        <v>128.2</v>
+        <v>130</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0.16</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="32">
@@ -2384,40 +2384,40 @@
         <v>7.61</v>
       </c>
       <c r="G32" t="n">
-        <v>79.84999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>5.65</v>
+        <v>4.55</v>
       </c>
       <c r="I32" t="n">
-        <v>7.61</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
-        <v>84.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K32" t="n">
-        <v>4.55</v>
+        <v>0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>5.7</v>
+        <v>0.95</v>
       </c>
       <c r="M32" t="n">
-        <v>85.2</v>
+        <v>88.25</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>0.95</v>
+        <v>3.58</v>
       </c>
       <c r="P32" t="n">
-        <v>85.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.8</v>
+        <v>-6.65</v>
       </c>
       <c r="R32" t="n">
-        <v>0.95</v>
+        <v>-7.54</v>
       </c>
     </row>
     <row r="33">
@@ -2446,40 +2446,40 @@
         <v>1.16</v>
       </c>
       <c r="G33" t="n">
-        <v>91.59999999999999</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>1.05</v>
+        <v>2.05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.16</v>
+        <v>2.24</v>
       </c>
       <c r="J33" t="n">
-        <v>93.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="K33" t="n">
-        <v>2.05</v>
+        <v>-2.95</v>
       </c>
       <c r="L33" t="n">
-        <v>2.24</v>
+        <v>-3.15</v>
       </c>
       <c r="M33" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.95</v>
+        <v>-0.4</v>
       </c>
       <c r="O33" t="n">
-        <v>-3.15</v>
+        <v>-0.44</v>
       </c>
       <c r="P33" t="n">
-        <v>90.7</v>
+        <v>91.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2.95</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>-3.15</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="34">
@@ -2508,40 +2508,40 @@
         <v>1.47</v>
       </c>
       <c r="G34" t="n">
-        <v>45.64</v>
+        <v>45.8</v>
       </c>
       <c r="H34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J34" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="P34" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.66</v>
       </c>
-      <c r="I34" t="n">
+      <c r="R34" t="n">
         <v>1.47</v>
-      </c>
-      <c r="J34" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M34" t="n">
-        <v>45.28</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="P34" t="n">
-        <v>45.28</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="R34" t="n">
-        <v>-1.14</v>
       </c>
     </row>
     <row r="35">
@@ -2570,40 +2570,40 @@
         <v>1.93</v>
       </c>
       <c r="G35" t="n">
-        <v>4.76</v>
+        <v>4.84</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="I35" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="J35" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="K35" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="L35" t="n">
-        <v>1.68</v>
+        <v>-0.83</v>
       </c>
       <c r="M35" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.83</v>
+        <v>-0.42</v>
       </c>
       <c r="P35" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2632,40 +2632,40 @@
         <v>1.89</v>
       </c>
       <c r="G36" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="H36" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="I36" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="J36" t="n">
-        <v>10.4</v>
+        <v>10.32</v>
       </c>
       <c r="K36" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="L36" t="n">
-        <v>1.76</v>
+        <v>-0.77</v>
       </c>
       <c r="M36" t="n">
-        <v>10.32</v>
+        <v>10.28</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.77</v>
+        <v>-0.39</v>
       </c>
       <c r="P36" t="n">
-        <v>10.32</v>
+        <v>10.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.77</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="37">
@@ -2694,40 +2694,40 @@
         <v>0.44</v>
       </c>
       <c r="G37" t="n">
-        <v>409.2</v>
+        <v>405.6</v>
       </c>
       <c r="H37" t="n">
-        <v>1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="I37" t="n">
-        <v>0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="J37" t="n">
-        <v>405.6</v>
+        <v>402.2</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.88</v>
+        <v>-0.84</v>
       </c>
       <c r="M37" t="n">
-        <v>402.2</v>
+        <v>396.2</v>
       </c>
       <c r="N37" t="n">
-        <v>-3.4</v>
+        <v>-6</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.84</v>
+        <v>-1.49</v>
       </c>
       <c r="P37" t="n">
-        <v>402.2</v>
+        <v>399.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.84</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="38">
@@ -2756,40 +2756,40 @@
         <v>-0.46</v>
       </c>
       <c r="G38" t="n">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.46</v>
+        <v>-0.26</v>
       </c>
       <c r="J38" t="n">
-        <v>15.1</v>
+        <v>15.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.26</v>
+        <v>-0.4</v>
       </c>
       <c r="M38" t="n">
-        <v>15.04</v>
+        <v>14.9</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.4</v>
+        <v>-0.93</v>
       </c>
       <c r="P38" t="n">
-        <v>15.04</v>
+        <v>15.33</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.06</v>
+        <v>0.43</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.4</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="39">
@@ -2818,40 +2818,40 @@
         <v>1.86</v>
       </c>
       <c r="G39" t="n">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="H39" t="n">
-        <v>12.5</v>
+        <v>-28</v>
       </c>
       <c r="I39" t="n">
-        <v>1.86</v>
+        <v>-4.08</v>
       </c>
       <c r="J39" t="n">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="K39" t="n">
-        <v>-28</v>
+        <v>42</v>
       </c>
       <c r="L39" t="n">
-        <v>-4.08</v>
+        <v>6.38</v>
       </c>
       <c r="M39" t="n">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="N39" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="O39" t="n">
-        <v>6.38</v>
+        <v>2.43</v>
       </c>
       <c r="P39" t="n">
-        <v>700</v>
+        <v>744.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>42</v>
+        <v>27.5</v>
       </c>
       <c r="R39" t="n">
-        <v>6.38</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="40">
@@ -2880,40 +2880,40 @@
         <v>3.3</v>
       </c>
       <c r="G40" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="J40" t="n">
-        <v>65.2</v>
+        <v>62.85</v>
       </c>
       <c r="K40" t="n">
-        <v>2.6</v>
+        <v>-2.35</v>
       </c>
       <c r="L40" t="n">
-        <v>4.15</v>
+        <v>-3.6</v>
       </c>
       <c r="M40" t="n">
-        <v>62.85</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>-2.35</v>
+        <v>3.5</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.6</v>
+        <v>5.57</v>
       </c>
       <c r="P40" t="n">
-        <v>62.85</v>
+        <v>63.85</v>
       </c>
       <c r="Q40" t="n">
-        <v>-2.35</v>
+        <v>-2.5</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.6</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="41">
@@ -2933,22 +2933,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.53</v>
+        <v>23.51</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="F41" t="n">
-        <v>0.86</v>
+        <v>-0.08</v>
       </c>
       <c r="G41" t="n">
-        <v>23.51</v>
+        <v>23.36</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.08</v>
+        <v>-0.64</v>
       </c>
       <c r="J41" t="n">
         <v>23.36</v>
@@ -2960,22 +2960,22 @@
         <v>-0.64</v>
       </c>
       <c r="M41" t="n">
-        <v>23.36</v>
+        <v>23.16</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.64</v>
+        <v>-0.86</v>
       </c>
       <c r="P41" t="n">
-        <v>23.36</v>
+        <v>23.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.15</v>
+        <v>0.24</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.64</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="42">
@@ -2995,22 +2995,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>62.1</v>
+        <v>62.18</v>
       </c>
       <c r="E42" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="F42" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="G42" t="n">
-        <v>62.18</v>
+        <v>62</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="J42" t="n">
         <v>62</v>
@@ -3022,22 +3022,22 @@
         <v>-0.29</v>
       </c>
       <c r="M42" t="n">
-        <v>62</v>
+        <v>61.93</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.29</v>
+        <v>-0.11</v>
       </c>
       <c r="P42" t="n">
-        <v>62</v>
+        <v>62.84</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.18</v>
+        <v>0.91</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.29</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="43">
@@ -3057,22 +3057,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.7</v>
+        <v>37.91</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="F43" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>37.91</v>
+        <v>37.72</v>
       </c>
       <c r="H43" t="n">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="J43" t="n">
         <v>37.72</v>
@@ -3084,22 +3084,22 @@
         <v>-0.5</v>
       </c>
       <c r="M43" t="n">
-        <v>37.72</v>
+        <v>37.69</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.5</v>
+        <v>-0.08</v>
       </c>
       <c r="P43" t="n">
-        <v>37.72</v>
+        <v>37.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.19</v>
+        <v>-0.09</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="44">
@@ -3119,22 +3119,22 @@
         </is>
       </c>
       <c r="D44" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G44" t="n">
         <v>6.21</v>
       </c>
-      <c r="E44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G44" t="n">
-        <v>6.22</v>
-      </c>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.16</v>
+        <v>-0.16</v>
       </c>
       <c r="J44" t="n">
         <v>6.21</v>
@@ -3146,22 +3146,22 @@
         <v>-0.16</v>
       </c>
       <c r="M44" t="n">
-        <v>6.21</v>
+        <v>6.31</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.16</v>
+        <v>1.61</v>
       </c>
       <c r="P44" t="n">
-        <v>6.21</v>
+        <v>6.39</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.16</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="45">
@@ -3181,22 +3181,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F45" t="n">
-        <v>0.45</v>
+        <v>-0.9</v>
       </c>
       <c r="G45" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="J45" t="n">
         <v>2.2</v>
@@ -3208,22 +3208,22 @@
         <v>-0.45</v>
       </c>
       <c r="M45" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.45</v>
+        <v>-1.36</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.45</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="46">
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="F46" t="n">
-        <v>0.92</v>
+        <v>2.74</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="I46" t="n">
-        <v>2.74</v>
+        <v>5.64</v>
       </c>
       <c r="J46" t="n">
         <v>3.56</v>
@@ -3270,22 +3270,22 @@
         <v>5.64</v>
       </c>
       <c r="M46" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="O46" t="n">
-        <v>5.64</v>
+        <v>6.74</v>
       </c>
       <c r="P46" t="n">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>5.64</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="47">
@@ -3305,22 +3305,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="E47" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="F47" t="n">
-        <v>1.44</v>
+        <v>-0.18</v>
       </c>
       <c r="G47" t="n">
-        <v>11.25</v>
+        <v>11.1</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.18</v>
+        <v>-1.33</v>
       </c>
       <c r="J47" t="n">
         <v>11.1</v>
@@ -3332,22 +3332,22 @@
         <v>-1.33</v>
       </c>
       <c r="M47" t="n">
-        <v>11.1</v>
+        <v>11.04</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="O47" t="n">
-        <v>-1.33</v>
+        <v>-0.54</v>
       </c>
       <c r="P47" t="n">
-        <v>11.1</v>
+        <v>11.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.15</v>
+        <v>0.34</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.33</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="48">
@@ -3367,22 +3367,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="E48" t="n">
         <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
       <c r="G48" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="H48" t="n">
         <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.49</v>
+        <v>-1.52</v>
       </c>
       <c r="J48" t="n">
         <v>0.325</v>
@@ -3397,19 +3397,19 @@
         <v>0.325</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.52</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.52</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="49">
@@ -3429,22 +3429,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.34</v>
+        <v>-1.09</v>
       </c>
       <c r="G49" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.09</v>
+        <v>-1.32</v>
       </c>
       <c r="J49" t="n">
         <v>4.48</v>
@@ -3456,22 +3456,22 @@
         <v>-1.32</v>
       </c>
       <c r="M49" t="n">
-        <v>4.48</v>
+        <v>4.36</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.32</v>
+        <v>-2.68</v>
       </c>
       <c r="P49" t="n">
-        <v>4.48</v>
+        <v>4.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R49" t="n">
-        <v>-1.32</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="50">
@@ -3527,13 +3527,13 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="51">
@@ -3553,22 +3553,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="E51" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="F51" t="n">
-        <v>2.16</v>
+        <v>-0.79</v>
       </c>
       <c r="G51" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.79</v>
+        <v>-1.33</v>
       </c>
       <c r="J51" t="n">
         <v>3.7</v>
@@ -3580,22 +3580,22 @@
         <v>-1.33</v>
       </c>
       <c r="M51" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.33</v>
+        <v>-1.62</v>
       </c>
       <c r="P51" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>-1.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3615,22 +3615,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.91</v>
+        <v>11.07</v>
       </c>
       <c r="E52" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="F52" t="n">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="G52" t="n">
-        <v>11.07</v>
+        <v>10.84</v>
       </c>
       <c r="H52" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="I52" t="n">
-        <v>1.47</v>
+        <v>-2.08</v>
       </c>
       <c r="J52" t="n">
         <v>10.84</v>
@@ -3642,22 +3642,22 @@
         <v>-2.08</v>
       </c>
       <c r="M52" t="n">
-        <v>10.84</v>
+        <v>10.72</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="O52" t="n">
-        <v>-2.08</v>
+        <v>-1.11</v>
       </c>
       <c r="P52" t="n">
-        <v>10.84</v>
+        <v>10.76</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.08</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="53">
@@ -3677,22 +3677,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.17</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="F53" t="n">
-        <v>0.25</v>
+        <v>3.43</v>
       </c>
       <c r="G53" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="H53" t="n">
-        <v>0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="I53" t="n">
-        <v>3.43</v>
+        <v>-2.49</v>
       </c>
       <c r="J53" t="n">
         <v>8.24</v>
@@ -3704,22 +3704,22 @@
         <v>-2.49</v>
       </c>
       <c r="M53" t="n">
-        <v>8.24</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.21</v>
+        <v>0.13</v>
       </c>
       <c r="O53" t="n">
-        <v>-2.49</v>
+        <v>1.58</v>
       </c>
       <c r="P53" t="n">
-        <v>8.24</v>
+        <v>8.58</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.21</v>
+        <v>0.21</v>
       </c>
       <c r="R53" t="n">
-        <v>-2.49</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="54">
@@ -3739,22 +3739,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="E54" t="n">
         <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
       <c r="G54" t="n">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="H54" t="n">
         <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0.45</v>
@@ -3769,19 +3769,19 @@
         <v>0.45</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3828,22 +3828,22 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="P55" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="56">
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="G56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.11</v>
+        <v>1.08</v>
       </c>
       <c r="J56" t="n">
         <v>0.47</v>
@@ -3890,22 +3890,22 @@
         <v>1.08</v>
       </c>
       <c r="M56" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="N56" t="n">
         <v>0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="P56" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>1.08</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="57">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.55</v>
+        <v>-0.28</v>
       </c>
       <c r="G57" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.28</v>
+        <v>-1.68</v>
       </c>
       <c r="J57" t="n">
         <v>3.52</v>
@@ -3952,22 +3952,22 @@
         <v>-1.68</v>
       </c>
       <c r="M57" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.68</v>
+        <v>-3.69</v>
       </c>
       <c r="P57" t="n">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.06</v>
+        <v>0.2</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.68</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="58">
@@ -3990,10 +3990,10 @@
         <v>0.079</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0.079</v>
@@ -4014,22 +4014,22 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="P58" t="n">
-        <v>0.079</v>
+        <v>0.082</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="59">
@@ -4049,22 +4049,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="E59" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="F59" t="n">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="G59" t="n">
-        <v>22.29</v>
+        <v>21.8</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.49</v>
+        <v>-2.2</v>
       </c>
       <c r="J59" t="n">
         <v>21.8</v>
@@ -4076,22 +4076,22 @@
         <v>-2.2</v>
       </c>
       <c r="M59" t="n">
-        <v>21.8</v>
+        <v>21.45</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="O59" t="n">
-        <v>-2.2</v>
+        <v>-1.61</v>
       </c>
       <c r="P59" t="n">
-        <v>21.8</v>
+        <v>21.88</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.49</v>
+        <v>0.43</v>
       </c>
       <c r="R59" t="n">
-        <v>-2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -4111,22 +4111,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="G60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="H60" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.95</v>
+        <v>-0.62</v>
       </c>
       <c r="J60" t="n">
         <v>3.18</v>
@@ -4138,22 +4138,22 @@
         <v>-0.62</v>
       </c>
       <c r="M60" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="P60" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.62</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="61">
@@ -4173,22 +4173,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.74</v>
+        <v>5.19</v>
       </c>
       <c r="G61" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="H61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="I61" t="n">
-        <v>5.19</v>
+        <v>-3.52</v>
       </c>
       <c r="J61" t="n">
         <v>1.37</v>
@@ -4200,22 +4200,22 @@
         <v>-3.52</v>
       </c>
       <c r="M61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.52</v>
+        <v>-2.19</v>
       </c>
       <c r="P61" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R61" t="n">
-        <v>-3.52</v>
+        <v>2.99</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-25 Close</t>
+          <t>2026-05-26 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change</t>
+          <t>2026-05-26 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-25 Change %</t>
+          <t>2026-05-26 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-26 Close</t>
+          <t>2026-05-27 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change</t>
+          <t>2026-05-27 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change %</t>
+          <t>2026-05-27 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-27 Close</t>
+          <t>2026-05-28 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change</t>
+          <t>2026-05-28 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change %</t>
+          <t>2026-05-28 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-28 Close</t>
+          <t>2026-05-29 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change</t>
+          <t>2026-05-29 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change %</t>
+          <t>2026-05-29 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-05-29 Close</t>
+          <t>2026-06-01 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change</t>
+          <t>2026-06-01 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change %</t>
+          <t>2026-06-01 Change %</t>
         </is>
       </c>
     </row>
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>143.9</v>
+        <v>145.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="G3" t="n">
-        <v>145.5</v>
+        <v>146.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="J3" t="n">
-        <v>146.6</v>
+        <v>145.3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.76</v>
+        <v>-0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>145.3</v>
+        <v>145.1</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.89</v>
+        <v>-0.14</v>
       </c>
       <c r="P3" t="n">
         <v>145.1</v>
@@ -639,40 +639,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>204</v>
+        <v>207.4</v>
       </c>
       <c r="E4" t="n">
         <v>3.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>207.4</v>
+        <v>209.2</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>0.87</v>
       </c>
       <c r="J4" t="n">
-        <v>209.2</v>
+        <v>206.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.87</v>
+        <v>-1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>206.4</v>
+        <v>206.6</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.8</v>
+        <v>0.2</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.34</v>
+        <v>0.1</v>
       </c>
       <c r="P4" t="n">
         <v>206.6</v>
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>0.68</v>
+        <v>-2.53</v>
       </c>
       <c r="G5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="M5" t="n">
         <v>5.77</v>
       </c>
-      <c r="H5" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.65</v>
-      </c>
       <c r="N5" t="n">
-        <v>-0.17</v>
+        <v>0.12</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.92</v>
+        <v>2.12</v>
       </c>
       <c r="P5" t="n">
         <v>5.77</v>
@@ -763,40 +763,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.85</v>
+        <v>6.78</v>
       </c>
       <c r="E6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.05</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="O6" t="n">
-        <v>-1.93</v>
+        <v>0.76</v>
       </c>
       <c r="P6" t="n">
         <v>6.64</v>
@@ -825,40 +825,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="F7" t="n">
-        <v>0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>5.19</v>
+        <v>5.13</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.19</v>
+        <v>-1.16</v>
       </c>
       <c r="M7" t="n">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="P7" t="n">
         <v>5.21</v>
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.77</v>
+        <v>8.73</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="G8" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.46</v>
+        <v>-1.72</v>
       </c>
       <c r="J8" t="n">
-        <v>8.58</v>
+        <v>8.48</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.72</v>
+        <v>-1.17</v>
       </c>
       <c r="M8" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.17</v>
+        <v>0.12</v>
       </c>
       <c r="P8" t="n">
         <v>8.49</v>
@@ -952,37 +952,37 @@
         <v>7.17</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7.17</v>
+        <v>7.13</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>7.13</v>
+        <v>7.07</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.84</v>
       </c>
       <c r="M9" t="n">
-        <v>7.07</v>
+        <v>7.3</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06</v>
+        <v>0.23</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.84</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
         <v>7.3</v>
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46.26</v>
+        <v>45.98</v>
       </c>
       <c r="E10" t="n">
-        <v>0.12</v>
+        <v>-0.28</v>
       </c>
       <c r="F10" t="n">
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
       <c r="G10" t="n">
-        <v>45.98</v>
+        <v>45.82</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.61</v>
+        <v>-0.35</v>
       </c>
       <c r="J10" t="n">
-        <v>45.82</v>
+        <v>45.92</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.35</v>
+        <v>0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>45.92</v>
+        <v>47.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1</v>
+        <v>1.18</v>
       </c>
       <c r="O10" t="n">
-        <v>0.22</v>
+        <v>2.57</v>
       </c>
       <c r="P10" t="n">
         <v>47.1</v>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="E11" t="n">
         <v>-0.01</v>
@@ -1082,25 +1082,25 @@
         <v>-0.23</v>
       </c>
       <c r="G11" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.23</v>
+        <v>-1.36</v>
       </c>
       <c r="J11" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="M11" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="N11" t="n">
         <v>-0.02</v>
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.83</v>
+        <v>10.91</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.01</v>
+        <v>0.74</v>
       </c>
       <c r="G12" t="n">
-        <v>10.91</v>
+        <v>10.7</v>
       </c>
       <c r="H12" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.08</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="L12" t="n">
-        <v>-1.92</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="O12" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="P12" t="n">
         <v>10.89</v>
@@ -1197,40 +1197,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.44</v>
+        <v>26.92</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>-0.52</v>
       </c>
       <c r="F13" t="n">
-        <v>0.51</v>
+        <v>-1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>26.92</v>
+        <v>26.32</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.52</v>
+        <v>-0.6</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9</v>
+        <v>-2.23</v>
       </c>
       <c r="J13" t="n">
-        <v>26.32</v>
+        <v>26.16</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6</v>
+        <v>-0.16</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.23</v>
+        <v>-0.61</v>
       </c>
       <c r="M13" t="n">
-        <v>26.16</v>
+        <v>26.4</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.16</v>
+        <v>0.24</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.61</v>
+        <v>0.92</v>
       </c>
       <c r="P13" t="n">
         <v>26.4</v>
@@ -1259,40 +1259,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="E14" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F14" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="L14" t="n">
-        <v>-2.09</v>
+        <v>-0.43</v>
       </c>
       <c r="M14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.43</v>
+        <v>-1.29</v>
       </c>
       <c r="P14" t="n">
         <v>2.3</v>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.22</v>
+        <v>5.23</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F15" t="n">
-        <v>1.36</v>
+        <v>0.19</v>
       </c>
       <c r="G15" t="n">
-        <v>5.23</v>
+        <v>5.16</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.19</v>
+        <v>-1.34</v>
       </c>
       <c r="J15" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>5.19</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.16</v>
+        <v>1.76</v>
       </c>
       <c r="P15" t="n">
         <v>5.19</v>
@@ -1383,40 +1383,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.64</v>
       </c>
       <c r="G16" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.64</v>
+        <v>0.21</v>
       </c>
       <c r="J16" t="n">
-        <v>4.82</v>
+        <v>4.77</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.21</v>
+        <v>-1.04</v>
       </c>
       <c r="M16" t="n">
-        <v>4.77</v>
+        <v>4.85</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.04</v>
+        <v>1.68</v>
       </c>
       <c r="P16" t="n">
         <v>4.85</v>
@@ -1445,40 +1445,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="H17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>-2.24</v>
       </c>
       <c r="J17" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.24</v>
+        <v>-1.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.15</v>
+        <v>1.74</v>
       </c>
       <c r="P17" t="n">
         <v>3.51</v>
@@ -1510,31 +1510,31 @@
         <v>3.43</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="J18" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.46</v>
+        <v>-0.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="N18" t="n">
         <v>-0.01</v>
@@ -1569,40 +1569,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60.85</v>
+        <v>60.65</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="G19" t="n">
-        <v>60.65</v>
+        <v>59.9</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.33</v>
+        <v>-1.24</v>
       </c>
       <c r="J19" t="n">
-        <v>59.9</v>
+        <v>59.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.75</v>
+        <v>-0.65</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.24</v>
+        <v>-1.09</v>
       </c>
       <c r="M19" t="n">
-        <v>59.25</v>
+        <v>60.05</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.65</v>
+        <v>0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.09</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
         <v>60.05</v>
@@ -1631,40 +1631,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.92</v>
+        <v>29.42</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7</v>
+        <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>29.42</v>
+        <v>28.84</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5</v>
+        <v>-0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>1.73</v>
+        <v>-1.97</v>
       </c>
       <c r="J20" t="n">
-        <v>28.84</v>
+        <v>28.56</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.58</v>
+        <v>-0.28</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.97</v>
+        <v>-0.97</v>
       </c>
       <c r="M20" t="n">
-        <v>28.56</v>
+        <v>28.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.28</v>
+        <v>0.32</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.97</v>
+        <v>1.12</v>
       </c>
       <c r="P20" t="n">
         <v>28.88</v>
@@ -1693,40 +1693,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.46</v>
+        <v>-1.11</v>
       </c>
       <c r="G21" t="n">
-        <v>5.33</v>
+        <v>5.28</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="K21" t="n">
         <v>-0.05</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="M21" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="N21" t="n">
         <v>-0.05</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="P21" t="n">
         <v>5.18</v>
@@ -1755,40 +1755,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.64</v>
+        <v>0.12</v>
       </c>
       <c r="G22" t="n">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.12</v>
+        <v>-0.47</v>
       </c>
       <c r="J22" t="n">
-        <v>85.2</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="M22" t="n">
-        <v>84.84999999999999</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.35</v>
+        <v>0.3</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.41</v>
+        <v>0.35</v>
       </c>
       <c r="P22" t="n">
         <v>85.15000000000001</v>
@@ -1817,40 +1817,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.48</v>
+        <v>24.92</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="F23" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="G23" t="n">
-        <v>24.92</v>
+        <v>24.6</v>
       </c>
       <c r="H23" t="n">
-        <v>0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>-1.28</v>
       </c>
       <c r="J23" t="n">
-        <v>24.6</v>
+        <v>27.82</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.32</v>
+        <v>3.22</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.28</v>
+        <v>13.09</v>
       </c>
       <c r="M23" t="n">
-        <v>27.82</v>
+        <v>26.78</v>
       </c>
       <c r="N23" t="n">
-        <v>3.22</v>
+        <v>-1.04</v>
       </c>
       <c r="O23" t="n">
-        <v>13.09</v>
+        <v>-3.74</v>
       </c>
       <c r="P23" t="n">
         <v>26.78</v>
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="F24" t="n">
-        <v>2.83</v>
+        <v>1.77</v>
       </c>
       <c r="G24" t="n">
-        <v>28.8</v>
+        <v>28.16</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
+        <v>-0.64</v>
       </c>
       <c r="I24" t="n">
-        <v>1.77</v>
+        <v>-2.22</v>
       </c>
       <c r="J24" t="n">
-        <v>28.16</v>
+        <v>28.26</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.22</v>
+        <v>0.36</v>
       </c>
       <c r="M24" t="n">
-        <v>28.26</v>
+        <v>30.14</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="O24" t="n">
-        <v>0.36</v>
+        <v>6.65</v>
       </c>
       <c r="P24" t="n">
         <v>30.14</v>
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>29.76</v>
       </c>
       <c r="E25" t="n">
-        <v>0.34</v>
+        <v>-0.24</v>
       </c>
       <c r="F25" t="n">
-        <v>1.15</v>
+        <v>-0.8</v>
       </c>
       <c r="G25" t="n">
-        <v>29.76</v>
+        <v>28.4</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.24</v>
+        <v>-1.36</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8</v>
+        <v>-4.57</v>
       </c>
       <c r="J25" t="n">
-        <v>28.4</v>
+        <v>28.56</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.36</v>
+        <v>0.16</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="N25" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.82</v>
       </c>
       <c r="P25" t="n">
         <v>28.04</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>48.88</v>
+        <v>51.1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="F26" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
       <c r="G26" t="n">
-        <v>51.1</v>
+        <v>52.65</v>
       </c>
       <c r="H26" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="I26" t="n">
-        <v>4.54</v>
+        <v>3.03</v>
       </c>
       <c r="J26" t="n">
-        <v>52.65</v>
+        <v>53.85</v>
       </c>
       <c r="K26" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="L26" t="n">
-        <v>3.03</v>
+        <v>2.28</v>
       </c>
       <c r="M26" t="n">
-        <v>53.85</v>
+        <v>61.75</v>
       </c>
       <c r="N26" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.28</v>
+        <v>14.67</v>
       </c>
       <c r="P26" t="n">
         <v>61.75</v>
@@ -2065,40 +2065,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>441.4</v>
+        <v>439</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="F27" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="G27" t="n">
-        <v>439</v>
+        <v>434.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.54</v>
+        <v>-1.05</v>
       </c>
       <c r="J27" t="n">
-        <v>434.4</v>
+        <v>425</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.6</v>
+        <v>-9.4</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.05</v>
+        <v>-2.16</v>
       </c>
       <c r="M27" t="n">
-        <v>425</v>
+        <v>427.2</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.4</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.16</v>
+        <v>0.52</v>
       </c>
       <c r="P27" t="n">
         <v>427.2</v>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>127</v>
+        <v>127.6</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="G28" t="n">
-        <v>127.6</v>
+        <v>124.3</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6</v>
+        <v>-3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.47</v>
+        <v>-2.59</v>
       </c>
       <c r="J28" t="n">
-        <v>124.3</v>
+        <v>121.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.3</v>
+        <v>-2.5</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.59</v>
+        <v>-2.01</v>
       </c>
       <c r="M28" t="n">
-        <v>121.8</v>
+        <v>120.9</v>
       </c>
       <c r="N28" t="n">
-        <v>-2.5</v>
+        <v>-0.9</v>
       </c>
       <c r="O28" t="n">
-        <v>-2.01</v>
+        <v>-0.74</v>
       </c>
       <c r="P28" t="n">
         <v>120.9</v>
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>121.7</v>
+        <v>118.6</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.46</v>
+        <v>-2.55</v>
       </c>
       <c r="G29" t="n">
-        <v>118.6</v>
+        <v>116.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.55</v>
+        <v>-1.94</v>
       </c>
       <c r="J29" t="n">
-        <v>116.3</v>
+        <v>114.2</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.94</v>
+        <v>-1.81</v>
       </c>
       <c r="M29" t="n">
-        <v>114.2</v>
+        <v>113.5</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.1</v>
+        <v>-0.7</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.81</v>
+        <v>-0.61</v>
       </c>
       <c r="P29" t="n">
         <v>113.5</v>
@@ -2251,40 +2251,40 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>81.34999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.75</v>
+        <v>-2.55</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.91</v>
+        <v>-3.13</v>
       </c>
       <c r="G30" t="n">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.55</v>
+        <v>-1.1</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.13</v>
+        <v>-1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>77.7</v>
+        <v>73.3</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.1</v>
+        <v>-4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>-1.4</v>
+        <v>-5.66</v>
       </c>
       <c r="M30" t="n">
-        <v>73.3</v>
+        <v>73.45</v>
       </c>
       <c r="N30" t="n">
-        <v>-4.4</v>
+        <v>0.15</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.66</v>
+        <v>0.2</v>
       </c>
       <c r="P30" t="n">
         <v>73.45</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="D31" t="n">
+        <v>128</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G31" t="n">
         <v>128.2</v>
       </c>
-      <c r="E31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G31" t="n">
-        <v>128</v>
-      </c>
       <c r="H31" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.16</v>
+        <v>0.16</v>
       </c>
       <c r="J31" t="n">
-        <v>128.2</v>
+        <v>125.6</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="L31" t="n">
-        <v>0.16</v>
+        <v>-2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>125.6</v>
+        <v>130</v>
       </c>
       <c r="N31" t="n">
-        <v>-2.6</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
-        <v>-2.03</v>
+        <v>3.5</v>
       </c>
       <c r="P31" t="n">
         <v>130</v>
@@ -2375,40 +2375,40 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>79.84999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>5.65</v>
+        <v>4.55</v>
       </c>
       <c r="F32" t="n">
-        <v>7.61</v>
+        <v>5.7</v>
       </c>
       <c r="G32" t="n">
-        <v>84.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="H32" t="n">
-        <v>4.55</v>
+        <v>0.8</v>
       </c>
       <c r="I32" t="n">
-        <v>5.7</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="n">
-        <v>85.2</v>
+        <v>88.25</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8</v>
+        <v>3.05</v>
       </c>
       <c r="L32" t="n">
-        <v>0.95</v>
+        <v>3.58</v>
       </c>
       <c r="M32" t="n">
-        <v>88.25</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>-6.65</v>
       </c>
       <c r="O32" t="n">
-        <v>3.58</v>
+        <v>-7.54</v>
       </c>
       <c r="P32" t="n">
         <v>81.59999999999999</v>
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>91.59999999999999</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1.05</v>
+        <v>2.05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.16</v>
+        <v>2.24</v>
       </c>
       <c r="G33" t="n">
-        <v>93.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H33" t="n">
-        <v>2.05</v>
+        <v>-2.95</v>
       </c>
       <c r="I33" t="n">
-        <v>2.24</v>
+        <v>-3.15</v>
       </c>
       <c r="J33" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.95</v>
+        <v>-0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>-3.15</v>
+        <v>-0.44</v>
       </c>
       <c r="M33" t="n">
-        <v>90.3</v>
+        <v>91.3</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.44</v>
+        <v>1.11</v>
       </c>
       <c r="P33" t="n">
         <v>91.3</v>
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45.64</v>
+        <v>45.8</v>
       </c>
       <c r="E34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G34" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="J34" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="M34" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="N34" t="n">
         <v>0.66</v>
       </c>
-      <c r="F34" t="n">
+      <c r="O34" t="n">
         <v>1.47</v>
-      </c>
-      <c r="G34" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J34" t="n">
-        <v>45.28</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="M34" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-0.88</v>
       </c>
       <c r="P34" t="n">
         <v>45.54</v>
@@ -2561,40 +2561,40 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.76</v>
+        <v>4.84</v>
       </c>
       <c r="E35" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F35" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="G35" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="H35" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="I35" t="n">
-        <v>1.68</v>
+        <v>-0.83</v>
       </c>
       <c r="J35" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.83</v>
+        <v>-0.42</v>
       </c>
       <c r="M35" t="n">
         <v>4.78</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>4.78</v>
@@ -2623,40 +2623,40 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F36" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="G36" t="n">
-        <v>10.4</v>
+        <v>10.32</v>
       </c>
       <c r="H36" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="I36" t="n">
-        <v>1.76</v>
+        <v>-0.77</v>
       </c>
       <c r="J36" t="n">
-        <v>10.32</v>
+        <v>10.28</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.77</v>
+        <v>-0.39</v>
       </c>
       <c r="M36" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.39</v>
+        <v>-0.29</v>
       </c>
       <c r="P36" t="n">
         <v>10.25</v>
@@ -2685,40 +2685,40 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>409.2</v>
+        <v>405.6</v>
       </c>
       <c r="E37" t="n">
-        <v>1.8</v>
+        <v>-3.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="G37" t="n">
-        <v>405.6</v>
+        <v>402.2</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.88</v>
+        <v>-0.84</v>
       </c>
       <c r="J37" t="n">
-        <v>402.2</v>
+        <v>396.2</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.4</v>
+        <v>-6</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.84</v>
+        <v>-1.49</v>
       </c>
       <c r="M37" t="n">
-        <v>396.2</v>
+        <v>399.8</v>
       </c>
       <c r="N37" t="n">
-        <v>-6</v>
+        <v>3.6</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.49</v>
+        <v>0.91</v>
       </c>
       <c r="P37" t="n">
         <v>399.8</v>
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.14</v>
+        <v>15.1</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.46</v>
+        <v>-0.26</v>
       </c>
       <c r="G38" t="n">
-        <v>15.1</v>
+        <v>15.04</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.26</v>
+        <v>-0.4</v>
       </c>
       <c r="J38" t="n">
-        <v>15.04</v>
+        <v>14.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.4</v>
+        <v>-0.93</v>
       </c>
       <c r="M38" t="n">
-        <v>14.9</v>
+        <v>15.33</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.93</v>
+        <v>2.89</v>
       </c>
       <c r="P38" t="n">
         <v>15.33</v>
@@ -2809,40 +2809,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="E39" t="n">
-        <v>12.5</v>
+        <v>-28</v>
       </c>
       <c r="F39" t="n">
-        <v>1.86</v>
+        <v>-4.08</v>
       </c>
       <c r="G39" t="n">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="H39" t="n">
-        <v>-28</v>
+        <v>42</v>
       </c>
       <c r="I39" t="n">
-        <v>-4.08</v>
+        <v>6.38</v>
       </c>
       <c r="J39" t="n">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="K39" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="L39" t="n">
-        <v>6.38</v>
+        <v>2.43</v>
       </c>
       <c r="M39" t="n">
-        <v>717</v>
+        <v>744.5</v>
       </c>
       <c r="N39" t="n">
-        <v>17</v>
+        <v>27.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="P39" t="n">
         <v>744.5</v>
@@ -2871,40 +2871,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="F40" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="G40" t="n">
-        <v>65.2</v>
+        <v>62.85</v>
       </c>
       <c r="H40" t="n">
-        <v>2.6</v>
+        <v>-2.35</v>
       </c>
       <c r="I40" t="n">
-        <v>4.15</v>
+        <v>-3.6</v>
       </c>
       <c r="J40" t="n">
-        <v>62.85</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.35</v>
+        <v>3.5</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.6</v>
+        <v>5.57</v>
       </c>
       <c r="M40" t="n">
-        <v>66.34999999999999</v>
+        <v>63.85</v>
       </c>
       <c r="N40" t="n">
-        <v>3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>5.57</v>
+        <v>-3.77</v>
       </c>
       <c r="P40" t="n">
         <v>63.85</v>
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.51</v>
+        <v>23.36</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.08</v>
+        <v>-0.64</v>
       </c>
       <c r="G41" t="n">
         <v>23.36</v>
@@ -2951,22 +2951,22 @@
         <v>-0.64</v>
       </c>
       <c r="J41" t="n">
-        <v>23.36</v>
+        <v>23.16</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.64</v>
+        <v>-0.86</v>
       </c>
       <c r="M41" t="n">
-        <v>23.16</v>
+        <v>23.4</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.2</v>
+        <v>0.24</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.86</v>
+        <v>1.04</v>
       </c>
       <c r="P41" t="n">
         <v>23.4</v>
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>62.18</v>
+        <v>62</v>
       </c>
       <c r="E42" t="n">
-        <v>0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="F42" t="n">
-        <v>0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="G42" t="n">
         <v>62</v>
@@ -3013,22 +3013,22 @@
         <v>-0.29</v>
       </c>
       <c r="J42" t="n">
-        <v>62</v>
+        <v>61.93</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.29</v>
+        <v>-0.11</v>
       </c>
       <c r="M42" t="n">
-        <v>61.93</v>
+        <v>62.84</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.11</v>
+        <v>1.47</v>
       </c>
       <c r="P42" t="n">
         <v>62.84</v>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.91</v>
+        <v>37.72</v>
       </c>
       <c r="E43" t="n">
-        <v>0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="G43" t="n">
         <v>37.72</v>
@@ -3075,22 +3075,22 @@
         <v>-0.5</v>
       </c>
       <c r="J43" t="n">
-        <v>37.72</v>
+        <v>37.69</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5</v>
+        <v>-0.08</v>
       </c>
       <c r="M43" t="n">
-        <v>37.69</v>
+        <v>37.6</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.08</v>
+        <v>-0.24</v>
       </c>
       <c r="P43" t="n">
         <v>37.6</v>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F44" t="n">
-        <v>0.16</v>
+        <v>-0.16</v>
       </c>
       <c r="G44" t="n">
         <v>6.21</v>
@@ -3137,22 +3137,22 @@
         <v>-0.16</v>
       </c>
       <c r="J44" t="n">
-        <v>6.21</v>
+        <v>6.31</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.16</v>
+        <v>1.61</v>
       </c>
       <c r="M44" t="n">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="O44" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="P44" t="n">
         <v>6.39</v>
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="G45" t="n">
         <v>2.2</v>
@@ -3199,22 +3199,22 @@
         <v>-0.45</v>
       </c>
       <c r="J45" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.45</v>
+        <v>-1.36</v>
       </c>
       <c r="M45" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="O45" t="n">
-        <v>-1.36</v>
+        <v>-2.3</v>
       </c>
       <c r="P45" t="n">
         <v>2.12</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="E46" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="F46" t="n">
-        <v>2.74</v>
+        <v>5.64</v>
       </c>
       <c r="G46" t="n">
         <v>3.56</v>
@@ -3261,22 +3261,22 @@
         <v>5.64</v>
       </c>
       <c r="J46" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="K46" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="L46" t="n">
-        <v>5.64</v>
+        <v>6.74</v>
       </c>
       <c r="M46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N46" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="O46" t="n">
-        <v>6.74</v>
+        <v>1.32</v>
       </c>
       <c r="P46" t="n">
         <v>3.85</v>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.25</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.18</v>
+        <v>-1.33</v>
       </c>
       <c r="G47" t="n">
         <v>11.1</v>
@@ -3323,22 +3323,22 @@
         <v>-1.33</v>
       </c>
       <c r="J47" t="n">
-        <v>11.1</v>
+        <v>11.04</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.33</v>
+        <v>-0.54</v>
       </c>
       <c r="M47" t="n">
-        <v>11.04</v>
+        <v>11.38</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.06</v>
+        <v>0.34</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.54</v>
+        <v>3.08</v>
       </c>
       <c r="P47" t="n">
         <v>11.38</v>
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="E48" t="n">
         <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.49</v>
+        <v>-1.52</v>
       </c>
       <c r="G48" t="n">
         <v>0.325</v>
@@ -3388,19 +3388,19 @@
         <v>0.325</v>
       </c>
       <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="P48" t="n">
         <v>0.32</v>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.09</v>
+        <v>-1.32</v>
       </c>
       <c r="G49" t="n">
         <v>4.48</v>
@@ -3447,22 +3447,22 @@
         <v>-1.32</v>
       </c>
       <c r="J49" t="n">
-        <v>4.48</v>
+        <v>4.36</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.32</v>
+        <v>-2.68</v>
       </c>
       <c r="M49" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="O49" t="n">
-        <v>-2.68</v>
+        <v>-0.46</v>
       </c>
       <c r="P49" t="n">
         <v>4.34</v>
@@ -3518,13 +3518,13 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="P50" t="n">
         <v>1.03</v>
@@ -3553,13 +3553,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.79</v>
+        <v>-1.33</v>
       </c>
       <c r="G51" t="n">
         <v>3.7</v>
@@ -3571,22 +3571,22 @@
         <v>-1.33</v>
       </c>
       <c r="J51" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.33</v>
+        <v>-1.62</v>
       </c>
       <c r="M51" t="n">
         <v>3.64</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>3.64</v>
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.07</v>
+        <v>10.84</v>
       </c>
       <c r="E52" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="F52" t="n">
-        <v>1.47</v>
+        <v>-2.08</v>
       </c>
       <c r="G52" t="n">
         <v>10.84</v>
@@ -3633,22 +3633,22 @@
         <v>-2.08</v>
       </c>
       <c r="J52" t="n">
-        <v>10.84</v>
+        <v>10.72</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.08</v>
+        <v>-1.11</v>
       </c>
       <c r="M52" t="n">
-        <v>10.72</v>
+        <v>10.76</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.11</v>
+        <v>0.37</v>
       </c>
       <c r="P52" t="n">
         <v>10.76</v>
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="E53" t="n">
-        <v>0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="F53" t="n">
-        <v>3.43</v>
+        <v>-2.49</v>
       </c>
       <c r="G53" t="n">
         <v>8.24</v>
@@ -3695,22 +3695,22 @@
         <v>-2.49</v>
       </c>
       <c r="J53" t="n">
-        <v>8.24</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.21</v>
+        <v>0.13</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.49</v>
+        <v>1.58</v>
       </c>
       <c r="M53" t="n">
-        <v>8.369999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="N53" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="O53" t="n">
-        <v>1.58</v>
+        <v>2.51</v>
       </c>
       <c r="P53" t="n">
         <v>8.58</v>
@@ -3739,13 +3739,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="E54" t="n">
         <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
       <c r="G54" t="n">
         <v>0.45</v>
@@ -3760,10 +3760,10 @@
         <v>0.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0.45</v>
@@ -3819,22 +3819,22 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M55" t="n">
-        <v>0.595</v>
+        <v>0.6</v>
       </c>
       <c r="N55" t="n">
         <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="P55" t="n">
         <v>0.6</v>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.11</v>
+        <v>1.08</v>
       </c>
       <c r="G56" t="n">
         <v>0.47</v>
@@ -3881,22 +3881,22 @@
         <v>1.08</v>
       </c>
       <c r="J56" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="K56" t="n">
         <v>0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="M56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="N56" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="O56" t="n">
-        <v>1.06</v>
+        <v>-2.11</v>
       </c>
       <c r="P56" t="n">
         <v>0.465</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.28</v>
+        <v>-1.68</v>
       </c>
       <c r="G57" t="n">
         <v>3.52</v>
@@ -3943,22 +3943,22 @@
         <v>-1.68</v>
       </c>
       <c r="J57" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.68</v>
+        <v>-3.69</v>
       </c>
       <c r="M57" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.13</v>
+        <v>0.2</v>
       </c>
       <c r="O57" t="n">
-        <v>-3.69</v>
+        <v>5.9</v>
       </c>
       <c r="P57" t="n">
         <v>3.59</v>
@@ -4005,22 +4005,22 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="M58" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.27</v>
+        <v>5.13</v>
       </c>
       <c r="P58" t="n">
         <v>0.082</v>
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.29</v>
+        <v>21.8</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.49</v>
+        <v>-2.2</v>
       </c>
       <c r="G59" t="n">
         <v>21.8</v>
@@ -4067,22 +4067,22 @@
         <v>-2.2</v>
       </c>
       <c r="J59" t="n">
-        <v>21.8</v>
+        <v>21.45</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="L59" t="n">
-        <v>-2.2</v>
+        <v>-1.61</v>
       </c>
       <c r="M59" t="n">
-        <v>21.45</v>
+        <v>21.88</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.35</v>
+        <v>0.43</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.61</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
         <v>21.88</v>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>0.95</v>
+        <v>-0.62</v>
       </c>
       <c r="G60" t="n">
         <v>3.18</v>
@@ -4129,22 +4129,22 @@
         <v>-0.62</v>
       </c>
       <c r="J60" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="M60" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.31</v>
+        <v>1.89</v>
       </c>
       <c r="P60" t="n">
         <v>3.23</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="E61" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="F61" t="n">
-        <v>5.19</v>
+        <v>-3.52</v>
       </c>
       <c r="G61" t="n">
         <v>1.37</v>
@@ -4191,22 +4191,22 @@
         <v>-3.52</v>
       </c>
       <c r="J61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.52</v>
+        <v>-2.19</v>
       </c>
       <c r="M61" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.19</v>
+        <v>2.99</v>
       </c>
       <c r="P61" t="n">
         <v>1.38</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-26 Close</t>
+          <t>2026-05-27 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change</t>
+          <t>2026-05-27 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-26 Change %</t>
+          <t>2026-05-27 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-27 Close</t>
+          <t>2026-05-28 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change</t>
+          <t>2026-05-28 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change %</t>
+          <t>2026-05-28 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-28 Close</t>
+          <t>2026-05-29 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change</t>
+          <t>2026-05-29 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change %</t>
+          <t>2026-05-29 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-05-29 Close</t>
+          <t>2026-06-01 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change</t>
+          <t>2026-06-01 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change %</t>
+          <t>2026-06-01 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-01 Close</t>
+          <t>2026-06-02 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change</t>
+          <t>2026-06-02 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change %</t>
+          <t>2026-06-02 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>145.5</v>
+        <v>146.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="G3" t="n">
-        <v>146.6</v>
+        <v>145.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.76</v>
+        <v>-0.89</v>
       </c>
       <c r="J3" t="n">
-        <v>145.3</v>
+        <v>145.1</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.89</v>
+        <v>-0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>145.1</v>
+        <v>146.3</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.14</v>
+        <v>0.83</v>
       </c>
       <c r="P3" t="n">
-        <v>145.1</v>
+        <v>146.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.14</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>207.4</v>
+        <v>209.2</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>0.87</v>
       </c>
       <c r="G4" t="n">
-        <v>209.2</v>
+        <v>206.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.87</v>
+        <v>-1.34</v>
       </c>
       <c r="J4" t="n">
-        <v>206.4</v>
+        <v>206.6</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.8</v>
+        <v>0.2</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.34</v>
+        <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>206.6</v>
+        <v>210.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1</v>
+        <v>1.94</v>
       </c>
       <c r="P4" t="n">
-        <v>206.6</v>
+        <v>210.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="J5" t="n">
         <v>5.77</v>
       </c>
-      <c r="E5" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.65</v>
-      </c>
       <c r="K5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="L5" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.12</v>
-      </c>
       <c r="P5" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.78</v>
+        <v>6.72</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.02</v>
+        <v>-0.88</v>
       </c>
       <c r="G6" t="n">
-        <v>6.72</v>
+        <v>6.59</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.88</v>
+        <v>-1.93</v>
       </c>
       <c r="J6" t="n">
-        <v>6.59</v>
+        <v>6.64</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.93</v>
+        <v>0.76</v>
       </c>
       <c r="M6" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0.76</v>
+        <v>0.15</v>
       </c>
       <c r="P6" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.76</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="G7" t="n">
-        <v>5.19</v>
+        <v>5.13</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.19</v>
+        <v>-1.16</v>
       </c>
       <c r="J7" t="n">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.56</v>
+        <v>0.19</v>
       </c>
       <c r="P7" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.46</v>
+        <v>-1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>8.58</v>
+        <v>8.48</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.72</v>
+        <v>-1.17</v>
       </c>
       <c r="J8" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.17</v>
+        <v>0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="O8" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="P8" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="R8" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.17</v>
+        <v>7.13</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>7.13</v>
+        <v>7.07</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.84</v>
       </c>
       <c r="J9" t="n">
-        <v>7.07</v>
+        <v>7.3</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.06</v>
+        <v>0.23</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.84</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="N9" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45.98</v>
+        <v>45.82</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.61</v>
+        <v>-0.35</v>
       </c>
       <c r="G10" t="n">
-        <v>45.82</v>
+        <v>45.92</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.35</v>
+        <v>0.22</v>
       </c>
       <c r="J10" t="n">
-        <v>45.92</v>
+        <v>47.1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1</v>
+        <v>1.18</v>
       </c>
       <c r="L10" t="n">
-        <v>0.22</v>
+        <v>2.57</v>
       </c>
       <c r="M10" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.18</v>
+        <v>0.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.57</v>
+        <v>0.64</v>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.18</v>
+        <v>0.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.57</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="11">
@@ -1073,25 +1073,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.23</v>
+        <v>-1.36</v>
       </c>
       <c r="G11" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="J11" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="K11" t="n">
         <v>-0.02</v>
@@ -1100,22 +1100,22 @@
         <v>-0.46</v>
       </c>
       <c r="M11" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.46</v>
+        <v>0.93</v>
       </c>
       <c r="P11" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.46</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M12" t="n">
         <v>10.91</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10.89</v>
-      </c>
       <c r="N12" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>0.18</v>
       </c>
       <c r="P12" t="n">
-        <v>10.89</v>
+        <v>10.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.92</v>
+        <v>26.32</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.52</v>
+        <v>-0.6</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9</v>
+        <v>-2.23</v>
       </c>
       <c r="G13" t="n">
-        <v>26.32</v>
+        <v>26.16</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6</v>
+        <v>-0.16</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.23</v>
+        <v>-0.61</v>
       </c>
       <c r="J13" t="n">
-        <v>26.16</v>
+        <v>26.4</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.16</v>
+        <v>0.24</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.61</v>
+        <v>0.92</v>
       </c>
       <c r="M13" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.85</v>
+        <v>-2.09</v>
       </c>
       <c r="G14" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.09</v>
+        <v>-0.43</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K14" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-1.29</v>
-      </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.29</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M15" t="n">
         <v>5.23</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.19</v>
-      </c>
       <c r="N15" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="O15" t="n">
-        <v>1.76</v>
+        <v>0.77</v>
       </c>
       <c r="P15" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.76</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.64</v>
+        <v>0.21</v>
       </c>
       <c r="G16" t="n">
-        <v>4.82</v>
+        <v>4.77</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.21</v>
+        <v>-1.04</v>
       </c>
       <c r="J16" t="n">
-        <v>4.77</v>
+        <v>4.85</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.04</v>
+        <v>1.68</v>
       </c>
       <c r="M16" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="P16" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="E17" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.06</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="P17" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="18">
@@ -1507,25 +1507,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="G18" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.46</v>
+        <v>-0.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="K18" t="n">
         <v>-0.01</v>
@@ -1534,22 +1534,22 @@
         <v>-0.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="P18" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60.65</v>
+        <v>59.9</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.33</v>
+        <v>-1.24</v>
       </c>
       <c r="G19" t="n">
-        <v>59.9</v>
+        <v>59.25</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.75</v>
+        <v>-0.65</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.24</v>
+        <v>-1.09</v>
       </c>
       <c r="J19" t="n">
-        <v>59.25</v>
+        <v>60.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.65</v>
+        <v>0.8</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.09</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>60.05</v>
+        <v>60.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
       <c r="P19" t="n">
-        <v>60.05</v>
+        <v>60.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.42</v>
+        <v>28.84</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>-0.58</v>
       </c>
       <c r="F20" t="n">
-        <v>1.73</v>
+        <v>-1.97</v>
       </c>
       <c r="G20" t="n">
-        <v>28.84</v>
+        <v>28.56</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.58</v>
+        <v>-0.28</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.97</v>
+        <v>-0.97</v>
       </c>
       <c r="J20" t="n">
-        <v>28.56</v>
+        <v>28.88</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.28</v>
+        <v>0.32</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.97</v>
+        <v>1.12</v>
       </c>
       <c r="M20" t="n">
-        <v>28.88</v>
+        <v>28.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.32</v>
+        <v>0.02</v>
       </c>
       <c r="O20" t="n">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>28.88</v>
+        <v>28.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.32</v>
+        <v>0.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.33</v>
+        <v>5.28</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="H21" t="n">
         <v>-0.05</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="J21" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="K21" t="n">
         <v>-0.05</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="M21" t="n">
-        <v>5.18</v>
+        <v>5.24</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.96</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>5.18</v>
+        <v>5.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.12</v>
+        <v>-0.47</v>
       </c>
       <c r="G22" t="n">
-        <v>85.2</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="J22" t="n">
-        <v>84.84999999999999</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.41</v>
+        <v>0.35</v>
       </c>
       <c r="M22" t="n">
         <v>85.15000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>85.15000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.92</v>
+        <v>24.6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8</v>
+        <v>-1.28</v>
       </c>
       <c r="G23" t="n">
-        <v>24.6</v>
+        <v>27.82</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.32</v>
+        <v>3.22</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.28</v>
+        <v>13.09</v>
       </c>
       <c r="J23" t="n">
-        <v>27.82</v>
+        <v>26.78</v>
       </c>
       <c r="K23" t="n">
-        <v>3.22</v>
+        <v>-1.04</v>
       </c>
       <c r="L23" t="n">
-        <v>13.09</v>
+        <v>-3.74</v>
       </c>
       <c r="M23" t="n">
-        <v>26.78</v>
+        <v>26.08</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.04</v>
+        <v>-0.7</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.74</v>
+        <v>-2.61</v>
       </c>
       <c r="P23" t="n">
-        <v>26.78</v>
+        <v>26.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.04</v>
+        <v>-0.7</v>
       </c>
       <c r="R23" t="n">
-        <v>-3.74</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.8</v>
+        <v>28.16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5</v>
+        <v>-0.64</v>
       </c>
       <c r="F24" t="n">
-        <v>1.77</v>
+        <v>-2.22</v>
       </c>
       <c r="G24" t="n">
-        <v>28.16</v>
+        <v>28.26</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.22</v>
+        <v>0.36</v>
       </c>
       <c r="J24" t="n">
-        <v>28.26</v>
+        <v>30.14</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="L24" t="n">
-        <v>0.36</v>
+        <v>6.65</v>
       </c>
       <c r="M24" t="n">
-        <v>30.14</v>
+        <v>30.22</v>
       </c>
       <c r="N24" t="n">
-        <v>1.88</v>
+        <v>0.08</v>
       </c>
       <c r="O24" t="n">
-        <v>6.65</v>
+        <v>0.27</v>
       </c>
       <c r="P24" t="n">
-        <v>30.14</v>
+        <v>30.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.88</v>
+        <v>0.08</v>
       </c>
       <c r="R24" t="n">
-        <v>6.65</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29.76</v>
+        <v>28.4</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.24</v>
+        <v>-1.36</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8</v>
+        <v>-4.57</v>
       </c>
       <c r="G25" t="n">
-        <v>28.4</v>
+        <v>28.56</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.36</v>
+        <v>0.16</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="K25" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.82</v>
       </c>
       <c r="M25" t="n">
-        <v>28.04</v>
+        <v>28.72</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.52</v>
+        <v>0.68</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
       <c r="P25" t="n">
-        <v>28.04</v>
+        <v>28.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.52</v>
+        <v>0.68</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51.1</v>
+        <v>52.65</v>
       </c>
       <c r="E26" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="F26" t="n">
-        <v>4.54</v>
+        <v>3.03</v>
       </c>
       <c r="G26" t="n">
-        <v>52.65</v>
+        <v>53.85</v>
       </c>
       <c r="H26" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3.03</v>
+        <v>2.28</v>
       </c>
       <c r="J26" t="n">
-        <v>53.85</v>
+        <v>61.75</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="L26" t="n">
-        <v>2.28</v>
+        <v>14.67</v>
       </c>
       <c r="M26" t="n">
-        <v>61.75</v>
+        <v>60.25</v>
       </c>
       <c r="N26" t="n">
-        <v>7.9</v>
+        <v>-1.5</v>
       </c>
       <c r="O26" t="n">
-        <v>14.67</v>
+        <v>-2.43</v>
       </c>
       <c r="P26" t="n">
-        <v>61.75</v>
+        <v>60.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.9</v>
+        <v>-1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>14.67</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>439</v>
+        <v>434.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.54</v>
+        <v>-1.05</v>
       </c>
       <c r="G27" t="n">
-        <v>434.4</v>
+        <v>425</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.6</v>
+        <v>-9.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.05</v>
+        <v>-2.16</v>
       </c>
       <c r="J27" t="n">
-        <v>425</v>
+        <v>427.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.4</v>
+        <v>2.2</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.16</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>427.2</v>
+        <v>436</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>0.52</v>
+        <v>2.06</v>
       </c>
       <c r="P27" t="n">
-        <v>427.2</v>
+        <v>436</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R27" t="n">
-        <v>0.52</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>127.6</v>
+        <v>124.3</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>-3.3</v>
       </c>
       <c r="F28" t="n">
-        <v>0.47</v>
+        <v>-2.59</v>
       </c>
       <c r="G28" t="n">
-        <v>124.3</v>
+        <v>121.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-3.3</v>
+        <v>-2.5</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.59</v>
+        <v>-2.01</v>
       </c>
       <c r="J28" t="n">
-        <v>121.8</v>
+        <v>120.9</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.5</v>
+        <v>-0.9</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.01</v>
+        <v>-0.74</v>
       </c>
       <c r="M28" t="n">
-        <v>120.9</v>
+        <v>122.8</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.9</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.74</v>
+        <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>120.9</v>
+        <v>122.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.9</v>
+        <v>1.9</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.74</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>118.6</v>
+        <v>116.3</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.55</v>
+        <v>-1.94</v>
       </c>
       <c r="G29" t="n">
-        <v>116.3</v>
+        <v>114.2</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.94</v>
+        <v>-1.81</v>
       </c>
       <c r="J29" t="n">
-        <v>114.2</v>
+        <v>113.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.1</v>
+        <v>-0.7</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.81</v>
+        <v>-0.61</v>
       </c>
       <c r="M29" t="n">
-        <v>113.5</v>
+        <v>112.4</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.61</v>
+        <v>-0.97</v>
       </c>
       <c r="P29" t="n">
-        <v>113.5</v>
+        <v>112.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.61</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.55</v>
+        <v>-1.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.13</v>
+        <v>-1.4</v>
       </c>
       <c r="G30" t="n">
-        <v>77.7</v>
+        <v>73.3</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.1</v>
+        <v>-4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.4</v>
+        <v>-5.66</v>
       </c>
       <c r="J30" t="n">
-        <v>73.3</v>
+        <v>73.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.4</v>
+        <v>0.15</v>
       </c>
       <c r="L30" t="n">
-        <v>-5.66</v>
+        <v>0.2</v>
       </c>
       <c r="M30" t="n">
-        <v>73.45</v>
+        <v>78.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0.15</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2</v>
+        <v>6.54</v>
       </c>
       <c r="P30" t="n">
-        <v>73.45</v>
+        <v>78.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.15</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>128</v>
+        <v>128.2</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.16</v>
+        <v>0.16</v>
       </c>
       <c r="G31" t="n">
-        <v>128.2</v>
+        <v>125.6</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="I31" t="n">
-        <v>0.16</v>
+        <v>-2.03</v>
       </c>
       <c r="J31" t="n">
-        <v>125.6</v>
+        <v>130</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.6</v>
+        <v>4.4</v>
       </c>
       <c r="L31" t="n">
-        <v>-2.03</v>
+        <v>3.5</v>
       </c>
       <c r="M31" t="n">
-        <v>130</v>
+        <v>129.1</v>
       </c>
       <c r="N31" t="n">
-        <v>4.4</v>
+        <v>-0.9</v>
       </c>
       <c r="O31" t="n">
-        <v>3.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>130</v>
+        <v>129.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.4</v>
+        <v>-0.9</v>
       </c>
       <c r="R31" t="n">
-        <v>3.5</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>84.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="E32" t="n">
-        <v>4.55</v>
+        <v>0.8</v>
       </c>
       <c r="F32" t="n">
-        <v>5.7</v>
+        <v>0.95</v>
       </c>
       <c r="G32" t="n">
-        <v>85.2</v>
+        <v>88.25</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8</v>
+        <v>3.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.95</v>
+        <v>3.58</v>
       </c>
       <c r="J32" t="n">
-        <v>88.25</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>3.05</v>
+        <v>-6.65</v>
       </c>
       <c r="L32" t="n">
-        <v>3.58</v>
+        <v>-7.54</v>
       </c>
       <c r="M32" t="n">
-        <v>81.59999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="N32" t="n">
-        <v>-6.65</v>
+        <v>-2.15</v>
       </c>
       <c r="O32" t="n">
-        <v>-7.54</v>
+        <v>-2.63</v>
       </c>
       <c r="P32" t="n">
-        <v>81.59999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>-6.65</v>
+        <v>-2.15</v>
       </c>
       <c r="R32" t="n">
-        <v>-7.54</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>93.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="E33" t="n">
-        <v>2.05</v>
+        <v>-2.95</v>
       </c>
       <c r="F33" t="n">
-        <v>2.24</v>
+        <v>-3.15</v>
       </c>
       <c r="G33" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.95</v>
+        <v>-0.4</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.15</v>
+        <v>-0.44</v>
       </c>
       <c r="J33" t="n">
-        <v>90.3</v>
+        <v>91.3</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.44</v>
+        <v>1.11</v>
       </c>
       <c r="M33" t="n">
-        <v>91.3</v>
+        <v>90.75</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>-0.55</v>
       </c>
       <c r="O33" t="n">
-        <v>1.11</v>
+        <v>-0.6</v>
       </c>
       <c r="P33" t="n">
-        <v>91.3</v>
+        <v>90.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>-0.55</v>
       </c>
       <c r="R33" t="n">
-        <v>1.11</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45.8</v>
+        <v>45.28</v>
       </c>
       <c r="E34" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="F34" t="n">
-        <v>0.35</v>
+        <v>-1.14</v>
       </c>
       <c r="G34" t="n">
-        <v>45.28</v>
+        <v>44.88</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.52</v>
+        <v>-0.4</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.14</v>
+        <v>-0.88</v>
       </c>
       <c r="J34" t="n">
-        <v>44.88</v>
+        <v>45.54</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.4</v>
+        <v>0.66</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.88</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
-        <v>45.54</v>
+        <v>46.54</v>
       </c>
       <c r="N34" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="P34" t="n">
-        <v>45.54</v>
+        <v>46.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="F35" t="n">
-        <v>1.68</v>
+        <v>-0.83</v>
       </c>
       <c r="G35" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.83</v>
+        <v>-0.42</v>
       </c>
       <c r="J35" t="n">
         <v>4.78</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P35" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>10.32</v>
       </c>
       <c r="E36" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="N36" t="n">
         <v>0.18</v>
       </c>
-      <c r="F36" t="n">
+      <c r="O36" t="n">
         <v>1.76</v>
       </c>
-      <c r="G36" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="J36" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="M36" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O36" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="P36" t="n">
-        <v>10.25</v>
+        <v>10.43</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.29</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>405.6</v>
+        <v>402.2</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.88</v>
+        <v>-0.84</v>
       </c>
       <c r="G37" t="n">
-        <v>402.2</v>
+        <v>396.2</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.4</v>
+        <v>-6</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.84</v>
+        <v>-1.49</v>
       </c>
       <c r="J37" t="n">
-        <v>396.2</v>
+        <v>399.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-6</v>
+        <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.49</v>
+        <v>0.91</v>
       </c>
       <c r="M37" t="n">
-        <v>399.8</v>
+        <v>400.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="O37" t="n">
-        <v>0.91</v>
+        <v>0.1</v>
       </c>
       <c r="P37" t="n">
-        <v>399.8</v>
+        <v>400.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0.91</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.1</v>
+        <v>15.04</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.26</v>
+        <v>-0.4</v>
       </c>
       <c r="G38" t="n">
-        <v>15.04</v>
+        <v>14.9</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4</v>
+        <v>-0.93</v>
       </c>
       <c r="J38" t="n">
-        <v>14.9</v>
+        <v>15.33</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.93</v>
+        <v>2.89</v>
       </c>
       <c r="M38" t="n">
-        <v>15.33</v>
+        <v>15.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="O38" t="n">
-        <v>2.89</v>
+        <v>3.72</v>
       </c>
       <c r="P38" t="n">
-        <v>15.33</v>
+        <v>15.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="R38" t="n">
-        <v>2.89</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>658</v>
+        <v>700</v>
       </c>
       <c r="E39" t="n">
-        <v>-28</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
-        <v>-4.08</v>
+        <v>6.38</v>
       </c>
       <c r="G39" t="n">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="H39" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I39" t="n">
-        <v>6.38</v>
+        <v>2.43</v>
       </c>
       <c r="J39" t="n">
-        <v>717</v>
+        <v>744.5</v>
       </c>
       <c r="K39" t="n">
-        <v>17</v>
+        <v>27.5</v>
       </c>
       <c r="L39" t="n">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="M39" t="n">
-        <v>744.5</v>
+        <v>753.5</v>
       </c>
       <c r="N39" t="n">
-        <v>27.5</v>
+        <v>9</v>
       </c>
       <c r="O39" t="n">
-        <v>3.84</v>
+        <v>1.21</v>
       </c>
       <c r="P39" t="n">
-        <v>744.5</v>
+        <v>753.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>27.5</v>
+        <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>3.84</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>65.2</v>
+        <v>62.85</v>
       </c>
       <c r="E40" t="n">
-        <v>2.6</v>
+        <v>-2.35</v>
       </c>
       <c r="F40" t="n">
-        <v>4.15</v>
+        <v>-3.6</v>
       </c>
       <c r="G40" t="n">
-        <v>62.85</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.35</v>
+        <v>3.5</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.6</v>
+        <v>5.57</v>
       </c>
       <c r="J40" t="n">
-        <v>66.34999999999999</v>
+        <v>63.85</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L40" t="n">
-        <v>5.57</v>
+        <v>-3.77</v>
       </c>
       <c r="M40" t="n">
-        <v>63.85</v>
+        <v>67.8</v>
       </c>
       <c r="N40" t="n">
-        <v>-2.5</v>
+        <v>3.95</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.77</v>
+        <v>6.19</v>
       </c>
       <c r="P40" t="n">
-        <v>63.85</v>
+        <v>67.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>-2.5</v>
+        <v>3.95</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.77</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="41">
@@ -2942,22 +2942,22 @@
         <v>-0.64</v>
       </c>
       <c r="G41" t="n">
-        <v>23.36</v>
+        <v>23.16</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.64</v>
+        <v>-0.86</v>
       </c>
       <c r="J41" t="n">
-        <v>23.16</v>
+        <v>23.4</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.2</v>
+        <v>0.24</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.86</v>
+        <v>1.04</v>
       </c>
       <c r="M41" t="n">
         <v>23.4</v>
@@ -3004,22 +3004,22 @@
         <v>-0.29</v>
       </c>
       <c r="G42" t="n">
-        <v>62</v>
+        <v>61.93</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.29</v>
+        <v>-0.11</v>
       </c>
       <c r="J42" t="n">
-        <v>61.93</v>
+        <v>62.84</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.11</v>
+        <v>1.47</v>
       </c>
       <c r="M42" t="n">
         <v>62.84</v>
@@ -3066,22 +3066,22 @@
         <v>-0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>37.72</v>
+        <v>37.69</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5</v>
+        <v>-0.08</v>
       </c>
       <c r="J43" t="n">
-        <v>37.69</v>
+        <v>37.6</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.08</v>
+        <v>-0.24</v>
       </c>
       <c r="M43" t="n">
         <v>37.6</v>
@@ -3128,22 +3128,22 @@
         <v>-0.16</v>
       </c>
       <c r="G44" t="n">
-        <v>6.21</v>
+        <v>6.31</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.16</v>
+        <v>1.61</v>
       </c>
       <c r="J44" t="n">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="L44" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="M44" t="n">
         <v>6.39</v>
@@ -3190,22 +3190,22 @@
         <v>-0.45</v>
       </c>
       <c r="G45" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.45</v>
+        <v>-1.36</v>
       </c>
       <c r="J45" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="L45" t="n">
-        <v>-1.36</v>
+        <v>-2.3</v>
       </c>
       <c r="M45" t="n">
         <v>2.12</v>
@@ -3252,22 +3252,22 @@
         <v>5.64</v>
       </c>
       <c r="G46" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="H46" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="I46" t="n">
-        <v>5.64</v>
+        <v>6.74</v>
       </c>
       <c r="J46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K46" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="L46" t="n">
-        <v>6.74</v>
+        <v>1.32</v>
       </c>
       <c r="M46" t="n">
         <v>3.85</v>
@@ -3314,22 +3314,22 @@
         <v>-1.33</v>
       </c>
       <c r="G47" t="n">
-        <v>11.1</v>
+        <v>11.04</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.33</v>
+        <v>-0.54</v>
       </c>
       <c r="J47" t="n">
-        <v>11.04</v>
+        <v>11.38</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.06</v>
+        <v>0.34</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.54</v>
+        <v>3.08</v>
       </c>
       <c r="M47" t="n">
         <v>11.38</v>
@@ -3379,19 +3379,19 @@
         <v>0.325</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="M48" t="n">
         <v>0.32</v>
@@ -3438,22 +3438,22 @@
         <v>-1.32</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48</v>
+        <v>4.36</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.32</v>
+        <v>-2.68</v>
       </c>
       <c r="J49" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="L49" t="n">
-        <v>-2.68</v>
+        <v>-0.46</v>
       </c>
       <c r="M49" t="n">
         <v>4.34</v>
@@ -3509,13 +3509,13 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="M50" t="n">
         <v>1.03</v>
@@ -3562,22 +3562,22 @@
         <v>-1.33</v>
       </c>
       <c r="G51" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.33</v>
+        <v>-1.62</v>
       </c>
       <c r="J51" t="n">
         <v>3.64</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>3.64</v>
@@ -3624,22 +3624,22 @@
         <v>-2.08</v>
       </c>
       <c r="G52" t="n">
-        <v>10.84</v>
+        <v>10.72</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.08</v>
+        <v>-1.11</v>
       </c>
       <c r="J52" t="n">
-        <v>10.72</v>
+        <v>10.76</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.11</v>
+        <v>0.37</v>
       </c>
       <c r="M52" t="n">
         <v>10.76</v>
@@ -3686,22 +3686,22 @@
         <v>-2.49</v>
       </c>
       <c r="G53" t="n">
-        <v>8.24</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.21</v>
+        <v>0.13</v>
       </c>
       <c r="I53" t="n">
-        <v>-2.49</v>
+        <v>1.58</v>
       </c>
       <c r="J53" t="n">
-        <v>8.369999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="K53" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="L53" t="n">
-        <v>1.58</v>
+        <v>2.51</v>
       </c>
       <c r="M53" t="n">
         <v>8.58</v>
@@ -3751,10 +3751,10 @@
         <v>0.45</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0.45</v>
@@ -3810,22 +3810,22 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="J55" t="n">
-        <v>0.595</v>
+        <v>0.6</v>
       </c>
       <c r="K55" t="n">
         <v>0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="M55" t="n">
         <v>0.6</v>
@@ -3872,22 +3872,22 @@
         <v>1.08</v>
       </c>
       <c r="G56" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="H56" t="n">
         <v>0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="K56" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="L56" t="n">
-        <v>1.06</v>
+        <v>-2.11</v>
       </c>
       <c r="M56" t="n">
         <v>0.465</v>
@@ -3934,22 +3934,22 @@
         <v>-1.68</v>
       </c>
       <c r="G57" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.68</v>
+        <v>-3.69</v>
       </c>
       <c r="J57" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.13</v>
+        <v>0.2</v>
       </c>
       <c r="L57" t="n">
-        <v>-3.69</v>
+        <v>5.9</v>
       </c>
       <c r="M57" t="n">
         <v>3.59</v>
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="J58" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.27</v>
+        <v>5.13</v>
       </c>
       <c r="M58" t="n">
         <v>0.082</v>
@@ -4058,22 +4058,22 @@
         <v>-2.2</v>
       </c>
       <c r="G59" t="n">
-        <v>21.8</v>
+        <v>21.45</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.2</v>
+        <v>-1.61</v>
       </c>
       <c r="J59" t="n">
-        <v>21.45</v>
+        <v>21.88</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.35</v>
+        <v>0.43</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.61</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>21.88</v>
@@ -4120,22 +4120,22 @@
         <v>-0.62</v>
       </c>
       <c r="G60" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="J60" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.31</v>
+        <v>1.89</v>
       </c>
       <c r="M60" t="n">
         <v>3.23</v>
@@ -4182,22 +4182,22 @@
         <v>-3.52</v>
       </c>
       <c r="G61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I61" t="n">
-        <v>-3.52</v>
+        <v>-2.19</v>
       </c>
       <c r="J61" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.19</v>
+        <v>2.99</v>
       </c>
       <c r="M61" t="n">
         <v>1.38</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-27 Close</t>
+          <t>2026-05-28 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change</t>
+          <t>2026-05-28 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-27 Change %</t>
+          <t>2026-05-28 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-28 Close</t>
+          <t>2026-05-29 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change</t>
+          <t>2026-05-29 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change %</t>
+          <t>2026-05-29 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-05-29 Close</t>
+          <t>2026-06-01 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change</t>
+          <t>2026-06-01 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change %</t>
+          <t>2026-06-01 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-01 Close</t>
+          <t>2026-06-02 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change</t>
+          <t>2026-06-02 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change %</t>
+          <t>2026-06-02 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-02 Close</t>
+          <t>2026-06-03 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change</t>
+          <t>2026-06-03 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change %</t>
+          <t>2026-06-03 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>146.6</v>
+        <v>145.3</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>-0.89</v>
       </c>
       <c r="G3" t="n">
-        <v>145.3</v>
+        <v>145.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.89</v>
+        <v>-0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>145.1</v>
+        <v>146.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.14</v>
+        <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>146.3</v>
+        <v>147.2</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="P3" t="n">
-        <v>146.3</v>
+        <v>147.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="R3" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>209.2</v>
+        <v>206.4</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.87</v>
+        <v>-1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>206.4</v>
+        <v>206.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.8</v>
+        <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.34</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>206.6</v>
+        <v>210.6</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1</v>
+        <v>1.94</v>
       </c>
       <c r="M4" t="n">
-        <v>210.6</v>
+        <v>215.2</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="P4" t="n">
-        <v>210.6</v>
+        <v>215.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.82</v>
+        <v>5.65</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>-2.92</v>
       </c>
       <c r="G5" t="n">
-        <v>5.65</v>
+        <v>5.77</v>
       </c>
       <c r="H5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="I5" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.12</v>
-      </c>
       <c r="M5" t="n">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.17</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.17</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.72</v>
+        <v>6.59</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.88</v>
+        <v>-1.93</v>
       </c>
       <c r="G6" t="n">
-        <v>6.59</v>
+        <v>6.64</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.93</v>
+        <v>0.76</v>
       </c>
       <c r="J6" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L6" t="n">
-        <v>0.76</v>
+        <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="O6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P6" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.15</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.19</v>
+        <v>5.13</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.19</v>
+        <v>-1.16</v>
       </c>
       <c r="G7" t="n">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="J7" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>0.19</v>
+        <v>1.72</v>
       </c>
       <c r="P7" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="R7" t="n">
-        <v>0.19</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.58</v>
+        <v>8.48</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.72</v>
+        <v>-1.17</v>
       </c>
       <c r="G8" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.17</v>
+        <v>0.12</v>
       </c>
       <c r="J8" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>8.529999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0.47</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>8.529999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="R8" t="n">
-        <v>0.47</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.13</v>
+        <v>7.07</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.84</v>
       </c>
       <c r="G9" t="n">
-        <v>7.07</v>
+        <v>7.3</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.06</v>
+        <v>0.23</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.84</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="K9" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="M9" t="n">
-        <v>7.38</v>
+        <v>7.51</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="P9" t="n">
-        <v>7.38</v>
+        <v>7.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45.82</v>
+        <v>45.92</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.16</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.35</v>
+        <v>0.22</v>
       </c>
       <c r="G10" t="n">
-        <v>45.92</v>
+        <v>47.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>1.18</v>
       </c>
       <c r="I10" t="n">
-        <v>0.22</v>
+        <v>2.57</v>
       </c>
       <c r="J10" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.18</v>
+        <v>0.3</v>
       </c>
       <c r="L10" t="n">
-        <v>2.57</v>
+        <v>0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>47.4</v>
+        <v>48.42</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>0.64</v>
+        <v>2.15</v>
       </c>
       <c r="P10" t="n">
-        <v>47.4</v>
+        <v>48.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0.64</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="11">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="G11" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="H11" t="n">
         <v>-0.02</v>
@@ -1091,31 +1091,31 @@
         <v>-0.46</v>
       </c>
       <c r="J11" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.46</v>
+        <v>0.93</v>
       </c>
       <c r="M11" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O11" t="n">
-        <v>0.93</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R11" t="n">
-        <v>0.93</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.7</v>
+        <v>10.78</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.21</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.92</v>
+        <v>0.75</v>
       </c>
       <c r="G12" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="J12" t="n">
-        <v>10.89</v>
+        <v>10.91</v>
       </c>
       <c r="K12" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="L12" t="n">
-        <v>1.02</v>
+        <v>0.18</v>
       </c>
       <c r="M12" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="O12" t="n">
-        <v>0.18</v>
+        <v>-1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="R12" t="n">
-        <v>0.18</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.32</v>
+        <v>26.16</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6</v>
+        <v>-0.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.23</v>
+        <v>-0.61</v>
       </c>
       <c r="G13" t="n">
-        <v>26.16</v>
+        <v>26.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.16</v>
+        <v>0.24</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.61</v>
+        <v>0.92</v>
       </c>
       <c r="J13" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>26.7</v>
+        <v>27.36</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>2.47</v>
       </c>
       <c r="P13" t="n">
-        <v>26.7</v>
+        <v>27.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.09</v>
+        <v>-0.43</v>
       </c>
       <c r="G14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="H14" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>-0.43</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1.29</v>
-      </c>
       <c r="M14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.43</v>
+        <v>-1.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.43</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1</v>
+        <v>5.19</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.16</v>
+        <v>1.76</v>
       </c>
       <c r="J15" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="L15" t="n">
-        <v>1.76</v>
+        <v>0.77</v>
       </c>
       <c r="M15" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="P15" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.82</v>
+        <v>4.77</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.21</v>
+        <v>-1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>4.77</v>
+        <v>4.85</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.04</v>
+        <v>1.68</v>
       </c>
       <c r="J16" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="M16" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="N16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O16" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.24</v>
+        <v>-1.15</v>
       </c>
       <c r="G17" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.15</v>
+        <v>1.74</v>
       </c>
       <c r="J17" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="M17" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="O17" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="P17" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="18">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.46</v>
+        <v>-0.3</v>
       </c>
       <c r="G18" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="H18" t="n">
         <v>-0.01</v>
@@ -1525,31 +1525,31 @@
         <v>-0.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6</v>
+        <v>1.48</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59.9</v>
+        <v>59.25</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.75</v>
+        <v>-0.65</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.24</v>
+        <v>-1.09</v>
       </c>
       <c r="G19" t="n">
-        <v>59.25</v>
+        <v>60.05</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.65</v>
+        <v>0.8</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.09</v>
+        <v>1.35</v>
       </c>
       <c r="J19" t="n">
-        <v>60.05</v>
+        <v>60.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
       <c r="M19" t="n">
-        <v>60.2</v>
+        <v>58.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.15</v>
+        <v>-1.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0.25</v>
+        <v>-2.66</v>
       </c>
       <c r="P19" t="n">
-        <v>60.2</v>
+        <v>58.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.15</v>
+        <v>-1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0.25</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.84</v>
+        <v>28.56</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.58</v>
+        <v>-0.28</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.97</v>
+        <v>-0.97</v>
       </c>
       <c r="G20" t="n">
-        <v>28.56</v>
+        <v>28.88</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.97</v>
+        <v>1.12</v>
       </c>
       <c r="J20" t="n">
-        <v>28.88</v>
+        <v>28.9</v>
       </c>
       <c r="K20" t="n">
-        <v>0.32</v>
+        <v>0.02</v>
       </c>
       <c r="L20" t="n">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>28.9</v>
+        <v>28.48</v>
       </c>
       <c r="N20" t="n">
-        <v>0.02</v>
+        <v>-0.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>28.9</v>
+        <v>28.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.02</v>
+        <v>-0.42</v>
       </c>
       <c r="R20" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="E21" t="n">
         <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="G21" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="H21" t="n">
         <v>-0.05</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="J21" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M21" t="n">
         <v>5.18</v>
       </c>
-      <c r="K21" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5.24</v>
-      </c>
       <c r="N21" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>1.16</v>
+        <v>-1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.2</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.47</v>
+        <v>-0.41</v>
       </c>
       <c r="G22" t="n">
-        <v>84.84999999999999</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.41</v>
+        <v>0.35</v>
       </c>
       <c r="J22" t="n">
         <v>85.15000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>85.15000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="P22" t="n">
-        <v>85.15000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.6</v>
+        <v>27.82</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.32</v>
+        <v>3.22</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.28</v>
+        <v>13.09</v>
       </c>
       <c r="G23" t="n">
-        <v>27.82</v>
+        <v>26.78</v>
       </c>
       <c r="H23" t="n">
-        <v>3.22</v>
+        <v>-1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>13.09</v>
+        <v>-3.74</v>
       </c>
       <c r="J23" t="n">
-        <v>26.78</v>
+        <v>26.08</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.04</v>
+        <v>-0.7</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.74</v>
+        <v>-2.61</v>
       </c>
       <c r="M23" t="n">
-        <v>26.08</v>
+        <v>27.68</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.61</v>
+        <v>6.13</v>
       </c>
       <c r="P23" t="n">
-        <v>26.08</v>
+        <v>27.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
-        <v>-2.61</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.16</v>
+        <v>28.26</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.22</v>
+        <v>0.36</v>
       </c>
       <c r="G24" t="n">
-        <v>28.26</v>
+        <v>30.14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="I24" t="n">
-        <v>0.36</v>
+        <v>6.65</v>
       </c>
       <c r="J24" t="n">
-        <v>30.14</v>
+        <v>30.22</v>
       </c>
       <c r="K24" t="n">
-        <v>1.88</v>
+        <v>0.08</v>
       </c>
       <c r="L24" t="n">
-        <v>6.65</v>
+        <v>0.27</v>
       </c>
       <c r="M24" t="n">
-        <v>30.22</v>
+        <v>30.88</v>
       </c>
       <c r="N24" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="O24" t="n">
-        <v>0.27</v>
+        <v>2.18</v>
       </c>
       <c r="P24" t="n">
-        <v>30.22</v>
+        <v>30.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="R24" t="n">
-        <v>0.27</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.4</v>
+        <v>28.56</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.36</v>
+        <v>0.16</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="H25" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.82</v>
       </c>
       <c r="J25" t="n">
-        <v>28.04</v>
+        <v>28.72</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.52</v>
+        <v>0.68</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
       <c r="M25" t="n">
-        <v>28.72</v>
+        <v>29.62</v>
       </c>
       <c r="N25" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.43</v>
+        <v>3.13</v>
       </c>
       <c r="P25" t="n">
-        <v>28.72</v>
+        <v>29.62</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="R25" t="n">
-        <v>2.43</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52.65</v>
+        <v>53.85</v>
       </c>
       <c r="E26" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="F26" t="n">
-        <v>3.03</v>
+        <v>2.28</v>
       </c>
       <c r="G26" t="n">
-        <v>53.85</v>
+        <v>61.75</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.28</v>
+        <v>14.67</v>
       </c>
       <c r="J26" t="n">
-        <v>61.75</v>
+        <v>60.25</v>
       </c>
       <c r="K26" t="n">
-        <v>7.9</v>
+        <v>-1.5</v>
       </c>
       <c r="L26" t="n">
-        <v>14.67</v>
+        <v>-2.43</v>
       </c>
       <c r="M26" t="n">
-        <v>60.25</v>
+        <v>61.65</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.43</v>
+        <v>2.32</v>
       </c>
       <c r="P26" t="n">
-        <v>60.25</v>
+        <v>61.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.5</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.43</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>434.4</v>
+        <v>425</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.6</v>
+        <v>-9.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.05</v>
+        <v>-2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>425</v>
+        <v>427.2</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.4</v>
+        <v>2.2</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.16</v>
+        <v>0.52</v>
       </c>
       <c r="J27" t="n">
-        <v>427.2</v>
+        <v>436</v>
       </c>
       <c r="K27" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>2.06</v>
       </c>
       <c r="M27" t="n">
-        <v>436</v>
+        <v>481.6</v>
       </c>
       <c r="N27" t="n">
-        <v>8.800000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.06</v>
+        <v>10.46</v>
       </c>
       <c r="P27" t="n">
-        <v>436</v>
+        <v>481.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.800000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.06</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>124.3</v>
+        <v>121.8</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.3</v>
+        <v>-2.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.59</v>
+        <v>-2.01</v>
       </c>
       <c r="G28" t="n">
-        <v>121.8</v>
+        <v>120.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.5</v>
+        <v>-0.9</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.01</v>
+        <v>-0.74</v>
       </c>
       <c r="J28" t="n">
-        <v>120.9</v>
+        <v>122.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.9</v>
+        <v>1.9</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.74</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>122.8</v>
+        <v>130.9</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>6.6</v>
       </c>
       <c r="P28" t="n">
-        <v>122.8</v>
+        <v>130.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>116.3</v>
+        <v>114.2</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.94</v>
+        <v>-1.81</v>
       </c>
       <c r="G29" t="n">
-        <v>114.2</v>
+        <v>113.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.1</v>
+        <v>-0.7</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.81</v>
+        <v>-0.61</v>
       </c>
       <c r="J29" t="n">
-        <v>113.5</v>
+        <v>112.4</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.61</v>
+        <v>-0.97</v>
       </c>
       <c r="M29" t="n">
-        <v>112.4</v>
+        <v>120.1</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.1</v>
+        <v>7.7</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.97</v>
+        <v>6.85</v>
       </c>
       <c r="P29" t="n">
-        <v>112.4</v>
+        <v>120.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.1</v>
+        <v>7.7</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.97</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>77.7</v>
+        <v>73.3</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.1</v>
+        <v>-4.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4</v>
+        <v>-5.66</v>
       </c>
       <c r="G30" t="n">
-        <v>73.3</v>
+        <v>73.45</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.4</v>
+        <v>0.15</v>
       </c>
       <c r="I30" t="n">
-        <v>-5.66</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
-        <v>73.45</v>
+        <v>78.25</v>
       </c>
       <c r="K30" t="n">
-        <v>0.15</v>
+        <v>4.8</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
+        <v>6.54</v>
       </c>
       <c r="M30" t="n">
-        <v>78.25</v>
+        <v>85.5</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>7.25</v>
       </c>
       <c r="O30" t="n">
-        <v>6.54</v>
+        <v>9.27</v>
       </c>
       <c r="P30" t="n">
-        <v>78.25</v>
+        <v>85.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.8</v>
+        <v>7.25</v>
       </c>
       <c r="R30" t="n">
-        <v>6.54</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>128.2</v>
+        <v>125.6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.16</v>
+        <v>-2.03</v>
       </c>
       <c r="G31" t="n">
-        <v>125.6</v>
+        <v>130</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.6</v>
+        <v>4.4</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.03</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
-        <v>130</v>
+        <v>129.1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.4</v>
+        <v>-0.9</v>
       </c>
       <c r="L31" t="n">
-        <v>3.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>129.1</v>
+        <v>134.7</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.9</v>
+        <v>5.6</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.6899999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="P31" t="n">
-        <v>129.1</v>
+        <v>134.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.9</v>
+        <v>5.6</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.6899999999999999</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>85.2</v>
+        <v>88.25</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8</v>
+        <v>3.05</v>
       </c>
       <c r="F32" t="n">
-        <v>0.95</v>
+        <v>3.58</v>
       </c>
       <c r="G32" t="n">
-        <v>88.25</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>3.05</v>
+        <v>-6.65</v>
       </c>
       <c r="I32" t="n">
-        <v>3.58</v>
+        <v>-7.54</v>
       </c>
       <c r="J32" t="n">
-        <v>81.59999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.65</v>
+        <v>-2.15</v>
       </c>
       <c r="L32" t="n">
-        <v>-7.54</v>
+        <v>-2.63</v>
       </c>
       <c r="M32" t="n">
-        <v>79.45</v>
+        <v>81.95</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.63</v>
+        <v>3.15</v>
       </c>
       <c r="P32" t="n">
-        <v>79.45</v>
+        <v>81.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2.15</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
-        <v>-2.63</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.95</v>
+        <v>-0.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.15</v>
+        <v>-0.44</v>
       </c>
       <c r="G33" t="n">
-        <v>90.3</v>
+        <v>91.3</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.44</v>
+        <v>1.11</v>
       </c>
       <c r="J33" t="n">
-        <v>91.3</v>
+        <v>90.75</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>-0.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.11</v>
+        <v>-0.6</v>
       </c>
       <c r="M33" t="n">
-        <v>90.75</v>
+        <v>96.75</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.55</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.6</v>
+        <v>6.61</v>
       </c>
       <c r="P33" t="n">
-        <v>90.75</v>
+        <v>96.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.55</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.6</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45.28</v>
+        <v>44.88</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.52</v>
+        <v>-0.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.14</v>
+        <v>-0.88</v>
       </c>
       <c r="G34" t="n">
-        <v>44.88</v>
+        <v>45.54</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4</v>
+        <v>0.66</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.88</v>
+        <v>1.47</v>
       </c>
       <c r="J34" t="n">
-        <v>45.54</v>
+        <v>46.54</v>
       </c>
       <c r="K34" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="M34" t="n">
-        <v>46.54</v>
+        <v>48.98</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>2.44</v>
       </c>
       <c r="O34" t="n">
-        <v>2.2</v>
+        <v>5.24</v>
       </c>
       <c r="P34" t="n">
-        <v>46.54</v>
+        <v>48.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>2.44</v>
       </c>
       <c r="R34" t="n">
-        <v>2.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.83</v>
+        <v>-0.42</v>
       </c>
       <c r="G35" t="n">
         <v>4.78</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M35" t="n">
-        <v>4.87</v>
+        <v>5.09</v>
       </c>
       <c r="N35" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="O35" t="n">
-        <v>1.88</v>
+        <v>4.52</v>
       </c>
       <c r="P35" t="n">
-        <v>4.87</v>
+        <v>5.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="R35" t="n">
-        <v>1.88</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.32</v>
+        <v>10.28</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.77</v>
+        <v>-0.39</v>
       </c>
       <c r="G36" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.39</v>
+        <v>-0.29</v>
       </c>
       <c r="J36" t="n">
-        <v>10.25</v>
+        <v>10.43</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.29</v>
+        <v>1.76</v>
       </c>
       <c r="M36" t="n">
-        <v>10.43</v>
+        <v>10.94</v>
       </c>
       <c r="N36" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="O36" t="n">
-        <v>1.76</v>
+        <v>4.89</v>
       </c>
       <c r="P36" t="n">
-        <v>10.43</v>
+        <v>10.94</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="R36" t="n">
-        <v>1.76</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>402.2</v>
+        <v>396.2</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.4</v>
+        <v>-6</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.84</v>
+        <v>-1.49</v>
       </c>
       <c r="G37" t="n">
-        <v>396.2</v>
+        <v>399.8</v>
       </c>
       <c r="H37" t="n">
-        <v>-6</v>
+        <v>3.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.49</v>
+        <v>0.91</v>
       </c>
       <c r="J37" t="n">
-        <v>399.8</v>
+        <v>400.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="L37" t="n">
-        <v>0.91</v>
+        <v>0.1</v>
       </c>
       <c r="M37" t="n">
-        <v>400.2</v>
+        <v>410.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0.4</v>
+        <v>10.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>400.2</v>
+        <v>410.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4</v>
+        <v>10.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.1</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.04</v>
+        <v>14.9</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.4</v>
+        <v>-0.93</v>
       </c>
       <c r="G38" t="n">
-        <v>14.9</v>
+        <v>15.33</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.93</v>
+        <v>2.89</v>
       </c>
       <c r="J38" t="n">
-        <v>15.33</v>
+        <v>15.9</v>
       </c>
       <c r="K38" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="L38" t="n">
-        <v>2.89</v>
+        <v>3.72</v>
       </c>
       <c r="M38" t="n">
-        <v>15.9</v>
+        <v>16.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="O38" t="n">
-        <v>3.72</v>
+        <v>2.83</v>
       </c>
       <c r="P38" t="n">
-        <v>15.9</v>
+        <v>16.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="R38" t="n">
-        <v>3.72</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F39" t="n">
-        <v>6.38</v>
+        <v>2.43</v>
       </c>
       <c r="G39" t="n">
-        <v>717</v>
+        <v>744.5</v>
       </c>
       <c r="H39" t="n">
-        <v>17</v>
+        <v>27.5</v>
       </c>
       <c r="I39" t="n">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="J39" t="n">
-        <v>744.5</v>
+        <v>753.5</v>
       </c>
       <c r="K39" t="n">
-        <v>27.5</v>
+        <v>9</v>
       </c>
       <c r="L39" t="n">
-        <v>3.84</v>
+        <v>1.21</v>
       </c>
       <c r="M39" t="n">
-        <v>753.5</v>
+        <v>779.5</v>
       </c>
       <c r="N39" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="O39" t="n">
-        <v>1.21</v>
+        <v>3.45</v>
       </c>
       <c r="P39" t="n">
-        <v>753.5</v>
+        <v>779.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="40">
@@ -2871,46 +2871,46 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62.85</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.35</v>
+        <v>3.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.6</v>
+        <v>5.57</v>
       </c>
       <c r="G40" t="n">
-        <v>66.34999999999999</v>
+        <v>63.85</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="I40" t="n">
-        <v>5.57</v>
+        <v>-3.77</v>
       </c>
       <c r="J40" t="n">
-        <v>63.85</v>
+        <v>67.8</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.5</v>
+        <v>3.95</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.77</v>
+        <v>6.19</v>
       </c>
       <c r="M40" t="n">
-        <v>67.8</v>
+        <v>72</v>
       </c>
       <c r="N40" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
         <v>6.19</v>
       </c>
       <c r="P40" t="n">
-        <v>67.8</v>
+        <v>72</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
         <v>6.19</v>
@@ -2933,22 +2933,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.36</v>
+        <v>23.16</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.64</v>
+        <v>-0.86</v>
       </c>
       <c r="G41" t="n">
-        <v>23.16</v>
+        <v>23.4</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.2</v>
+        <v>0.24</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.86</v>
+        <v>1.04</v>
       </c>
       <c r="J41" t="n">
         <v>23.4</v>
@@ -2960,22 +2960,22 @@
         <v>1.04</v>
       </c>
       <c r="M41" t="n">
-        <v>23.4</v>
+        <v>24.08</v>
       </c>
       <c r="N41" t="n">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="O41" t="n">
-        <v>1.04</v>
+        <v>2.91</v>
       </c>
       <c r="P41" t="n">
-        <v>23.4</v>
+        <v>24.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="R41" t="n">
-        <v>1.04</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="42">
@@ -2995,22 +2995,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>62</v>
+        <v>61.93</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.29</v>
+        <v>-0.11</v>
       </c>
       <c r="G42" t="n">
-        <v>61.93</v>
+        <v>62.84</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.11</v>
+        <v>1.47</v>
       </c>
       <c r="J42" t="n">
         <v>62.84</v>
@@ -3022,22 +3022,22 @@
         <v>1.47</v>
       </c>
       <c r="M42" t="n">
-        <v>62.84</v>
+        <v>64.67</v>
       </c>
       <c r="N42" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="O42" t="n">
-        <v>1.47</v>
+        <v>2.91</v>
       </c>
       <c r="P42" t="n">
-        <v>62.84</v>
+        <v>64.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="R42" t="n">
-        <v>1.47</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="43">
@@ -3057,22 +3057,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.72</v>
+        <v>37.69</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.5</v>
+        <v>-0.08</v>
       </c>
       <c r="G43" t="n">
-        <v>37.69</v>
+        <v>37.6</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.08</v>
+        <v>-0.24</v>
       </c>
       <c r="J43" t="n">
         <v>37.6</v>
@@ -3084,22 +3084,22 @@
         <v>-0.24</v>
       </c>
       <c r="M43" t="n">
-        <v>37.6</v>
+        <v>38.4</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.09</v>
+        <v>0.8</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.24</v>
+        <v>2.13</v>
       </c>
       <c r="P43" t="n">
-        <v>37.6</v>
+        <v>38.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.09</v>
+        <v>0.8</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.24</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="44">
@@ -3119,22 +3119,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.21</v>
+        <v>6.31</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.16</v>
+        <v>1.61</v>
       </c>
       <c r="G44" t="n">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I44" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="J44" t="n">
         <v>6.39</v>
@@ -3146,22 +3146,22 @@
         <v>1.27</v>
       </c>
       <c r="M44" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="N44" t="n">
-        <v>0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="O44" t="n">
-        <v>1.27</v>
+        <v>-1.72</v>
       </c>
       <c r="P44" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="45">
@@ -3181,22 +3181,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.45</v>
+        <v>-1.36</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.36</v>
+        <v>-2.3</v>
       </c>
       <c r="J45" t="n">
         <v>2.12</v>
@@ -3208,22 +3208,22 @@
         <v>-2.3</v>
       </c>
       <c r="M45" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.3</v>
+        <v>-1.89</v>
       </c>
       <c r="P45" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.3</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="46">
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="E46" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="F46" t="n">
-        <v>5.64</v>
+        <v>6.74</v>
       </c>
       <c r="G46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H46" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="I46" t="n">
-        <v>6.74</v>
+        <v>1.32</v>
       </c>
       <c r="J46" t="n">
         <v>3.85</v>
@@ -3270,22 +3270,22 @@
         <v>1.32</v>
       </c>
       <c r="M46" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="P46" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="47">
@@ -3305,22 +3305,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.04</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.33</v>
+        <v>-0.54</v>
       </c>
       <c r="G47" t="n">
-        <v>11.04</v>
+        <v>11.38</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.06</v>
+        <v>0.34</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.54</v>
+        <v>3.08</v>
       </c>
       <c r="J47" t="n">
         <v>11.38</v>
@@ -3332,22 +3332,22 @@
         <v>3.08</v>
       </c>
       <c r="M47" t="n">
-        <v>11.38</v>
+        <v>11.16</v>
       </c>
       <c r="N47" t="n">
-        <v>0.34</v>
+        <v>-0.22</v>
       </c>
       <c r="O47" t="n">
-        <v>3.08</v>
+        <v>-1.93</v>
       </c>
       <c r="P47" t="n">
-        <v>11.38</v>
+        <v>11.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.34</v>
+        <v>-0.22</v>
       </c>
       <c r="R47" t="n">
-        <v>3.08</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="48">
@@ -3370,19 +3370,19 @@
         <v>0.325</v>
       </c>
       <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="J48" t="n">
         <v>0.32</v>
@@ -3397,19 +3397,19 @@
         <v>0.32</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.32</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,22 +3429,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.48</v>
+        <v>4.36</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.32</v>
+        <v>-2.68</v>
       </c>
       <c r="G49" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="I49" t="n">
-        <v>-2.68</v>
+        <v>-0.46</v>
       </c>
       <c r="J49" t="n">
         <v>4.34</v>
@@ -3459,19 +3459,19 @@
         <v>4.34</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>4.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3500,13 +3500,13 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="J50" t="n">
         <v>1.03</v>
@@ -3521,19 +3521,19 @@
         <v>1.03</v>
       </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.03</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,22 +3553,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.33</v>
+        <v>-1.62</v>
       </c>
       <c r="G51" t="n">
         <v>3.64</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>3.64</v>
@@ -3580,22 +3580,22 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="P51" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="52">
@@ -3615,22 +3615,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.84</v>
+        <v>10.72</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.08</v>
+        <v>-1.11</v>
       </c>
       <c r="G52" t="n">
-        <v>10.72</v>
+        <v>10.76</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.11</v>
+        <v>0.37</v>
       </c>
       <c r="J52" t="n">
         <v>10.76</v>
@@ -3642,22 +3642,22 @@
         <v>0.37</v>
       </c>
       <c r="M52" t="n">
-        <v>10.76</v>
+        <v>10.95</v>
       </c>
       <c r="N52" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="O52" t="n">
-        <v>0.37</v>
+        <v>1.77</v>
       </c>
       <c r="P52" t="n">
-        <v>10.76</v>
+        <v>10.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="R52" t="n">
-        <v>0.37</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="53">
@@ -3677,22 +3677,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.24</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.21</v>
+        <v>0.13</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.49</v>
+        <v>1.58</v>
       </c>
       <c r="G53" t="n">
-        <v>8.369999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="H53" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="I53" t="n">
-        <v>1.58</v>
+        <v>2.51</v>
       </c>
       <c r="J53" t="n">
         <v>8.58</v>
@@ -3704,22 +3704,22 @@
         <v>2.51</v>
       </c>
       <c r="M53" t="n">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="N53" t="n">
-        <v>0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="O53" t="n">
-        <v>2.51</v>
+        <v>-1.63</v>
       </c>
       <c r="P53" t="n">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="R53" t="n">
-        <v>2.51</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="54">
@@ -3742,10 +3742,10 @@
         <v>0.45</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0.45</v>
@@ -3766,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.45</v>
+        <v>0.435</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>-3.33</v>
       </c>
       <c r="P54" t="n">
-        <v>0.45</v>
+        <v>0.435</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="55">
@@ -3801,22 +3801,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="G55" t="n">
-        <v>0.595</v>
+        <v>0.6</v>
       </c>
       <c r="H55" t="n">
         <v>0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="J55" t="n">
         <v>0.6</v>
@@ -3828,22 +3828,22 @@
         <v>0.84</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="N55" t="n">
         <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="Q55" t="n">
         <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="56">
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="E56" t="n">
         <v>0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="G56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="H56" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="I56" t="n">
-        <v>1.06</v>
+        <v>-2.11</v>
       </c>
       <c r="J56" t="n">
         <v>0.465</v>
@@ -3893,19 +3893,19 @@
         <v>0.465</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.465</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,22 +3925,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.68</v>
+        <v>-3.69</v>
       </c>
       <c r="G57" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.13</v>
+        <v>0.2</v>
       </c>
       <c r="I57" t="n">
-        <v>-3.69</v>
+        <v>5.9</v>
       </c>
       <c r="J57" t="n">
         <v>3.59</v>
@@ -3952,22 +3952,22 @@
         <v>5.9</v>
       </c>
       <c r="M57" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="N57" t="n">
-        <v>0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="O57" t="n">
-        <v>5.9</v>
+        <v>-4.18</v>
       </c>
       <c r="P57" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="R57" t="n">
-        <v>5.9</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="58">
@@ -3987,22 +3987,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="G58" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.27</v>
+        <v>5.13</v>
       </c>
       <c r="J58" t="n">
         <v>0.082</v>
@@ -4014,22 +4014,22 @@
         <v>5.13</v>
       </c>
       <c r="M58" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="N58" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O58" t="n">
-        <v>5.13</v>
+        <v>2.44</v>
       </c>
       <c r="P58" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="R58" t="n">
-        <v>5.13</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="59">
@@ -4049,22 +4049,22 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.8</v>
+        <v>21.45</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.2</v>
+        <v>-1.61</v>
       </c>
       <c r="G59" t="n">
-        <v>21.45</v>
+        <v>21.88</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.35</v>
+        <v>0.43</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.61</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>21.88</v>
@@ -4076,22 +4076,22 @@
         <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>21.88</v>
+        <v>21.98</v>
       </c>
       <c r="N59" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>0.46</v>
       </c>
       <c r="P59" t="n">
-        <v>21.88</v>
+        <v>21.98</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="60">
@@ -4111,22 +4111,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="G60" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.31</v>
+        <v>1.89</v>
       </c>
       <c r="J60" t="n">
         <v>3.23</v>
@@ -4138,22 +4138,22 @@
         <v>1.89</v>
       </c>
       <c r="M60" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="O60" t="n">
-        <v>1.89</v>
+        <v>-0.93</v>
       </c>
       <c r="P60" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="R60" t="n">
-        <v>1.89</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="61">
@@ -4173,22 +4173,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.52</v>
+        <v>-2.19</v>
       </c>
       <c r="G61" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.19</v>
+        <v>2.99</v>
       </c>
       <c r="J61" t="n">
         <v>1.38</v>
@@ -4200,22 +4200,22 @@
         <v>2.99</v>
       </c>
       <c r="M61" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="N61" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="O61" t="n">
-        <v>2.99</v>
+        <v>-7.25</v>
       </c>
       <c r="P61" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="R61" t="n">
-        <v>2.99</v>
+        <v>-7.25</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-28 Close</t>
+          <t>2026-05-29 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change</t>
+          <t>2026-05-29 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-28 Change %</t>
+          <t>2026-05-29 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-05-29 Close</t>
+          <t>2026-06-01 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change</t>
+          <t>2026-06-01 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change %</t>
+          <t>2026-06-01 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-01 Close</t>
+          <t>2026-06-02 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change</t>
+          <t>2026-06-02 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change %</t>
+          <t>2026-06-02 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-02 Close</t>
+          <t>2026-06-03 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change</t>
+          <t>2026-06-03 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change %</t>
+          <t>2026-06-03 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-03 Close</t>
+          <t>2026-06-04 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change</t>
+          <t>2026-06-04 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change %</t>
+          <t>2026-06-04 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>145.3</v>
+        <v>145.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.89</v>
+        <v>-0.14</v>
       </c>
       <c r="G3" t="n">
-        <v>145.1</v>
+        <v>146.3</v>
       </c>
       <c r="H3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J3" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M3" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="O3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="J3" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="M3" t="n">
-        <v>147.2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.62</v>
-      </c>
       <c r="P3" t="n">
-        <v>147.2</v>
+        <v>146.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0.62</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>206.4</v>
+        <v>206.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.34</v>
+        <v>0.1</v>
       </c>
       <c r="G4" t="n">
-        <v>206.6</v>
+        <v>210.6</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>1.94</v>
       </c>
       <c r="J4" t="n">
-        <v>210.6</v>
+        <v>215.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="M4" t="n">
-        <v>215.2</v>
+        <v>217</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.18</v>
+        <v>0.84</v>
       </c>
       <c r="P4" t="n">
-        <v>215.2</v>
+        <v>211.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>-5.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.18</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.65</v>
+        <v>5.77</v>
       </c>
       <c r="E5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="F5" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.12</v>
-      </c>
       <c r="J5" t="n">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="K5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="N5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="M5" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="P5" t="n">
-        <v>5.85</v>
+        <v>5.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.59</v>
+        <v>6.64</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.93</v>
+        <v>0.76</v>
       </c>
       <c r="G6" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.76</v>
+        <v>0.15</v>
       </c>
       <c r="J6" t="n">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.15</v>
+        <v>2.26</v>
       </c>
       <c r="M6" t="n">
-        <v>6.8</v>
+        <v>6.72</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.26</v>
+        <v>-1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>6.8</v>
+        <v>6.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1.56</v>
+        <v>0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0.19</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>5.31</v>
+        <v>5.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="O7" t="n">
-        <v>1.72</v>
+        <v>-0.75</v>
       </c>
       <c r="P7" t="n">
-        <v>5.31</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.72</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.17</v>
+        <v>0.12</v>
       </c>
       <c r="G8" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="J8" t="n">
-        <v>8.529999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="L8" t="n">
-        <v>0.47</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
-        <v>8.66</v>
+        <v>8.57</v>
       </c>
       <c r="N8" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>-1.04</v>
       </c>
       <c r="P8" t="n">
-        <v>8.66</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.07</v>
+        <v>7.3</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06</v>
+        <v>0.23</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.84</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="H9" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>7.38</v>
+        <v>7.51</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>7.51</v>
+        <v>7.42</v>
       </c>
       <c r="N9" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.76</v>
+        <v>-1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>7.51</v>
+        <v>7.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.13</v>
+        <v>-0.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.76</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45.92</v>
+        <v>47.1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>1.18</v>
       </c>
       <c r="F10" t="n">
-        <v>0.22</v>
+        <v>2.57</v>
       </c>
       <c r="G10" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.18</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.57</v>
+        <v>0.64</v>
       </c>
       <c r="J10" t="n">
-        <v>47.4</v>
+        <v>48.42</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="L10" t="n">
-        <v>0.64</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>48.42</v>
+        <v>47.86</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>2.15</v>
+        <v>-1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>48.42</v>
+        <v>47.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.02</v>
+        <v>-0.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="11">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="E11" t="n">
         <v>-0.02</v>
@@ -1082,40 +1082,40 @@
         <v>-0.46</v>
       </c>
       <c r="G11" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="H11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="N11" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I11" t="n">
+      <c r="O11" t="n">
         <v>-0.46</v>
       </c>
-      <c r="J11" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="P11" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.78</v>
+        <v>10.89</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="G12" t="n">
-        <v>10.89</v>
+        <v>10.91</v>
       </c>
       <c r="H12" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>1.02</v>
+        <v>0.18</v>
       </c>
       <c r="J12" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="L12" t="n">
-        <v>0.18</v>
+        <v>-1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.47</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>10.75</v>
+        <v>10.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.47</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.16</v>
+        <v>26.4</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.16</v>
+        <v>0.24</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.61</v>
+        <v>0.92</v>
       </c>
       <c r="G13" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="H13" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="J13" t="n">
-        <v>26.7</v>
+        <v>27.36</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="L13" t="n">
-        <v>1.14</v>
+        <v>2.47</v>
       </c>
       <c r="M13" t="n">
-        <v>27.36</v>
+        <v>27.26</v>
       </c>
       <c r="N13" t="n">
-        <v>0.66</v>
+        <v>-0.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.47</v>
+        <v>-0.37</v>
       </c>
       <c r="P13" t="n">
-        <v>27.36</v>
+        <v>27.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.66</v>
+        <v>-0.24</v>
       </c>
       <c r="R13" t="n">
-        <v>2.47</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="E14" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>-0.43</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-1.29</v>
-      </c>
       <c r="J14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.43</v>
+        <v>-1.75</v>
       </c>
       <c r="M14" t="n">
         <v>2.25</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.75</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.1</v>
+        <v>5.19</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.16</v>
+        <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="I15" t="n">
-        <v>1.76</v>
+        <v>0.77</v>
       </c>
       <c r="J15" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="K15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="M15" t="n">
-        <v>5.28</v>
+        <v>5.36</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="O15" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0.96</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.77</v>
+        <v>4.85</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.04</v>
+        <v>1.68</v>
       </c>
       <c r="G16" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="K16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L16" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="N16" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>0.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.15</v>
+        <v>1.74</v>
       </c>
       <c r="G17" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="J17" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L17" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="M17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="O17" t="n">
-        <v>2.23</v>
+        <v>-0.27</v>
       </c>
       <c r="P17" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.23</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="18">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="E18" t="n">
         <v>-0.01</v>
@@ -1516,40 +1516,40 @@
         <v>-0.3</v>
       </c>
       <c r="G18" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="H18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N18" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I18" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.05</v>
-      </c>
       <c r="O18" t="n">
-        <v>1.48</v>
+        <v>-0.29</v>
       </c>
       <c r="P18" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59.25</v>
+        <v>60.05</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.65</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.09</v>
+        <v>1.35</v>
       </c>
       <c r="G19" t="n">
-        <v>60.05</v>
+        <v>60.2</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
       <c r="J19" t="n">
-        <v>60.2</v>
+        <v>58.6</v>
       </c>
       <c r="K19" t="n">
-        <v>0.15</v>
+        <v>-1.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>-2.66</v>
       </c>
       <c r="M19" t="n">
-        <v>58.6</v>
+        <v>57.8</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.66</v>
+        <v>-1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>58.6</v>
+        <v>57.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6</v>
+        <v>-0.75</v>
       </c>
       <c r="R19" t="n">
-        <v>-2.66</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.56</v>
+        <v>28.88</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.28</v>
+        <v>0.32</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.97</v>
+        <v>1.12</v>
       </c>
       <c r="G20" t="n">
-        <v>28.88</v>
+        <v>28.9</v>
       </c>
       <c r="H20" t="n">
-        <v>0.32</v>
+        <v>0.02</v>
       </c>
       <c r="I20" t="n">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>28.9</v>
+        <v>28.48</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02</v>
+        <v>-0.42</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>28.48</v>
+        <v>27.9</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.42</v>
+        <v>-0.58</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.45</v>
+        <v>-2.04</v>
       </c>
       <c r="P20" t="n">
-        <v>28.48</v>
+        <v>28</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.42</v>
+        <v>0.1</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.45</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="E21" t="n">
         <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="G21" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J21" t="n">
         <v>5.18</v>
       </c>
-      <c r="H21" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5.24</v>
-      </c>
       <c r="K21" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>1.16</v>
+        <v>-1.15</v>
       </c>
       <c r="M21" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.15</v>
+        <v>-1.74</v>
       </c>
       <c r="P21" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.15</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>84.84999999999999</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.41</v>
+        <v>0.35</v>
       </c>
       <c r="G22" t="n">
         <v>85.15000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>85.15000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="M22" t="n">
-        <v>85.90000000000001</v>
+        <v>85.55</v>
       </c>
       <c r="N22" t="n">
-        <v>0.75</v>
+        <v>-0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>0.88</v>
+        <v>-0.41</v>
       </c>
       <c r="P22" t="n">
-        <v>85.90000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.75</v>
+        <v>-0.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0.88</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.82</v>
+        <v>26.78</v>
       </c>
       <c r="E23" t="n">
-        <v>3.22</v>
+        <v>-1.04</v>
       </c>
       <c r="F23" t="n">
-        <v>13.09</v>
+        <v>-3.74</v>
       </c>
       <c r="G23" t="n">
-        <v>26.78</v>
+        <v>26.08</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.04</v>
+        <v>-0.7</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.74</v>
+        <v>-2.61</v>
       </c>
       <c r="J23" t="n">
-        <v>26.08</v>
+        <v>27.68</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.61</v>
+        <v>6.13</v>
       </c>
       <c r="M23" t="n">
-        <v>27.68</v>
+        <v>26.96</v>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>-0.72</v>
       </c>
       <c r="O23" t="n">
-        <v>6.13</v>
+        <v>-2.6</v>
       </c>
       <c r="P23" t="n">
-        <v>27.68</v>
+        <v>28.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="R23" t="n">
-        <v>6.13</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.26</v>
+        <v>30.14</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="F24" t="n">
-        <v>0.36</v>
+        <v>6.65</v>
       </c>
       <c r="G24" t="n">
-        <v>30.14</v>
+        <v>30.22</v>
       </c>
       <c r="H24" t="n">
-        <v>1.88</v>
+        <v>0.08</v>
       </c>
       <c r="I24" t="n">
-        <v>6.65</v>
+        <v>0.27</v>
       </c>
       <c r="J24" t="n">
-        <v>30.22</v>
+        <v>30.88</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="L24" t="n">
-        <v>0.27</v>
+        <v>2.18</v>
       </c>
       <c r="M24" t="n">
-        <v>30.88</v>
+        <v>29.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.66</v>
+        <v>-1.78</v>
       </c>
       <c r="O24" t="n">
-        <v>2.18</v>
+        <v>-5.76</v>
       </c>
       <c r="P24" t="n">
-        <v>30.88</v>
+        <v>28</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.66</v>
+        <v>-1.1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.18</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="E25" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.82</v>
       </c>
       <c r="G25" t="n">
-        <v>28.04</v>
+        <v>28.72</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.52</v>
+        <v>0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
       <c r="J25" t="n">
-        <v>28.72</v>
+        <v>29.62</v>
       </c>
       <c r="K25" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="L25" t="n">
-        <v>2.43</v>
+        <v>3.13</v>
       </c>
       <c r="M25" t="n">
-        <v>29.62</v>
+        <v>28.58</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9</v>
+        <v>-1.04</v>
       </c>
       <c r="O25" t="n">
-        <v>3.13</v>
+        <v>-3.51</v>
       </c>
       <c r="P25" t="n">
-        <v>29.62</v>
+        <v>28.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="R25" t="n">
-        <v>3.13</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>53.85</v>
+        <v>61.75</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="F26" t="n">
-        <v>2.28</v>
+        <v>14.67</v>
       </c>
       <c r="G26" t="n">
-        <v>61.75</v>
+        <v>60.25</v>
       </c>
       <c r="H26" t="n">
-        <v>7.9</v>
+        <v>-1.5</v>
       </c>
       <c r="I26" t="n">
-        <v>14.67</v>
+        <v>-2.43</v>
       </c>
       <c r="J26" t="n">
-        <v>60.25</v>
+        <v>61.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.43</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>61.65</v>
+        <v>62.35</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.32</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>61.65</v>
+        <v>59.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>-2.7</v>
       </c>
       <c r="R26" t="n">
-        <v>2.32</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>425</v>
+        <v>427.2</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.4</v>
+        <v>2.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.16</v>
+        <v>0.52</v>
       </c>
       <c r="G27" t="n">
-        <v>427.2</v>
+        <v>436</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.52</v>
+        <v>2.06</v>
       </c>
       <c r="J27" t="n">
-        <v>436</v>
+        <v>481.6</v>
       </c>
       <c r="K27" t="n">
-        <v>8.800000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="L27" t="n">
-        <v>2.06</v>
+        <v>10.46</v>
       </c>
       <c r="M27" t="n">
-        <v>481.6</v>
+        <v>466.4</v>
       </c>
       <c r="N27" t="n">
-        <v>45.6</v>
+        <v>-15.2</v>
       </c>
       <c r="O27" t="n">
-        <v>10.46</v>
+        <v>-3.16</v>
       </c>
       <c r="P27" t="n">
-        <v>481.6</v>
+        <v>459</v>
       </c>
       <c r="Q27" t="n">
-        <v>45.6</v>
+        <v>-7.4</v>
       </c>
       <c r="R27" t="n">
-        <v>10.46</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>121.8</v>
+        <v>120.9</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.5</v>
+        <v>-0.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.01</v>
+        <v>-0.74</v>
       </c>
       <c r="G28" t="n">
-        <v>120.9</v>
+        <v>122.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9</v>
+        <v>1.9</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.74</v>
+        <v>1.57</v>
       </c>
       <c r="J28" t="n">
-        <v>122.8</v>
+        <v>130.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>6.6</v>
       </c>
       <c r="M28" t="n">
-        <v>130.9</v>
+        <v>126.6</v>
       </c>
       <c r="N28" t="n">
-        <v>8.1</v>
+        <v>-4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>6.6</v>
+        <v>-3.28</v>
       </c>
       <c r="P28" t="n">
-        <v>130.9</v>
+        <v>123.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.1</v>
+        <v>-3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>6.6</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>114.2</v>
+        <v>113.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.1</v>
+        <v>-0.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.81</v>
+        <v>-0.61</v>
       </c>
       <c r="G29" t="n">
-        <v>113.5</v>
+        <v>112.4</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.61</v>
+        <v>-0.97</v>
       </c>
       <c r="J29" t="n">
-        <v>112.4</v>
+        <v>120.1</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.1</v>
+        <v>7.7</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.97</v>
+        <v>6.85</v>
       </c>
       <c r="M29" t="n">
-        <v>120.1</v>
+        <v>115.1</v>
       </c>
       <c r="N29" t="n">
-        <v>7.7</v>
+        <v>-5</v>
       </c>
       <c r="O29" t="n">
-        <v>6.85</v>
+        <v>-4.16</v>
       </c>
       <c r="P29" t="n">
-        <v>120.1</v>
+        <v>115</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.7</v>
+        <v>-0.1</v>
       </c>
       <c r="R29" t="n">
-        <v>6.85</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73.3</v>
+        <v>73.45</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.4</v>
+        <v>0.15</v>
       </c>
       <c r="F30" t="n">
-        <v>-5.66</v>
+        <v>0.2</v>
       </c>
       <c r="G30" t="n">
-        <v>73.45</v>
+        <v>78.25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.15</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>6.54</v>
       </c>
       <c r="J30" t="n">
-        <v>78.25</v>
+        <v>85.5</v>
       </c>
       <c r="K30" t="n">
-        <v>4.8</v>
+        <v>7.25</v>
       </c>
       <c r="L30" t="n">
-        <v>6.54</v>
+        <v>9.27</v>
       </c>
       <c r="M30" t="n">
-        <v>85.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>7.25</v>
+        <v>-5.1</v>
       </c>
       <c r="O30" t="n">
-        <v>9.27</v>
+        <v>-5.96</v>
       </c>
       <c r="P30" t="n">
-        <v>85.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.25</v>
+        <v>-1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>9.27</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>125.6</v>
+        <v>130</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.6</v>
+        <v>4.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.03</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>130</v>
+        <v>129.1</v>
       </c>
       <c r="H31" t="n">
-        <v>4.4</v>
+        <v>-0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>129.1</v>
+        <v>134.7</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.9</v>
+        <v>5.6</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.6899999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="M31" t="n">
-        <v>134.7</v>
+        <v>132.9</v>
       </c>
       <c r="N31" t="n">
-        <v>5.6</v>
+        <v>-1.8</v>
       </c>
       <c r="O31" t="n">
-        <v>4.34</v>
+        <v>-1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>134.7</v>
+        <v>130.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.6</v>
+        <v>-2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>4.34</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>88.25</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>3.05</v>
+        <v>-6.65</v>
       </c>
       <c r="F32" t="n">
-        <v>3.58</v>
+        <v>-7.54</v>
       </c>
       <c r="G32" t="n">
-        <v>81.59999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="H32" t="n">
-        <v>-6.65</v>
+        <v>-2.15</v>
       </c>
       <c r="I32" t="n">
-        <v>-7.54</v>
+        <v>-2.63</v>
       </c>
       <c r="J32" t="n">
-        <v>79.45</v>
+        <v>81.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.15</v>
+        <v>2.5</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.63</v>
+        <v>3.15</v>
       </c>
       <c r="M32" t="n">
-        <v>81.95</v>
+        <v>82.95</v>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>3.15</v>
+        <v>1.22</v>
       </c>
       <c r="P32" t="n">
-        <v>81.95</v>
+        <v>81.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>-1.45</v>
       </c>
       <c r="R32" t="n">
-        <v>3.15</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>90.3</v>
+        <v>91.3</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.44</v>
+        <v>1.11</v>
       </c>
       <c r="G33" t="n">
-        <v>91.3</v>
+        <v>90.75</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>-0.55</v>
       </c>
       <c r="I33" t="n">
-        <v>1.11</v>
+        <v>-0.6</v>
       </c>
       <c r="J33" t="n">
-        <v>90.75</v>
+        <v>96.75</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.55</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.6</v>
+        <v>6.61</v>
       </c>
       <c r="M33" t="n">
-        <v>96.75</v>
+        <v>93.25</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>-3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>6.61</v>
+        <v>-3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>96.75</v>
+        <v>91.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>-1.45</v>
       </c>
       <c r="R33" t="n">
-        <v>6.61</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>44.88</v>
+        <v>45.54</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4</v>
+        <v>0.66</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.88</v>
+        <v>1.47</v>
       </c>
       <c r="G34" t="n">
-        <v>45.54</v>
+        <v>46.54</v>
       </c>
       <c r="H34" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
-        <v>46.54</v>
+        <v>48.98</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>2.44</v>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>5.24</v>
       </c>
       <c r="M34" t="n">
-        <v>48.98</v>
+        <v>46.74</v>
       </c>
       <c r="N34" t="n">
-        <v>2.44</v>
+        <v>-2.24</v>
       </c>
       <c r="O34" t="n">
-        <v>5.24</v>
+        <v>-4.57</v>
       </c>
       <c r="P34" t="n">
-        <v>48.98</v>
+        <v>46.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.44</v>
+        <v>0.2</v>
       </c>
       <c r="R34" t="n">
-        <v>5.24</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="35">
@@ -2564,46 +2564,46 @@
         <v>4.78</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="J35" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="P35" t="n">
         <v>4.87</v>
       </c>
-      <c r="K35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O35" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="P35" t="n">
-        <v>5.09</v>
-      </c>
       <c r="Q35" t="n">
-        <v>0.22</v>
+        <v>-0.08</v>
       </c>
       <c r="R35" t="n">
-        <v>4.52</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.39</v>
+        <v>-0.29</v>
       </c>
       <c r="G36" t="n">
-        <v>10.25</v>
+        <v>10.43</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.29</v>
+        <v>1.76</v>
       </c>
       <c r="J36" t="n">
-        <v>10.43</v>
+        <v>10.94</v>
       </c>
       <c r="K36" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="L36" t="n">
-        <v>1.76</v>
+        <v>4.89</v>
       </c>
       <c r="M36" t="n">
-        <v>10.94</v>
+        <v>10.64</v>
       </c>
       <c r="N36" t="n">
-        <v>0.51</v>
+        <v>-0.3</v>
       </c>
       <c r="O36" t="n">
-        <v>4.89</v>
+        <v>-2.74</v>
       </c>
       <c r="P36" t="n">
-        <v>10.94</v>
+        <v>10.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.51</v>
+        <v>-0.17</v>
       </c>
       <c r="R36" t="n">
-        <v>4.89</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>396.2</v>
+        <v>399.8</v>
       </c>
       <c r="E37" t="n">
-        <v>-6</v>
+        <v>3.6</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.49</v>
+        <v>0.91</v>
       </c>
       <c r="G37" t="n">
-        <v>399.8</v>
+        <v>400.2</v>
       </c>
       <c r="H37" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.91</v>
+        <v>0.1</v>
       </c>
       <c r="J37" t="n">
-        <v>400.2</v>
+        <v>410.4</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4</v>
+        <v>10.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>410.4</v>
+        <v>409.4</v>
       </c>
       <c r="N37" t="n">
-        <v>10.2</v>
+        <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>2.55</v>
+        <v>-0.24</v>
       </c>
       <c r="P37" t="n">
-        <v>410.4</v>
+        <v>400.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>10.2</v>
+        <v>-8.6</v>
       </c>
       <c r="R37" t="n">
-        <v>2.55</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.9</v>
+        <v>15.33</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.14</v>
+        <v>0.43</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.93</v>
+        <v>2.89</v>
       </c>
       <c r="G38" t="n">
-        <v>15.33</v>
+        <v>15.9</v>
       </c>
       <c r="H38" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="I38" t="n">
-        <v>2.89</v>
+        <v>3.72</v>
       </c>
       <c r="J38" t="n">
-        <v>15.9</v>
+        <v>16.35</v>
       </c>
       <c r="K38" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="L38" t="n">
-        <v>3.72</v>
+        <v>2.83</v>
       </c>
       <c r="M38" t="n">
-        <v>16.35</v>
+        <v>16.03</v>
       </c>
       <c r="N38" t="n">
-        <v>0.45</v>
+        <v>-0.32</v>
       </c>
       <c r="O38" t="n">
-        <v>2.83</v>
+        <v>-1.96</v>
       </c>
       <c r="P38" t="n">
-        <v>16.35</v>
+        <v>15.76</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.45</v>
+        <v>-0.27</v>
       </c>
       <c r="R38" t="n">
-        <v>2.83</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>717</v>
+        <v>744.5</v>
       </c>
       <c r="E39" t="n">
-        <v>17</v>
+        <v>27.5</v>
       </c>
       <c r="F39" t="n">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="G39" t="n">
-        <v>744.5</v>
+        <v>753.5</v>
       </c>
       <c r="H39" t="n">
-        <v>27.5</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
-        <v>3.84</v>
+        <v>1.21</v>
       </c>
       <c r="J39" t="n">
-        <v>753.5</v>
+        <v>779.5</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>1.21</v>
+        <v>3.45</v>
       </c>
       <c r="M39" t="n">
-        <v>779.5</v>
+        <v>778</v>
       </c>
       <c r="N39" t="n">
-        <v>26</v>
+        <v>-1.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3.45</v>
+        <v>-0.19</v>
       </c>
       <c r="P39" t="n">
-        <v>779.5</v>
+        <v>723.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>-54.5</v>
       </c>
       <c r="R39" t="n">
-        <v>3.45</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>66.34999999999999</v>
+        <v>63.85</v>
       </c>
       <c r="E40" t="n">
-        <v>3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F40" t="n">
-        <v>5.57</v>
+        <v>-3.77</v>
       </c>
       <c r="G40" t="n">
-        <v>63.85</v>
+        <v>67.8</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.5</v>
+        <v>3.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.77</v>
+        <v>6.19</v>
       </c>
       <c r="J40" t="n">
-        <v>67.8</v>
+        <v>72</v>
       </c>
       <c r="K40" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L40" t="n">
         <v>6.19</v>
       </c>
       <c r="M40" t="n">
-        <v>72</v>
+        <v>68.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>-3.95</v>
       </c>
       <c r="O40" t="n">
-        <v>6.19</v>
+        <v>-5.49</v>
       </c>
       <c r="P40" t="n">
-        <v>72</v>
+        <v>66.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>-1.6</v>
       </c>
       <c r="R40" t="n">
-        <v>6.19</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="41">
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.16</v>
+        <v>23.4</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.86</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="n">
         <v>23.4</v>
@@ -2951,31 +2951,31 @@
         <v>1.04</v>
       </c>
       <c r="J41" t="n">
-        <v>23.4</v>
+        <v>24.08</v>
       </c>
       <c r="K41" t="n">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="L41" t="n">
-        <v>1.04</v>
+        <v>2.91</v>
       </c>
       <c r="M41" t="n">
-        <v>24.08</v>
+        <v>24.53</v>
       </c>
       <c r="N41" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="O41" t="n">
-        <v>2.91</v>
+        <v>1.87</v>
       </c>
       <c r="P41" t="n">
-        <v>24.08</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.68</v>
+        <v>-0.53</v>
       </c>
       <c r="R41" t="n">
-        <v>2.91</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="42">
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>61.93</v>
+        <v>62.84</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.11</v>
+        <v>1.47</v>
       </c>
       <c r="G42" t="n">
         <v>62.84</v>
@@ -3013,31 +3013,31 @@
         <v>1.47</v>
       </c>
       <c r="J42" t="n">
-        <v>62.84</v>
+        <v>64.67</v>
       </c>
       <c r="K42" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="L42" t="n">
-        <v>1.47</v>
+        <v>2.91</v>
       </c>
       <c r="M42" t="n">
-        <v>64.67</v>
+        <v>65.05</v>
       </c>
       <c r="N42" t="n">
-        <v>1.83</v>
+        <v>0.38</v>
       </c>
       <c r="O42" t="n">
-        <v>2.91</v>
+        <v>0.59</v>
       </c>
       <c r="P42" t="n">
-        <v>64.67</v>
+        <v>64.14</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.83</v>
+        <v>-0.91</v>
       </c>
       <c r="R42" t="n">
-        <v>2.91</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="43">
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.69</v>
+        <v>37.6</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.08</v>
+        <v>-0.24</v>
       </c>
       <c r="G43" t="n">
         <v>37.6</v>
@@ -3075,31 +3075,31 @@
         <v>-0.24</v>
       </c>
       <c r="J43" t="n">
-        <v>37.6</v>
+        <v>38.4</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.09</v>
+        <v>0.8</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.24</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="N43" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.13</v>
+        <v>1.04</v>
       </c>
       <c r="P43" t="n">
-        <v>38.4</v>
+        <v>38.31</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.8</v>
+        <v>-0.49</v>
       </c>
       <c r="R43" t="n">
-        <v>2.13</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="44">
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F44" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="G44" t="n">
         <v>6.39</v>
@@ -3137,31 +3137,31 @@
         <v>1.27</v>
       </c>
       <c r="J44" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="K44" t="n">
-        <v>0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="L44" t="n">
-        <v>1.27</v>
+        <v>-1.72</v>
       </c>
       <c r="M44" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="O44" t="n">
-        <v>-1.72</v>
+        <v>0.16</v>
       </c>
       <c r="P44" t="n">
-        <v>6.28</v>
+        <v>6.21</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.72</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="45">
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.36</v>
+        <v>-2.3</v>
       </c>
       <c r="G45" t="n">
         <v>2.12</v>
@@ -3199,31 +3199,31 @@
         <v>-2.3</v>
       </c>
       <c r="J45" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.3</v>
+        <v>-1.89</v>
       </c>
       <c r="M45" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-1.89</v>
+        <v>0.48</v>
       </c>
       <c r="P45" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.89</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="46">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="E46" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="F46" t="n">
-        <v>6.74</v>
+        <v>1.32</v>
       </c>
       <c r="G46" t="n">
         <v>3.85</v>
@@ -3261,31 +3261,31 @@
         <v>1.32</v>
       </c>
       <c r="J46" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K46" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O46" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="P46" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>2.6</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="47">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.04</v>
+        <v>11.38</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.06</v>
+        <v>0.34</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.54</v>
+        <v>3.08</v>
       </c>
       <c r="G47" t="n">
         <v>11.38</v>
@@ -3323,31 +3323,31 @@
         <v>3.08</v>
       </c>
       <c r="J47" t="n">
-        <v>11.38</v>
+        <v>11.16</v>
       </c>
       <c r="K47" t="n">
-        <v>0.34</v>
+        <v>-0.22</v>
       </c>
       <c r="L47" t="n">
-        <v>3.08</v>
+        <v>-1.93</v>
       </c>
       <c r="M47" t="n">
-        <v>11.16</v>
+        <v>11.27</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.22</v>
+        <v>0.11</v>
       </c>
       <c r="O47" t="n">
-        <v>-1.93</v>
+        <v>0.99</v>
       </c>
       <c r="P47" t="n">
-        <v>11.16</v>
+        <v>11.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.93</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="48">
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="G48" t="n">
         <v>0.32</v>
@@ -3388,22 +3388,22 @@
         <v>0.32</v>
       </c>
       <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="P48" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.68</v>
+        <v>-0.46</v>
       </c>
       <c r="G49" t="n">
         <v>4.34</v>
@@ -3450,28 +3450,28 @@
         <v>4.34</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="P49" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3491,13 +3491,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="G50" t="n">
         <v>1.03</v>
@@ -3512,28 +3512,28 @@
         <v>1.03</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="P50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="51">
@@ -3556,10 +3556,10 @@
         <v>3.64</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>3.64</v>
@@ -3571,31 +3571,31 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="M51" t="n">
         <v>3.58</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="R51" t="n">
-        <v>-1.65</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="52">
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.72</v>
+        <v>10.76</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.11</v>
+        <v>0.37</v>
       </c>
       <c r="G52" t="n">
         <v>10.76</v>
@@ -3633,31 +3633,31 @@
         <v>0.37</v>
       </c>
       <c r="J52" t="n">
-        <v>10.76</v>
+        <v>10.95</v>
       </c>
       <c r="K52" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="L52" t="n">
-        <v>0.37</v>
+        <v>1.77</v>
       </c>
       <c r="M52" t="n">
-        <v>10.95</v>
+        <v>10.87</v>
       </c>
       <c r="N52" t="n">
-        <v>0.19</v>
+        <v>-0.08</v>
       </c>
       <c r="O52" t="n">
-        <v>1.77</v>
+        <v>-0.73</v>
       </c>
       <c r="P52" t="n">
-        <v>10.95</v>
+        <v>10.66</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="R52" t="n">
-        <v>1.77</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="53">
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.369999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="E53" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="F53" t="n">
-        <v>1.58</v>
+        <v>2.51</v>
       </c>
       <c r="G53" t="n">
         <v>8.58</v>
@@ -3695,31 +3695,31 @@
         <v>2.51</v>
       </c>
       <c r="J53" t="n">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="K53" t="n">
-        <v>0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="L53" t="n">
-        <v>2.51</v>
+        <v>-1.63</v>
       </c>
       <c r="M53" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.63</v>
+        <v>-0.47</v>
       </c>
       <c r="P53" t="n">
-        <v>8.44</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.63</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="54">
@@ -3757,31 +3757,31 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.45</v>
+        <v>0.435</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-3.33</v>
       </c>
       <c r="M54" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>-3.33</v>
+        <v>-1.15</v>
       </c>
       <c r="P54" t="n">
-        <v>0.435</v>
+        <v>0.425</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-3.33</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="55">
@@ -3801,13 +3801,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.595</v>
+        <v>0.6</v>
       </c>
       <c r="E55" t="n">
         <v>0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="G55" t="n">
         <v>0.6</v>
@@ -3819,31 +3819,31 @@
         <v>0.84</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="K55" t="n">
         <v>0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="M55" t="n">
-        <v>0.605</v>
+        <v>0.615</v>
       </c>
       <c r="N55" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O55" t="n">
-        <v>0.83</v>
+        <v>1.65</v>
       </c>
       <c r="P55" t="n">
-        <v>0.605</v>
+        <v>0.615</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.475</v>
+        <v>0.465</v>
       </c>
       <c r="E56" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>1.06</v>
+        <v>-2.11</v>
       </c>
       <c r="G56" t="n">
         <v>0.465</v>
@@ -3884,22 +3884,22 @@
         <v>0.465</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.13</v>
+        <v>0.2</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.69</v>
+        <v>5.9</v>
       </c>
       <c r="G57" t="n">
         <v>3.59</v>
@@ -3943,31 +3943,31 @@
         <v>5.9</v>
       </c>
       <c r="J57" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="K57" t="n">
-        <v>0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="L57" t="n">
-        <v>5.9</v>
+        <v>-4.18</v>
       </c>
       <c r="M57" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
       <c r="O57" t="n">
-        <v>-4.18</v>
+        <v>1.16</v>
       </c>
       <c r="P57" t="n">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.18</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="58">
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.27</v>
+        <v>5.13</v>
       </c>
       <c r="G58" t="n">
         <v>0.082</v>
@@ -4005,31 +4005,31 @@
         <v>5.13</v>
       </c>
       <c r="J58" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="P58" t="n">
         <v>0.082</v>
       </c>
-      <c r="K58" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L58" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.08400000000000001</v>
-      </c>
       <c r="Q58" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>2.44</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="59">
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.45</v>
+        <v>21.88</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.35</v>
+        <v>0.43</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.61</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
         <v>21.88</v>
@@ -4067,31 +4067,31 @@
         <v>2</v>
       </c>
       <c r="J59" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M59" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P59" t="n">
         <v>21.88</v>
       </c>
-      <c r="K59" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L59" t="n">
-        <v>2</v>
-      </c>
-      <c r="M59" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P59" t="n">
-        <v>21.98</v>
-      </c>
       <c r="Q59" t="n">
-        <v>0.1</v>
+        <v>-0.43</v>
       </c>
       <c r="R59" t="n">
-        <v>0.46</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="60">
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.31</v>
+        <v>1.89</v>
       </c>
       <c r="G60" t="n">
         <v>3.23</v>
@@ -4129,31 +4129,31 @@
         <v>1.89</v>
       </c>
       <c r="J60" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="K60" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="L60" t="n">
-        <v>1.89</v>
+        <v>-0.93</v>
       </c>
       <c r="M60" t="n">
         <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.93</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="61">
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.19</v>
+        <v>2.99</v>
       </c>
       <c r="G61" t="n">
         <v>1.38</v>
@@ -4191,31 +4191,31 @@
         <v>2.99</v>
       </c>
       <c r="J61" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="K61" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="L61" t="n">
-        <v>2.99</v>
+        <v>-7.25</v>
       </c>
       <c r="M61" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="O61" t="n">
-        <v>-7.25</v>
+        <v>1.56</v>
       </c>
       <c r="P61" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R61" t="n">
-        <v>-7.25</v>
+        <v>-5.38</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-05-29 Close</t>
+          <t>2026-06-01 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change</t>
+          <t>2026-06-01 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-05-29 Change %</t>
+          <t>2026-06-01 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-06-01 Close</t>
+          <t>2026-06-02 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change</t>
+          <t>2026-06-02 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change %</t>
+          <t>2026-06-02 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-02 Close</t>
+          <t>2026-06-03 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change</t>
+          <t>2026-06-03 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change %</t>
+          <t>2026-06-03 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-03 Close</t>
+          <t>2026-06-04 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change</t>
+          <t>2026-06-04 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change %</t>
+          <t>2026-06-04 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-04 Close</t>
+          <t>2026-06-05 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change</t>
+          <t>2026-06-05 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change %</t>
+          <t>2026-06-05 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>145.1</v>
+        <v>146.3</v>
       </c>
       <c r="E3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G3" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J3" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="L3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="G3" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="J3" t="n">
-        <v>147.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.62</v>
-      </c>
       <c r="M3" t="n">
-        <v>146.9</v>
+        <v>146.4</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="P3" t="n">
-        <v>146.4</v>
+        <v>141.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5</v>
+        <v>-4.6</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.34</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>206.6</v>
+        <v>210.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1</v>
+        <v>1.94</v>
       </c>
       <c r="G4" t="n">
-        <v>210.6</v>
+        <v>215.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="J4" t="n">
-        <v>215.2</v>
+        <v>217</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="n">
-        <v>2.18</v>
+        <v>0.84</v>
       </c>
       <c r="M4" t="n">
-        <v>217</v>
+        <v>211.8</v>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>-5.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.84</v>
+        <v>-2.4</v>
       </c>
       <c r="P4" t="n">
-        <v>211.8</v>
+        <v>201.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.2</v>
+        <v>-10.4</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.4</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>-0.17</v>
       </c>
       <c r="G5" t="n">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="H5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="K5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="J5" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="M5" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.17</v>
+        <v>-0.51</v>
       </c>
       <c r="P5" t="n">
-        <v>5.81</v>
+        <v>5.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.51</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.76</v>
+        <v>0.15</v>
       </c>
       <c r="G6" t="n">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>0.15</v>
+        <v>2.26</v>
       </c>
       <c r="J6" t="n">
-        <v>6.8</v>
+        <v>6.72</v>
       </c>
       <c r="K6" t="n">
-        <v>0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.26</v>
+        <v>-1.18</v>
       </c>
       <c r="M6" t="n">
         <v>6.72</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6.72</v>
+        <v>6.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>1.56</v>
+        <v>0.19</v>
       </c>
       <c r="G7" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.19</v>
+        <v>1.72</v>
       </c>
       <c r="J7" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="P7" t="n">
         <v>5.31</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.25</v>
-      </c>
       <c r="Q7" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.38</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="G8" t="n">
-        <v>8.529999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.47</v>
+        <v>1.52</v>
       </c>
       <c r="J8" t="n">
-        <v>8.66</v>
+        <v>8.57</v>
       </c>
       <c r="K8" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>-1.04</v>
       </c>
       <c r="M8" t="n">
-        <v>8.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="P8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.02</v>
+        <v>0.17</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.23</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="E9" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>7.38</v>
+        <v>7.51</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="J9" t="n">
-        <v>7.51</v>
+        <v>7.42</v>
       </c>
       <c r="K9" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>-1.2</v>
       </c>
       <c r="M9" t="n">
-        <v>7.42</v>
+        <v>7.37</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2</v>
+        <v>-0.67</v>
       </c>
       <c r="P9" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.67</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="E10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M10" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.18</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="G10" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J10" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="M10" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="P10" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="11">
@@ -1073,34 +1073,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="E11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K11" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F11" t="n">
+      <c r="L11" t="n">
         <v>-0.46</v>
       </c>
-      <c r="G11" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="M11" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="N11" t="n">
         <v>-0.02</v>
@@ -1109,13 +1109,13 @@
         <v>-0.46</v>
       </c>
       <c r="P11" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.46</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.89</v>
+        <v>10.91</v>
       </c>
       <c r="E12" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>0.18</v>
       </c>
       <c r="G12" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.18</v>
+        <v>-1.47</v>
       </c>
       <c r="J12" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.47</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>10.69</v>
+        <v>10.55</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="P12" t="n">
         <v>10.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="G13" t="n">
-        <v>26.7</v>
+        <v>27.36</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="I13" t="n">
-        <v>1.14</v>
+        <v>2.47</v>
       </c>
       <c r="J13" t="n">
-        <v>27.36</v>
+        <v>27.26</v>
       </c>
       <c r="K13" t="n">
-        <v>0.66</v>
+        <v>-0.1</v>
       </c>
       <c r="L13" t="n">
-        <v>2.47</v>
+        <v>-0.37</v>
       </c>
       <c r="M13" t="n">
-        <v>27.26</v>
+        <v>27.02</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.37</v>
+        <v>-0.88</v>
       </c>
       <c r="P13" t="n">
-        <v>27.02</v>
+        <v>26.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.88</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.29</v>
+        <v>-0.43</v>
       </c>
       <c r="G14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.43</v>
+        <v>-1.75</v>
       </c>
       <c r="J14" t="n">
         <v>2.25</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="P14" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="R14" t="n">
-        <v>0.89</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="F15" t="n">
-        <v>1.76</v>
+        <v>0.77</v>
       </c>
       <c r="G15" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="J15" t="n">
-        <v>5.28</v>
+        <v>5.36</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="L15" t="n">
-        <v>0.96</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>0.19</v>
       </c>
       <c r="P15" t="n">
-        <v>5.37</v>
+        <v>5.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>0.19</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="J16" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
         <v>4.98</v>
       </c>
       <c r="N16" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="G17" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="H17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I17" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="J17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>2.23</v>
+        <v>-0.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.27</v>
+        <v>-1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.37</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="E18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K18" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F18" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="L18" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="P18" t="n">
         <v>3.38</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.02</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60.05</v>
+        <v>60.2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>1.35</v>
+        <v>0.25</v>
       </c>
       <c r="G19" t="n">
-        <v>60.2</v>
+        <v>58.6</v>
       </c>
       <c r="H19" t="n">
-        <v>0.15</v>
+        <v>-1.6</v>
       </c>
       <c r="I19" t="n">
-        <v>0.25</v>
+        <v>-2.66</v>
       </c>
       <c r="J19" t="n">
-        <v>58.6</v>
+        <v>57.8</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.66</v>
+        <v>-1.37</v>
       </c>
       <c r="M19" t="n">
-        <v>57.8</v>
+        <v>57.05</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>57.05</v>
+        <v>56.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.3</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.88</v>
+        <v>28.9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.32</v>
+        <v>0.02</v>
       </c>
       <c r="F20" t="n">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>28.9</v>
+        <v>28.48</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02</v>
+        <v>-0.42</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="J20" t="n">
-        <v>28.48</v>
+        <v>27.9</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.42</v>
+        <v>-0.58</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.45</v>
+        <v>-2.04</v>
       </c>
       <c r="M20" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.58</v>
+        <v>0.1</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.04</v>
+        <v>0.36</v>
       </c>
       <c r="P20" t="n">
         <v>28</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G21" t="n">
         <v>5.18</v>
       </c>
-      <c r="E21" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.24</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>1.16</v>
+        <v>-1.15</v>
       </c>
       <c r="J21" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.15</v>
+        <v>-1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.74</v>
+        <v>-1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.38</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="22">
@@ -1758,46 +1758,46 @@
         <v>85.15000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>85.15000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J22" t="n">
-        <v>85.90000000000001</v>
+        <v>85.55</v>
       </c>
       <c r="K22" t="n">
-        <v>0.75</v>
+        <v>-0.35</v>
       </c>
       <c r="L22" t="n">
-        <v>0.88</v>
+        <v>-0.41</v>
       </c>
       <c r="M22" t="n">
-        <v>85.55</v>
+        <v>84.75</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.35</v>
+        <v>-0.8</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.41</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>84.75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.8</v>
+        <v>-2.35</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.78</v>
+        <v>26.08</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.04</v>
+        <v>-0.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.74</v>
+        <v>-2.61</v>
       </c>
       <c r="G23" t="n">
-        <v>26.08</v>
+        <v>27.68</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.61</v>
+        <v>6.13</v>
       </c>
       <c r="J23" t="n">
-        <v>27.68</v>
+        <v>26.96</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6</v>
+        <v>-0.72</v>
       </c>
       <c r="L23" t="n">
-        <v>6.13</v>
+        <v>-2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>26.96</v>
+        <v>28.38</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.72</v>
+        <v>1.42</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.6</v>
+        <v>5.27</v>
       </c>
       <c r="P23" t="n">
-        <v>28.38</v>
+        <v>29.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="R23" t="n">
-        <v>5.27</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.14</v>
+        <v>30.22</v>
       </c>
       <c r="E24" t="n">
-        <v>1.88</v>
+        <v>0.08</v>
       </c>
       <c r="F24" t="n">
-        <v>6.65</v>
+        <v>0.27</v>
       </c>
       <c r="G24" t="n">
-        <v>30.22</v>
+        <v>30.88</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>0.27</v>
+        <v>2.18</v>
       </c>
       <c r="J24" t="n">
-        <v>30.88</v>
+        <v>29.1</v>
       </c>
       <c r="K24" t="n">
-        <v>0.66</v>
+        <v>-1.78</v>
       </c>
       <c r="L24" t="n">
-        <v>2.18</v>
+        <v>-5.76</v>
       </c>
       <c r="M24" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.78</v>
+        <v>-1.1</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.76</v>
+        <v>-3.78</v>
       </c>
       <c r="P24" t="n">
-        <v>28</v>
+        <v>26.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1</v>
+        <v>-1.88</v>
       </c>
       <c r="R24" t="n">
-        <v>-3.78</v>
+        <v>-6.71</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.04</v>
+        <v>28.72</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.52</v>
+        <v>0.68</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
       <c r="G25" t="n">
-        <v>28.72</v>
+        <v>29.62</v>
       </c>
       <c r="H25" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.43</v>
+        <v>3.13</v>
       </c>
       <c r="J25" t="n">
-        <v>29.62</v>
+        <v>28.58</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9</v>
+        <v>-1.04</v>
       </c>
       <c r="L25" t="n">
-        <v>3.13</v>
+        <v>-3.51</v>
       </c>
       <c r="M25" t="n">
-        <v>28.58</v>
+        <v>28.38</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.04</v>
+        <v>-0.2</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.51</v>
+        <v>-0.7</v>
       </c>
       <c r="P25" t="n">
-        <v>28.38</v>
+        <v>27.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.7</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>61.75</v>
+        <v>60.25</v>
       </c>
       <c r="E26" t="n">
-        <v>7.9</v>
+        <v>-1.5</v>
       </c>
       <c r="F26" t="n">
-        <v>14.67</v>
+        <v>-2.43</v>
       </c>
       <c r="G26" t="n">
-        <v>60.25</v>
+        <v>61.65</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.43</v>
+        <v>2.32</v>
       </c>
       <c r="J26" t="n">
-        <v>61.65</v>
+        <v>62.35</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>1.14</v>
       </c>
       <c r="M26" t="n">
-        <v>62.35</v>
+        <v>59.65</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7</v>
+        <v>-2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.14</v>
+        <v>-4.33</v>
       </c>
       <c r="P26" t="n">
-        <v>59.65</v>
+        <v>55.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.7</v>
+        <v>-3.85</v>
       </c>
       <c r="R26" t="n">
-        <v>-4.33</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>427.2</v>
+        <v>436</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.52</v>
+        <v>2.06</v>
       </c>
       <c r="G27" t="n">
-        <v>436</v>
+        <v>481.6</v>
       </c>
       <c r="H27" t="n">
-        <v>8.800000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2.06</v>
+        <v>10.46</v>
       </c>
       <c r="J27" t="n">
-        <v>481.6</v>
+        <v>466.4</v>
       </c>
       <c r="K27" t="n">
-        <v>45.6</v>
+        <v>-15.2</v>
       </c>
       <c r="L27" t="n">
-        <v>10.46</v>
+        <v>-3.16</v>
       </c>
       <c r="M27" t="n">
-        <v>466.4</v>
+        <v>459</v>
       </c>
       <c r="N27" t="n">
-        <v>-15.2</v>
+        <v>-7.4</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.16</v>
+        <v>-1.59</v>
       </c>
       <c r="P27" t="n">
-        <v>459</v>
+        <v>453.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.4</v>
+        <v>-5.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.59</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>120.9</v>
+        <v>122.8</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.9</v>
+        <v>1.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.74</v>
+        <v>1.57</v>
       </c>
       <c r="G28" t="n">
-        <v>122.8</v>
+        <v>130.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="I28" t="n">
-        <v>1.57</v>
+        <v>6.6</v>
       </c>
       <c r="J28" t="n">
-        <v>130.9</v>
+        <v>126.6</v>
       </c>
       <c r="K28" t="n">
-        <v>8.1</v>
+        <v>-4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>6.6</v>
+        <v>-3.28</v>
       </c>
       <c r="M28" t="n">
-        <v>126.6</v>
+        <v>123.5</v>
       </c>
       <c r="N28" t="n">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.28</v>
+        <v>-2.45</v>
       </c>
       <c r="P28" t="n">
-        <v>123.5</v>
+        <v>122.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.1</v>
+        <v>-1.1</v>
       </c>
       <c r="R28" t="n">
-        <v>-2.45</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>113.5</v>
+        <v>112.4</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.61</v>
+        <v>-0.97</v>
       </c>
       <c r="G29" t="n">
-        <v>112.4</v>
+        <v>120.1</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1</v>
+        <v>7.7</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.97</v>
+        <v>6.85</v>
       </c>
       <c r="J29" t="n">
-        <v>120.1</v>
+        <v>115.1</v>
       </c>
       <c r="K29" t="n">
-        <v>7.7</v>
+        <v>-5</v>
       </c>
       <c r="L29" t="n">
-        <v>6.85</v>
+        <v>-4.16</v>
       </c>
       <c r="M29" t="n">
-        <v>115.1</v>
+        <v>115</v>
       </c>
       <c r="N29" t="n">
-        <v>-5</v>
+        <v>-0.1</v>
       </c>
       <c r="O29" t="n">
-        <v>-4.16</v>
+        <v>-0.09</v>
       </c>
       <c r="P29" t="n">
-        <v>115</v>
+        <v>115.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.09</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73.45</v>
+        <v>78.25</v>
       </c>
       <c r="E30" t="n">
-        <v>0.15</v>
+        <v>4.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2</v>
+        <v>6.54</v>
       </c>
       <c r="G30" t="n">
-        <v>78.25</v>
+        <v>85.5</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>7.25</v>
       </c>
       <c r="I30" t="n">
-        <v>6.54</v>
+        <v>9.27</v>
       </c>
       <c r="J30" t="n">
-        <v>85.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>7.25</v>
+        <v>-5.1</v>
       </c>
       <c r="L30" t="n">
-        <v>9.27</v>
+        <v>-5.96</v>
       </c>
       <c r="M30" t="n">
-        <v>80.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>-5.1</v>
+        <v>-1.8</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.96</v>
+        <v>-2.24</v>
       </c>
       <c r="P30" t="n">
-        <v>78.59999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.8</v>
+        <v>1.35</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.24</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>130</v>
+        <v>129.1</v>
       </c>
       <c r="E31" t="n">
-        <v>4.4</v>
+        <v>-0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>129.1</v>
+        <v>134.7</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9</v>
+        <v>5.6</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6899999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="J31" t="n">
-        <v>134.7</v>
+        <v>132.9</v>
       </c>
       <c r="K31" t="n">
-        <v>5.6</v>
+        <v>-1.8</v>
       </c>
       <c r="L31" t="n">
-        <v>4.34</v>
+        <v>-1.34</v>
       </c>
       <c r="M31" t="n">
-        <v>132.9</v>
+        <v>130.1</v>
       </c>
       <c r="N31" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.34</v>
+        <v>-2.11</v>
       </c>
       <c r="P31" t="n">
-        <v>130.1</v>
+        <v>125.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>-2.8</v>
+        <v>-4.5</v>
       </c>
       <c r="R31" t="n">
-        <v>-2.11</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>81.59999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="E32" t="n">
-        <v>-6.65</v>
+        <v>-2.15</v>
       </c>
       <c r="F32" t="n">
-        <v>-7.54</v>
+        <v>-2.63</v>
       </c>
       <c r="G32" t="n">
-        <v>79.45</v>
+        <v>81.95</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.15</v>
+        <v>2.5</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.63</v>
+        <v>3.15</v>
       </c>
       <c r="J32" t="n">
-        <v>81.95</v>
+        <v>82.95</v>
       </c>
       <c r="K32" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>3.15</v>
+        <v>1.22</v>
       </c>
       <c r="M32" t="n">
-        <v>82.95</v>
+        <v>81.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>-1.45</v>
       </c>
       <c r="O32" t="n">
-        <v>1.22</v>
+        <v>-1.75</v>
       </c>
       <c r="P32" t="n">
-        <v>81.5</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.45</v>
+        <v>-5.85</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.75</v>
+        <v>-7.18</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>91.3</v>
+        <v>90.75</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>-0.55</v>
       </c>
       <c r="F33" t="n">
-        <v>1.11</v>
+        <v>-0.6</v>
       </c>
       <c r="G33" t="n">
-        <v>90.75</v>
+        <v>96.75</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.55</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6</v>
+        <v>6.61</v>
       </c>
       <c r="J33" t="n">
-        <v>96.75</v>
+        <v>93.25</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>-3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>6.61</v>
+        <v>-3.62</v>
       </c>
       <c r="M33" t="n">
-        <v>93.25</v>
+        <v>91.8</v>
       </c>
       <c r="N33" t="n">
-        <v>-3.5</v>
+        <v>-1.45</v>
       </c>
       <c r="O33" t="n">
-        <v>-3.62</v>
+        <v>-1.55</v>
       </c>
       <c r="P33" t="n">
-        <v>91.8</v>
+        <v>89.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.45</v>
+        <v>-2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.55</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45.54</v>
+        <v>46.54</v>
       </c>
       <c r="E34" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>46.54</v>
+        <v>48.98</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2.44</v>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>5.24</v>
       </c>
       <c r="J34" t="n">
-        <v>48.98</v>
+        <v>46.74</v>
       </c>
       <c r="K34" t="n">
-        <v>2.44</v>
+        <v>-2.24</v>
       </c>
       <c r="L34" t="n">
-        <v>5.24</v>
+        <v>-4.57</v>
       </c>
       <c r="M34" t="n">
-        <v>46.74</v>
+        <v>46.94</v>
       </c>
       <c r="N34" t="n">
-        <v>-2.24</v>
+        <v>0.2</v>
       </c>
       <c r="O34" t="n">
-        <v>-4.57</v>
+        <v>0.43</v>
       </c>
       <c r="P34" t="n">
-        <v>46.94</v>
+        <v>46.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="R34" t="n">
-        <v>0.43</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="G35" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="M35" t="n">
         <v>4.87</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J35" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L35" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.95</v>
-      </c>
       <c r="N35" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="O35" t="n">
-        <v>-2.75</v>
+        <v>-1.62</v>
       </c>
       <c r="P35" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="Q35" t="n">
         <v>-0.08</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.62</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.25</v>
+        <v>10.43</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.29</v>
+        <v>1.76</v>
       </c>
       <c r="G36" t="n">
-        <v>10.43</v>
+        <v>10.94</v>
       </c>
       <c r="H36" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="I36" t="n">
-        <v>1.76</v>
+        <v>4.89</v>
       </c>
       <c r="J36" t="n">
-        <v>10.94</v>
+        <v>10.64</v>
       </c>
       <c r="K36" t="n">
-        <v>0.51</v>
+        <v>-0.3</v>
       </c>
       <c r="L36" t="n">
-        <v>4.89</v>
+        <v>-2.74</v>
       </c>
       <c r="M36" t="n">
-        <v>10.64</v>
+        <v>10.47</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="O36" t="n">
-        <v>-2.74</v>
+        <v>-1.6</v>
       </c>
       <c r="P36" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.6</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>399.8</v>
+        <v>400.2</v>
       </c>
       <c r="E37" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.91</v>
+        <v>0.1</v>
       </c>
       <c r="G37" t="n">
-        <v>400.2</v>
+        <v>410.4</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4</v>
+        <v>10.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1</v>
+        <v>2.55</v>
       </c>
       <c r="J37" t="n">
-        <v>410.4</v>
+        <v>409.4</v>
       </c>
       <c r="K37" t="n">
-        <v>10.2</v>
+        <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>-0.24</v>
       </c>
       <c r="M37" t="n">
-        <v>409.4</v>
+        <v>400.8</v>
       </c>
       <c r="N37" t="n">
-        <v>-1</v>
+        <v>-8.6</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.24</v>
+        <v>-2.1</v>
       </c>
       <c r="P37" t="n">
-        <v>400.8</v>
+        <v>396.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>-8.6</v>
+        <v>-4.4</v>
       </c>
       <c r="R37" t="n">
-        <v>-2.1</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.33</v>
+        <v>15.9</v>
       </c>
       <c r="E38" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="F38" t="n">
-        <v>2.89</v>
+        <v>3.72</v>
       </c>
       <c r="G38" t="n">
-        <v>15.9</v>
+        <v>16.35</v>
       </c>
       <c r="H38" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="I38" t="n">
-        <v>3.72</v>
+        <v>2.83</v>
       </c>
       <c r="J38" t="n">
-        <v>16.35</v>
+        <v>16.03</v>
       </c>
       <c r="K38" t="n">
-        <v>0.45</v>
+        <v>-0.32</v>
       </c>
       <c r="L38" t="n">
-        <v>2.83</v>
+        <v>-1.96</v>
       </c>
       <c r="M38" t="n">
-        <v>16.03</v>
+        <v>15.76</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.96</v>
+        <v>-1.68</v>
       </c>
       <c r="P38" t="n">
-        <v>15.76</v>
+        <v>15.21</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.27</v>
+        <v>-0.55</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.68</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>744.5</v>
+        <v>753.5</v>
       </c>
       <c r="E39" t="n">
-        <v>27.5</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>3.84</v>
+        <v>1.21</v>
       </c>
       <c r="G39" t="n">
-        <v>753.5</v>
+        <v>779.5</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I39" t="n">
-        <v>1.21</v>
+        <v>3.45</v>
       </c>
       <c r="J39" t="n">
-        <v>779.5</v>
+        <v>778</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>-1.5</v>
       </c>
       <c r="L39" t="n">
-        <v>3.45</v>
+        <v>-0.19</v>
       </c>
       <c r="M39" t="n">
-        <v>778</v>
+        <v>723.5</v>
       </c>
       <c r="N39" t="n">
-        <v>-1.5</v>
+        <v>-54.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.19</v>
+        <v>-7.01</v>
       </c>
       <c r="P39" t="n">
-        <v>723.5</v>
+        <v>711</v>
       </c>
       <c r="Q39" t="n">
-        <v>-54.5</v>
+        <v>-12.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-7.01</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>63.85</v>
+        <v>67.8</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.5</v>
+        <v>3.95</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.77</v>
+        <v>6.19</v>
       </c>
       <c r="G40" t="n">
-        <v>67.8</v>
+        <v>72</v>
       </c>
       <c r="H40" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I40" t="n">
         <v>6.19</v>
       </c>
       <c r="J40" t="n">
-        <v>72</v>
+        <v>68.05</v>
       </c>
       <c r="K40" t="n">
-        <v>4.2</v>
+        <v>-3.95</v>
       </c>
       <c r="L40" t="n">
-        <v>6.19</v>
+        <v>-5.49</v>
       </c>
       <c r="M40" t="n">
-        <v>68.05</v>
+        <v>66.45</v>
       </c>
       <c r="N40" t="n">
-        <v>-3.95</v>
+        <v>-1.6</v>
       </c>
       <c r="O40" t="n">
-        <v>-5.49</v>
+        <v>-2.35</v>
       </c>
       <c r="P40" t="n">
-        <v>66.45</v>
+        <v>65</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.6</v>
+        <v>-1.45</v>
       </c>
       <c r="R40" t="n">
-        <v>-2.35</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="41">
@@ -2942,40 +2942,40 @@
         <v>1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>23.4</v>
+        <v>24.08</v>
       </c>
       <c r="H41" t="n">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="I41" t="n">
-        <v>1.04</v>
+        <v>2.91</v>
       </c>
       <c r="J41" t="n">
-        <v>24.08</v>
+        <v>24.53</v>
       </c>
       <c r="K41" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="L41" t="n">
-        <v>2.91</v>
+        <v>1.87</v>
       </c>
       <c r="M41" t="n">
-        <v>24.53</v>
+        <v>24</v>
       </c>
       <c r="N41" t="n">
-        <v>0.45</v>
+        <v>-0.53</v>
       </c>
       <c r="O41" t="n">
-        <v>1.87</v>
+        <v>-2.16</v>
       </c>
       <c r="P41" t="n">
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.53</v>
+        <v>-0.06</v>
       </c>
       <c r="R41" t="n">
-        <v>-2.16</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="42">
@@ -3004,40 +3004,40 @@
         <v>1.47</v>
       </c>
       <c r="G42" t="n">
-        <v>62.84</v>
+        <v>64.67</v>
       </c>
       <c r="H42" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="I42" t="n">
-        <v>1.47</v>
+        <v>2.91</v>
       </c>
       <c r="J42" t="n">
-        <v>64.67</v>
+        <v>65.05</v>
       </c>
       <c r="K42" t="n">
-        <v>1.83</v>
+        <v>0.38</v>
       </c>
       <c r="L42" t="n">
-        <v>2.91</v>
+        <v>0.59</v>
       </c>
       <c r="M42" t="n">
-        <v>65.05</v>
+        <v>64.14</v>
       </c>
       <c r="N42" t="n">
-        <v>0.38</v>
+        <v>-0.91</v>
       </c>
       <c r="O42" t="n">
-        <v>0.59</v>
+        <v>-1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>64.14</v>
+        <v>63.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.91</v>
+        <v>-0.36</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.4</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3066,40 +3066,40 @@
         <v>-0.24</v>
       </c>
       <c r="G43" t="n">
-        <v>37.6</v>
+        <v>38.4</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.09</v>
+        <v>0.8</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.24</v>
+        <v>2.13</v>
       </c>
       <c r="J43" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>1.04</v>
       </c>
       <c r="M43" t="n">
-        <v>38.8</v>
+        <v>38.31</v>
       </c>
       <c r="N43" t="n">
-        <v>0.4</v>
+        <v>-0.49</v>
       </c>
       <c r="O43" t="n">
-        <v>1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="P43" t="n">
-        <v>38.31</v>
+        <v>38.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.49</v>
+        <v>0.24</v>
       </c>
       <c r="R43" t="n">
-        <v>-1.26</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="44">
@@ -3128,40 +3128,40 @@
         <v>1.27</v>
       </c>
       <c r="G44" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="I44" t="n">
-        <v>1.27</v>
+        <v>-1.72</v>
       </c>
       <c r="J44" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.72</v>
+        <v>0.16</v>
       </c>
       <c r="M44" t="n">
-        <v>6.29</v>
+        <v>6.21</v>
       </c>
       <c r="N44" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="O44" t="n">
-        <v>0.16</v>
+        <v>-1.27</v>
       </c>
       <c r="P44" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="Q44" t="n">
         <v>-0.08</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.27</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="45">
@@ -3190,40 +3190,40 @@
         <v>-2.3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.3</v>
+        <v>-1.89</v>
       </c>
       <c r="J45" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="L45" t="n">
-        <v>-1.89</v>
+        <v>0.48</v>
       </c>
       <c r="M45" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="N45" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O45" t="n">
-        <v>0.48</v>
+        <v>-2.87</v>
       </c>
       <c r="P45" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.87</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="46">
@@ -3252,40 +3252,40 @@
         <v>1.32</v>
       </c>
       <c r="G46" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I46" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L46" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="M46" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="N46" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="O46" t="n">
-        <v>2.28</v>
+        <v>-1.24</v>
       </c>
       <c r="P46" t="n">
         <v>3.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3314,40 +3314,40 @@
         <v>3.08</v>
       </c>
       <c r="G47" t="n">
-        <v>11.38</v>
+        <v>11.16</v>
       </c>
       <c r="H47" t="n">
-        <v>0.34</v>
+        <v>-0.22</v>
       </c>
       <c r="I47" t="n">
-        <v>3.08</v>
+        <v>-1.93</v>
       </c>
       <c r="J47" t="n">
-        <v>11.16</v>
+        <v>11.27</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.22</v>
+        <v>0.11</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.93</v>
+        <v>0.99</v>
       </c>
       <c r="M47" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="N47" t="n">
-        <v>0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="O47" t="n">
-        <v>0.99</v>
+        <v>-2.22</v>
       </c>
       <c r="P47" t="n">
-        <v>11.02</v>
+        <v>10.89</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.25</v>
+        <v>-0.13</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.22</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="48">
@@ -3379,28 +3379,28 @@
         <v>0.32</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="M48" t="n">
         <v>0.315</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.315</v>
@@ -3441,31 +3441,31 @@
         <v>4.34</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="M49" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="N49" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O49" t="n">
-        <v>0.23</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="Q49" t="n">
         <v>-0.03</v>
@@ -3503,37 +3503,37 @@
         <v>1.03</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="M50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N50" t="n">
         <v>-0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="P50" t="n">
         <v>1.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3562,40 +3562,40 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="J51" t="n">
         <v>3.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>-3.35</v>
       </c>
       <c r="P51" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="R51" t="n">
-        <v>-3.35</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="52">
@@ -3624,40 +3624,40 @@
         <v>0.37</v>
       </c>
       <c r="G52" t="n">
-        <v>10.76</v>
+        <v>10.95</v>
       </c>
       <c r="H52" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="I52" t="n">
-        <v>0.37</v>
+        <v>1.77</v>
       </c>
       <c r="J52" t="n">
-        <v>10.95</v>
+        <v>10.87</v>
       </c>
       <c r="K52" t="n">
-        <v>0.19</v>
+        <v>-0.08</v>
       </c>
       <c r="L52" t="n">
-        <v>1.77</v>
+        <v>-0.73</v>
       </c>
       <c r="M52" t="n">
-        <v>10.87</v>
+        <v>10.66</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.73</v>
+        <v>-1.93</v>
       </c>
       <c r="P52" t="n">
-        <v>10.66</v>
+        <v>10.59</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.93</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="53">
@@ -3686,40 +3686,40 @@
         <v>2.51</v>
       </c>
       <c r="G53" t="n">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="H53" t="n">
-        <v>0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="I53" t="n">
-        <v>2.51</v>
+        <v>-1.63</v>
       </c>
       <c r="J53" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.63</v>
+        <v>-0.47</v>
       </c>
       <c r="M53" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="P53" t="n">
-        <v>8.390000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.12</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="54">
@@ -3748,40 +3748,40 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.45</v>
+        <v>0.435</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>-3.33</v>
       </c>
       <c r="J54" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.33</v>
+        <v>-1.15</v>
       </c>
       <c r="M54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="N54" t="n">
         <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="P54" t="n">
-        <v>0.425</v>
+        <v>0.43</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.16</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="55">
@@ -3810,31 +3810,31 @@
         <v>0.84</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="H55" t="n">
         <v>0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="J55" t="n">
-        <v>0.605</v>
+        <v>0.615</v>
       </c>
       <c r="K55" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L55" t="n">
-        <v>0.83</v>
+        <v>1.65</v>
       </c>
       <c r="M55" t="n">
         <v>0.615</v>
       </c>
       <c r="N55" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0.615</v>
@@ -3875,37 +3875,37 @@
         <v>0.465</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M56" t="n">
         <v>0.47</v>
       </c>
       <c r="N56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="57">
@@ -3934,40 +3934,40 @@
         <v>5.9</v>
       </c>
       <c r="G57" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="I57" t="n">
-        <v>5.9</v>
+        <v>-4.18</v>
       </c>
       <c r="J57" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
       <c r="L57" t="n">
-        <v>-4.18</v>
+        <v>1.16</v>
       </c>
       <c r="M57" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="N57" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="O57" t="n">
-        <v>1.16</v>
+        <v>0.29</v>
       </c>
       <c r="P57" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="R57" t="n">
-        <v>0.29</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="58">
@@ -3996,40 +3996,40 @@
         <v>5.13</v>
       </c>
       <c r="G58" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.082</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="I58" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.083</v>
       </c>
       <c r="N58" t="n">
         <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="P58" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="Q58" t="n">
         <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="59">
@@ -4058,40 +4058,40 @@
         <v>2</v>
       </c>
       <c r="G59" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J59" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M59" t="n">
         <v>21.88</v>
       </c>
-      <c r="H59" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M59" t="n">
-        <v>22.31</v>
-      </c>
       <c r="N59" t="n">
-        <v>0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="O59" t="n">
-        <v>1.5</v>
+        <v>-1.93</v>
       </c>
       <c r="P59" t="n">
-        <v>21.88</v>
+        <v>21.74</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.43</v>
+        <v>-0.14</v>
       </c>
       <c r="R59" t="n">
-        <v>-1.93</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="60">
@@ -4120,40 +4120,40 @@
         <v>1.89</v>
       </c>
       <c r="G60" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="I60" t="n">
-        <v>1.89</v>
+        <v>-0.93</v>
       </c>
       <c r="J60" t="n">
         <v>3.2</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="P60" t="n">
         <v>3.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4182,40 +4182,40 @@
         <v>2.99</v>
       </c>
       <c r="G61" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="H61" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="I61" t="n">
-        <v>2.99</v>
+        <v>-7.25</v>
       </c>
       <c r="J61" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="L61" t="n">
-        <v>-7.25</v>
+        <v>1.56</v>
       </c>
       <c r="M61" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="N61" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O61" t="n">
-        <v>1.56</v>
+        <v>-5.38</v>
       </c>
       <c r="P61" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="R61" t="n">
-        <v>-5.38</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-06-01 Close</t>
+          <t>2026-06-02 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change</t>
+          <t>2026-06-02 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-06-01 Change %</t>
+          <t>2026-06-02 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-06-02 Close</t>
+          <t>2026-06-03 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change</t>
+          <t>2026-06-03 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change %</t>
+          <t>2026-06-03 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-03 Close</t>
+          <t>2026-06-04 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change</t>
+          <t>2026-06-04 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change %</t>
+          <t>2026-06-04 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-04 Close</t>
+          <t>2026-06-05 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change</t>
+          <t>2026-06-05 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change %</t>
+          <t>2026-06-05 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-05 Close</t>
+          <t>2026-06-08 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change</t>
+          <t>2026-06-08 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change %</t>
+          <t>2026-06-08 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>146.3</v>
+        <v>147.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="G3" t="n">
-        <v>147.2</v>
+        <v>146.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.62</v>
+        <v>-0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>146.9</v>
+        <v>146.4</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>146.4</v>
+        <v>141.8</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5</v>
+        <v>-4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.34</v>
+        <v>-3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>141.8</v>
+        <v>142.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.6</v>
+        <v>0.5</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.14</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>210.6</v>
+        <v>215.2</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>215.2</v>
+        <v>217</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.18</v>
+        <v>0.84</v>
       </c>
       <c r="J4" t="n">
-        <v>217</v>
+        <v>211.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8</v>
+        <v>-5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.84</v>
+        <v>-2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>211.8</v>
+        <v>201.4</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.2</v>
+        <v>-10.4</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4</v>
+        <v>-4.91</v>
       </c>
       <c r="P4" t="n">
-        <v>201.4</v>
+        <v>202.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.4</v>
+        <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>-4.91</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="E5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="H5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="G5" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.56</v>
-      </c>
       <c r="J5" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="K5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L5" t="n">
+      <c r="R5" t="n">
         <v>-0.17</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.34</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="F6" t="n">
-        <v>0.15</v>
+        <v>2.26</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>6.72</v>
       </c>
       <c r="H6" t="n">
-        <v>0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.26</v>
+        <v>-1.18</v>
       </c>
       <c r="J6" t="n">
         <v>6.72</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.72</v>
+        <v>6.83</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P6" t="n">
-        <v>6.83</v>
+        <v>6.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>0.19</v>
+        <v>1.72</v>
       </c>
       <c r="G7" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M7" t="n">
         <v>5.31</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5.25</v>
-      </c>
       <c r="N7" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.38</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.529999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="E8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.04</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.17</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.38</v>
+        <v>7.51</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>7.51</v>
+        <v>7.42</v>
       </c>
       <c r="H9" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.76</v>
+        <v>-1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>7.42</v>
+        <v>7.37</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2</v>
+        <v>-0.67</v>
       </c>
       <c r="M9" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>7.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.4</v>
+        <v>48.42</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="F10" t="n">
-        <v>0.64</v>
+        <v>2.15</v>
       </c>
       <c r="G10" t="n">
-        <v>48.42</v>
+        <v>47.86</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2.15</v>
+        <v>-1.16</v>
       </c>
       <c r="J10" t="n">
-        <v>47.86</v>
+        <v>47.62</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.16</v>
+        <v>-0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>47.62</v>
+        <v>48.18</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>48.18</v>
+        <v>48.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="11">
@@ -1073,25 +1073,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F11" t="n">
-        <v>0.93</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="J11" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="K11" t="n">
         <v>-0.02</v>
@@ -1100,22 +1100,22 @@
         <v>-0.46</v>
       </c>
       <c r="M11" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.46</v>
+        <v>-1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.38</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="F12" t="n">
-        <v>0.18</v>
+        <v>-1.47</v>
       </c>
       <c r="G12" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.47</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>10.69</v>
+        <v>10.55</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="M12" t="n">
         <v>10.55</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>10.55</v>
+        <v>10.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.7</v>
+        <v>27.36</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="F13" t="n">
-        <v>1.14</v>
+        <v>2.47</v>
       </c>
       <c r="G13" t="n">
-        <v>27.36</v>
+        <v>27.26</v>
       </c>
       <c r="H13" t="n">
-        <v>0.66</v>
+        <v>-0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>2.47</v>
+        <v>-0.37</v>
       </c>
       <c r="J13" t="n">
-        <v>27.26</v>
+        <v>27.02</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.37</v>
+        <v>-0.88</v>
       </c>
       <c r="M13" t="n">
-        <v>27.02</v>
+        <v>26.54</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.88</v>
+        <v>-1.78</v>
       </c>
       <c r="P13" t="n">
-        <v>26.54</v>
+        <v>27.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.48</v>
+        <v>0.52</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.78</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.43</v>
+        <v>-1.75</v>
       </c>
       <c r="G14" t="n">
         <v>2.25</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I14" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="R14" t="n">
-        <v>-2.64</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="G15" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="P15" t="n">
         <v>5.28</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="Q15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.3</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F16" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>1.22</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
         <v>4.98</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>5.03</v>
+        <v>4.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="G17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>2.23</v>
+        <v>-0.27</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.27</v>
+        <v>-1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.37</v>
+        <v>1.11</v>
       </c>
       <c r="P17" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="R17" t="n">
-        <v>1.11</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.38</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.4</v>
       </c>
       <c r="N18" t="n">
         <v>-0.02</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="P18" t="n">
         <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60.2</v>
+        <v>58.6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.15</v>
+        <v>-1.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.25</v>
+        <v>-2.66</v>
       </c>
       <c r="G19" t="n">
-        <v>58.6</v>
+        <v>57.8</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.66</v>
+        <v>-1.37</v>
       </c>
       <c r="J19" t="n">
-        <v>57.8</v>
+        <v>57.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>57.05</v>
+        <v>56.9</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3</v>
+        <v>-0.26</v>
       </c>
       <c r="P19" t="n">
-        <v>56.9</v>
+        <v>56.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.9</v>
+        <v>28.48</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02</v>
+        <v>-0.42</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="G20" t="n">
-        <v>28.48</v>
+        <v>27.9</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.42</v>
+        <v>-0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.45</v>
+        <v>-2.04</v>
       </c>
       <c r="J20" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.58</v>
+        <v>0.1</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.04</v>
+        <v>0.36</v>
       </c>
       <c r="M20" t="n">
         <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>28</v>
+        <v>27.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>1.16</v>
+        <v>-1.15</v>
       </c>
       <c r="G21" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.15</v>
+        <v>-1.74</v>
       </c>
       <c r="J21" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.74</v>
+        <v>-1.38</v>
       </c>
       <c r="M21" t="n">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.38</v>
+        <v>-0.6</v>
       </c>
       <c r="P21" t="n">
-        <v>4.99</v>
+        <v>4.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.15000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="G22" t="n">
-        <v>85.90000000000001</v>
+        <v>85.55</v>
       </c>
       <c r="H22" t="n">
-        <v>0.75</v>
+        <v>-0.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.88</v>
+        <v>-0.41</v>
       </c>
       <c r="J22" t="n">
-        <v>85.55</v>
+        <v>84.75</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.35</v>
+        <v>-0.8</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.41</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>84.75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8</v>
+        <v>-2.35</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.77</v>
       </c>
       <c r="P22" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.08</v>
+        <v>27.68</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.61</v>
+        <v>6.13</v>
       </c>
       <c r="G23" t="n">
-        <v>27.68</v>
+        <v>26.96</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6</v>
+        <v>-0.72</v>
       </c>
       <c r="I23" t="n">
-        <v>6.13</v>
+        <v>-2.6</v>
       </c>
       <c r="J23" t="n">
-        <v>26.96</v>
+        <v>28.38</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.72</v>
+        <v>1.42</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6</v>
+        <v>5.27</v>
       </c>
       <c r="M23" t="n">
-        <v>28.38</v>
+        <v>29.66</v>
       </c>
       <c r="N23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="O23" t="n">
-        <v>5.27</v>
+        <v>4.51</v>
       </c>
       <c r="P23" t="n">
-        <v>29.66</v>
+        <v>27.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.28</v>
+        <v>-2.12</v>
       </c>
       <c r="R23" t="n">
-        <v>4.51</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.22</v>
+        <v>30.88</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="F24" t="n">
-        <v>0.27</v>
+        <v>2.18</v>
       </c>
       <c r="G24" t="n">
-        <v>30.88</v>
+        <v>29.1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.66</v>
+        <v>-1.78</v>
       </c>
       <c r="I24" t="n">
-        <v>2.18</v>
+        <v>-5.76</v>
       </c>
       <c r="J24" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.78</v>
+        <v>-1.1</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.76</v>
+        <v>-3.78</v>
       </c>
       <c r="M24" t="n">
-        <v>28</v>
+        <v>26.12</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1</v>
+        <v>-1.88</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.78</v>
+        <v>-6.71</v>
       </c>
       <c r="P24" t="n">
-        <v>26.12</v>
+        <v>25.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.88</v>
+        <v>-0.84</v>
       </c>
       <c r="R24" t="n">
-        <v>-6.71</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.72</v>
+        <v>29.62</v>
       </c>
       <c r="E25" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>2.43</v>
+        <v>3.13</v>
       </c>
       <c r="G25" t="n">
-        <v>29.62</v>
+        <v>28.58</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9</v>
+        <v>-1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3.13</v>
+        <v>-3.51</v>
       </c>
       <c r="J25" t="n">
-        <v>28.58</v>
+        <v>28.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.04</v>
+        <v>-0.2</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.51</v>
+        <v>-0.7</v>
       </c>
       <c r="M25" t="n">
-        <v>28.38</v>
+        <v>27.8</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7</v>
+        <v>-2.04</v>
       </c>
       <c r="P25" t="n">
-        <v>27.8</v>
+        <v>27.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.58</v>
+        <v>-0.42</v>
       </c>
       <c r="R25" t="n">
-        <v>-2.04</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60.25</v>
+        <v>61.65</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.43</v>
+        <v>2.32</v>
       </c>
       <c r="G26" t="n">
-        <v>61.65</v>
+        <v>62.35</v>
       </c>
       <c r="H26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J26" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="M26" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="P26" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1.4</v>
       </c>
-      <c r="I26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J26" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="M26" t="n">
-        <v>59.65</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="P26" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-3.85</v>
-      </c>
       <c r="R26" t="n">
-        <v>-6.45</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>436</v>
+        <v>481.6</v>
       </c>
       <c r="E27" t="n">
-        <v>8.800000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="F27" t="n">
-        <v>2.06</v>
+        <v>10.46</v>
       </c>
       <c r="G27" t="n">
-        <v>481.6</v>
+        <v>466.4</v>
       </c>
       <c r="H27" t="n">
-        <v>45.6</v>
+        <v>-15.2</v>
       </c>
       <c r="I27" t="n">
-        <v>10.46</v>
+        <v>-3.16</v>
       </c>
       <c r="J27" t="n">
-        <v>466.4</v>
+        <v>459</v>
       </c>
       <c r="K27" t="n">
-        <v>-15.2</v>
+        <v>-7.4</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.16</v>
+        <v>-1.59</v>
       </c>
       <c r="M27" t="n">
-        <v>459</v>
+        <v>453.2</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.4</v>
+        <v>-5.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.59</v>
+        <v>-1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>453.2</v>
+        <v>446.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5.8</v>
+        <v>-6.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.26</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>122.8</v>
+        <v>130.9</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1.57</v>
+        <v>6.6</v>
       </c>
       <c r="G28" t="n">
-        <v>130.9</v>
+        <v>126.6</v>
       </c>
       <c r="H28" t="n">
-        <v>8.1</v>
+        <v>-4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>6.6</v>
+        <v>-3.28</v>
       </c>
       <c r="J28" t="n">
-        <v>126.6</v>
+        <v>123.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="L28" t="n">
-        <v>-3.28</v>
+        <v>-2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>123.5</v>
+        <v>122.4</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.1</v>
+        <v>-1.1</v>
       </c>
       <c r="O28" t="n">
-        <v>-2.45</v>
+        <v>-0.89</v>
       </c>
       <c r="P28" t="n">
-        <v>122.4</v>
+        <v>118.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.1</v>
+        <v>-3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.89</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>112.4</v>
+        <v>120.1</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.1</v>
+        <v>7.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.97</v>
+        <v>6.85</v>
       </c>
       <c r="G29" t="n">
-        <v>120.1</v>
+        <v>115.1</v>
       </c>
       <c r="H29" t="n">
-        <v>7.7</v>
+        <v>-5</v>
       </c>
       <c r="I29" t="n">
-        <v>6.85</v>
+        <v>-4.16</v>
       </c>
       <c r="J29" t="n">
-        <v>115.1</v>
+        <v>115</v>
       </c>
       <c r="K29" t="n">
-        <v>-5</v>
+        <v>-0.1</v>
       </c>
       <c r="L29" t="n">
-        <v>-4.16</v>
+        <v>-0.09</v>
       </c>
       <c r="M29" t="n">
-        <v>115</v>
+        <v>115.8</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.09</v>
+        <v>0.7</v>
       </c>
       <c r="P29" t="n">
-        <v>115.8</v>
+        <v>113.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78.25</v>
+        <v>85.5</v>
       </c>
       <c r="E30" t="n">
-        <v>4.8</v>
+        <v>7.25</v>
       </c>
       <c r="F30" t="n">
-        <v>6.54</v>
+        <v>9.27</v>
       </c>
       <c r="G30" t="n">
-        <v>85.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>7.25</v>
+        <v>-5.1</v>
       </c>
       <c r="I30" t="n">
-        <v>9.27</v>
+        <v>-5.96</v>
       </c>
       <c r="J30" t="n">
-        <v>80.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.1</v>
+        <v>-1.8</v>
       </c>
       <c r="L30" t="n">
-        <v>-5.96</v>
+        <v>-2.24</v>
       </c>
       <c r="M30" t="n">
-        <v>78.59999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.8</v>
+        <v>1.35</v>
       </c>
       <c r="O30" t="n">
-        <v>-2.24</v>
+        <v>1.72</v>
       </c>
       <c r="P30" t="n">
-        <v>79.95</v>
+        <v>76.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.35</v>
+        <v>-3.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.72</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>129.1</v>
+        <v>134.7</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.9</v>
+        <v>5.6</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6899999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="G31" t="n">
-        <v>134.7</v>
+        <v>132.9</v>
       </c>
       <c r="H31" t="n">
-        <v>5.6</v>
+        <v>-1.8</v>
       </c>
       <c r="I31" t="n">
-        <v>4.34</v>
+        <v>-1.34</v>
       </c>
       <c r="J31" t="n">
-        <v>132.9</v>
+        <v>130.1</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.34</v>
+        <v>-2.11</v>
       </c>
       <c r="M31" t="n">
-        <v>130.1</v>
+        <v>125.6</v>
       </c>
       <c r="N31" t="n">
-        <v>-2.8</v>
+        <v>-4.5</v>
       </c>
       <c r="O31" t="n">
-        <v>-2.11</v>
+        <v>-3.46</v>
       </c>
       <c r="P31" t="n">
-        <v>125.6</v>
+        <v>116</v>
       </c>
       <c r="Q31" t="n">
-        <v>-4.5</v>
+        <v>-9.6</v>
       </c>
       <c r="R31" t="n">
-        <v>-3.46</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>79.45</v>
+        <v>81.95</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.15</v>
+        <v>2.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.63</v>
+        <v>3.15</v>
       </c>
       <c r="G32" t="n">
-        <v>81.95</v>
+        <v>82.95</v>
       </c>
       <c r="H32" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>3.15</v>
+        <v>1.22</v>
       </c>
       <c r="J32" t="n">
-        <v>82.95</v>
+        <v>81.5</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>-1.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.22</v>
+        <v>-1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>81.5</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.45</v>
+        <v>-5.85</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.75</v>
+        <v>-7.18</v>
       </c>
       <c r="P32" t="n">
-        <v>75.65000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>-5.85</v>
+        <v>-3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>-7.18</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>90.75</v>
+        <v>96.75</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.55</v>
+        <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6</v>
+        <v>6.61</v>
       </c>
       <c r="G33" t="n">
-        <v>96.75</v>
+        <v>93.25</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>-3.5</v>
       </c>
       <c r="I33" t="n">
-        <v>6.61</v>
+        <v>-3.62</v>
       </c>
       <c r="J33" t="n">
-        <v>93.25</v>
+        <v>91.8</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.5</v>
+        <v>-1.45</v>
       </c>
       <c r="L33" t="n">
-        <v>-3.62</v>
+        <v>-1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>91.8</v>
+        <v>89.7</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.45</v>
+        <v>-2.1</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.55</v>
+        <v>-2.29</v>
       </c>
       <c r="P33" t="n">
-        <v>89.7</v>
+        <v>88.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2.1</v>
+        <v>-1.65</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.29</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>46.54</v>
+        <v>48.98</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2.44</v>
       </c>
       <c r="F34" t="n">
-        <v>2.2</v>
+        <v>5.24</v>
       </c>
       <c r="G34" t="n">
-        <v>48.98</v>
+        <v>46.74</v>
       </c>
       <c r="H34" t="n">
-        <v>2.44</v>
+        <v>-2.24</v>
       </c>
       <c r="I34" t="n">
-        <v>5.24</v>
+        <v>-4.57</v>
       </c>
       <c r="J34" t="n">
-        <v>46.74</v>
+        <v>46.94</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.24</v>
+        <v>0.2</v>
       </c>
       <c r="L34" t="n">
-        <v>-4.57</v>
+        <v>0.43</v>
       </c>
       <c r="M34" t="n">
-        <v>46.94</v>
+        <v>46.86</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="O34" t="n">
-        <v>0.43</v>
+        <v>-0.17</v>
       </c>
       <c r="P34" t="n">
-        <v>46.86</v>
+        <v>44.14</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.08</v>
+        <v>-2.72</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.17</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="J35" t="n">
         <v>4.87</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="G35" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I35" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.95</v>
-      </c>
       <c r="K35" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.75</v>
+        <v>-1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="N35" t="n">
         <v>-0.08</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.62</v>
+        <v>-1.64</v>
       </c>
       <c r="P35" t="n">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.64</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.43</v>
+        <v>10.94</v>
       </c>
       <c r="E36" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="F36" t="n">
-        <v>1.76</v>
+        <v>4.89</v>
       </c>
       <c r="G36" t="n">
-        <v>10.94</v>
+        <v>10.64</v>
       </c>
       <c r="H36" t="n">
-        <v>0.51</v>
+        <v>-0.3</v>
       </c>
       <c r="I36" t="n">
-        <v>4.89</v>
+        <v>-2.74</v>
       </c>
       <c r="J36" t="n">
-        <v>10.64</v>
+        <v>10.47</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.74</v>
+        <v>-1.6</v>
       </c>
       <c r="M36" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="O36" t="n">
-        <v>-1.6</v>
+        <v>-1.91</v>
       </c>
       <c r="P36" t="n">
-        <v>10.27</v>
+        <v>10.01</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.2</v>
+        <v>-0.26</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.91</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>400.2</v>
+        <v>410.4</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4</v>
+        <v>10.2</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1</v>
+        <v>2.55</v>
       </c>
       <c r="G37" t="n">
-        <v>410.4</v>
+        <v>409.4</v>
       </c>
       <c r="H37" t="n">
-        <v>10.2</v>
+        <v>-1</v>
       </c>
       <c r="I37" t="n">
-        <v>2.55</v>
+        <v>-0.24</v>
       </c>
       <c r="J37" t="n">
-        <v>409.4</v>
+        <v>400.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-1</v>
+        <v>-8.6</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.24</v>
+        <v>-2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>400.8</v>
+        <v>396.4</v>
       </c>
       <c r="N37" t="n">
-        <v>-8.6</v>
+        <v>-4.4</v>
       </c>
       <c r="O37" t="n">
-        <v>-2.1</v>
+        <v>-1.1</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4</v>
+        <v>386.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>-4.4</v>
+        <v>-9.6</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.1</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.9</v>
+        <v>16.35</v>
       </c>
       <c r="E38" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="F38" t="n">
-        <v>3.72</v>
+        <v>2.83</v>
       </c>
       <c r="G38" t="n">
-        <v>16.35</v>
+        <v>16.03</v>
       </c>
       <c r="H38" t="n">
-        <v>0.45</v>
+        <v>-0.32</v>
       </c>
       <c r="I38" t="n">
-        <v>2.83</v>
+        <v>-1.96</v>
       </c>
       <c r="J38" t="n">
-        <v>16.03</v>
+        <v>15.76</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.96</v>
+        <v>-1.68</v>
       </c>
       <c r="M38" t="n">
-        <v>15.76</v>
+        <v>15.21</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.27</v>
+        <v>-0.55</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.68</v>
+        <v>-3.49</v>
       </c>
       <c r="P38" t="n">
-        <v>15.21</v>
+        <v>14.82</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.55</v>
+        <v>-0.39</v>
       </c>
       <c r="R38" t="n">
-        <v>-3.49</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>753.5</v>
+        <v>779.5</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>1.21</v>
+        <v>3.45</v>
       </c>
       <c r="G39" t="n">
-        <v>779.5</v>
+        <v>778</v>
       </c>
       <c r="H39" t="n">
-        <v>26</v>
+        <v>-1.5</v>
       </c>
       <c r="I39" t="n">
-        <v>3.45</v>
+        <v>-0.19</v>
       </c>
       <c r="J39" t="n">
-        <v>778</v>
+        <v>723.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.5</v>
+        <v>-54.5</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.19</v>
+        <v>-7.01</v>
       </c>
       <c r="M39" t="n">
-        <v>723.5</v>
+        <v>711</v>
       </c>
       <c r="N39" t="n">
-        <v>-54.5</v>
+        <v>-12.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-7.01</v>
+        <v>-1.73</v>
       </c>
       <c r="P39" t="n">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="Q39" t="n">
-        <v>-12.5</v>
+        <v>-28</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.73</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>67.8</v>
+        <v>72</v>
       </c>
       <c r="E40" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="F40" t="n">
         <v>6.19</v>
       </c>
       <c r="G40" t="n">
-        <v>72</v>
+        <v>68.05</v>
       </c>
       <c r="H40" t="n">
-        <v>4.2</v>
+        <v>-3.95</v>
       </c>
       <c r="I40" t="n">
-        <v>6.19</v>
+        <v>-5.49</v>
       </c>
       <c r="J40" t="n">
-        <v>68.05</v>
+        <v>66.45</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.95</v>
+        <v>-1.6</v>
       </c>
       <c r="L40" t="n">
-        <v>-5.49</v>
+        <v>-2.35</v>
       </c>
       <c r="M40" t="n">
-        <v>66.45</v>
+        <v>65</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.6</v>
+        <v>-1.45</v>
       </c>
       <c r="O40" t="n">
-        <v>-2.35</v>
+        <v>-2.18</v>
       </c>
       <c r="P40" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.45</v>
+        <v>-3</v>
       </c>
       <c r="R40" t="n">
-        <v>-2.18</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G41" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J41" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="M41" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P41" t="n">
         <v>23.4</v>
       </c>
-      <c r="E41" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G41" t="n">
-        <v>24.08</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="J41" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="M41" t="n">
-        <v>24</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="P41" t="n">
-        <v>23.94</v>
-      </c>
       <c r="Q41" t="n">
-        <v>-0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.25</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>62.84</v>
+        <v>64.67</v>
       </c>
       <c r="E42" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="F42" t="n">
-        <v>1.47</v>
+        <v>2.91</v>
       </c>
       <c r="G42" t="n">
-        <v>64.67</v>
+        <v>65.05</v>
       </c>
       <c r="H42" t="n">
-        <v>1.83</v>
+        <v>0.38</v>
       </c>
       <c r="I42" t="n">
-        <v>2.91</v>
+        <v>0.59</v>
       </c>
       <c r="J42" t="n">
-        <v>65.05</v>
+        <v>64.14</v>
       </c>
       <c r="K42" t="n">
-        <v>0.38</v>
+        <v>-0.91</v>
       </c>
       <c r="L42" t="n">
-        <v>0.59</v>
+        <v>-1.4</v>
       </c>
       <c r="M42" t="n">
-        <v>64.14</v>
+        <v>63.78</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.91</v>
+        <v>-0.36</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>63.78</v>
+        <v>62.76</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.36</v>
+        <v>-1.02</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>37.6</v>
+        <v>38.4</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.09</v>
+        <v>0.8</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.24</v>
+        <v>2.13</v>
       </c>
       <c r="G43" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I43" t="n">
-        <v>2.13</v>
+        <v>1.04</v>
       </c>
       <c r="J43" t="n">
-        <v>38.8</v>
+        <v>38.31</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4</v>
+        <v>-0.49</v>
       </c>
       <c r="L43" t="n">
-        <v>1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="M43" t="n">
-        <v>38.31</v>
+        <v>38.55</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.49</v>
+        <v>0.24</v>
       </c>
       <c r="O43" t="n">
-        <v>-1.26</v>
+        <v>0.63</v>
       </c>
       <c r="P43" t="n">
-        <v>38.55</v>
+        <v>37.79</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.24</v>
+        <v>-0.76</v>
       </c>
       <c r="R43" t="n">
-        <v>0.63</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="F44" t="n">
-        <v>1.27</v>
+        <v>-1.72</v>
       </c>
       <c r="G44" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.72</v>
+        <v>0.16</v>
       </c>
       <c r="J44" t="n">
-        <v>6.29</v>
+        <v>6.21</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="L44" t="n">
-        <v>0.16</v>
+        <v>-1.27</v>
       </c>
       <c r="M44" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="N44" t="n">
         <v>-0.08</v>
       </c>
       <c r="O44" t="n">
-        <v>-1.27</v>
+        <v>-1.29</v>
       </c>
       <c r="P44" t="n">
-        <v>6.13</v>
+        <v>6.06</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.29</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.3</v>
+        <v>-1.89</v>
       </c>
       <c r="G45" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.89</v>
+        <v>0.48</v>
       </c>
       <c r="J45" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="K45" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L45" t="n">
-        <v>0.48</v>
+        <v>-2.87</v>
       </c>
       <c r="M45" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.87</v>
+        <v>-0.49</v>
       </c>
       <c r="P45" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q45" t="n">
         <v>-0.01</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F46" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="J46" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="K46" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="L46" t="n">
-        <v>2.28</v>
+        <v>-1.24</v>
       </c>
       <c r="M46" t="n">
         <v>3.99</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.38</v>
+        <v>11.16</v>
       </c>
       <c r="E47" t="n">
-        <v>0.34</v>
+        <v>-0.22</v>
       </c>
       <c r="F47" t="n">
-        <v>3.08</v>
+        <v>-1.93</v>
       </c>
       <c r="G47" t="n">
-        <v>11.16</v>
+        <v>11.27</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.22</v>
+        <v>0.11</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.93</v>
+        <v>0.99</v>
       </c>
       <c r="J47" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="K47" t="n">
-        <v>0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="L47" t="n">
-        <v>0.99</v>
+        <v>-2.22</v>
       </c>
       <c r="M47" t="n">
-        <v>11.02</v>
+        <v>10.89</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.25</v>
+        <v>-0.13</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.22</v>
+        <v>-1.18</v>
       </c>
       <c r="P47" t="n">
-        <v>10.89</v>
+        <v>10.62</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.18</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="48">
@@ -3370,28 +3370,28 @@
         <v>0.32</v>
       </c>
       <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="J48" t="n">
         <v>0.315</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0.315</v>
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="49">
@@ -3432,31 +3432,31 @@
         <v>4.34</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="J49" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="K49" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L49" t="n">
-        <v>0.23</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="N49" t="n">
         <v>-0.03</v>
@@ -3465,13 +3465,13 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="50">
@@ -3494,37 +3494,37 @@
         <v>1.03</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="J50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K50" t="n">
         <v>-0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="M50" t="n">
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.01</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="G51" t="n">
         <v>3.58</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-3.35</v>
       </c>
       <c r="M51" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="O51" t="n">
-        <v>-3.35</v>
+        <v>2.31</v>
       </c>
       <c r="P51" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="R51" t="n">
-        <v>2.31</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.76</v>
+        <v>10.95</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="F52" t="n">
-        <v>0.37</v>
+        <v>1.77</v>
       </c>
       <c r="G52" t="n">
-        <v>10.95</v>
+        <v>10.87</v>
       </c>
       <c r="H52" t="n">
-        <v>0.19</v>
+        <v>-0.08</v>
       </c>
       <c r="I52" t="n">
-        <v>1.77</v>
+        <v>-0.73</v>
       </c>
       <c r="J52" t="n">
-        <v>10.87</v>
+        <v>10.66</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.73</v>
+        <v>-1.93</v>
       </c>
       <c r="M52" t="n">
-        <v>10.66</v>
+        <v>10.59</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.93</v>
+        <v>-0.66</v>
       </c>
       <c r="P52" t="n">
-        <v>10.59</v>
+        <v>10.46</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.66</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="E53" t="n">
-        <v>0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="F53" t="n">
-        <v>2.51</v>
+        <v>-1.63</v>
       </c>
       <c r="G53" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.63</v>
+        <v>-0.47</v>
       </c>
       <c r="J53" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="M53" t="n">
-        <v>8.390000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.12</v>
+        <v>-0.36</v>
       </c>
       <c r="P53" t="n">
-        <v>8.359999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.36</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.45</v>
+        <v>0.435</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-3.33</v>
       </c>
       <c r="G54" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>-3.33</v>
+        <v>-1.15</v>
       </c>
       <c r="J54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="K54" t="n">
         <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="M54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P54" t="n">
         <v>0.425</v>
       </c>
-      <c r="N54" t="n">
+      <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="O54" t="n">
+      <c r="R54" t="n">
         <v>-1.16</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.18</v>
       </c>
     </row>
     <row r="55">
@@ -3801,31 +3801,31 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="E55" t="n">
         <v>0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G55" t="n">
-        <v>0.605</v>
+        <v>0.615</v>
       </c>
       <c r="H55" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="I55" t="n">
-        <v>0.83</v>
+        <v>1.65</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
       </c>
       <c r="K55" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.615</v>
@@ -3837,13 +3837,13 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.615</v>
+        <v>0.61</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3866,46 +3866,46 @@
         <v>0.465</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="J56" t="n">
         <v>0.47</v>
       </c>
       <c r="K56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-1.06</v>
       </c>
       <c r="P56" t="n">
         <v>0.465</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="F57" t="n">
-        <v>5.9</v>
+        <v>-4.18</v>
       </c>
       <c r="G57" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.18</v>
+        <v>1.16</v>
       </c>
       <c r="J57" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="K57" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="L57" t="n">
-        <v>1.16</v>
+        <v>0.29</v>
       </c>
       <c r="M57" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="N57" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O57" t="n">
-        <v>0.29</v>
+        <v>-1.72</v>
       </c>
       <c r="P57" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.72</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.082</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F58" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.083</v>
       </c>
       <c r="K58" t="n">
         <v>-0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="M58" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="N58" t="n">
         <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
       <c r="P58" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.22</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G59" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J59" t="n">
         <v>21.88</v>
       </c>
-      <c r="E59" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J59" t="n">
-        <v>22.31</v>
-      </c>
       <c r="K59" t="n">
-        <v>0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="L59" t="n">
-        <v>1.5</v>
+        <v>-1.93</v>
       </c>
       <c r="M59" t="n">
-        <v>21.88</v>
+        <v>21.74</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.43</v>
+        <v>-0.14</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.93</v>
+        <v>-0.64</v>
       </c>
       <c r="P59" t="n">
-        <v>21.74</v>
+        <v>21.44</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.14</v>
+        <v>-0.3</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.64</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>1.89</v>
+        <v>-0.93</v>
       </c>
       <c r="G60" t="n">
         <v>3.2</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="M60" t="n">
         <v>3.18</v>
       </c>
       <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Q60" t="n">
         <v>-0.02</v>
       </c>
-      <c r="O60" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="E61" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="F61" t="n">
-        <v>2.99</v>
+        <v>-7.25</v>
       </c>
       <c r="G61" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I61" t="n">
-        <v>-7.25</v>
+        <v>1.56</v>
       </c>
       <c r="J61" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="K61" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>1.56</v>
+        <v>-5.38</v>
       </c>
       <c r="M61" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="O61" t="n">
-        <v>-5.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P61" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R61" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.03</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-06-02 Close</t>
+          <t>2026-06-03 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change</t>
+          <t>2026-06-03 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-06-02 Change %</t>
+          <t>2026-06-03 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-06-03 Close</t>
+          <t>2026-06-04 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change</t>
+          <t>2026-06-04 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change %</t>
+          <t>2026-06-04 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-04 Close</t>
+          <t>2026-06-05 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change</t>
+          <t>2026-06-05 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change %</t>
+          <t>2026-06-05 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-05 Close</t>
+          <t>2026-06-08 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change</t>
+          <t>2026-06-08 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change %</t>
+          <t>2026-06-08 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-08 Close</t>
+          <t>2026-06-09 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change</t>
+          <t>2026-06-09 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change %</t>
+          <t>2026-06-09 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>147.2</v>
+        <v>146.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.62</v>
+        <v>-0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>146.9</v>
+        <v>146.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="I3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="J3" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="J3" t="n">
-        <v>146.4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="M3" t="n">
-        <v>141.8</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-3.14</v>
-      </c>
-      <c r="P3" t="n">
-        <v>142.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="R3" t="n">
-        <v>0.35</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>215.2</v>
+        <v>217</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>0.84</v>
       </c>
       <c r="G4" t="n">
-        <v>217</v>
+        <v>211.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8</v>
+        <v>-5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.84</v>
+        <v>-2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>211.8</v>
+        <v>201.4</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.2</v>
+        <v>-10.4</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.4</v>
+        <v>-4.91</v>
       </c>
       <c r="M4" t="n">
-        <v>201.4</v>
+        <v>202.6</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.4</v>
+        <v>1.2</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.91</v>
+        <v>0.6</v>
       </c>
       <c r="P4" t="n">
-        <v>202.6</v>
+        <v>198.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>1.56</v>
+        <v>-0.17</v>
       </c>
       <c r="G5" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="H5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="N5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I5" t="n">
+      <c r="O5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="J5" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.34</v>
-      </c>
       <c r="P5" t="n">
-        <v>5.82</v>
+        <v>5.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.17</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.8</v>
+        <v>6.72</v>
       </c>
       <c r="E6" t="n">
-        <v>0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.26</v>
+        <v>-1.18</v>
       </c>
       <c r="G6" t="n">
         <v>6.72</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6.72</v>
+        <v>6.83</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
-        <v>6.83</v>
+        <v>6.93</v>
       </c>
       <c r="N6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
         <v>6.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J7" t="n">
         <v>5.31</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.25</v>
-      </c>
       <c r="K7" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.38</v>
+        <v>1.14</v>
       </c>
       <c r="M7" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.66</v>
+        <v>8.57</v>
       </c>
       <c r="E8" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>-1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>8.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="J8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02</v>
+        <v>0.17</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.23</v>
+        <v>1.99</v>
       </c>
       <c r="M8" t="n">
-        <v>8.720000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="N8" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="O8" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="P8" t="n">
-        <v>8.76</v>
+        <v>8.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.46</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.51</v>
+        <v>7.42</v>
       </c>
       <c r="E9" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>-1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>7.42</v>
+        <v>7.37</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2</v>
+        <v>-0.67</v>
       </c>
       <c r="J9" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>7.43</v>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.06</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>0.8100000000000001</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.42</v>
+        <v>47.86</v>
       </c>
       <c r="E10" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.15</v>
+        <v>-1.16</v>
       </c>
       <c r="G10" t="n">
-        <v>47.86</v>
+        <v>47.62</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.16</v>
+        <v>-0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>47.62</v>
+        <v>48.18</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5</v>
+        <v>1.18</v>
       </c>
       <c r="M10" t="n">
-        <v>48.18</v>
+        <v>48.16</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>-0.04</v>
       </c>
       <c r="P10" t="n">
-        <v>48.16</v>
+        <v>47.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.04</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="11">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="G11" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="H11" t="n">
         <v>-0.02</v>
@@ -1091,31 +1091,31 @@
         <v>-0.46</v>
       </c>
       <c r="J11" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.46</v>
+        <v>-1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.38</v>
+        <v>-3.73</v>
       </c>
       <c r="P11" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.73</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.47</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>10.69</v>
+        <v>10.55</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="J12" t="n">
         <v>10.55</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>10.55</v>
+        <v>10.69</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>10.69</v>
+        <v>10.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.14</v>
+        <v>-0.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.36</v>
+        <v>27.26</v>
       </c>
       <c r="E13" t="n">
-        <v>0.66</v>
+        <v>-0.1</v>
       </c>
       <c r="F13" t="n">
-        <v>2.47</v>
+        <v>-0.37</v>
       </c>
       <c r="G13" t="n">
-        <v>27.26</v>
+        <v>27.02</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.37</v>
+        <v>-0.88</v>
       </c>
       <c r="J13" t="n">
-        <v>27.02</v>
+        <v>26.54</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.88</v>
+        <v>-1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>26.54</v>
+        <v>27.06</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.48</v>
+        <v>0.52</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.78</v>
+        <v>1.96</v>
       </c>
       <c r="P13" t="n">
-        <v>27.06</v>
+        <v>26.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.96</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="14">
@@ -1262,46 +1262,46 @@
         <v>2.25</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N14" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F14" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="O14" t="n">
-        <v>-2.64</v>
+        <v>-1.81</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.81</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="M15" t="n">
         <v>5.28</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="N15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3</v>
+        <v>-0.38</v>
       </c>
       <c r="P15" t="n">
-        <v>5.28</v>
+        <v>5.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.38</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>1.22</v>
+        <v>0.4</v>
       </c>
       <c r="G16" t="n">
         <v>4.98</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>5.03</v>
+        <v>4.93</v>
       </c>
       <c r="N16" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>-1.99</v>
       </c>
       <c r="P16" t="n">
-        <v>4.93</v>
+        <v>5.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1</v>
+        <v>0.12</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.99</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>2.23</v>
+        <v>-0.27</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.27</v>
+        <v>-1.37</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.37</v>
+        <v>1.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="O17" t="n">
-        <v>1.11</v>
+        <v>-2.47</v>
       </c>
       <c r="P17" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="R17" t="n">
-        <v>-2.47</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>1.48</v>
+        <v>-0.29</v>
       </c>
       <c r="G18" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.29</v>
+        <v>-0.58</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="K18" t="n">
         <v>-0.02</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="M18" t="n">
         <v>3.38</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.6</v>
+        <v>57.8</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.66</v>
+        <v>-1.37</v>
       </c>
       <c r="G19" t="n">
-        <v>57.8</v>
+        <v>57.05</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>57.05</v>
+        <v>56.9</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3</v>
+        <v>-0.26</v>
       </c>
       <c r="M19" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="P19" t="n">
         <v>56.9</v>
       </c>
-      <c r="N19" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="P19" t="n">
-        <v>56.85</v>
-      </c>
       <c r="Q19" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.48</v>
+        <v>27.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.42</v>
+        <v>-0.58</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.45</v>
+        <v>-2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.58</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.04</v>
+        <v>0.36</v>
       </c>
       <c r="J20" t="n">
         <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
+        <v>27.48</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-1.86</v>
       </c>
       <c r="P20" t="n">
-        <v>27.48</v>
+        <v>27.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.52</v>
+        <v>-0.1</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.86</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.15</v>
+        <v>-1.74</v>
       </c>
       <c r="G21" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.74</v>
+        <v>-1.38</v>
       </c>
       <c r="J21" t="n">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.38</v>
+        <v>-0.6</v>
       </c>
       <c r="M21" t="n">
-        <v>4.99</v>
+        <v>4.94</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="P21" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.90000000000001</v>
+        <v>85.55</v>
       </c>
       <c r="E22" t="n">
-        <v>0.75</v>
+        <v>-0.35</v>
       </c>
       <c r="F22" t="n">
-        <v>0.88</v>
+        <v>-0.41</v>
       </c>
       <c r="G22" t="n">
-        <v>85.55</v>
+        <v>84.75</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.35</v>
+        <v>-0.8</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.41</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>84.75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8</v>
+        <v>-2.35</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.77</v>
       </c>
       <c r="M22" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.35</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.68</v>
+        <v>26.96</v>
       </c>
       <c r="E23" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="J23" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="P23" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="G23" t="n">
-        <v>26.96</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="M23" t="n">
-        <v>29.66</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="P23" t="n">
-        <v>27.54</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="R23" t="n">
-        <v>-7.15</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.88</v>
+        <v>29.1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.66</v>
+        <v>-1.78</v>
       </c>
       <c r="F24" t="n">
-        <v>2.18</v>
+        <v>-5.76</v>
       </c>
       <c r="G24" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.78</v>
+        <v>-1.1</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.76</v>
+        <v>-3.78</v>
       </c>
       <c r="J24" t="n">
-        <v>28</v>
+        <v>26.12</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1</v>
+        <v>-1.88</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.78</v>
+        <v>-6.71</v>
       </c>
       <c r="M24" t="n">
-        <v>26.12</v>
+        <v>25.28</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.88</v>
+        <v>-0.84</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.71</v>
+        <v>-3.22</v>
       </c>
       <c r="P24" t="n">
-        <v>25.28</v>
+        <v>25.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.84</v>
+        <v>-0.12</v>
       </c>
       <c r="R24" t="n">
-        <v>-3.22</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>29.62</v>
+        <v>28.58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>-1.04</v>
       </c>
       <c r="F25" t="n">
-        <v>3.13</v>
+        <v>-3.51</v>
       </c>
       <c r="G25" t="n">
-        <v>28.58</v>
+        <v>28.38</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.04</v>
+        <v>-0.2</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.51</v>
+        <v>-0.7</v>
       </c>
       <c r="J25" t="n">
-        <v>28.38</v>
+        <v>27.8</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7</v>
+        <v>-2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>27.8</v>
+        <v>27.38</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.58</v>
+        <v>-0.42</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.04</v>
+        <v>-1.51</v>
       </c>
       <c r="P25" t="n">
-        <v>27.38</v>
+        <v>27.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.42</v>
+        <v>-0.18</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>61.65</v>
+        <v>62.35</v>
       </c>
       <c r="E26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G26" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="J26" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="N26" t="n">
         <v>1.4</v>
       </c>
-      <c r="F26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G26" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J26" t="n">
-        <v>59.65</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="O26" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P26" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-2.7</v>
       </c>
-      <c r="L26" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="M26" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-6.45</v>
-      </c>
-      <c r="P26" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="R26" t="n">
-        <v>2.51</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>481.6</v>
+        <v>466.4</v>
       </c>
       <c r="E27" t="n">
-        <v>45.6</v>
+        <v>-15.2</v>
       </c>
       <c r="F27" t="n">
-        <v>10.46</v>
+        <v>-3.16</v>
       </c>
       <c r="G27" t="n">
-        <v>466.4</v>
+        <v>459</v>
       </c>
       <c r="H27" t="n">
-        <v>-15.2</v>
+        <v>-7.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.16</v>
+        <v>-1.59</v>
       </c>
       <c r="J27" t="n">
-        <v>459</v>
+        <v>453.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.4</v>
+        <v>-5.8</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.59</v>
+        <v>-1.26</v>
       </c>
       <c r="M27" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="P27" t="n">
         <v>453.2</v>
       </c>
-      <c r="N27" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="P27" t="n">
-        <v>446.4</v>
-      </c>
       <c r="Q27" t="n">
-        <v>-6.8</v>
+        <v>6.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>130.9</v>
+        <v>126.6</v>
       </c>
       <c r="E28" t="n">
-        <v>8.1</v>
+        <v>-4.3</v>
       </c>
       <c r="F28" t="n">
-        <v>6.6</v>
+        <v>-3.28</v>
       </c>
       <c r="G28" t="n">
-        <v>126.6</v>
+        <v>123.5</v>
       </c>
       <c r="H28" t="n">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.28</v>
+        <v>-2.45</v>
       </c>
       <c r="J28" t="n">
-        <v>123.5</v>
+        <v>122.4</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.1</v>
+        <v>-1.1</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.45</v>
+        <v>-0.89</v>
       </c>
       <c r="M28" t="n">
-        <v>122.4</v>
+        <v>118.8</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.1</v>
+        <v>-3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.89</v>
+        <v>-2.94</v>
       </c>
       <c r="P28" t="n">
-        <v>118.8</v>
+        <v>117.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.6</v>
+        <v>-1.7</v>
       </c>
       <c r="R28" t="n">
-        <v>-2.94</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>120.1</v>
+        <v>115.1</v>
       </c>
       <c r="E29" t="n">
-        <v>7.7</v>
+        <v>-5</v>
       </c>
       <c r="F29" t="n">
-        <v>6.85</v>
+        <v>-4.16</v>
       </c>
       <c r="G29" t="n">
-        <v>115.1</v>
+        <v>115</v>
       </c>
       <c r="H29" t="n">
-        <v>-5</v>
+        <v>-0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>-4.16</v>
+        <v>-0.09</v>
       </c>
       <c r="J29" t="n">
-        <v>115</v>
+        <v>115.8</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.09</v>
+        <v>0.7</v>
       </c>
       <c r="M29" t="n">
-        <v>115.8</v>
+        <v>113.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7</v>
+        <v>-1.99</v>
       </c>
       <c r="P29" t="n">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.99</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>85.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>7.25</v>
+        <v>-5.1</v>
       </c>
       <c r="F30" t="n">
-        <v>9.27</v>
+        <v>-5.96</v>
       </c>
       <c r="G30" t="n">
-        <v>80.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-5.1</v>
+        <v>-1.8</v>
       </c>
       <c r="I30" t="n">
-        <v>-5.96</v>
+        <v>-2.24</v>
       </c>
       <c r="J30" t="n">
-        <v>78.59999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.8</v>
+        <v>1.35</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.24</v>
+        <v>1.72</v>
       </c>
       <c r="M30" t="n">
-        <v>79.95</v>
+        <v>76.25</v>
       </c>
       <c r="N30" t="n">
-        <v>1.35</v>
+        <v>-3.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.72</v>
+        <v>-4.63</v>
       </c>
       <c r="P30" t="n">
-        <v>76.25</v>
+        <v>77.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>-3.7</v>
+        <v>0.95</v>
       </c>
       <c r="R30" t="n">
-        <v>-4.63</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>134.7</v>
+        <v>132.9</v>
       </c>
       <c r="E31" t="n">
-        <v>5.6</v>
+        <v>-1.8</v>
       </c>
       <c r="F31" t="n">
-        <v>4.34</v>
+        <v>-1.34</v>
       </c>
       <c r="G31" t="n">
-        <v>132.9</v>
+        <v>130.1</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.34</v>
+        <v>-2.11</v>
       </c>
       <c r="J31" t="n">
-        <v>130.1</v>
+        <v>125.6</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.8</v>
+        <v>-4.5</v>
       </c>
       <c r="L31" t="n">
-        <v>-2.11</v>
+        <v>-3.46</v>
       </c>
       <c r="M31" t="n">
-        <v>125.6</v>
+        <v>116</v>
       </c>
       <c r="N31" t="n">
-        <v>-4.5</v>
+        <v>-9.6</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.46</v>
+        <v>-7.64</v>
       </c>
       <c r="P31" t="n">
-        <v>116</v>
+        <v>116.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>-9.6</v>
+        <v>0.6</v>
       </c>
       <c r="R31" t="n">
-        <v>-7.64</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>81.95</v>
+        <v>82.95</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>3.15</v>
+        <v>1.22</v>
       </c>
       <c r="G32" t="n">
-        <v>82.95</v>
+        <v>81.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>-1.45</v>
       </c>
       <c r="I32" t="n">
-        <v>1.22</v>
+        <v>-1.75</v>
       </c>
       <c r="J32" t="n">
-        <v>81.5</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.45</v>
+        <v>-5.85</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.75</v>
+        <v>-7.18</v>
       </c>
       <c r="M32" t="n">
-        <v>75.65000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="N32" t="n">
-        <v>-5.85</v>
+        <v>-3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>-7.18</v>
+        <v>-4.1</v>
       </c>
       <c r="P32" t="n">
-        <v>72.55</v>
+        <v>75</v>
       </c>
       <c r="Q32" t="n">
-        <v>-3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R32" t="n">
-        <v>-4.1</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>96.75</v>
+        <v>93.25</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>-3.5</v>
       </c>
       <c r="F33" t="n">
-        <v>6.61</v>
+        <v>-3.62</v>
       </c>
       <c r="G33" t="n">
-        <v>93.25</v>
+        <v>91.8</v>
       </c>
       <c r="H33" t="n">
-        <v>-3.5</v>
+        <v>-1.45</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.62</v>
+        <v>-1.55</v>
       </c>
       <c r="J33" t="n">
-        <v>91.8</v>
+        <v>89.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.45</v>
+        <v>-2.1</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.55</v>
+        <v>-2.29</v>
       </c>
       <c r="M33" t="n">
-        <v>89.7</v>
+        <v>88.05</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.1</v>
+        <v>-1.65</v>
       </c>
       <c r="O33" t="n">
-        <v>-2.29</v>
+        <v>-1.84</v>
       </c>
       <c r="P33" t="n">
-        <v>88.05</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.65</v>
+        <v>0.35</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.84</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>48.98</v>
+        <v>46.74</v>
       </c>
       <c r="E34" t="n">
-        <v>2.44</v>
+        <v>-2.24</v>
       </c>
       <c r="F34" t="n">
-        <v>5.24</v>
+        <v>-4.57</v>
       </c>
       <c r="G34" t="n">
-        <v>46.74</v>
+        <v>46.94</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.24</v>
+        <v>0.2</v>
       </c>
       <c r="I34" t="n">
-        <v>-4.57</v>
+        <v>0.43</v>
       </c>
       <c r="J34" t="n">
-        <v>46.94</v>
+        <v>46.86</v>
       </c>
       <c r="K34" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="M34" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="P34" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="M34" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="P34" t="n">
-        <v>44.14</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>-2.72</v>
-      </c>
       <c r="R34" t="n">
-        <v>-5.8</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="E35" t="n">
-        <v>0.22</v>
+        <v>-0.14</v>
       </c>
       <c r="F35" t="n">
-        <v>4.52</v>
+        <v>-2.75</v>
       </c>
       <c r="G35" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.75</v>
+        <v>-1.62</v>
       </c>
       <c r="J35" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="K35" t="n">
         <v>-0.08</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.62</v>
+        <v>-1.64</v>
       </c>
       <c r="M35" t="n">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.64</v>
+        <v>-2.71</v>
       </c>
       <c r="P35" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="R35" t="n">
-        <v>-2.71</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.94</v>
+        <v>10.64</v>
       </c>
       <c r="E36" t="n">
-        <v>0.51</v>
+        <v>-0.3</v>
       </c>
       <c r="F36" t="n">
-        <v>4.89</v>
+        <v>-2.74</v>
       </c>
       <c r="G36" t="n">
-        <v>10.64</v>
+        <v>10.47</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.74</v>
+        <v>-1.6</v>
       </c>
       <c r="J36" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.6</v>
+        <v>-1.91</v>
       </c>
       <c r="M36" t="n">
-        <v>10.27</v>
+        <v>10.01</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.2</v>
+        <v>-0.26</v>
       </c>
       <c r="O36" t="n">
-        <v>-1.91</v>
+        <v>-2.53</v>
       </c>
       <c r="P36" t="n">
-        <v>10.01</v>
+        <v>10.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.26</v>
+        <v>0.04</v>
       </c>
       <c r="R36" t="n">
-        <v>-2.53</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>410.4</v>
+        <v>409.4</v>
       </c>
       <c r="E37" t="n">
-        <v>10.2</v>
+        <v>-1</v>
       </c>
       <c r="F37" t="n">
-        <v>2.55</v>
+        <v>-0.24</v>
       </c>
       <c r="G37" t="n">
-        <v>409.4</v>
+        <v>400.8</v>
       </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>-8.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.24</v>
+        <v>-2.1</v>
       </c>
       <c r="J37" t="n">
-        <v>400.8</v>
+        <v>396.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.6</v>
+        <v>-4.4</v>
       </c>
       <c r="L37" t="n">
-        <v>-2.1</v>
+        <v>-1.1</v>
       </c>
       <c r="M37" t="n">
-        <v>396.4</v>
+        <v>386.8</v>
       </c>
       <c r="N37" t="n">
-        <v>-4.4</v>
+        <v>-9.6</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.1</v>
+        <v>-2.42</v>
       </c>
       <c r="P37" t="n">
-        <v>386.8</v>
+        <v>384</v>
       </c>
       <c r="Q37" t="n">
-        <v>-9.6</v>
+        <v>-2.8</v>
       </c>
       <c r="R37" t="n">
-        <v>-2.42</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.35</v>
+        <v>16.03</v>
       </c>
       <c r="E38" t="n">
-        <v>0.45</v>
+        <v>-0.32</v>
       </c>
       <c r="F38" t="n">
-        <v>2.83</v>
+        <v>-1.96</v>
       </c>
       <c r="G38" t="n">
-        <v>16.03</v>
+        <v>15.76</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.96</v>
+        <v>-1.68</v>
       </c>
       <c r="J38" t="n">
-        <v>15.76</v>
+        <v>15.21</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.27</v>
+        <v>-0.55</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.68</v>
+        <v>-3.49</v>
       </c>
       <c r="M38" t="n">
-        <v>15.21</v>
+        <v>14.82</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.55</v>
+        <v>-0.39</v>
       </c>
       <c r="O38" t="n">
-        <v>-3.49</v>
+        <v>-2.56</v>
       </c>
       <c r="P38" t="n">
-        <v>14.82</v>
+        <v>14.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.39</v>
+        <v>-0.02</v>
       </c>
       <c r="R38" t="n">
-        <v>-2.56</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>779.5</v>
+        <v>778</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>-1.5</v>
       </c>
       <c r="F39" t="n">
-        <v>3.45</v>
+        <v>-0.19</v>
       </c>
       <c r="G39" t="n">
-        <v>778</v>
+        <v>723.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5</v>
+        <v>-54.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.19</v>
+        <v>-7.01</v>
       </c>
       <c r="J39" t="n">
-        <v>723.5</v>
+        <v>711</v>
       </c>
       <c r="K39" t="n">
-        <v>-54.5</v>
+        <v>-12.5</v>
       </c>
       <c r="L39" t="n">
-        <v>-7.01</v>
+        <v>-1.73</v>
       </c>
       <c r="M39" t="n">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="N39" t="n">
-        <v>-12.5</v>
+        <v>-28</v>
       </c>
       <c r="O39" t="n">
-        <v>-1.73</v>
+        <v>-3.94</v>
       </c>
       <c r="P39" t="n">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="Q39" t="n">
-        <v>-28</v>
+        <v>8</v>
       </c>
       <c r="R39" t="n">
-        <v>-3.94</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>72</v>
+        <v>68.05</v>
       </c>
       <c r="E40" t="n">
-        <v>4.2</v>
+        <v>-3.95</v>
       </c>
       <c r="F40" t="n">
-        <v>6.19</v>
+        <v>-5.49</v>
       </c>
       <c r="G40" t="n">
-        <v>68.05</v>
+        <v>66.45</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.95</v>
+        <v>-1.6</v>
       </c>
       <c r="I40" t="n">
-        <v>-5.49</v>
+        <v>-2.35</v>
       </c>
       <c r="J40" t="n">
-        <v>66.45</v>
+        <v>65</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.6</v>
+        <v>-1.45</v>
       </c>
       <c r="L40" t="n">
-        <v>-2.35</v>
+        <v>-2.18</v>
       </c>
       <c r="M40" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.45</v>
+        <v>-3</v>
       </c>
       <c r="O40" t="n">
-        <v>-2.18</v>
+        <v>-4.62</v>
       </c>
       <c r="P40" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>-3</v>
+        <v>-0.7</v>
       </c>
       <c r="R40" t="n">
-        <v>-4.62</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>24.08</v>
+        <v>24.53</v>
       </c>
       <c r="E41" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="F41" t="n">
-        <v>2.91</v>
+        <v>1.87</v>
       </c>
       <c r="G41" t="n">
-        <v>24.53</v>
+        <v>24</v>
       </c>
       <c r="H41" t="n">
-        <v>0.45</v>
+        <v>-0.53</v>
       </c>
       <c r="I41" t="n">
-        <v>1.87</v>
+        <v>-2.16</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.53</v>
+        <v>-0.06</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.16</v>
+        <v>-0.25</v>
       </c>
       <c r="M41" t="n">
-        <v>23.94</v>
+        <v>23.4</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.25</v>
+        <v>-2.26</v>
       </c>
       <c r="P41" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.54</v>
+        <v>0.4</v>
       </c>
       <c r="R41" t="n">
-        <v>-2.26</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>64.67</v>
+        <v>65.05</v>
       </c>
       <c r="E42" t="n">
-        <v>1.83</v>
+        <v>0.38</v>
       </c>
       <c r="F42" t="n">
-        <v>2.91</v>
+        <v>0.59</v>
       </c>
       <c r="G42" t="n">
-        <v>65.05</v>
+        <v>64.14</v>
       </c>
       <c r="H42" t="n">
-        <v>0.38</v>
+        <v>-0.91</v>
       </c>
       <c r="I42" t="n">
-        <v>0.59</v>
+        <v>-1.4</v>
       </c>
       <c r="J42" t="n">
-        <v>64.14</v>
+        <v>63.78</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.91</v>
+        <v>-0.36</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>63.78</v>
+        <v>62.76</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.36</v>
+        <v>-1.02</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.6</v>
       </c>
       <c r="P42" t="n">
-        <v>62.76</v>
+        <v>63.76</v>
       </c>
       <c r="Q42" t="n">
-        <v>-1.02</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.6</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F43" t="n">
-        <v>2.13</v>
+        <v>1.04</v>
       </c>
       <c r="G43" t="n">
-        <v>38.8</v>
+        <v>38.31</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4</v>
+        <v>-0.49</v>
       </c>
       <c r="I43" t="n">
-        <v>1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="J43" t="n">
-        <v>38.31</v>
+        <v>38.55</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.49</v>
+        <v>0.24</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.26</v>
+        <v>0.63</v>
       </c>
       <c r="M43" t="n">
-        <v>38.55</v>
+        <v>37.79</v>
       </c>
       <c r="N43" t="n">
-        <v>0.24</v>
+        <v>-0.76</v>
       </c>
       <c r="O43" t="n">
-        <v>0.63</v>
+        <v>-1.97</v>
       </c>
       <c r="P43" t="n">
-        <v>37.79</v>
+        <v>38.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.76</v>
+        <v>0.59</v>
       </c>
       <c r="R43" t="n">
-        <v>-1.97</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.72</v>
+        <v>0.16</v>
       </c>
       <c r="G44" t="n">
-        <v>6.29</v>
+        <v>6.21</v>
       </c>
       <c r="H44" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="I44" t="n">
-        <v>0.16</v>
+        <v>-1.27</v>
       </c>
       <c r="J44" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="K44" t="n">
         <v>-0.08</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.27</v>
+        <v>-1.29</v>
       </c>
       <c r="M44" t="n">
-        <v>6.13</v>
+        <v>6.06</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>-1.29</v>
+        <v>-1.14</v>
       </c>
       <c r="P44" t="n">
-        <v>6.06</v>
+        <v>6.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.14</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.89</v>
+        <v>0.48</v>
       </c>
       <c r="G45" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="H45" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I45" t="n">
-        <v>0.48</v>
+        <v>-2.87</v>
       </c>
       <c r="J45" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.87</v>
+        <v>-0.49</v>
       </c>
       <c r="M45" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="N45" t="n">
         <v>-0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="P45" t="n">
         <v>2.01</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F46" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="G46" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="I46" t="n">
-        <v>2.28</v>
+        <v>-1.24</v>
       </c>
       <c r="J46" t="n">
         <v>3.99</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="P46" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.13</v>
+        <v>0.06</v>
       </c>
       <c r="R46" t="n">
-        <v>-3.26</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.16</v>
+        <v>11.27</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.22</v>
+        <v>0.11</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.93</v>
+        <v>0.99</v>
       </c>
       <c r="G47" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="H47" t="n">
-        <v>0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="I47" t="n">
-        <v>0.99</v>
+        <v>-2.22</v>
       </c>
       <c r="J47" t="n">
-        <v>11.02</v>
+        <v>10.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.25</v>
+        <v>-0.13</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.22</v>
+        <v>-1.18</v>
       </c>
       <c r="M47" t="n">
-        <v>10.89</v>
+        <v>10.62</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="O47" t="n">
-        <v>-1.18</v>
+        <v>-2.48</v>
       </c>
       <c r="P47" t="n">
-        <v>10.62</v>
+        <v>10.59</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.27</v>
+        <v>-0.03</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.48</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="48">
@@ -3367,22 +3367,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="G48" t="n">
         <v>0.315</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0.315</v>
@@ -3394,22 +3394,22 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="P48" t="n">
-        <v>0.31</v>
+        <v>0.325</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.59</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="49">
@@ -3429,25 +3429,25 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="G49" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="H49" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.23</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="K49" t="n">
         <v>-0.03</v>
@@ -3456,22 +3456,22 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.86</v>
       </c>
       <c r="P49" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="R49" t="n">
-        <v>-1.86</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="50">
@@ -3491,31 +3491,31 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="G50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="H50" t="n">
         <v>-0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="J50" t="n">
         <v>1.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>1.01</v>
@@ -3527,13 +3527,13 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="51">
@@ -3556,46 +3556,46 @@
         <v>3.58</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>-3.35</v>
       </c>
       <c r="J51" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="L51" t="n">
-        <v>-3.35</v>
+        <v>2.31</v>
       </c>
       <c r="M51" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="N51" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="O51" t="n">
-        <v>2.31</v>
+        <v>-2.82</v>
       </c>
       <c r="P51" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.82</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.95</v>
+        <v>10.87</v>
       </c>
       <c r="E52" t="n">
-        <v>0.19</v>
+        <v>-0.08</v>
       </c>
       <c r="F52" t="n">
-        <v>1.77</v>
+        <v>-0.73</v>
       </c>
       <c r="G52" t="n">
-        <v>10.87</v>
+        <v>10.66</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.73</v>
+        <v>-1.93</v>
       </c>
       <c r="J52" t="n">
-        <v>10.66</v>
+        <v>10.59</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.93</v>
+        <v>-0.66</v>
       </c>
       <c r="M52" t="n">
-        <v>10.59</v>
+        <v>10.46</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.66</v>
+        <v>-1.23</v>
       </c>
       <c r="P52" t="n">
-        <v>10.46</v>
+        <v>10.51</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.23</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.63</v>
+        <v>-0.47</v>
       </c>
       <c r="G53" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="J53" t="n">
-        <v>8.390000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.12</v>
+        <v>-0.36</v>
       </c>
       <c r="M53" t="n">
-        <v>8.359999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.36</v>
+        <v>-1.79</v>
       </c>
       <c r="P53" t="n">
-        <v>8.210000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.79</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.33</v>
+        <v>-1.15</v>
       </c>
       <c r="G54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="H54" t="n">
         <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="J54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M54" t="n">
         <v>0.425</v>
       </c>
-      <c r="K54" t="n">
+      <c r="N54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L54" t="n">
+      <c r="O54" t="n">
         <v>-1.16</v>
       </c>
-      <c r="M54" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.18</v>
-      </c>
       <c r="P54" t="n">
-        <v>0.425</v>
+        <v>0.44</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.16</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="55">
@@ -3801,22 +3801,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.605</v>
+        <v>0.615</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F55" t="n">
-        <v>0.83</v>
+        <v>1.65</v>
       </c>
       <c r="G55" t="n">
         <v>0.615</v>
       </c>
       <c r="H55" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
@@ -3828,22 +3828,22 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.615</v>
+        <v>0.61</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="Q55" t="n">
         <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.465</v>
+        <v>0.47</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="G56" t="n">
         <v>0.47</v>
       </c>
       <c r="H56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1.06</v>
       </c>
       <c r="M56" t="n">
         <v>0.465</v>
       </c>
       <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="O56" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.18</v>
+        <v>1.16</v>
       </c>
       <c r="G57" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="H57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="P57" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="Q57" t="n">
         <v>0.04</v>
       </c>
-      <c r="I57" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="R57" t="n">
-        <v>-2.33</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>2.44</v>
+        <v>-1.19</v>
       </c>
       <c r="G58" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="H58" t="n">
         <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="J58" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="K58" t="n">
         <v>-0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
       <c r="M58" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.22</v>
+        <v>-3.7</v>
       </c>
       <c r="P58" t="n">
-        <v>0.078</v>
+        <v>0.079</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>-3.7</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.98</v>
+        <v>22.31</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="F59" t="n">
-        <v>0.46</v>
+        <v>1.5</v>
       </c>
       <c r="G59" t="n">
-        <v>22.31</v>
+        <v>21.88</v>
       </c>
       <c r="H59" t="n">
-        <v>0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>-1.93</v>
       </c>
       <c r="J59" t="n">
-        <v>21.88</v>
+        <v>21.74</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.43</v>
+        <v>-0.14</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.93</v>
+        <v>-0.64</v>
       </c>
       <c r="M59" t="n">
-        <v>21.74</v>
+        <v>21.44</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.14</v>
+        <v>-0.3</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.64</v>
+        <v>-1.38</v>
       </c>
       <c r="P59" t="n">
-        <v>21.44</v>
+        <v>21.71</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.3</v>
+        <v>0.27</v>
       </c>
       <c r="R59" t="n">
-        <v>-1.38</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="60">
@@ -4114,46 +4114,46 @@
         <v>3.2</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="J60" t="n">
         <v>3.18</v>
       </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N60" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L60" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="P60" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.63</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-7.25</v>
+        <v>1.56</v>
       </c>
       <c r="G61" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="H61" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>1.56</v>
+        <v>-5.38</v>
       </c>
       <c r="J61" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>-5.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M61" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="N61" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.03</v>
       </c>
       <c r="P61" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="R61" t="n">
-        <v>-4.03</v>
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-06-03 Close</t>
+          <t>2026-06-04 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change</t>
+          <t>2026-06-04 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-06-03 Change %</t>
+          <t>2026-06-04 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-06-04 Close</t>
+          <t>2026-06-05 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change</t>
+          <t>2026-06-05 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change %</t>
+          <t>2026-06-05 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-05 Close</t>
+          <t>2026-06-08 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change</t>
+          <t>2026-06-08 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change %</t>
+          <t>2026-06-08 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-08 Close</t>
+          <t>2026-06-09 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change</t>
+          <t>2026-06-09 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change %</t>
+          <t>2026-06-09 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-09 Close</t>
+          <t>2026-06-10 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-09 Change</t>
+          <t>2026-06-10 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-09 Change %</t>
+          <t>2026-06-10 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>146.9</v>
+        <v>146.4</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="G3" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="J3" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="N3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>146.4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="J3" t="n">
-        <v>141.8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-3.14</v>
-      </c>
-      <c r="M3" t="n">
-        <v>142.3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O3" t="n">
-        <v>0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="P3" t="n">
-        <v>142.1</v>
+        <v>135.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2</v>
+        <v>-6.8</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.14</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>217</v>
+        <v>211.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8</v>
+        <v>-5.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.84</v>
+        <v>-2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>211.8</v>
+        <v>201.4</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.2</v>
+        <v>-10.4</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4</v>
+        <v>-4.91</v>
       </c>
       <c r="J4" t="n">
-        <v>201.4</v>
+        <v>202.6</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.4</v>
+        <v>1.2</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.91</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>202.6</v>
+        <v>198.9</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6</v>
+        <v>-1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>198.9</v>
+        <v>189.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.7</v>
+        <v>-9.6</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.83</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="E5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="K5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F5" t="n">
+      <c r="L5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="G5" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.34</v>
-      </c>
       <c r="M5" t="n">
-        <v>5.82</v>
+        <v>5.73</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.17</v>
+        <v>-1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.55</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="6">
@@ -766,46 +766,46 @@
         <v>6.72</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.72</v>
+        <v>6.83</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="J6" t="n">
-        <v>6.83</v>
+        <v>6.93</v>
       </c>
       <c r="K6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>6.93</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="7">
@@ -825,43 +825,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.75</v>
+        <v>-0.38</v>
       </c>
       <c r="G7" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.38</v>
+        <v>1.14</v>
       </c>
       <c r="J7" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="Q7" t="n">
         <v>0.03</v>
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="G8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02</v>
+        <v>0.17</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.23</v>
+        <v>1.99</v>
       </c>
       <c r="J8" t="n">
-        <v>8.720000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="K8" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="L8" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>8.76</v>
+        <v>8.69</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.46</v>
+        <v>-0.8</v>
       </c>
       <c r="P8" t="n">
-        <v>8.69</v>
+        <v>8.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.42</v>
+        <v>7.37</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2</v>
+        <v>-0.67</v>
       </c>
       <c r="G9" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J9" t="n">
         <v>7.43</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.06</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>0.8100000000000001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>7.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.86</v>
+        <v>47.62</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.16</v>
+        <v>-0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>47.62</v>
+        <v>48.18</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5</v>
+        <v>1.18</v>
       </c>
       <c r="J10" t="n">
-        <v>48.18</v>
+        <v>48.16</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="L10" t="n">
-        <v>1.18</v>
+        <v>-0.04</v>
       </c>
       <c r="M10" t="n">
-        <v>48.16</v>
+        <v>47.96</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04</v>
+        <v>-0.42</v>
       </c>
       <c r="P10" t="n">
-        <v>47.96</v>
+        <v>48.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2</v>
+        <v>0.52</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.42</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="E11" t="n">
         <v>-0.02</v>
@@ -1082,40 +1082,40 @@
         <v>-0.46</v>
       </c>
       <c r="G11" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.46</v>
+        <v>-1.38</v>
       </c>
       <c r="J11" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.38</v>
+        <v>-3.73</v>
       </c>
       <c r="M11" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.73</v>
+        <v>-0.73</v>
       </c>
       <c r="P11" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.73</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.69</v>
+        <v>10.55</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="G12" t="n">
         <v>10.55</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>10.55</v>
+        <v>10.69</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>10.69</v>
+        <v>10.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.14</v>
+        <v>-0.49</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>-4.58</v>
       </c>
       <c r="P12" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="Q12" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R12" t="n">
         <v>-0.49</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-4.58</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.26</v>
+        <v>27.02</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.37</v>
+        <v>-0.88</v>
       </c>
       <c r="G13" t="n">
-        <v>27.02</v>
+        <v>26.54</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.88</v>
+        <v>-1.78</v>
       </c>
       <c r="J13" t="n">
-        <v>26.54</v>
+        <v>27.06</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.48</v>
+        <v>0.52</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.78</v>
+        <v>1.96</v>
       </c>
       <c r="M13" t="n">
-        <v>27.06</v>
+        <v>26.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="O13" t="n">
-        <v>1.96</v>
+        <v>-1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>26.7</v>
+        <v>25.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.36</v>
+        <v>-1.14</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.33</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="G14" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="H14" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0.02</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-1.81</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P15" t="n">
         <v>5.36</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.31</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1386,46 +1386,46 @@
         <v>4.98</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>5.03</v>
+        <v>4.93</v>
       </c>
       <c r="K16" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>-1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>4.93</v>
+        <v>5.05</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1</v>
+        <v>0.12</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.99</v>
+        <v>2.43</v>
       </c>
       <c r="P16" t="n">
         <v>5.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.27</v>
+        <v>-1.37</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.37</v>
+        <v>1.11</v>
       </c>
       <c r="J17" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="L17" t="n">
-        <v>1.11</v>
+        <v>-2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.47</v>
+        <v>0.28</v>
       </c>
       <c r="P17" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R17" t="n">
-        <v>0.28</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.29</v>
+        <v>-0.58</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="H18" t="n">
         <v>-0.02</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="J18" t="n">
         <v>3.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.18</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57.8</v>
+        <v>57.05</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="G19" t="n">
-        <v>57.05</v>
+        <v>56.9</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3</v>
+        <v>-0.26</v>
       </c>
       <c r="J19" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M19" t="n">
         <v>56.9</v>
       </c>
-      <c r="K19" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="M19" t="n">
-        <v>56.85</v>
-      </c>
       <c r="N19" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="P19" t="n">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0.09</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.58</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.04</v>
+        <v>0.36</v>
       </c>
       <c r="G20" t="n">
         <v>28</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>28</v>
+        <v>27.48</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.86</v>
       </c>
       <c r="M20" t="n">
-        <v>27.48</v>
+        <v>27.38</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.52</v>
+        <v>-0.1</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.86</v>
+        <v>-0.36</v>
       </c>
       <c r="P20" t="n">
-        <v>27.38</v>
+        <v>28.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1</v>
+        <v>0.82</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.36</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.74</v>
+        <v>-1.38</v>
       </c>
       <c r="G21" t="n">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.38</v>
+        <v>-0.6</v>
       </c>
       <c r="J21" t="n">
-        <v>4.99</v>
+        <v>4.94</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="M21" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="O21" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="P21" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.4</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.55</v>
+        <v>84.75</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.35</v>
+        <v>-0.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.41</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>84.75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8</v>
+        <v>-2.35</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.77</v>
       </c>
       <c r="J22" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.35</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="P22" t="n">
-        <v>82.3</v>
+        <v>82.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.12</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.96</v>
+        <v>28.38</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.72</v>
+        <v>1.42</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6</v>
+        <v>5.27</v>
       </c>
       <c r="G23" t="n">
-        <v>28.38</v>
+        <v>29.66</v>
       </c>
       <c r="H23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="I23" t="n">
-        <v>5.27</v>
+        <v>4.51</v>
       </c>
       <c r="J23" t="n">
-        <v>29.66</v>
+        <v>27.54</v>
       </c>
       <c r="K23" t="n">
-        <v>1.28</v>
+        <v>-2.12</v>
       </c>
       <c r="L23" t="n">
-        <v>4.51</v>
+        <v>-7.15</v>
       </c>
       <c r="M23" t="n">
-        <v>27.54</v>
+        <v>27.98</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.12</v>
+        <v>0.44</v>
       </c>
       <c r="O23" t="n">
-        <v>-7.15</v>
+        <v>1.6</v>
       </c>
       <c r="P23" t="n">
-        <v>27.98</v>
+        <v>26.82</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.44</v>
+        <v>-1.16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.78</v>
+        <v>-1.1</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.76</v>
+        <v>-3.78</v>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>26.12</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1</v>
+        <v>-1.88</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.78</v>
+        <v>-6.71</v>
       </c>
       <c r="J24" t="n">
-        <v>26.12</v>
+        <v>25.28</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.88</v>
+        <v>-0.84</v>
       </c>
       <c r="L24" t="n">
-        <v>-6.71</v>
+        <v>-3.22</v>
       </c>
       <c r="M24" t="n">
-        <v>25.28</v>
+        <v>25.16</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.84</v>
+        <v>-0.12</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.22</v>
+        <v>-0.47</v>
       </c>
       <c r="P24" t="n">
-        <v>25.16</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.12</v>
+        <v>-1.16</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.47</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.58</v>
+        <v>28.38</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.04</v>
+        <v>-0.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.51</v>
+        <v>-0.7</v>
       </c>
       <c r="G25" t="n">
-        <v>28.38</v>
+        <v>27.8</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7</v>
+        <v>-2.04</v>
       </c>
       <c r="J25" t="n">
-        <v>27.8</v>
+        <v>27.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.58</v>
+        <v>-0.42</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.04</v>
+        <v>-1.51</v>
       </c>
       <c r="M25" t="n">
-        <v>27.38</v>
+        <v>27.2</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.42</v>
+        <v>-0.18</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="P25" t="n">
-        <v>27.2</v>
+        <v>26.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.18</v>
+        <v>-0.88</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.66</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62.35</v>
+        <v>59.65</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7</v>
+        <v>-2.7</v>
       </c>
       <c r="F26" t="n">
-        <v>1.14</v>
+        <v>-4.33</v>
       </c>
       <c r="G26" t="n">
-        <v>59.65</v>
+        <v>55.8</v>
       </c>
       <c r="H26" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="J26" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M26" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="N26" t="n">
         <v>-2.7</v>
       </c>
-      <c r="I26" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="J26" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-6.45</v>
-      </c>
-      <c r="M26" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="O26" t="n">
-        <v>2.51</v>
+        <v>-4.72</v>
       </c>
       <c r="P26" t="n">
-        <v>54.5</v>
+        <v>55.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.7</v>
+        <v>0.9</v>
       </c>
       <c r="R26" t="n">
-        <v>-4.72</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>466.4</v>
+        <v>459</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.2</v>
+        <v>-7.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.16</v>
+        <v>-1.59</v>
       </c>
       <c r="G27" t="n">
-        <v>459</v>
+        <v>453.2</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.4</v>
+        <v>-5.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.59</v>
+        <v>-1.26</v>
       </c>
       <c r="J27" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="M27" t="n">
         <v>453.2</v>
       </c>
-      <c r="K27" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="M27" t="n">
-        <v>446.4</v>
-      </c>
       <c r="N27" t="n">
-        <v>-6.8</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P27" t="n">
-        <v>453.2</v>
+        <v>465.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.8</v>
+        <v>12.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>126.6</v>
+        <v>123.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.28</v>
+        <v>-2.45</v>
       </c>
       <c r="G28" t="n">
-        <v>123.5</v>
+        <v>122.4</v>
       </c>
       <c r="H28" t="n">
-        <v>-3.1</v>
+        <v>-1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.45</v>
+        <v>-0.89</v>
       </c>
       <c r="J28" t="n">
-        <v>122.4</v>
+        <v>118.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.1</v>
+        <v>-3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.89</v>
+        <v>-2.94</v>
       </c>
       <c r="M28" t="n">
-        <v>118.8</v>
+        <v>117.1</v>
       </c>
       <c r="N28" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="P28" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="Q28" t="n">
         <v>-3.6</v>
       </c>
-      <c r="O28" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="P28" t="n">
-        <v>117.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-1.7</v>
-      </c>
       <c r="R28" t="n">
-        <v>-1.43</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>115.1</v>
+        <v>115</v>
       </c>
       <c r="E29" t="n">
-        <v>-5</v>
+        <v>-0.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.16</v>
+        <v>-0.09</v>
       </c>
       <c r="G29" t="n">
-        <v>115</v>
+        <v>115.8</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.09</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
-        <v>115.8</v>
+        <v>113.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7</v>
+        <v>-1.99</v>
       </c>
       <c r="M29" t="n">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.99</v>
+        <v>0.44</v>
       </c>
       <c r="P29" t="n">
-        <v>114</v>
+        <v>112.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0.44</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.1</v>
+        <v>-1.8</v>
       </c>
       <c r="F30" t="n">
-        <v>-5.96</v>
+        <v>-2.24</v>
       </c>
       <c r="G30" t="n">
-        <v>78.59999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.8</v>
+        <v>1.35</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.24</v>
+        <v>1.72</v>
       </c>
       <c r="J30" t="n">
-        <v>79.95</v>
+        <v>76.25</v>
       </c>
       <c r="K30" t="n">
-        <v>1.35</v>
+        <v>-3.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.72</v>
+        <v>-4.63</v>
       </c>
       <c r="M30" t="n">
-        <v>76.25</v>
+        <v>77.2</v>
       </c>
       <c r="N30" t="n">
-        <v>-3.7</v>
+        <v>0.95</v>
       </c>
       <c r="O30" t="n">
-        <v>-4.63</v>
+        <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>77.2</v>
+        <v>79</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.95</v>
+        <v>1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>132.9</v>
+        <v>130.1</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.34</v>
+        <v>-2.11</v>
       </c>
       <c r="G31" t="n">
-        <v>130.1</v>
+        <v>125.6</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.8</v>
+        <v>-4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.11</v>
+        <v>-3.46</v>
       </c>
       <c r="J31" t="n">
-        <v>125.6</v>
+        <v>116</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.5</v>
+        <v>-9.6</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.46</v>
+        <v>-7.64</v>
       </c>
       <c r="M31" t="n">
-        <v>116</v>
+        <v>116.6</v>
       </c>
       <c r="N31" t="n">
-        <v>-9.6</v>
+        <v>0.6</v>
       </c>
       <c r="O31" t="n">
-        <v>-7.64</v>
+        <v>0.52</v>
       </c>
       <c r="P31" t="n">
-        <v>116.6</v>
+        <v>116.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.52</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>82.95</v>
+        <v>81.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>-1.45</v>
       </c>
       <c r="F32" t="n">
-        <v>1.22</v>
+        <v>-1.75</v>
       </c>
       <c r="G32" t="n">
-        <v>81.5</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.45</v>
+        <v>-5.85</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.75</v>
+        <v>-7.18</v>
       </c>
       <c r="J32" t="n">
-        <v>75.65000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.85</v>
+        <v>-3.1</v>
       </c>
       <c r="L32" t="n">
-        <v>-7.18</v>
+        <v>-4.1</v>
       </c>
       <c r="M32" t="n">
-        <v>72.55</v>
+        <v>75</v>
       </c>
       <c r="N32" t="n">
-        <v>-3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O32" t="n">
-        <v>-4.1</v>
+        <v>3.38</v>
       </c>
       <c r="P32" t="n">
-        <v>75</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.45</v>
+        <v>-2.65</v>
       </c>
       <c r="R32" t="n">
-        <v>3.38</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>93.25</v>
+        <v>91.8</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.5</v>
+        <v>-1.45</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.62</v>
+        <v>-1.55</v>
       </c>
       <c r="G33" t="n">
-        <v>91.8</v>
+        <v>89.7</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.45</v>
+        <v>-2.1</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.55</v>
+        <v>-2.29</v>
       </c>
       <c r="J33" t="n">
-        <v>89.7</v>
+        <v>88.05</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.1</v>
+        <v>-1.65</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.29</v>
+        <v>-1.84</v>
       </c>
       <c r="M33" t="n">
-        <v>88.05</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.65</v>
+        <v>0.35</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.84</v>
+        <v>0.4</v>
       </c>
       <c r="P33" t="n">
-        <v>88.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.35</v>
+        <v>-1.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>46.74</v>
+        <v>46.94</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.24</v>
+        <v>0.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.57</v>
+        <v>0.43</v>
       </c>
       <c r="G34" t="n">
-        <v>46.94</v>
+        <v>46.86</v>
       </c>
       <c r="H34" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="J34" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="N34" t="n">
         <v>0.2</v>
       </c>
-      <c r="I34" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J34" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="M34" t="n">
-        <v>44.14</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-2.72</v>
-      </c>
       <c r="O34" t="n">
-        <v>-5.8</v>
+        <v>0.45</v>
       </c>
       <c r="P34" t="n">
-        <v>44.34</v>
+        <v>46.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>1.68</v>
       </c>
       <c r="R34" t="n">
-        <v>0.45</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.75</v>
+        <v>-1.62</v>
       </c>
       <c r="G35" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="H35" t="n">
         <v>-0.08</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.62</v>
+        <v>-1.64</v>
       </c>
       <c r="J35" t="n">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.64</v>
+        <v>-2.71</v>
       </c>
       <c r="M35" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="O35" t="n">
-        <v>-2.71</v>
+        <v>0.43</v>
       </c>
       <c r="P35" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.64</v>
+        <v>10.47</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.74</v>
+        <v>-1.6</v>
       </c>
       <c r="G36" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.6</v>
+        <v>-1.91</v>
       </c>
       <c r="J36" t="n">
-        <v>10.27</v>
+        <v>10.01</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.2</v>
+        <v>-0.26</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.91</v>
+        <v>-2.53</v>
       </c>
       <c r="M36" t="n">
-        <v>10.01</v>
+        <v>10.05</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.26</v>
+        <v>0.04</v>
       </c>
       <c r="O36" t="n">
-        <v>-2.53</v>
+        <v>0.4</v>
       </c>
       <c r="P36" t="n">
-        <v>10.05</v>
+        <v>9.93</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="R36" t="n">
-        <v>0.4</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>409.4</v>
+        <v>400.8</v>
       </c>
       <c r="E37" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>396.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="M37" t="n">
+        <v>384</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="P37" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q37" t="n">
         <v>-1</v>
       </c>
-      <c r="F37" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G37" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="I37" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>396.4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>386.8</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="O37" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="P37" t="n">
-        <v>384</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>-2.8</v>
-      </c>
       <c r="R37" t="n">
-        <v>-0.72</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.03</v>
+        <v>15.76</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.96</v>
+        <v>-1.68</v>
       </c>
       <c r="G38" t="n">
-        <v>15.76</v>
+        <v>15.21</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.27</v>
+        <v>-0.55</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.68</v>
+        <v>-3.49</v>
       </c>
       <c r="J38" t="n">
-        <v>15.21</v>
+        <v>14.82</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.55</v>
+        <v>-0.39</v>
       </c>
       <c r="L38" t="n">
-        <v>-3.49</v>
+        <v>-2.56</v>
       </c>
       <c r="M38" t="n">
-        <v>14.82</v>
+        <v>14.8</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.39</v>
+        <v>-0.02</v>
       </c>
       <c r="O38" t="n">
-        <v>-2.56</v>
+        <v>-0.13</v>
       </c>
       <c r="P38" t="n">
-        <v>14.8</v>
+        <v>14.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.13</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>778</v>
+        <v>723.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5</v>
+        <v>-54.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.19</v>
+        <v>-7.01</v>
       </c>
       <c r="G39" t="n">
-        <v>723.5</v>
+        <v>711</v>
       </c>
       <c r="H39" t="n">
-        <v>-54.5</v>
+        <v>-12.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-7.01</v>
+        <v>-1.73</v>
       </c>
       <c r="J39" t="n">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.5</v>
+        <v>-28</v>
       </c>
       <c r="L39" t="n">
-        <v>-1.73</v>
+        <v>-3.94</v>
       </c>
       <c r="M39" t="n">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="N39" t="n">
-        <v>-28</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>-3.94</v>
+        <v>1.17</v>
       </c>
       <c r="P39" t="n">
-        <v>691</v>
+        <v>653.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>-37.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.17</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>68.05</v>
+        <v>66.45</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.95</v>
+        <v>-1.6</v>
       </c>
       <c r="F40" t="n">
-        <v>-5.49</v>
+        <v>-2.35</v>
       </c>
       <c r="G40" t="n">
-        <v>66.45</v>
+        <v>65</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6</v>
+        <v>-1.45</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.35</v>
+        <v>-2.18</v>
       </c>
       <c r="J40" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.45</v>
+        <v>-3</v>
       </c>
       <c r="L40" t="n">
-        <v>-2.18</v>
+        <v>-4.62</v>
       </c>
       <c r="M40" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="N40" t="n">
-        <v>-3</v>
+        <v>-0.7</v>
       </c>
       <c r="O40" t="n">
-        <v>-4.62</v>
+        <v>-1.13</v>
       </c>
       <c r="P40" t="n">
-        <v>61.3</v>
+        <v>59.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.7</v>
+        <v>-1.75</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.13</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>24.53</v>
+        <v>24</v>
       </c>
       <c r="E41" t="n">
-        <v>0.45</v>
+        <v>-0.53</v>
       </c>
       <c r="F41" t="n">
-        <v>1.87</v>
+        <v>-2.16</v>
       </c>
       <c r="G41" t="n">
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.53</v>
+        <v>-0.06</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.16</v>
+        <v>-0.25</v>
       </c>
       <c r="J41" t="n">
-        <v>23.94</v>
+        <v>23.4</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.25</v>
+        <v>-2.26</v>
       </c>
       <c r="M41" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.54</v>
+        <v>0.4</v>
       </c>
       <c r="O41" t="n">
-        <v>-2.26</v>
+        <v>1.71</v>
       </c>
       <c r="P41" t="n">
-        <v>23.8</v>
+        <v>23.23</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4</v>
+        <v>-0.57</v>
       </c>
       <c r="R41" t="n">
-        <v>1.71</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>65.05</v>
+        <v>64.14</v>
       </c>
       <c r="E42" t="n">
-        <v>0.38</v>
+        <v>-0.91</v>
       </c>
       <c r="F42" t="n">
-        <v>0.59</v>
+        <v>-1.4</v>
       </c>
       <c r="G42" t="n">
-        <v>64.14</v>
+        <v>63.78</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.91</v>
+        <v>-0.36</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>63.78</v>
+        <v>62.76</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.36</v>
+        <v>-1.02</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>62.76</v>
+        <v>63.76</v>
       </c>
       <c r="N42" t="n">
-        <v>-1.02</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P42" t="n">
-        <v>63.76</v>
+        <v>61.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>-1.93</v>
       </c>
       <c r="R42" t="n">
-        <v>1.59</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>38.8</v>
+        <v>38.31</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4</v>
+        <v>-0.49</v>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="G43" t="n">
-        <v>38.31</v>
+        <v>38.55</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.49</v>
+        <v>0.24</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.26</v>
+        <v>0.63</v>
       </c>
       <c r="J43" t="n">
-        <v>38.55</v>
+        <v>37.79</v>
       </c>
       <c r="K43" t="n">
-        <v>0.24</v>
+        <v>-0.76</v>
       </c>
       <c r="L43" t="n">
-        <v>0.63</v>
+        <v>-1.97</v>
       </c>
       <c r="M43" t="n">
-        <v>37.79</v>
+        <v>38.38</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.76</v>
+        <v>0.59</v>
       </c>
       <c r="O43" t="n">
-        <v>-1.97</v>
+        <v>1.56</v>
       </c>
       <c r="P43" t="n">
-        <v>38.38</v>
+        <v>37.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.56</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.29</v>
+        <v>6.21</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="F44" t="n">
-        <v>0.16</v>
+        <v>-1.27</v>
       </c>
       <c r="G44" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="H44" t="n">
         <v>-0.08</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.27</v>
+        <v>-1.29</v>
       </c>
       <c r="J44" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P44" t="n">
         <v>6.13</v>
       </c>
-      <c r="K44" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="O44" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="P44" t="n">
-        <v>6.14</v>
-      </c>
       <c r="Q44" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="R44" t="n">
-        <v>1.32</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F45" t="n">
-        <v>0.48</v>
+        <v>-2.87</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.87</v>
+        <v>-0.49</v>
       </c>
       <c r="J45" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="K45" t="n">
         <v>-0.01</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="M45" t="n">
         <v>2.01</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="E46" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="F46" t="n">
-        <v>2.28</v>
+        <v>-1.24</v>
       </c>
       <c r="G46" t="n">
         <v>3.99</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="M46" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.13</v>
+        <v>0.06</v>
       </c>
       <c r="O46" t="n">
-        <v>-3.26</v>
+        <v>1.55</v>
       </c>
       <c r="P46" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="47">
@@ -3305,43 +3305,43 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="E47" t="n">
-        <v>0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="F47" t="n">
-        <v>0.99</v>
+        <v>-2.22</v>
       </c>
       <c r="G47" t="n">
-        <v>11.02</v>
+        <v>10.89</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.25</v>
+        <v>-0.13</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.22</v>
+        <v>-1.18</v>
       </c>
       <c r="J47" t="n">
-        <v>10.89</v>
+        <v>10.62</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.18</v>
+        <v>-2.48</v>
       </c>
       <c r="M47" t="n">
-        <v>10.62</v>
+        <v>10.59</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.27</v>
+        <v>-0.03</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.48</v>
+        <v>-0.28</v>
       </c>
       <c r="P47" t="n">
-        <v>10.59</v>
+        <v>10.56</v>
       </c>
       <c r="Q47" t="n">
         <v>-0.03</v>
@@ -3370,10 +3370,10 @@
         <v>0.315</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0.315</v>
@@ -3385,31 +3385,31 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="M48" t="n">
-        <v>0.31</v>
+        <v>0.325</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.59</v>
+        <v>4.84</v>
       </c>
       <c r="P48" t="n">
         <v>0.325</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,16 +3429,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F49" t="n">
-        <v>0.23</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="H49" t="n">
         <v>-0.03</v>
@@ -3447,31 +3447,31 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.86</v>
       </c>
       <c r="M49" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.86</v>
+        <v>2.61</v>
       </c>
       <c r="P49" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="R49" t="n">
-        <v>2.61</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="50">
@@ -3491,22 +3491,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="E50" t="n">
         <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="G50" t="n">
         <v>1.01</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>1.01</v>
@@ -3518,22 +3518,22 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="P50" t="n">
         <v>1.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-3.35</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="I51" t="n">
-        <v>-3.35</v>
+        <v>2.31</v>
       </c>
       <c r="J51" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="K51" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="L51" t="n">
-        <v>2.31</v>
+        <v>-2.82</v>
       </c>
       <c r="M51" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.82</v>
+        <v>-0.87</v>
       </c>
       <c r="P51" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.87</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.87</v>
+        <v>10.66</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.08</v>
+        <v>-0.21</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.73</v>
+        <v>-1.93</v>
       </c>
       <c r="G52" t="n">
-        <v>10.66</v>
+        <v>10.59</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.93</v>
+        <v>-0.66</v>
       </c>
       <c r="J52" t="n">
-        <v>10.59</v>
+        <v>10.46</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.66</v>
+        <v>-1.23</v>
       </c>
       <c r="M52" t="n">
-        <v>10.46</v>
+        <v>10.51</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.23</v>
+        <v>0.48</v>
       </c>
       <c r="P52" t="n">
-        <v>10.51</v>
+        <v>10.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R52" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="G53" t="n">
-        <v>8.390000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.12</v>
+        <v>-0.36</v>
       </c>
       <c r="J53" t="n">
-        <v>8.359999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.36</v>
+        <v>-1.79</v>
       </c>
       <c r="M53" t="n">
-        <v>8.210000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.79</v>
+        <v>0.37</v>
       </c>
       <c r="P53" t="n">
-        <v>8.24</v>
+        <v>8.27</v>
       </c>
       <c r="Q53" t="n">
         <v>0.03</v>
       </c>
       <c r="R53" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="E54" t="n">
         <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="G54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.425</v>
       </c>
-      <c r="H54" t="n">
+      <c r="K54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I54" t="n">
+      <c r="L54" t="n">
         <v>-1.16</v>
       </c>
-      <c r="J54" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.18</v>
-      </c>
       <c r="M54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="P54" t="n">
         <v>0.425</v>
       </c>
-      <c r="N54" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="O54" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.44</v>
-      </c>
       <c r="Q54" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="R54" t="n">
-        <v>3.53</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="55">
@@ -3804,10 +3804,10 @@
         <v>0.615</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0.615</v>
@@ -3819,31 +3819,31 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.615</v>
+        <v>0.61</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="N55" t="n">
         <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="P55" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="56">
@@ -3866,46 +3866,46 @@
         <v>0.47</v>
       </c>
       <c r="E56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-1.06</v>
       </c>
       <c r="J56" t="n">
         <v>0.465</v>
       </c>
       <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L56" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="P56" t="n">
         <v>0.46</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="E57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N57" t="n">
         <v>0.04</v>
       </c>
-      <c r="F57" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="K57" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="O57" t="n">
-        <v>-2.33</v>
+        <v>1.19</v>
       </c>
       <c r="P57" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="R57" t="n">
-        <v>1.19</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="E58" t="n">
         <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="G58" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="H58" t="n">
         <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
       <c r="J58" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="K58" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="Q58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="L58" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="O58" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.001</v>
-      </c>
       <c r="R58" t="n">
-        <v>1.28</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.31</v>
+        <v>21.88</v>
       </c>
       <c r="E59" t="n">
-        <v>0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="F59" t="n">
-        <v>1.5</v>
+        <v>-1.93</v>
       </c>
       <c r="G59" t="n">
-        <v>21.88</v>
+        <v>21.74</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.43</v>
+        <v>-0.14</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.93</v>
+        <v>-0.64</v>
       </c>
       <c r="J59" t="n">
-        <v>21.74</v>
+        <v>21.44</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.14</v>
+        <v>-0.3</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.64</v>
+        <v>-1.38</v>
       </c>
       <c r="M59" t="n">
-        <v>21.44</v>
+        <v>21.71</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.38</v>
+        <v>1.26</v>
       </c>
       <c r="P59" t="n">
-        <v>21.71</v>
+        <v>21.7</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.27</v>
+        <v>-0.01</v>
       </c>
       <c r="R59" t="n">
-        <v>1.26</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="G60" t="n">
         <v>3.18</v>
       </c>
       <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K60" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I60" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P60" t="n">
         <v>3.18</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O60" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.19</v>
-      </c>
       <c r="Q60" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>0.95</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>1.56</v>
+        <v>-5.38</v>
       </c>
       <c r="G61" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I61" t="n">
-        <v>-5.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="K61" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.03</v>
       </c>
       <c r="M61" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="O61" t="n">
-        <v>-4.03</v>
+        <v>-0.84</v>
       </c>
       <c r="P61" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Q61" t="n">
         <v>-0.01</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-06-04 Close</t>
+          <t>2026-06-05 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change</t>
+          <t>2026-06-05 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-06-04 Change %</t>
+          <t>2026-06-05 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-06-05 Close</t>
+          <t>2026-06-08 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change</t>
+          <t>2026-06-08 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change %</t>
+          <t>2026-06-08 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-08 Close</t>
+          <t>2026-06-09 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change</t>
+          <t>2026-06-09 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change %</t>
+          <t>2026-06-09 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-09 Close</t>
+          <t>2026-06-10 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-09 Change</t>
+          <t>2026-06-10 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-09 Change %</t>
+          <t>2026-06-10 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-10 Close</t>
+          <t>2026-06-11 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-10 Change</t>
+          <t>2026-06-11 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-10 Change %</t>
+          <t>2026-06-11 Change %</t>
         </is>
       </c>
     </row>
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>146.4</v>
+        <v>141.8</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5</v>
+        <v>-4.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.34</v>
+        <v>-3.14</v>
       </c>
       <c r="G3" t="n">
-        <v>141.8</v>
+        <v>142.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.6</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.14</v>
+        <v>0.35</v>
       </c>
       <c r="J3" t="n">
-        <v>142.3</v>
+        <v>142.1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>142.1</v>
+        <v>135.3</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2</v>
+        <v>-6.8</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.14</v>
+        <v>-4.79</v>
       </c>
       <c r="P3" t="n">
         <v>135.3</v>
@@ -639,40 +639,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>211.8</v>
+        <v>201.4</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.2</v>
+        <v>-10.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4</v>
+        <v>-4.91</v>
       </c>
       <c r="G4" t="n">
-        <v>201.4</v>
+        <v>202.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.4</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.91</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
-        <v>202.6</v>
+        <v>198.9</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>-1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>198.9</v>
+        <v>189.3</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.7</v>
+        <v>-9.6</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.83</v>
+        <v>-4.83</v>
       </c>
       <c r="P4" t="n">
         <v>189.3</v>
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.81</v>
+        <v>5.83</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.51</v>
+        <v>0.34</v>
       </c>
       <c r="G5" t="n">
-        <v>5.83</v>
+        <v>5.82</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.34</v>
+        <v>-0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>5.82</v>
+        <v>5.73</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.17</v>
+        <v>-1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.55</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
         <v>5.8</v>
@@ -763,40 +763,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.72</v>
+        <v>6.83</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>6.83</v>
+        <v>6.93</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="J6" t="n">
         <v>6.93</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>7</v>
@@ -825,34 +825,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.38</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="N7" t="n">
         <v>0.03</v>
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>0.17</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.23</v>
+        <v>1.99</v>
       </c>
       <c r="G8" t="n">
-        <v>8.720000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="H8" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="J8" t="n">
-        <v>8.76</v>
+        <v>8.69</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.46</v>
+        <v>-0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>8.69</v>
+        <v>8.75</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P8" t="n">
         <v>8.75</v>
@@ -949,40 +949,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>7.43</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.06</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>0.8100000000000001</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>7.49</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>7.49</v>
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.62</v>
+        <v>48.18</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5</v>
+        <v>1.18</v>
       </c>
       <c r="G10" t="n">
-        <v>48.18</v>
+        <v>48.16</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="I10" t="n">
-        <v>1.18</v>
+        <v>-0.04</v>
       </c>
       <c r="J10" t="n">
-        <v>48.16</v>
+        <v>47.96</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.04</v>
+        <v>-0.42</v>
       </c>
       <c r="M10" t="n">
-        <v>47.96</v>
+        <v>48.48</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2</v>
+        <v>0.52</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.42</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
         <v>48.48</v>
@@ -1073,40 +1073,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.46</v>
+        <v>-1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.38</v>
+        <v>-3.73</v>
       </c>
       <c r="J11" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.73</v>
+        <v>-0.73</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.73</v>
+        <v>0.24</v>
       </c>
       <c r="P11" t="n">
         <v>4.11</v>
@@ -1138,37 +1138,37 @@
         <v>10.55</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>10.55</v>
+        <v>10.69</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="J12" t="n">
-        <v>10.69</v>
+        <v>10.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.14</v>
+        <v>-0.49</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>-4.58</v>
       </c>
       <c r="M12" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="N12" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O12" t="n">
         <v>-0.49</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-4.58</v>
       </c>
       <c r="P12" t="n">
         <v>10.15</v>
@@ -1197,40 +1197,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.02</v>
+        <v>26.54</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.88</v>
+        <v>-1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>26.54</v>
+        <v>27.06</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.48</v>
+        <v>0.52</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.78</v>
+        <v>1.96</v>
       </c>
       <c r="J13" t="n">
-        <v>27.06</v>
+        <v>26.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="L13" t="n">
-        <v>1.96</v>
+        <v>-1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>26.7</v>
+        <v>25.56</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.36</v>
+        <v>-1.14</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.33</v>
+        <v>-4.27</v>
       </c>
       <c r="P13" t="n">
         <v>25.56</v>
@@ -1259,40 +1259,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="E14" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N14" t="n">
         <v>0.02</v>
       </c>
-      <c r="F14" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1.81</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.03</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>0.91</v>
       </c>
       <c r="P14" t="n">
         <v>2.22</v>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.37</v>
+        <v>5.3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.19</v>
+        <v>-1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3</v>
+        <v>5.28</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3</v>
+        <v>-0.38</v>
       </c>
       <c r="J15" t="n">
-        <v>5.28</v>
+        <v>5.31</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.38</v>
+        <v>0.57</v>
       </c>
       <c r="M15" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P15" t="n">
         <v>5.36</v>
@@ -1383,40 +1383,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03</v>
+        <v>4.93</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>-1.99</v>
       </c>
       <c r="J16" t="n">
-        <v>4.93</v>
+        <v>5.05</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1</v>
+        <v>0.12</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.99</v>
+        <v>2.43</v>
       </c>
       <c r="M16" t="n">
         <v>5.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>5.05</v>
@@ -1445,40 +1445,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.37</v>
+        <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>1.11</v>
+        <v>-2.47</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.47</v>
+        <v>0.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O17" t="n">
-        <v>0.28</v>
+        <v>-0.84</v>
       </c>
       <c r="P17" t="n">
         <v>3.53</v>
@@ -1507,40 +1507,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="E18" t="n">
         <v>-0.02</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="G18" t="n">
         <v>3.38</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="M18" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.18</v>
+        <v>0.9</v>
       </c>
       <c r="P18" t="n">
         <v>3.37</v>
@@ -1569,40 +1569,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57.05</v>
+        <v>56.9</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3</v>
+        <v>-0.26</v>
       </c>
       <c r="G19" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J19" t="n">
         <v>56.9</v>
       </c>
-      <c r="H19" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="J19" t="n">
-        <v>56.85</v>
-      </c>
       <c r="K19" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="M19" t="n">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09</v>
+        <v>0.53</v>
       </c>
       <c r="P19" t="n">
         <v>57.2</v>
@@ -1634,37 +1634,37 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>28</v>
+        <v>27.48</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-1.86</v>
       </c>
       <c r="J20" t="n">
-        <v>27.48</v>
+        <v>27.38</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.52</v>
+        <v>-0.1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.86</v>
+        <v>-0.36</v>
       </c>
       <c r="M20" t="n">
-        <v>27.38</v>
+        <v>28.2</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1</v>
+        <v>0.82</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.36</v>
+        <v>2.99</v>
       </c>
       <c r="P20" t="n">
         <v>28.2</v>
@@ -1693,40 +1693,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.38</v>
+        <v>-0.6</v>
       </c>
       <c r="G21" t="n">
-        <v>4.99</v>
+        <v>4.94</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="J21" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="L21" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4</v>
+        <v>3.05</v>
       </c>
       <c r="P21" t="n">
         <v>5.07</v>
@@ -1755,40 +1755,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>84.75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8</v>
+        <v>-2.35</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.77</v>
       </c>
       <c r="G22" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.35</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="M22" t="n">
-        <v>82.3</v>
+        <v>82.45</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.12</v>
+        <v>0.18</v>
       </c>
       <c r="P22" t="n">
         <v>82.45</v>
@@ -1817,40 +1817,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.38</v>
+        <v>29.66</v>
       </c>
       <c r="E23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="F23" t="n">
-        <v>5.27</v>
+        <v>4.51</v>
       </c>
       <c r="G23" t="n">
-        <v>29.66</v>
+        <v>27.54</v>
       </c>
       <c r="H23" t="n">
-        <v>1.28</v>
+        <v>-2.12</v>
       </c>
       <c r="I23" t="n">
-        <v>4.51</v>
+        <v>-7.15</v>
       </c>
       <c r="J23" t="n">
-        <v>27.54</v>
+        <v>27.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.12</v>
+        <v>0.44</v>
       </c>
       <c r="L23" t="n">
-        <v>-7.15</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>27.98</v>
+        <v>26.82</v>
       </c>
       <c r="N23" t="n">
-        <v>0.44</v>
+        <v>-1.16</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6</v>
+        <v>-4.15</v>
       </c>
       <c r="P23" t="n">
         <v>26.82</v>
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>26.12</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1</v>
+        <v>-1.88</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.78</v>
+        <v>-6.71</v>
       </c>
       <c r="G24" t="n">
-        <v>26.12</v>
+        <v>25.28</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.88</v>
+        <v>-0.84</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.71</v>
+        <v>-3.22</v>
       </c>
       <c r="J24" t="n">
-        <v>25.28</v>
+        <v>25.16</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.84</v>
+        <v>-0.12</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.22</v>
+        <v>-0.47</v>
       </c>
       <c r="M24" t="n">
-        <v>25.16</v>
+        <v>24</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.12</v>
+        <v>-1.16</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.47</v>
+        <v>-4.61</v>
       </c>
       <c r="P24" t="n">
         <v>24</v>
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.38</v>
+        <v>27.8</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7</v>
+        <v>-2.04</v>
       </c>
       <c r="G25" t="n">
-        <v>27.8</v>
+        <v>27.38</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.58</v>
+        <v>-0.42</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.04</v>
+        <v>-1.51</v>
       </c>
       <c r="J25" t="n">
-        <v>27.38</v>
+        <v>27.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.42</v>
+        <v>-0.18</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="M25" t="n">
-        <v>27.2</v>
+        <v>26.32</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.18</v>
+        <v>-0.88</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.66</v>
+        <v>-3.24</v>
       </c>
       <c r="P25" t="n">
         <v>26.32</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.65</v>
+        <v>55.8</v>
       </c>
       <c r="E26" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="G26" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J26" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K26" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F26" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="G26" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-6.45</v>
-      </c>
-      <c r="J26" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="L26" t="n">
-        <v>2.51</v>
+        <v>-4.72</v>
       </c>
       <c r="M26" t="n">
-        <v>54.5</v>
+        <v>55.4</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.7</v>
+        <v>0.9</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.72</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
         <v>55.4</v>
@@ -2065,40 +2065,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>459</v>
+        <v>453.2</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.4</v>
+        <v>-5.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.59</v>
+        <v>-1.26</v>
       </c>
       <c r="G27" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="J27" t="n">
         <v>453.2</v>
       </c>
-      <c r="H27" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="J27" t="n">
-        <v>446.4</v>
-      </c>
       <c r="K27" t="n">
-        <v>-6.8</v>
+        <v>6.8</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M27" t="n">
-        <v>453.2</v>
+        <v>465.6</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>12.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.52</v>
+        <v>2.74</v>
       </c>
       <c r="P27" t="n">
         <v>465.6</v>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>123.5</v>
+        <v>122.4</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.45</v>
+        <v>-0.89</v>
       </c>
       <c r="G28" t="n">
-        <v>122.4</v>
+        <v>118.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1</v>
+        <v>-3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.89</v>
+        <v>-2.94</v>
       </c>
       <c r="J28" t="n">
-        <v>118.8</v>
+        <v>117.1</v>
       </c>
       <c r="K28" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="M28" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="N28" t="n">
         <v>-3.6</v>
       </c>
-      <c r="L28" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="M28" t="n">
-        <v>117.1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-1.7</v>
-      </c>
       <c r="O28" t="n">
-        <v>-1.43</v>
+        <v>-3.07</v>
       </c>
       <c r="P28" t="n">
         <v>113.5</v>
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>115</v>
+        <v>115.8</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.09</v>
+        <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>115.8</v>
+        <v>113.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>-1.99</v>
       </c>
       <c r="J29" t="n">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.99</v>
+        <v>0.44</v>
       </c>
       <c r="M29" t="n">
-        <v>114</v>
+        <v>112.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="O29" t="n">
-        <v>0.44</v>
+        <v>-1.58</v>
       </c>
       <c r="P29" t="n">
         <v>112.2</v>
@@ -2251,40 +2251,40 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78.59999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.8</v>
+        <v>1.35</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.24</v>
+        <v>1.72</v>
       </c>
       <c r="G30" t="n">
-        <v>79.95</v>
+        <v>76.25</v>
       </c>
       <c r="H30" t="n">
-        <v>1.35</v>
+        <v>-3.7</v>
       </c>
       <c r="I30" t="n">
-        <v>1.72</v>
+        <v>-4.63</v>
       </c>
       <c r="J30" t="n">
-        <v>76.25</v>
+        <v>77.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.7</v>
+        <v>0.95</v>
       </c>
       <c r="L30" t="n">
-        <v>-4.63</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="n">
-        <v>77.2</v>
+        <v>79</v>
       </c>
       <c r="N30" t="n">
-        <v>0.95</v>
+        <v>1.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
       <c r="P30" t="n">
         <v>79</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>130.1</v>
+        <v>125.6</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.8</v>
+        <v>-4.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.11</v>
+        <v>-3.46</v>
       </c>
       <c r="G31" t="n">
-        <v>125.6</v>
+        <v>116</v>
       </c>
       <c r="H31" t="n">
-        <v>-4.5</v>
+        <v>-9.6</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.46</v>
+        <v>-7.64</v>
       </c>
       <c r="J31" t="n">
-        <v>116</v>
+        <v>116.6</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.6</v>
+        <v>0.6</v>
       </c>
       <c r="L31" t="n">
-        <v>-7.64</v>
+        <v>0.52</v>
       </c>
       <c r="M31" t="n">
-        <v>116.6</v>
+        <v>116.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.52</v>
+        <v>0.09</v>
       </c>
       <c r="P31" t="n">
         <v>116.7</v>
@@ -2375,40 +2375,40 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>81.5</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.45</v>
+        <v>-5.85</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.75</v>
+        <v>-7.18</v>
       </c>
       <c r="G32" t="n">
-        <v>75.65000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.85</v>
+        <v>-3.1</v>
       </c>
       <c r="I32" t="n">
-        <v>-7.18</v>
+        <v>-4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>72.55</v>
+        <v>75</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.1</v>
+        <v>2.45</v>
       </c>
       <c r="L32" t="n">
-        <v>-4.1</v>
+        <v>3.38</v>
       </c>
       <c r="M32" t="n">
-        <v>75</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>-2.65</v>
       </c>
       <c r="O32" t="n">
-        <v>3.38</v>
+        <v>-3.53</v>
       </c>
       <c r="P32" t="n">
         <v>72.34999999999999</v>
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>91.8</v>
+        <v>89.7</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.45</v>
+        <v>-2.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.55</v>
+        <v>-2.29</v>
       </c>
       <c r="G33" t="n">
-        <v>89.7</v>
+        <v>88.05</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.1</v>
+        <v>-1.65</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.29</v>
+        <v>-1.84</v>
       </c>
       <c r="J33" t="n">
-        <v>88.05</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.65</v>
+        <v>0.35</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.84</v>
+        <v>0.4</v>
       </c>
       <c r="M33" t="n">
-        <v>88.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>0.35</v>
+        <v>-1.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0.4</v>
+        <v>-2.04</v>
       </c>
       <c r="P33" t="n">
         <v>86.59999999999999</v>
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>46.94</v>
+        <v>46.86</v>
       </c>
       <c r="E34" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="G34" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="K34" t="n">
         <v>0.2</v>
       </c>
-      <c r="F34" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G34" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="J34" t="n">
-        <v>44.14</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-2.72</v>
-      </c>
       <c r="L34" t="n">
-        <v>-5.8</v>
+        <v>0.45</v>
       </c>
       <c r="M34" t="n">
-        <v>44.34</v>
+        <v>46.02</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2</v>
+        <v>1.68</v>
       </c>
       <c r="O34" t="n">
-        <v>0.45</v>
+        <v>3.79</v>
       </c>
       <c r="P34" t="n">
         <v>46.02</v>
@@ -2561,40 +2561,40 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="E35" t="n">
         <v>-0.08</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.62</v>
+        <v>-1.64</v>
       </c>
       <c r="G35" t="n">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.64</v>
+        <v>-2.71</v>
       </c>
       <c r="J35" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.71</v>
+        <v>0.43</v>
       </c>
       <c r="M35" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="N35" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
       <c r="P35" t="n">
         <v>4.63</v>
@@ -2623,40 +2623,40 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6</v>
+        <v>-1.91</v>
       </c>
       <c r="G36" t="n">
-        <v>10.27</v>
+        <v>10.01</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2</v>
+        <v>-0.26</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.91</v>
+        <v>-2.53</v>
       </c>
       <c r="J36" t="n">
-        <v>10.01</v>
+        <v>10.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.26</v>
+        <v>0.04</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.53</v>
+        <v>0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>10.05</v>
+        <v>9.93</v>
       </c>
       <c r="N36" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="O36" t="n">
-        <v>0.4</v>
+        <v>-1.19</v>
       </c>
       <c r="P36" t="n">
         <v>9.93</v>
@@ -2685,40 +2685,40 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>400.8</v>
+        <v>396.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-8.6</v>
+        <v>-4.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.1</v>
+        <v>-1.1</v>
       </c>
       <c r="G37" t="n">
-        <v>396.4</v>
+        <v>386.8</v>
       </c>
       <c r="H37" t="n">
-        <v>-4.4</v>
+        <v>-9.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1</v>
+        <v>-2.42</v>
       </c>
       <c r="J37" t="n">
-        <v>386.8</v>
+        <v>384</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.6</v>
+        <v>-2.8</v>
       </c>
       <c r="L37" t="n">
-        <v>-2.42</v>
+        <v>-0.72</v>
       </c>
       <c r="M37" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.8</v>
+        <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.72</v>
+        <v>-0.26</v>
       </c>
       <c r="P37" t="n">
         <v>383</v>
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.76</v>
+        <v>15.21</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.27</v>
+        <v>-0.55</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.68</v>
+        <v>-3.49</v>
       </c>
       <c r="G38" t="n">
-        <v>15.21</v>
+        <v>14.82</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.55</v>
+        <v>-0.39</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.49</v>
+        <v>-2.56</v>
       </c>
       <c r="J38" t="n">
-        <v>14.82</v>
+        <v>14.8</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.39</v>
+        <v>-0.02</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.56</v>
+        <v>-0.13</v>
       </c>
       <c r="M38" t="n">
-        <v>14.8</v>
+        <v>14.89</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.13</v>
+        <v>0.61</v>
       </c>
       <c r="P38" t="n">
         <v>14.89</v>
@@ -2809,40 +2809,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>723.5</v>
+        <v>711</v>
       </c>
       <c r="E39" t="n">
-        <v>-54.5</v>
+        <v>-12.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-7.01</v>
+        <v>-1.73</v>
       </c>
       <c r="G39" t="n">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="H39" t="n">
-        <v>-12.5</v>
+        <v>-28</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.73</v>
+        <v>-3.94</v>
       </c>
       <c r="J39" t="n">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="K39" t="n">
-        <v>-28</v>
+        <v>8</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.94</v>
+        <v>1.17</v>
       </c>
       <c r="M39" t="n">
-        <v>691</v>
+        <v>653.5</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>-37.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.17</v>
+        <v>-5.43</v>
       </c>
       <c r="P39" t="n">
         <v>653.5</v>
@@ -2871,40 +2871,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>66.45</v>
+        <v>65</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6</v>
+        <v>-1.45</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.35</v>
+        <v>-2.18</v>
       </c>
       <c r="G40" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.45</v>
+        <v>-3</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.18</v>
+        <v>-4.62</v>
       </c>
       <c r="J40" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="K40" t="n">
-        <v>-3</v>
+        <v>-0.7</v>
       </c>
       <c r="L40" t="n">
-        <v>-4.62</v>
+        <v>-1.13</v>
       </c>
       <c r="M40" t="n">
-        <v>61.3</v>
+        <v>59.55</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.7</v>
+        <v>-1.75</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.13</v>
+        <v>-2.85</v>
       </c>
       <c r="P40" t="n">
         <v>59.55</v>
@@ -2933,40 +2933,40 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.53</v>
+        <v>-0.06</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.16</v>
+        <v>-0.25</v>
       </c>
       <c r="G41" t="n">
-        <v>23.94</v>
+        <v>23.4</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.25</v>
+        <v>-2.26</v>
       </c>
       <c r="J41" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.54</v>
+        <v>0.4</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.26</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>23.8</v>
+        <v>23.23</v>
       </c>
       <c r="N41" t="n">
-        <v>0.4</v>
+        <v>-0.57</v>
       </c>
       <c r="O41" t="n">
-        <v>1.71</v>
+        <v>-2.39</v>
       </c>
       <c r="P41" t="n">
         <v>23.23</v>
@@ -2995,40 +2995,40 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>64.14</v>
+        <v>63.78</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.91</v>
+        <v>-0.36</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>63.78</v>
+        <v>62.76</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.36</v>
+        <v>-1.02</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.6</v>
       </c>
       <c r="J42" t="n">
-        <v>62.76</v>
+        <v>63.76</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.02</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M42" t="n">
-        <v>63.76</v>
+        <v>61.83</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>-1.93</v>
       </c>
       <c r="O42" t="n">
-        <v>1.59</v>
+        <v>-3.03</v>
       </c>
       <c r="P42" t="n">
         <v>61.83</v>
@@ -3057,40 +3057,40 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>38.31</v>
+        <v>38.55</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.49</v>
+        <v>0.24</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.26</v>
+        <v>0.63</v>
       </c>
       <c r="G43" t="n">
-        <v>38.55</v>
+        <v>37.79</v>
       </c>
       <c r="H43" t="n">
-        <v>0.24</v>
+        <v>-0.76</v>
       </c>
       <c r="I43" t="n">
-        <v>0.63</v>
+        <v>-1.97</v>
       </c>
       <c r="J43" t="n">
-        <v>37.79</v>
+        <v>38.38</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.76</v>
+        <v>0.59</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.97</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>38.38</v>
+        <v>37.88</v>
       </c>
       <c r="N43" t="n">
-        <v>0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="O43" t="n">
-        <v>1.56</v>
+        <v>-1.3</v>
       </c>
       <c r="P43" t="n">
         <v>37.88</v>
@@ -3119,40 +3119,40 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="E44" t="n">
         <v>-0.08</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.27</v>
+        <v>-1.29</v>
       </c>
       <c r="G44" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M44" t="n">
         <v>6.13</v>
       </c>
-      <c r="H44" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I44" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.14</v>
-      </c>
       <c r="N44" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="O44" t="n">
-        <v>1.32</v>
+        <v>-0.16</v>
       </c>
       <c r="P44" t="n">
         <v>6.13</v>
@@ -3181,40 +3181,40 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.87</v>
+        <v>-0.49</v>
       </c>
       <c r="G45" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H45" t="n">
         <v>-0.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="J45" t="n">
         <v>2.01</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="P45" t="n">
         <v>1.97</v>
@@ -3246,37 +3246,37 @@
         <v>3.99</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="J46" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.13</v>
+        <v>0.06</v>
       </c>
       <c r="L46" t="n">
-        <v>-3.26</v>
+        <v>1.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="N46" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="O46" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="P46" t="n">
         <v>3.97</v>
@@ -3305,34 +3305,34 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.02</v>
+        <v>10.89</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.25</v>
+        <v>-0.13</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.22</v>
+        <v>-1.18</v>
       </c>
       <c r="G47" t="n">
-        <v>10.89</v>
+        <v>10.62</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.18</v>
+        <v>-2.48</v>
       </c>
       <c r="J47" t="n">
-        <v>10.62</v>
+        <v>10.59</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.27</v>
+        <v>-0.03</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.48</v>
+        <v>-0.28</v>
       </c>
       <c r="M47" t="n">
-        <v>10.59</v>
+        <v>10.56</v>
       </c>
       <c r="N47" t="n">
         <v>-0.03</v>
@@ -3376,31 +3376,31 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="J48" t="n">
-        <v>0.31</v>
+        <v>0.325</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.59</v>
+        <v>4.84</v>
       </c>
       <c r="M48" t="n">
         <v>0.325</v>
       </c>
       <c r="N48" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.325</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="E49" t="n">
         <v>-0.03</v>
@@ -3438,31 +3438,31 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.86</v>
       </c>
       <c r="J49" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.86</v>
+        <v>2.61</v>
       </c>
       <c r="M49" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="N49" t="n">
-        <v>0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="O49" t="n">
-        <v>2.61</v>
+        <v>-1.16</v>
       </c>
       <c r="P49" t="n">
         <v>4.27</v>
@@ -3494,10 +3494,10 @@
         <v>1.01</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>1.01</v>
@@ -3509,22 +3509,22 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="M50" t="n">
         <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.02</v>
@@ -3553,40 +3553,40 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.12</v>
+        <v>0.08</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.35</v>
+        <v>2.31</v>
       </c>
       <c r="G51" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="H51" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="I51" t="n">
-        <v>2.31</v>
+        <v>-2.82</v>
       </c>
       <c r="J51" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.82</v>
+        <v>-0.87</v>
       </c>
       <c r="M51" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.87</v>
+        <v>-1.17</v>
       </c>
       <c r="P51" t="n">
         <v>3.37</v>
@@ -3615,40 +3615,40 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.66</v>
+        <v>10.59</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.93</v>
+        <v>-0.66</v>
       </c>
       <c r="G52" t="n">
-        <v>10.59</v>
+        <v>10.46</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.66</v>
+        <v>-1.23</v>
       </c>
       <c r="J52" t="n">
-        <v>10.46</v>
+        <v>10.51</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.23</v>
+        <v>0.48</v>
       </c>
       <c r="M52" t="n">
-        <v>10.51</v>
+        <v>10.55</v>
       </c>
       <c r="N52" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O52" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="P52" t="n">
         <v>10.55</v>
@@ -3677,40 +3677,40 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.390000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.12</v>
+        <v>-0.36</v>
       </c>
       <c r="G53" t="n">
-        <v>8.359999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.36</v>
+        <v>-1.79</v>
       </c>
       <c r="J53" t="n">
-        <v>8.210000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.79</v>
+        <v>0.37</v>
       </c>
       <c r="M53" t="n">
-        <v>8.24</v>
+        <v>8.27</v>
       </c>
       <c r="N53" t="n">
         <v>0.03</v>
       </c>
       <c r="O53" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="P53" t="n">
         <v>8.27</v>
@@ -3739,40 +3739,40 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.425</v>
       </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F54" t="n">
+      <c r="I54" t="n">
         <v>-1.16</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1.18</v>
-      </c>
       <c r="J54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L54" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="M54" t="n">
         <v>0.425</v>
       </c>
-      <c r="K54" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="L54" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.44</v>
-      </c>
       <c r="N54" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="O54" t="n">
-        <v>3.53</v>
+        <v>-3.41</v>
       </c>
       <c r="P54" t="n">
         <v>0.425</v>
@@ -3810,31 +3810,31 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.615</v>
+        <v>0.61</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="K55" t="n">
         <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="M55" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
       <c r="P55" t="n">
         <v>0.61</v>
@@ -3863,40 +3863,40 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-1.06</v>
       </c>
       <c r="G56" t="n">
         <v>0.465</v>
       </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I56" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="M56" t="n">
         <v>0.46</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.46</v>
@@ -3925,40 +3925,40 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F57" t="n">
-        <v>0.29</v>
+        <v>-1.72</v>
       </c>
       <c r="G57" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.72</v>
+        <v>-2.33</v>
       </c>
       <c r="J57" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.33</v>
+        <v>1.19</v>
       </c>
       <c r="M57" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="O57" t="n">
-        <v>1.19</v>
+        <v>3.24</v>
       </c>
       <c r="P57" t="n">
         <v>3.5</v>
@@ -3987,40 +3987,40 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="E58" t="n">
         <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.2</v>
+        <v>-1.22</v>
       </c>
       <c r="G58" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="H58" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="N58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="I58" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="K58" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.001</v>
-      </c>
       <c r="O58" t="n">
-        <v>1.28</v>
+        <v>-1.27</v>
       </c>
       <c r="P58" t="n">
         <v>0.078</v>
@@ -4049,40 +4049,40 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.88</v>
+        <v>21.74</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.43</v>
+        <v>-0.14</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.93</v>
+        <v>-0.64</v>
       </c>
       <c r="G59" t="n">
-        <v>21.74</v>
+        <v>21.44</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.14</v>
+        <v>-0.3</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.64</v>
+        <v>-1.38</v>
       </c>
       <c r="J59" t="n">
-        <v>21.44</v>
+        <v>21.71</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.3</v>
+        <v>0.27</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.38</v>
+        <v>1.26</v>
       </c>
       <c r="M59" t="n">
-        <v>21.71</v>
+        <v>21.7</v>
       </c>
       <c r="N59" t="n">
-        <v>0.27</v>
+        <v>-0.01</v>
       </c>
       <c r="O59" t="n">
-        <v>1.26</v>
+        <v>-0.05</v>
       </c>
       <c r="P59" t="n">
         <v>21.7</v>
@@ -4114,37 +4114,37 @@
         <v>3.18</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H60" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F60" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M60" t="n">
         <v>3.18</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="K60" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L60" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.19</v>
-      </c>
       <c r="N60" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="O60" t="n">
-        <v>0.95</v>
+        <v>-0.31</v>
       </c>
       <c r="P60" t="n">
         <v>3.18</v>
@@ -4173,40 +4173,40 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F61" t="n">
-        <v>-5.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.03</v>
       </c>
       <c r="J61" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>-4.03</v>
+        <v>-0.84</v>
       </c>
       <c r="M61" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N61" t="n">
         <v>-0.01</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="P61" t="n">
         <v>1.17</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-06-05 Close</t>
+          <t>2026-06-08 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change</t>
+          <t>2026-06-08 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-06-05 Change %</t>
+          <t>2026-06-08 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-06-08 Close</t>
+          <t>2026-06-09 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change</t>
+          <t>2026-06-09 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-06-08 Change %</t>
+          <t>2026-06-09 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-09 Close</t>
+          <t>2026-06-10 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-06-09 Change</t>
+          <t>2026-06-10 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-06-09 Change %</t>
+          <t>2026-06-10 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-06-10 Close</t>
+          <t>2026-06-11 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-06-10 Change</t>
+          <t>2026-06-11 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-06-10 Change %</t>
+          <t>2026-06-11 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-06-11 Close</t>
+          <t>2026-06-12 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-06-11 Change</t>
+          <t>2026-06-12 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-06-11 Change %</t>
+          <t>2026-06-12 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141.8</v>
+        <v>142.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.6</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.14</v>
+        <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>142.3</v>
+        <v>142.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>142.1</v>
+        <v>135.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2</v>
+        <v>-6.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.14</v>
+        <v>-4.79</v>
       </c>
       <c r="M3" t="n">
-        <v>135.3</v>
+        <v>138.5</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.8</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.79</v>
+        <v>2.37</v>
       </c>
       <c r="P3" t="n">
-        <v>135.3</v>
+        <v>142.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.8</v>
+        <v>4.3</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.79</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>201.4</v>
+        <v>202.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.4</v>
+        <v>1.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.91</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>202.6</v>
+        <v>198.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>-1.83</v>
       </c>
       <c r="J4" t="n">
-        <v>198.9</v>
+        <v>189.3</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.7</v>
+        <v>-9.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.83</v>
+        <v>-4.83</v>
       </c>
       <c r="M4" t="n">
-        <v>189.3</v>
+        <v>193.2</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.6</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.83</v>
+        <v>2.06</v>
       </c>
       <c r="P4" t="n">
-        <v>189.3</v>
+        <v>199.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9.6</v>
+        <v>6.5</v>
       </c>
       <c r="R4" t="n">
-        <v>-4.83</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.83</v>
+        <v>5.82</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>0.34</v>
+        <v>-0.17</v>
       </c>
       <c r="G5" t="n">
-        <v>5.82</v>
+        <v>5.73</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.17</v>
+        <v>-1.55</v>
       </c>
       <c r="J5" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.55</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8</v>
+        <v>5.88</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>5.8</v>
+        <v>6.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.83</v>
+        <v>6.93</v>
       </c>
       <c r="E6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
         <v>6.93</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>6.98</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>-0.29</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.01</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="7">
@@ -825,25 +825,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="K7" t="n">
         <v>0.03</v>
@@ -852,22 +852,22 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>5.42</v>
+        <v>5.37</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.92</v>
       </c>
       <c r="P7" t="n">
-        <v>5.42</v>
+        <v>5.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.720000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="G8" t="n">
-        <v>8.76</v>
+        <v>8.69</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.46</v>
+        <v>-0.8</v>
       </c>
       <c r="J8" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M8" t="n">
         <v>8.69</v>
       </c>
-      <c r="K8" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8.75</v>
-      </c>
       <c r="N8" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>8.75</v>
+        <v>8.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="9">
@@ -952,46 +952,46 @@
         <v>7.43</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.06</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>0.8100000000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>7.49</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.49</v>
+        <v>7.48</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="P9" t="n">
-        <v>7.49</v>
+        <v>7.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.18</v>
+        <v>48.16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="F10" t="n">
-        <v>1.18</v>
+        <v>-0.04</v>
       </c>
       <c r="G10" t="n">
-        <v>48.16</v>
+        <v>47.96</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04</v>
+        <v>-0.42</v>
       </c>
       <c r="J10" t="n">
-        <v>47.96</v>
+        <v>48.48</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2</v>
+        <v>0.52</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.42</v>
+        <v>1.08</v>
       </c>
       <c r="M10" t="n">
-        <v>48.48</v>
+        <v>48.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.52</v>
+        <v>-0.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.08</v>
+        <v>-0.58</v>
       </c>
       <c r="P10" t="n">
-        <v>48.48</v>
+        <v>49.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.38</v>
+        <v>-3.73</v>
       </c>
       <c r="G11" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.73</v>
+        <v>-0.73</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.73</v>
+        <v>0.24</v>
       </c>
       <c r="M11" t="n">
         <v>4.11</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="R11" t="n">
-        <v>0.24</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.55</v>
+        <v>10.69</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>10.69</v>
+        <v>10.2</v>
       </c>
       <c r="H12" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.14</v>
       </c>
-      <c r="I12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="R12" t="n">
-        <v>-0.49</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.54</v>
+        <v>27.06</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.48</v>
+        <v>0.52</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.78</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>27.06</v>
+        <v>26.7</v>
       </c>
       <c r="H13" t="n">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="I13" t="n">
-        <v>1.96</v>
+        <v>-1.33</v>
       </c>
       <c r="J13" t="n">
-        <v>26.7</v>
+        <v>25.56</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.36</v>
+        <v>-1.14</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.33</v>
+        <v>-4.27</v>
       </c>
       <c r="M13" t="n">
-        <v>25.56</v>
+        <v>24.72</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.14</v>
+        <v>-0.84</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.27</v>
+        <v>-3.29</v>
       </c>
       <c r="P13" t="n">
-        <v>25.56</v>
+        <v>24.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.14</v>
+        <v>0.2</v>
       </c>
       <c r="R13" t="n">
-        <v>-4.27</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.64</v>
+        <v>-1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.81</v>
+        <v>1.38</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>0.91</v>
       </c>
       <c r="M14" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0.91</v>
+        <v>-1.35</v>
       </c>
       <c r="P14" t="n">
         <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R14" t="n">
-        <v>0.91</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.3</v>
+        <v>5.28</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3</v>
+        <v>-0.38</v>
       </c>
       <c r="G15" t="n">
-        <v>5.28</v>
+        <v>5.31</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.38</v>
+        <v>0.57</v>
       </c>
       <c r="J15" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>5.36</v>
+        <v>5.32</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.03</v>
+        <v>4.93</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>-1.99</v>
       </c>
       <c r="G16" t="n">
-        <v>4.93</v>
+        <v>5.05</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.99</v>
+        <v>2.43</v>
       </c>
       <c r="J16" t="n">
         <v>5.05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.05</v>
+        <v>5.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="P16" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1.11</v>
+        <v>-2.47</v>
       </c>
       <c r="G17" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.47</v>
+        <v>0.28</v>
       </c>
       <c r="J17" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L17" t="n">
-        <v>0.28</v>
+        <v>-0.84</v>
       </c>
       <c r="M17" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.84</v>
+        <v>-0.57</v>
       </c>
       <c r="P17" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.03</v>
+        <v>0.11</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.84</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="18">
@@ -1510,46 +1510,46 @@
         <v>3.38</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="J18" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.34</v>
       </c>
-      <c r="K18" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.37</v>
-      </c>
       <c r="N18" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9</v>
+        <v>-0.89</v>
       </c>
       <c r="P18" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -1569,43 +1569,43 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G19" t="n">
         <v>56.9</v>
       </c>
-      <c r="E19" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J19" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M19" t="n">
         <v>56.85</v>
       </c>
-      <c r="H19" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="J19" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="M19" t="n">
-        <v>57.2</v>
-      </c>
       <c r="N19" t="n">
-        <v>0.3</v>
+        <v>-0.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0.53</v>
+        <v>-0.61</v>
       </c>
       <c r="P19" t="n">
-        <v>57.2</v>
+        <v>57.15</v>
       </c>
       <c r="Q19" t="n">
         <v>0.3</v>
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>27.48</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-1.86</v>
       </c>
       <c r="G20" t="n">
-        <v>27.48</v>
+        <v>27.38</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.52</v>
+        <v>-0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.86</v>
+        <v>-0.36</v>
       </c>
       <c r="J20" t="n">
-        <v>27.38</v>
+        <v>28.2</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1</v>
+        <v>0.82</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.36</v>
+        <v>2.99</v>
       </c>
       <c r="M20" t="n">
-        <v>28.2</v>
+        <v>28.26</v>
       </c>
       <c r="N20" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
       <c r="O20" t="n">
-        <v>2.99</v>
+        <v>0.21</v>
       </c>
       <c r="P20" t="n">
-        <v>28.2</v>
+        <v>30.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.82</v>
+        <v>1.86</v>
       </c>
       <c r="R20" t="n">
-        <v>2.99</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.99</v>
+        <v>4.94</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="G21" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="I21" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4</v>
+        <v>3.05</v>
       </c>
       <c r="M21" t="n">
-        <v>5.07</v>
+        <v>5.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>3.05</v>
+        <v>-1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>5.07</v>
+        <v>4.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="R21" t="n">
-        <v>3.05</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="22">
@@ -1758,46 +1758,46 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.35</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="J22" t="n">
-        <v>82.3</v>
+        <v>82.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.12</v>
+        <v>0.18</v>
       </c>
       <c r="M22" t="n">
-        <v>82.45</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0.18</v>
+        <v>-0.73</v>
       </c>
       <c r="P22" t="n">
-        <v>82.45</v>
+        <v>81.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.18</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.66</v>
+        <v>27.54</v>
       </c>
       <c r="E23" t="n">
-        <v>1.28</v>
+        <v>-2.12</v>
       </c>
       <c r="F23" t="n">
-        <v>4.51</v>
+        <v>-7.15</v>
       </c>
       <c r="G23" t="n">
-        <v>27.54</v>
+        <v>27.98</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.12</v>
+        <v>0.44</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.15</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>27.98</v>
+        <v>26.82</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>-1.16</v>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>-4.15</v>
       </c>
       <c r="M23" t="n">
-        <v>26.82</v>
+        <v>26.2</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.16</v>
+        <v>-0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.15</v>
+        <v>-2.31</v>
       </c>
       <c r="P23" t="n">
-        <v>26.82</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.16</v>
+        <v>-0.2</v>
       </c>
       <c r="R23" t="n">
-        <v>-4.15</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26.12</v>
+        <v>25.28</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.88</v>
+        <v>-0.84</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.71</v>
+        <v>-3.22</v>
       </c>
       <c r="G24" t="n">
-        <v>25.28</v>
+        <v>25.16</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.84</v>
+        <v>-0.12</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.22</v>
+        <v>-0.47</v>
       </c>
       <c r="J24" t="n">
-        <v>25.16</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.12</v>
+        <v>-1.16</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.47</v>
+        <v>-4.61</v>
       </c>
       <c r="M24" t="n">
-   